--- a/Översikt VÄXJÖ.xlsx
+++ b/Översikt VÄXJÖ.xlsx
@@ -601,7 +601,7 @@
         <v>44974</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         <v>45895</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -859,7 +859,7 @@
         <v>45770</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -976,7 +976,7 @@
         <v>45384</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v>45468</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
         <v>45888</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1313,7 +1313,7 @@
         <v>46175</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
         <v>45127</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>45812</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
         <v>45964</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
         <v>46188</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1882,7 +1882,7 @@
         <v>46188</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1996,7 +1996,7 @@
         <v>46199</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2110,7 +2110,7 @@
         <v>44958</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2223,7 +2223,7 @@
         <v>45081</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2336,7 +2336,7 @@
         <v>45294</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2453,7 +2453,7 @@
         <v>45995</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2565,7 +2565,7 @@
         <v>46247</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
         <v>45490</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2790,7 +2790,7 @@
         <v>46244</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2901,7 +2901,7 @@
         <v>46204</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3017,7 +3017,7 @@
         <v>45356</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3128,7 +3128,7 @@
         <v>45344</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3239,7 +3239,7 @@
         <v>46098</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3346,7 +3346,7 @@
         <v>44532</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3461,7 +3461,7 @@
         <v>45874</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3572,7 +3572,7 @@
         <v>46147</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3678,7 +3678,7 @@
         <v>45190</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3784,7 +3784,7 @@
         <v>46161</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3894,7 +3894,7 @@
         <v>45687</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4000,7 +4000,7 @@
         <v>46182</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4115,7 +4115,7 @@
         <v>45093</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4225,7 +4225,7 @@
         <v>45587</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4335,7 +4335,7 @@
         <v>45447</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         <v>45649</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4547,7 +4547,7 @@
         <v>45545</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4653,7 +4653,7 @@
         <v>45554</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4759,7 +4759,7 @@
         <v>45883</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4865,7 +4865,7 @@
         <v>44704</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4971,7 +4971,7 @@
         <v>45460</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5077,7 +5077,7 @@
         <v>44704</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5187,7 +5187,7 @@
         <v>45348</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5293,7 +5293,7 @@
         <v>45351</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5399,7 +5399,7 @@
         <v>45674</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5510,7 +5510,7 @@
         <v>46100</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5616,7 +5616,7 @@
         <v>44721</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5721,7 +5721,7 @@
         <v>44704</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5826,7 +5826,7 @@
         <v>44468</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5931,7 +5931,7 @@
         <v>44645</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6036,7 +6036,7 @@
         <v>44490</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6141,7 +6141,7 @@
         <v>45594</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         <v>45594</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6361,7 +6361,7 @@
         <v>45392</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6471,7 +6471,7 @@
         <v>44705</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6580,7 +6580,7 @@
         <v>45643</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6685,7 +6685,7 @@
         <v>44741</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6790,7 +6790,7 @@
         <v>45279</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6895,7 +6895,7 @@
         <v>45280</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7000,7 +7000,7 @@
         <v>45327</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7105,7 +7105,7 @@
         <v>44673</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7210,7 +7210,7 @@
         <v>45824</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7315,7 +7315,7 @@
         <v>45428</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7425,7 +7425,7 @@
         <v>44746</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7530,7 +7530,7 @@
         <v>44872</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7635,7 +7635,7 @@
         <v>45964</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7744,7 +7744,7 @@
         <v>45978</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7853,7 +7853,7 @@
         <v>46161</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7958,7 +7958,7 @@
         <v>45754</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8063,7 +8063,7 @@
         <v>46161</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8168,7 +8168,7 @@
         <v>45688</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8273,7 +8273,7 @@
         <v>46045</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8378,7 +8378,7 @@
         <v>45273</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8483,7 +8483,7 @@
         <v>45533</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8588,7 +8588,7 @@
         <v>45594</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8702,7 +8702,7 @@
         <v>45098</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8807,7 +8807,7 @@
         <v>46199</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8912,7 +8912,7 @@
         <v>45280</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9017,7 +9017,7 @@
         <v>45369</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9122,7 +9122,7 @@
         <v>46246</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9227,7 +9227,7 @@
         <v>44894</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9332,7 +9332,7 @@
         <v>46281</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9437,7 +9437,7 @@
         <v>45617</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9547,7 +9547,7 @@
         <v>45606</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9652,7 +9652,7 @@
         <v>44634</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9757,7 +9757,7 @@
         <v>44712</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9862,7 +9862,7 @@
         <v>44950</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9967,7 +9967,7 @@
         <v>45436</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10072,7 +10072,7 @@
         <v>45726</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10177,7 +10177,7 @@
         <v>45805</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10282,7 +10282,7 @@
         <v>45939</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10391,7 +10391,7 @@
         <v>46100</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10496,7 +10496,7 @@
         <v>44693</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10569,7 +10569,7 @@
         <v>44812</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10642,7 +10642,7 @@
         <v>44458</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10715,7 +10715,7 @@
         <v>44518</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10788,7 +10788,7 @@
         <v>44536</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10861,7 +10861,7 @@
         <v>44764</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10934,7 +10934,7 @@
         <v>44463</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11007,7 +11007,7 @@
         <v>44519</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11080,7 +11080,7 @@
         <v>44501</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11153,7 +11153,7 @@
         <v>44645</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11226,7 +11226,7 @@
         <v>44814</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11299,7 +11299,7 @@
         <v>44643</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11372,7 +11372,7 @@
         <v>44515</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11445,7 +11445,7 @@
         <v>44814</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11518,7 +11518,7 @@
         <v>44480</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11591,7 +11591,7 @@
         <v>44525</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11664,7 +11664,7 @@
         <v>44578</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11737,7 +11737,7 @@
         <v>44516</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11815,7 +11815,7 @@
         <v>44803</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11888,7 +11888,7 @@
         <v>44470</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11961,7 +11961,7 @@
         <v>44466</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12034,7 +12034,7 @@
         <v>44691</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12107,7 +12107,7 @@
         <v>44739</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12180,7 +12180,7 @@
         <v>44590</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12258,7 +12258,7 @@
         <v>44820</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12336,7 +12336,7 @@
         <v>44814</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12409,7 +12409,7 @@
         <v>44769</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12487,7 +12487,7 @@
         <v>44711</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12560,7 +12560,7 @@
         <v>44474</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12633,7 +12633,7 @@
         <v>44820</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12706,7 +12706,7 @@
         <v>44880</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12779,7 +12779,7 @@
         <v>44508</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12852,7 +12852,7 @@
         <v>44495</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12925,7 +12925,7 @@
         <v>44599</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12998,7 +12998,7 @@
         <v>44515</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13071,7 +13071,7 @@
         <v>44476</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13144,7 +13144,7 @@
         <v>44495</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13217,7 +13217,7 @@
         <v>44599</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13290,7 +13290,7 @@
         <v>44651</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13363,7 +13363,7 @@
         <v>44876</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13441,7 +13441,7 @@
         <v>44671</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13514,7 +13514,7 @@
         <v>44466</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13587,7 +13587,7 @@
         <v>44496</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13660,7 +13660,7 @@
         <v>44750</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13733,7 +13733,7 @@
         <v>44568</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13806,7 +13806,7 @@
         <v>44543</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13879,7 +13879,7 @@
         <v>44606</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13952,7 +13952,7 @@
         <v>44470</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14025,7 +14025,7 @@
         <v>44746</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14098,7 +14098,7 @@
         <v>44613</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14171,7 +14171,7 @@
         <v>44474</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14244,7 +14244,7 @@
         <v>44610</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14317,7 +14317,7 @@
         <v>44610</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14390,7 +14390,7 @@
         <v>44491</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14463,7 +14463,7 @@
         <v>44740</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14536,7 +14536,7 @@
         <v>44483</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14609,7 +14609,7 @@
         <v>44617</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14682,7 +14682,7 @@
         <v>44726</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14755,7 +14755,7 @@
         <v>44468</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14828,7 +14828,7 @@
         <v>44551</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14901,7 +14901,7 @@
         <v>44599</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14974,7 +14974,7 @@
         <v>44463</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15047,7 +15047,7 @@
         <v>44781</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15120,7 +15120,7 @@
         <v>44704</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15193,7 +15193,7 @@
         <v>44494</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15266,7 +15266,7 @@
         <v>44522</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15339,7 +15339,7 @@
         <v>44532</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15412,7 +15412,7 @@
         <v>44532</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15485,7 +15485,7 @@
         <v>44498</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15558,7 +15558,7 @@
         <v>44860</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15631,7 +15631,7 @@
         <v>44596</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15704,7 +15704,7 @@
         <v>44573</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15777,7 +15777,7 @@
         <v>44712</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15850,7 +15850,7 @@
         <v>44579</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15923,7 +15923,7 @@
         <v>44711</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15996,7 +15996,7 @@
         <v>44769</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16074,7 +16074,7 @@
         <v>44502</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16152,7 +16152,7 @@
         <v>44812</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16225,7 +16225,7 @@
         <v>44489</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16298,7 +16298,7 @@
         <v>44489</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16371,7 +16371,7 @@
         <v>44483</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16444,7 +16444,7 @@
         <v>44508</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16517,7 +16517,7 @@
         <v>44574</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16590,7 +16590,7 @@
         <v>44537</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16663,7 +16663,7 @@
         <v>44537</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16736,7 +16736,7 @@
         <v>44571</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16809,7 +16809,7 @@
         <v>44487</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16882,7 +16882,7 @@
         <v>44489</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16955,7 +16955,7 @@
         <v>44603</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17033,7 +17033,7 @@
         <v>44596</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17106,7 +17106,7 @@
         <v>44473</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17179,7 +17179,7 @@
         <v>44560</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17252,7 +17252,7 @@
         <v>44474</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17325,7 +17325,7 @@
         <v>44820</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17403,7 +17403,7 @@
         <v>44820</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17481,7 +17481,7 @@
         <v>44802</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17554,7 +17554,7 @@
         <v>45386</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17627,7 +17627,7 @@
         <v>44573</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17700,7 +17700,7 @@
         <v>45236</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17773,7 +17773,7 @@
         <v>45420</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17846,7 +17846,7 @@
         <v>45477</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17924,7 +17924,7 @@
         <v>44967</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17997,7 +17997,7 @@
         <v>45460</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18070,7 +18070,7 @@
         <v>44502</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18148,7 +18148,7 @@
         <v>45324</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18221,7 +18221,7 @@
         <v>44894</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18299,7 +18299,7 @@
         <v>45672</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18372,7 +18372,7 @@
         <v>44537</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18445,7 +18445,7 @@
         <v>45594</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18523,7 +18523,7 @@
         <v>45594</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18601,7 +18601,7 @@
         <v>45554</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18674,7 +18674,7 @@
         <v>44764</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18747,7 +18747,7 @@
         <v>45762</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18825,7 +18825,7 @@
         <v>45558</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18898,7 +18898,7 @@
         <v>44915</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18971,7 +18971,7 @@
         <v>44523</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19044,7 +19044,7 @@
         <v>45057</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19117,7 +19117,7 @@
         <v>45775</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19190,7 +19190,7 @@
         <v>45056</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19263,7 +19263,7 @@
         <v>45679</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19336,7 +19336,7 @@
         <v>44656</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19409,7 +19409,7 @@
         <v>44988</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19482,7 +19482,7 @@
         <v>45152</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19555,7 +19555,7 @@
         <v>44970</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19628,7 +19628,7 @@
         <v>45330</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19701,7 +19701,7 @@
         <v>44991</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19774,7 +19774,7 @@
         <v>45181</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19847,7 +19847,7 @@
         <v>44900</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19920,7 +19920,7 @@
         <v>45322</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19993,7 +19993,7 @@
         <v>45397</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20066,7 +20066,7 @@
         <v>44979</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20139,7 +20139,7 @@
         <v>44713</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20212,7 +20212,7 @@
         <v>45033</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20290,7 +20290,7 @@
         <v>44532</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20363,7 +20363,7 @@
         <v>44602</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20436,7 +20436,7 @@
         <v>45561</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20509,7 +20509,7 @@
         <v>44894</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20582,7 +20582,7 @@
         <v>44620</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20655,7 +20655,7 @@
         <v>45726</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20728,7 +20728,7 @@
         <v>45541</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20801,7 +20801,7 @@
         <v>44599</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20874,7 +20874,7 @@
         <v>45219</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20947,7 +20947,7 @@
         <v>45594</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21025,7 +21025,7 @@
         <v>45594</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21103,7 +21103,7 @@
         <v>45594</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21181,7 +21181,7 @@
         <v>45594</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21259,7 +21259,7 @@
         <v>45594</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21337,7 +21337,7 @@
         <v>45392</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21415,7 +21415,7 @@
         <v>45341</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21488,7 +21488,7 @@
         <v>45315</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21561,7 +21561,7 @@
         <v>45715</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21639,7 +21639,7 @@
         <v>45114</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21712,7 +21712,7 @@
         <v>45330</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21785,7 +21785,7 @@
         <v>45714</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21858,7 +21858,7 @@
         <v>45105</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21931,7 +21931,7 @@
         <v>45359</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22004,7 +22004,7 @@
         <v>45555</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22077,7 +22077,7 @@
         <v>45557</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22150,7 +22150,7 @@
         <v>45583</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22223,7 +22223,7 @@
         <v>45691</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22296,7 +22296,7 @@
         <v>45408</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22369,7 +22369,7 @@
         <v>45586</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22442,7 +22442,7 @@
         <v>45309</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22515,7 +22515,7 @@
         <v>44854</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22588,7 +22588,7 @@
         <v>45579</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22661,7 +22661,7 @@
         <v>45460</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22734,7 +22734,7 @@
         <v>45737</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22807,7 +22807,7 @@
         <v>45211</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22880,7 +22880,7 @@
         <v>45557</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22953,7 +22953,7 @@
         <v>45309</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23026,7 +23026,7 @@
         <v>44909</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23099,7 +23099,7 @@
         <v>45253</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23172,7 +23172,7 @@
         <v>45686</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23245,7 +23245,7 @@
         <v>45233</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23318,7 +23318,7 @@
         <v>44552</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23391,7 +23391,7 @@
         <v>45309</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23464,7 +23464,7 @@
         <v>45244</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23537,7 +23537,7 @@
         <v>45244</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23610,7 +23610,7 @@
         <v>44814</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23683,7 +23683,7 @@
         <v>44814</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23756,7 +23756,7 @@
         <v>45061</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23829,7 +23829,7 @@
         <v>45300</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23902,7 +23902,7 @@
         <v>44858</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23975,7 +23975,7 @@
         <v>44929</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24053,7 +24053,7 @@
         <v>45280</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24126,7 +24126,7 @@
         <v>45372</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24199,7 +24199,7 @@
         <v>44746</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24272,7 +24272,7 @@
         <v>44981</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24345,7 +24345,7 @@
         <v>45412</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24418,7 +24418,7 @@
         <v>44896</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24491,7 +24491,7 @@
         <v>45194</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24564,7 +24564,7 @@
         <v>45246</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24637,7 +24637,7 @@
         <v>45140</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24710,7 +24710,7 @@
         <v>45112</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24783,7 +24783,7 @@
         <v>45019</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24856,7 +24856,7 @@
         <v>45219</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24929,7 +24929,7 @@
         <v>44959</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25002,7 +25002,7 @@
         <v>45714</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25075,7 +25075,7 @@
         <v>45168</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25148,7 +25148,7 @@
         <v>45222</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25221,7 +25221,7 @@
         <v>45244</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25294,7 +25294,7 @@
         <v>45166</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25367,7 +25367,7 @@
         <v>45611</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25440,7 +25440,7 @@
         <v>45162</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25513,7 +25513,7 @@
         <v>45162</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25586,7 +25586,7 @@
         <v>45090</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25659,7 +25659,7 @@
         <v>44679</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25732,7 +25732,7 @@
         <v>44963</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25805,7 +25805,7 @@
         <v>44963</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25878,7 +25878,7 @@
         <v>45128</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25951,7 +25951,7 @@
         <v>44963</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26024,7 +26024,7 @@
         <v>44866</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26097,7 +26097,7 @@
         <v>45304</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26170,7 +26170,7 @@
         <v>44529</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26243,7 +26243,7 @@
         <v>45686</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26316,7 +26316,7 @@
         <v>45686</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26389,7 +26389,7 @@
         <v>45278</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26462,7 +26462,7 @@
         <v>45111</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26535,7 +26535,7 @@
         <v>45245</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26608,7 +26608,7 @@
         <v>44678</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26681,7 +26681,7 @@
         <v>44915</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26754,7 +26754,7 @@
         <v>45104</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26827,7 +26827,7 @@
         <v>45304</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26900,7 +26900,7 @@
         <v>45236</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26973,7 +26973,7 @@
         <v>45236</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27046,7 +27046,7 @@
         <v>45190</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27119,7 +27119,7 @@
         <v>45279</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27192,7 +27192,7 @@
         <v>45753</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27265,7 +27265,7 @@
         <v>45317</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27338,7 +27338,7 @@
         <v>45121</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27411,7 +27411,7 @@
         <v>45121</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27484,7 +27484,7 @@
         <v>45121</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27557,7 +27557,7 @@
         <v>45638</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27630,7 +27630,7 @@
         <v>44537</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27703,7 +27703,7 @@
         <v>44950</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27776,7 +27776,7 @@
         <v>45169</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27849,7 +27849,7 @@
         <v>45036</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27922,7 +27922,7 @@
         <v>45194</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27995,7 +27995,7 @@
         <v>45048</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28068,7 +28068,7 @@
         <v>45230</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28141,7 +28141,7 @@
         <v>45240</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28214,7 +28214,7 @@
         <v>45463</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28287,7 +28287,7 @@
         <v>45154</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28360,7 +28360,7 @@
         <v>45715</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28433,7 +28433,7 @@
         <v>45769</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28506,7 +28506,7 @@
         <v>45328</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28579,7 +28579,7 @@
         <v>45328</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28652,7 +28652,7 @@
         <v>45194</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28725,7 +28725,7 @@
         <v>44922</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28798,7 +28798,7 @@
         <v>45632</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28871,7 +28871,7 @@
         <v>45058</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28944,7 +28944,7 @@
         <v>44908</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29017,7 +29017,7 @@
         <v>45446</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29090,7 +29090,7 @@
         <v>45281</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29163,7 +29163,7 @@
         <v>45274</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29236,7 +29236,7 @@
         <v>45594</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29314,7 +29314,7 @@
         <v>45594</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29392,7 +29392,7 @@
         <v>45611</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29465,7 +29465,7 @@
         <v>45281</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29538,7 +29538,7 @@
         <v>45883</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29611,7 +29611,7 @@
         <v>45883</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29684,7 +29684,7 @@
         <v>45827</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29757,7 +29757,7 @@
         <v>45201</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29830,7 +29830,7 @@
         <v>45030</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29903,7 +29903,7 @@
         <v>45638</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29976,7 +29976,7 @@
         <v>45743</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30049,7 +30049,7 @@
         <v>45210</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30122,7 +30122,7 @@
         <v>45791</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30195,7 +30195,7 @@
         <v>45112</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30268,7 +30268,7 @@
         <v>44966</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30341,7 +30341,7 @@
         <v>45670</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30414,7 +30414,7 @@
         <v>45280</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30487,7 +30487,7 @@
         <v>45387</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30560,7 +30560,7 @@
         <v>45560</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30633,7 +30633,7 @@
         <v>45833</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30706,7 +30706,7 @@
         <v>45091</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30784,7 +30784,7 @@
         <v>45225</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30857,7 +30857,7 @@
         <v>45127</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30930,7 +30930,7 @@
         <v>44741</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31003,7 +31003,7 @@
         <v>44741</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31076,7 +31076,7 @@
         <v>45782</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31149,7 +31149,7 @@
         <v>45715</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31227,7 +31227,7 @@
         <v>44687</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31300,7 +31300,7 @@
         <v>45909</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31373,7 +31373,7 @@
         <v>44880</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31446,7 +31446,7 @@
         <v>45775</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31519,7 +31519,7 @@
         <v>45436</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31592,7 +31592,7 @@
         <v>45260</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31665,7 +31665,7 @@
         <v>45148</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31738,7 +31738,7 @@
         <v>45148</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31811,7 +31811,7 @@
         <v>44545</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31884,7 +31884,7 @@
         <v>45835</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31957,7 +31957,7 @@
         <v>45091</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32030,7 +32030,7 @@
         <v>44487</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32103,7 +32103,7 @@
         <v>45390</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32176,7 +32176,7 @@
         <v>45841</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32249,7 +32249,7 @@
         <v>45124</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32322,7 +32322,7 @@
         <v>45826</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32400,7 +32400,7 @@
         <v>45385</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32478,7 +32478,7 @@
         <v>45281</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32551,7 +32551,7 @@
         <v>45960</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32624,7 +32624,7 @@
         <v>45426</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32697,7 +32697,7 @@
         <v>44547</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32770,7 +32770,7 @@
         <v>45905</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32843,7 +32843,7 @@
         <v>45890</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32916,7 +32916,7 @@
         <v>45342</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32989,7 +32989,7 @@
         <v>45895</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33062,7 +33062,7 @@
         <v>45894</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33135,7 +33135,7 @@
         <v>45161</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33208,7 +33208,7 @@
         <v>45240</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33281,7 +33281,7 @@
         <v>45049</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33354,7 +33354,7 @@
         <v>45856</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33427,7 +33427,7 @@
         <v>45244</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33500,7 +33500,7 @@
         <v>45629</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33573,7 +33573,7 @@
         <v>45846</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33646,7 +33646,7 @@
         <v>45599</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33719,7 +33719,7 @@
         <v>45145</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33792,7 +33792,7 @@
         <v>45897</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33870,7 +33870,7 @@
         <v>45222</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33943,7 +33943,7 @@
         <v>44845</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34016,7 +34016,7 @@
         <v>45698</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34089,7 +34089,7 @@
         <v>45169</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34162,7 +34162,7 @@
         <v>45754</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34235,7 +34235,7 @@
         <v>44711</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34308,7 +34308,7 @@
         <v>45622</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34381,7 +34381,7 @@
         <v>45288</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34454,7 +34454,7 @@
         <v>45229</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34527,7 +34527,7 @@
         <v>45153</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34600,7 +34600,7 @@
         <v>45278</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34673,7 +34673,7 @@
         <v>44938</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34746,7 +34746,7 @@
         <v>45902</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34819,7 +34819,7 @@
         <v>45810</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34897,7 +34897,7 @@
         <v>45104</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34970,7 +34970,7 @@
         <v>45702</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35043,7 +35043,7 @@
         <v>45719</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35116,7 +35116,7 @@
         <v>45645</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35189,7 +35189,7 @@
         <v>45835</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35262,7 +35262,7 @@
         <v>45387</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35335,7 +35335,7 @@
         <v>45902</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35408,7 +35408,7 @@
         <v>45827</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35481,7 +35481,7 @@
         <v>45818</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35554,7 +35554,7 @@
         <v>45810</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35632,7 +35632,7 @@
         <v>45902</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35705,7 +35705,7 @@
         <v>45905</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35778,7 +35778,7 @@
         <v>44522</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35851,7 +35851,7 @@
         <v>45909</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35924,7 +35924,7 @@
         <v>45329</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35997,7 +35997,7 @@
         <v>45113</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36070,7 +36070,7 @@
         <v>45686</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36143,7 +36143,7 @@
         <v>45911</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36216,7 +36216,7 @@
         <v>45910</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36289,7 +36289,7 @@
         <v>45787</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36362,7 +36362,7 @@
         <v>45579</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36435,7 +36435,7 @@
         <v>44577</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36508,7 +36508,7 @@
         <v>45419</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36581,7 +36581,7 @@
         <v>45513</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36654,7 +36654,7 @@
         <v>45877</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36727,7 +36727,7 @@
         <v>45215</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36800,7 +36800,7 @@
         <v>44532</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36873,7 +36873,7 @@
         <v>45540</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36946,7 +36946,7 @@
         <v>45916</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37019,7 +37019,7 @@
         <v>45224</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37097,7 +37097,7 @@
         <v>44641</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37170,7 +37170,7 @@
         <v>45918</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37243,7 +37243,7 @@
         <v>45070</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37316,7 +37316,7 @@
         <v>45918</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37389,7 +37389,7 @@
         <v>45918</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37462,7 +37462,7 @@
         <v>45128</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37535,7 +37535,7 @@
         <v>45259</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37608,7 +37608,7 @@
         <v>45309</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37681,7 +37681,7 @@
         <v>45309</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37754,7 +37754,7 @@
         <v>45488</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37827,7 +37827,7 @@
         <v>45009</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37905,7 +37905,7 @@
         <v>45924</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -37978,7 +37978,7 @@
         <v>45925</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38051,7 +38051,7 @@
         <v>45686</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38124,7 +38124,7 @@
         <v>45103</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38197,7 +38197,7 @@
         <v>44858</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38270,7 +38270,7 @@
         <v>45253</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38343,7 +38343,7 @@
         <v>45250</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38416,7 +38416,7 @@
         <v>45016</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38489,7 +38489,7 @@
         <v>45670</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38562,7 +38562,7 @@
         <v>45250</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38635,7 +38635,7 @@
         <v>44986</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38708,7 +38708,7 @@
         <v>46146</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38781,7 +38781,7 @@
         <v>46146</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38854,7 +38854,7 @@
         <v>45937</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -38927,7 +38927,7 @@
         <v>46146</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39000,7 +39000,7 @@
         <v>45937</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39073,7 +39073,7 @@
         <v>46147</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39146,7 +39146,7 @@
         <v>46147</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39219,7 +39219,7 @@
         <v>46147</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39292,7 +39292,7 @@
         <v>45896</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39365,7 +39365,7 @@
         <v>45183</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39438,7 +39438,7 @@
         <v>46147</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39511,7 +39511,7 @@
         <v>46147</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39584,7 +39584,7 @@
         <v>44977</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39657,7 +39657,7 @@
         <v>45114</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39730,7 +39730,7 @@
         <v>45114</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39803,7 +39803,7 @@
         <v>45296</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -39876,7 +39876,7 @@
         <v>46021</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -39949,7 +39949,7 @@
         <v>45181</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40022,7 +40022,7 @@
         <v>45090</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40095,7 +40095,7 @@
         <v>44867</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40168,7 +40168,7 @@
         <v>45597</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40241,7 +40241,7 @@
         <v>45401</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40314,7 +40314,7 @@
         <v>46149</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40387,7 +40387,7 @@
         <v>45685</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40460,7 +40460,7 @@
         <v>45397</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40533,7 +40533,7 @@
         <v>44972</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40606,7 +40606,7 @@
         <v>46148</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -40679,7 +40679,7 @@
         <v>46021</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40752,7 +40752,7 @@
         <v>45950</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -40825,7 +40825,7 @@
         <v>44928</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -40898,7 +40898,7 @@
         <v>45923</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -40971,7 +40971,7 @@
         <v>45568</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41044,7 +41044,7 @@
         <v>46153</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41117,7 +41117,7 @@
         <v>45061</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41190,7 +41190,7 @@
         <v>45952</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41263,7 +41263,7 @@
         <v>44904</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41336,7 +41336,7 @@
         <v>44904</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41409,7 +41409,7 @@
         <v>45420</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -41482,7 +41482,7 @@
         <v>45504</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -41555,7 +41555,7 @@
         <v>45583</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -41633,7 +41633,7 @@
         <v>45753</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -41706,7 +41706,7 @@
         <v>45617</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -41779,7 +41779,7 @@
         <v>45946</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -41852,7 +41852,7 @@
         <v>44670</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -41925,7 +41925,7 @@
         <v>45953</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -41998,7 +41998,7 @@
         <v>45324</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42071,7 +42071,7 @@
         <v>45029</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42144,7 +42144,7 @@
         <v>45964</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42217,7 +42217,7 @@
         <v>44651</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42290,7 +42290,7 @@
         <v>45533</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42363,7 +42363,7 @@
         <v>45924</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42436,7 +42436,7 @@
         <v>45147</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42509,7 +42509,7 @@
         <v>45995</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -42582,7 +42582,7 @@
         <v>45789</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -42655,7 +42655,7 @@
         <v>45392</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -42733,7 +42733,7 @@
         <v>45392</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -42806,7 +42806,7 @@
         <v>45103</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -42879,7 +42879,7 @@
         <v>45103</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -42952,7 +42952,7 @@
         <v>45103</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43025,7 +43025,7 @@
         <v>45247</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43098,7 +43098,7 @@
         <v>45559</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43171,7 +43171,7 @@
         <v>45971</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -43244,7 +43244,7 @@
         <v>45579</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -43317,7 +43317,7 @@
         <v>45427</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -43390,7 +43390,7 @@
         <v>45250</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -43463,7 +43463,7 @@
         <v>45733</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -43536,7 +43536,7 @@
         <v>45973</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -43609,7 +43609,7 @@
         <v>45973</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -43682,7 +43682,7 @@
         <v>44552</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -43755,7 +43755,7 @@
         <v>45517</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -43828,7 +43828,7 @@
         <v>45180</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -43901,7 +43901,7 @@
         <v>45580</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -43974,7 +43974,7 @@
         <v>44761</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44052,7 +44052,7 @@
         <v>45477</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44130,7 +44130,7 @@
         <v>45979</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -44203,7 +44203,7 @@
         <v>45979</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -44276,7 +44276,7 @@
         <v>45980</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -44349,7 +44349,7 @@
         <v>45559</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -44422,7 +44422,7 @@
         <v>45153</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -44495,7 +44495,7 @@
         <v>45631</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -44568,7 +44568,7 @@
         <v>45421</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -44641,7 +44641,7 @@
         <v>44811</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -44714,7 +44714,7 @@
         <v>45113</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -44787,7 +44787,7 @@
         <v>45113</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -44860,7 +44860,7 @@
         <v>46161</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -44933,7 +44933,7 @@
         <v>44896</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45006,7 +45006,7 @@
         <v>45538</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -45084,7 +45084,7 @@
         <v>44903</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -45157,7 +45157,7 @@
         <v>44502</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -45230,7 +45230,7 @@
         <v>45538</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -45303,7 +45303,7 @@
         <v>45301</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -45376,7 +45376,7 @@
         <v>45623</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -45449,7 +45449,7 @@
         <v>44595</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -45522,7 +45522,7 @@
         <v>45330</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -45600,7 +45600,7 @@
         <v>45250</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -45673,7 +45673,7 @@
         <v>46162</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -45746,7 +45746,7 @@
         <v>46163</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -45819,7 +45819,7 @@
         <v>46163</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -45892,7 +45892,7 @@
         <v>44592</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -45965,7 +45965,7 @@
         <v>45780</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -46038,7 +46038,7 @@
         <v>46162</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -46111,7 +46111,7 @@
         <v>45722</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -46184,7 +46184,7 @@
         <v>46163</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -46257,7 +46257,7 @@
         <v>46163</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -46330,7 +46330,7 @@
         <v>46163</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -46403,7 +46403,7 @@
         <v>45557</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -46476,7 +46476,7 @@
         <v>46162</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -46549,7 +46549,7 @@
         <v>46163</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -46622,7 +46622,7 @@
         <v>45719</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -46695,7 +46695,7 @@
         <v>45993</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -46768,7 +46768,7 @@
         <v>45993</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -46841,7 +46841,7 @@
         <v>45432</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -46914,7 +46914,7 @@
         <v>44686</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -46987,7 +46987,7 @@
         <v>45988</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -47060,7 +47060,7 @@
         <v>45999</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -47133,7 +47133,7 @@
         <v>46162</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -47206,7 +47206,7 @@
         <v>45400</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -47279,7 +47279,7 @@
         <v>44705</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -47352,7 +47352,7 @@
         <v>45315</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -47425,7 +47425,7 @@
         <v>45065</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -47498,7 +47498,7 @@
         <v>46000</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -47571,7 +47571,7 @@
         <v>44743</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -47644,7 +47644,7 @@
         <v>45121</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -47717,7 +47717,7 @@
         <v>44831</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -47790,7 +47790,7 @@
         <v>46001</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -47863,7 +47863,7 @@
         <v>45302</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -47936,7 +47936,7 @@
         <v>45573</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -48009,7 +48009,7 @@
         <v>44676</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -48087,7 +48087,7 @@
         <v>46167</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -48160,7 +48160,7 @@
         <v>45036</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -48233,7 +48233,7 @@
         <v>45302</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -48306,7 +48306,7 @@
         <v>45812</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -48379,7 +48379,7 @@
         <v>45632</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -48452,7 +48452,7 @@
         <v>45188</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -48525,7 +48525,7 @@
         <v>46007</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -48598,7 +48598,7 @@
         <v>46168</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -48671,7 +48671,7 @@
         <v>45552</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -48744,7 +48744,7 @@
         <v>45181</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -48817,7 +48817,7 @@
         <v>46008</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -48890,7 +48890,7 @@
         <v>45071</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -48968,7 +48968,7 @@
         <v>45558</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -49041,7 +49041,7 @@
         <v>45594</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -49119,7 +49119,7 @@
         <v>45594</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -49197,7 +49197,7 @@
         <v>45594</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -49275,7 +49275,7 @@
         <v>46010</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -49348,7 +49348,7 @@
         <v>46010</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -49421,7 +49421,7 @@
         <v>46010</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -49494,7 +49494,7 @@
         <v>45693</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -49567,7 +49567,7 @@
         <v>45764</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -49640,7 +49640,7 @@
         <v>46019</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -49713,7 +49713,7 @@
         <v>45644</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -49786,7 +49786,7 @@
         <v>45056</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -49859,7 +49859,7 @@
         <v>45037</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -49932,7 +49932,7 @@
         <v>45037</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -50005,7 +50005,7 @@
         <v>46168</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -50078,7 +50078,7 @@
         <v>45933</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -50151,7 +50151,7 @@
         <v>45581</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -50224,7 +50224,7 @@
         <v>44609</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -50297,7 +50297,7 @@
         <v>44652</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -50370,7 +50370,7 @@
         <v>46099</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -50443,7 +50443,7 @@
         <v>44956</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -50516,7 +50516,7 @@
         <v>45300</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -50589,7 +50589,7 @@
         <v>45211</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -50662,7 +50662,7 @@
         <v>46019</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -50735,7 +50735,7 @@
         <v>46029</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -50808,7 +50808,7 @@
         <v>46029</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -50881,7 +50881,7 @@
         <v>45210</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -50954,7 +50954,7 @@
         <v>45533</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -51027,7 +51027,7 @@
         <v>44986</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -51100,7 +51100,7 @@
         <v>44741</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -51173,7 +51173,7 @@
         <v>45338</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -51246,7 +51246,7 @@
         <v>44960</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -51319,7 +51319,7 @@
         <v>46031</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -51397,7 +51397,7 @@
         <v>44843</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -51470,7 +51470,7 @@
         <v>46031</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -51548,7 +51548,7 @@
         <v>46100</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -51621,7 +51621,7 @@
         <v>45665</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -51694,7 +51694,7 @@
         <v>46170</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -51767,7 +51767,7 @@
         <v>46171</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -51840,7 +51840,7 @@
         <v>45216</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -51913,7 +51913,7 @@
         <v>46035</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -51991,7 +51991,7 @@
         <v>46035</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -52069,7 +52069,7 @@
         <v>46035</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -52147,7 +52147,7 @@
         <v>44874</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -52220,7 +52220,7 @@
         <v>44874</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -52293,7 +52293,7 @@
         <v>46036</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -52366,7 +52366,7 @@
         <v>46036</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -52439,7 +52439,7 @@
         <v>44963</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -52512,7 +52512,7 @@
         <v>46036</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -52585,7 +52585,7 @@
         <v>45921</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -52658,7 +52658,7 @@
         <v>46041</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -52731,7 +52731,7 @@
         <v>44600</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -52809,7 +52809,7 @@
         <v>45412</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -52882,7 +52882,7 @@
         <v>45412</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -52955,7 +52955,7 @@
         <v>45757</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -53028,7 +53028,7 @@
         <v>45316</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -53101,7 +53101,7 @@
         <v>45316</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -53174,7 +53174,7 @@
         <v>46112</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -53247,7 +53247,7 @@
         <v>46171</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -53320,7 +53320,7 @@
         <v>45551</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -53393,7 +53393,7 @@
         <v>46043</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -53466,7 +53466,7 @@
         <v>46010</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -53539,7 +53539,7 @@
         <v>44896</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -53612,7 +53612,7 @@
         <v>46045</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -53685,7 +53685,7 @@
         <v>46045</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -53758,7 +53758,7 @@
         <v>45601</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -53831,7 +53831,7 @@
         <v>46171</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -53904,7 +53904,7 @@
         <v>45679</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -53977,7 +53977,7 @@
         <v>46049</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -54050,7 +54050,7 @@
         <v>46048</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -54123,7 +54123,7 @@
         <v>45316</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -54196,7 +54196,7 @@
         <v>46049</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -54269,7 +54269,7 @@
         <v>45140</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -54342,7 +54342,7 @@
         <v>46049</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -54415,7 +54415,7 @@
         <v>46049</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -54488,7 +54488,7 @@
         <v>45446</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -54566,7 +54566,7 @@
         <v>45392</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -54644,7 +54644,7 @@
         <v>46051</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -54717,7 +54717,7 @@
         <v>45166</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -54790,7 +54790,7 @@
         <v>45345</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -54863,7 +54863,7 @@
         <v>44915</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -54936,7 +54936,7 @@
         <v>44972</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -55009,7 +55009,7 @@
         <v>44998</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -55082,7 +55082,7 @@
         <v>46134</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -55155,7 +55155,7 @@
         <v>46134</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -55228,7 +55228,7 @@
         <v>46057</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -55301,7 +55301,7 @@
         <v>45468</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -55374,7 +55374,7 @@
         <v>46056</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -55447,7 +55447,7 @@
         <v>46057</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -55520,7 +55520,7 @@
         <v>46056</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -55593,7 +55593,7 @@
         <v>46057</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -55666,7 +55666,7 @@
         <v>44880</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -55739,7 +55739,7 @@
         <v>46056</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -55812,7 +55812,7 @@
         <v>45676</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -55890,7 +55890,7 @@
         <v>46059</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -55963,7 +55963,7 @@
         <v>46059</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -56036,7 +56036,7 @@
         <v>46059</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -56109,7 +56109,7 @@
         <v>45127</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -56182,7 +56182,7 @@
         <v>45288</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -56255,7 +56255,7 @@
         <v>45022</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -56328,7 +56328,7 @@
         <v>44869</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -56401,7 +56401,7 @@
         <v>46061</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -56474,7 +56474,7 @@
         <v>46134</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -56547,7 +56547,7 @@
         <v>44998</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -56620,7 +56620,7 @@
         <v>46170</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -56693,7 +56693,7 @@
         <v>45217</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -56766,7 +56766,7 @@
         <v>45085</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -56839,7 +56839,7 @@
         <v>44609</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -56912,7 +56912,7 @@
         <v>46073</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -56985,7 +56985,7 @@
         <v>46073</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -57058,7 +57058,7 @@
         <v>46072</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -57131,7 +57131,7 @@
         <v>45722</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -57204,7 +57204,7 @@
         <v>46183</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -57277,7 +57277,7 @@
         <v>45560</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -57350,7 +57350,7 @@
         <v>46183</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -57423,7 +57423,7 @@
         <v>46183</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -57496,7 +57496,7 @@
         <v>44831</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -57569,7 +57569,7 @@
         <v>46075</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -57642,7 +57642,7 @@
         <v>45611</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -57715,7 +57715,7 @@
         <v>46183</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -57788,7 +57788,7 @@
         <v>45679</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -57861,7 +57861,7 @@
         <v>46079</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -57934,7 +57934,7 @@
         <v>45679</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -58007,7 +58007,7 @@
         <v>46079</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -58080,7 +58080,7 @@
         <v>45030</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -58153,7 +58153,7 @@
         <v>46183</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -58226,7 +58226,7 @@
         <v>46084</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -58299,7 +58299,7 @@
         <v>46083</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -58372,7 +58372,7 @@
         <v>45300</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -58445,7 +58445,7 @@
         <v>46083</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -58518,7 +58518,7 @@
         <v>46083</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -58591,7 +58591,7 @@
         <v>46083</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -58664,7 +58664,7 @@
         <v>44774</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -58737,7 +58737,7 @@
         <v>45128</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -58810,7 +58810,7 @@
         <v>45128</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -58883,7 +58883,7 @@
         <v>45111</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -58956,7 +58956,7 @@
         <v>46083</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -59029,7 +59029,7 @@
         <v>45638</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -59102,7 +59102,7 @@
         <v>46188</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -59175,7 +59175,7 @@
         <v>45386</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -59248,7 +59248,7 @@
         <v>46188</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -59321,7 +59321,7 @@
         <v>45165</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -59394,7 +59394,7 @@
         <v>45555</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -59467,7 +59467,7 @@
         <v>45141</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -59540,7 +59540,7 @@
         <v>45141</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -59613,7 +59613,7 @@
         <v>46163</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -59686,7 +59686,7 @@
         <v>46188</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -59759,7 +59759,7 @@
         <v>46087</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -59832,7 +59832,7 @@
         <v>44496</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -59905,7 +59905,7 @@
         <v>45579</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -59978,7 +59978,7 @@
         <v>46189</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -60051,7 +60051,7 @@
         <v>46190</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -60124,7 +60124,7 @@
         <v>45754</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -60197,7 +60197,7 @@
         <v>46191</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -60270,7 +60270,7 @@
         <v>45754</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -60343,7 +60343,7 @@
         <v>46191</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -60416,7 +60416,7 @@
         <v>45924</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -60489,7 +60489,7 @@
         <v>46108</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -60562,7 +60562,7 @@
         <v>46191</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -60635,7 +60635,7 @@
         <v>46191</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -60708,7 +60708,7 @@
         <v>46191</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -60781,7 +60781,7 @@
         <v>46100</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -60854,7 +60854,7 @@
         <v>46100</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -60927,7 +60927,7 @@
         <v>46099</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -61000,7 +61000,7 @@
         <v>46100</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -61073,7 +61073,7 @@
         <v>46100</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -61146,7 +61146,7 @@
         <v>45012</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -61219,7 +61219,7 @@
         <v>46195</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -61292,7 +61292,7 @@
         <v>45222</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -61365,7 +61365,7 @@
         <v>45127</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -61438,7 +61438,7 @@
         <v>46198</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -61511,7 +61511,7 @@
         <v>44867</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -61584,7 +61584,7 @@
         <v>46198</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -61657,7 +61657,7 @@
         <v>46198</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -61730,7 +61730,7 @@
         <v>45552</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -61803,7 +61803,7 @@
         <v>45247</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -61876,7 +61876,7 @@
         <v>45511</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -61949,7 +61949,7 @@
         <v>46198</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -62022,7 +62022,7 @@
         <v>46107</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -62095,7 +62095,7 @@
         <v>44922</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -62168,7 +62168,7 @@
         <v>45048</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -62241,7 +62241,7 @@
         <v>46108</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -62314,7 +62314,7 @@
         <v>45205</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -62387,7 +62387,7 @@
         <v>44501</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -62460,7 +62460,7 @@
         <v>46112</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -62533,7 +62533,7 @@
         <v>46245</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -62606,7 +62606,7 @@
         <v>44769</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -62684,7 +62684,7 @@
         <v>44995</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -62757,7 +62757,7 @@
         <v>44876</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -62835,7 +62835,7 @@
         <v>44769</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -62913,7 +62913,7 @@
         <v>45495</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -62986,7 +62986,7 @@
         <v>44963</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -63059,7 +63059,7 @@
         <v>46112</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -63132,7 +63132,7 @@
         <v>46244</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -63205,7 +63205,7 @@
         <v>45106</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -63278,7 +63278,7 @@
         <v>45385</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -63356,7 +63356,7 @@
         <v>45385</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -63434,7 +63434,7 @@
         <v>44900</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -63507,7 +63507,7 @@
         <v>44473</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -63580,7 +63580,7 @@
         <v>45199</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -63653,7 +63653,7 @@
         <v>46113</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -63726,7 +63726,7 @@
         <v>46199</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -63799,7 +63799,7 @@
         <v>45070</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -63872,7 +63872,7 @@
         <v>45594</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -63950,7 +63950,7 @@
         <v>44494</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -64023,7 +64023,7 @@
         <v>45594</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -64101,7 +64101,7 @@
         <v>46119</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -64174,7 +64174,7 @@
         <v>45754</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -64247,7 +64247,7 @@
         <v>45224</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -64320,7 +64320,7 @@
         <v>45161</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -64393,7 +64393,7 @@
         <v>46245</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -64466,7 +64466,7 @@
         <v>46244</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -64544,7 +64544,7 @@
         <v>46244</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -64622,7 +64622,7 @@
         <v>44711</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -64695,7 +64695,7 @@
         <v>46244</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -64773,7 +64773,7 @@
         <v>44782</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -64851,7 +64851,7 @@
         <v>45572</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -64924,7 +64924,7 @@
         <v>46199</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -64997,7 +64997,7 @@
         <v>46244</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -65075,7 +65075,7 @@
         <v>45204</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -65148,7 +65148,7 @@
         <v>46244</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -65221,7 +65221,7 @@
         <v>46244</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -65299,7 +65299,7 @@
         <v>46244</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -65377,7 +65377,7 @@
         <v>45443</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -65450,7 +65450,7 @@
         <v>46129</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -65523,7 +65523,7 @@
         <v>45726</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -65596,7 +65596,7 @@
         <v>45139</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -65669,7 +65669,7 @@
         <v>45373</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -65742,7 +65742,7 @@
         <v>45369</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -65815,7 +65815,7 @@
         <v>45127</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -65888,7 +65888,7 @@
         <v>45127</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -65961,7 +65961,7 @@
         <v>45372</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -66034,7 +66034,7 @@
         <v>45219</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -66107,7 +66107,7 @@
         <v>45594</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -66185,7 +66185,7 @@
         <v>45594</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -66263,7 +66263,7 @@
         <v>44690</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -66336,7 +66336,7 @@
         <v>45881</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -66409,7 +66409,7 @@
         <v>45385</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -66487,7 +66487,7 @@
         <v>45702</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -66560,7 +66560,7 @@
         <v>45000</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -66633,7 +66633,7 @@
         <v>45446</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -66706,7 +66706,7 @@
         <v>44858</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -66779,7 +66779,7 @@
         <v>45677</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -66852,7 +66852,7 @@
         <v>45582</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -66925,7 +66925,7 @@
         <v>45594</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -67003,7 +67003,7 @@
         <v>45594</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -67081,7 +67081,7 @@
         <v>45594</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -67159,7 +67159,7 @@
         <v>45594</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -67237,7 +67237,7 @@
         <v>45594</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -67315,7 +67315,7 @@
         <v>45594</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -67393,7 +67393,7 @@
         <v>45302</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -67466,7 +67466,7 @@
         <v>45302</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -67539,7 +67539,7 @@
         <v>45923</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -67612,7 +67612,7 @@
         <v>44959</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -67685,7 +67685,7 @@
         <v>46199</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -67758,7 +67758,7 @@
         <v>44894</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -67831,7 +67831,7 @@
         <v>45267</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -67904,7 +67904,7 @@
         <v>45939</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -67977,7 +67977,7 @@
         <v>45198</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -68050,7 +68050,7 @@
         <v>44651</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -68123,7 +68123,7 @@
         <v>44468</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -68196,7 +68196,7 @@
         <v>45894</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -68269,7 +68269,7 @@
         <v>45923</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -68342,7 +68342,7 @@
         <v>45509</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -68415,7 +68415,7 @@
         <v>45541</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -68488,7 +68488,7 @@
         <v>46246</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -68566,7 +68566,7 @@
         <v>45447</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -68639,7 +68639,7 @@
         <v>46199</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -68712,7 +68712,7 @@
         <v>46199</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -68785,7 +68785,7 @@
         <v>45378</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -68858,7 +68858,7 @@
         <v>45495</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -68931,7 +68931,7 @@
         <v>45446</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -69004,7 +69004,7 @@
         <v>45008</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -69077,7 +69077,7 @@
         <v>44739</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -69150,7 +69150,7 @@
         <v>45519</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -69223,7 +69223,7 @@
         <v>46206</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -69301,7 +69301,7 @@
         <v>45176</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -69374,7 +69374,7 @@
         <v>45176</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -69447,7 +69447,7 @@
         <v>45644</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -69520,7 +69520,7 @@
         <v>44812</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -69593,7 +69593,7 @@
         <v>44992</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -69666,7 +69666,7 @@
         <v>45139</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -69739,7 +69739,7 @@
         <v>46205</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -69812,7 +69812,7 @@
         <v>45244</v>
       </c>
       <c r="E900" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -69885,7 +69885,7 @@
         <v>46205</v>
       </c>
       <c r="E901" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>
@@ -69958,7 +69958,7 @@
         <v>46252</v>
       </c>
       <c r="E902" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F902" t="inlineStr">
         <is>
@@ -70031,7 +70031,7 @@
         <v>45232</v>
       </c>
       <c r="E903" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F903" t="inlineStr">
         <is>
@@ -70104,7 +70104,7 @@
         <v>45705</v>
       </c>
       <c r="E904" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F904" t="inlineStr">
         <is>
@@ -70182,7 +70182,7 @@
         <v>45078</v>
       </c>
       <c r="E905" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F905" t="inlineStr">
         <is>
@@ -70260,7 +70260,7 @@
         <v>45737</v>
       </c>
       <c r="E906" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F906" t="inlineStr">
         <is>
@@ -70333,7 +70333,7 @@
         <v>45108</v>
       </c>
       <c r="E907" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F907" t="inlineStr">
         <is>
@@ -70406,7 +70406,7 @@
         <v>46253</v>
       </c>
       <c r="E908" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F908" t="inlineStr">
         <is>
@@ -70479,7 +70479,7 @@
         <v>46210</v>
       </c>
       <c r="E909" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F909" t="inlineStr">
         <is>
@@ -70557,7 +70557,7 @@
         <v>46252</v>
       </c>
       <c r="E910" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F910" t="inlineStr">
         <is>
@@ -70630,7 +70630,7 @@
         <v>44749</v>
       </c>
       <c r="E911" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F911" t="inlineStr">
         <is>
@@ -70703,7 +70703,7 @@
         <v>46210</v>
       </c>
       <c r="E912" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F912" t="inlineStr">
         <is>
@@ -70781,7 +70781,7 @@
         <v>45468</v>
       </c>
       <c r="E913" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F913" t="inlineStr">
         <is>
@@ -70854,7 +70854,7 @@
         <v>45127</v>
       </c>
       <c r="E914" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F914" t="inlineStr">
         <is>
@@ -70927,7 +70927,7 @@
         <v>45273</v>
       </c>
       <c r="E915" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F915" t="inlineStr">
         <is>
@@ -71000,7 +71000,7 @@
         <v>45392</v>
       </c>
       <c r="E916" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F916" t="inlineStr">
         <is>
@@ -71078,7 +71078,7 @@
         <v>45608</v>
       </c>
       <c r="E917" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F917" t="inlineStr">
         <is>
@@ -71151,7 +71151,7 @@
         <v>44894</v>
       </c>
       <c r="E918" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F918" t="inlineStr">
         <is>
@@ -71224,7 +71224,7 @@
         <v>44677</v>
       </c>
       <c r="E919" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F919" t="inlineStr">
         <is>
@@ -71297,7 +71297,7 @@
         <v>45089</v>
       </c>
       <c r="E920" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F920" t="inlineStr">
         <is>
@@ -71370,7 +71370,7 @@
         <v>45236</v>
       </c>
       <c r="E921" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F921" t="inlineStr">
         <is>
@@ -71443,7 +71443,7 @@
         <v>45392</v>
       </c>
       <c r="E922" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F922" t="inlineStr">
         <is>
@@ -71521,7 +71521,7 @@
         <v>45342</v>
       </c>
       <c r="E923" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F923" t="inlineStr">
         <is>
@@ -71594,7 +71594,7 @@
         <v>45189</v>
       </c>
       <c r="E924" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F924" t="inlineStr">
         <is>
@@ -71667,7 +71667,7 @@
         <v>45189</v>
       </c>
       <c r="E925" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F925" t="inlineStr">
         <is>
@@ -71740,7 +71740,7 @@
         <v>44909</v>
       </c>
       <c r="E926" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F926" t="inlineStr">
         <is>
@@ -71818,7 +71818,7 @@
         <v>45190</v>
       </c>
       <c r="E927" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F927" t="inlineStr">
         <is>
@@ -71891,7 +71891,7 @@
         <v>45714</v>
       </c>
       <c r="E928" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F928" t="inlineStr">
         <is>
@@ -71964,7 +71964,7 @@
         <v>44599</v>
       </c>
       <c r="E929" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F929" t="inlineStr">
         <is>
@@ -72037,7 +72037,7 @@
         <v>45614</v>
       </c>
       <c r="E930" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F930" t="inlineStr">
         <is>
@@ -72110,7 +72110,7 @@
         <v>46258</v>
       </c>
       <c r="E931" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F931" t="inlineStr">
         <is>
@@ -72183,7 +72183,7 @@
         <v>45692</v>
       </c>
       <c r="E932" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F932" t="inlineStr">
         <is>
@@ -72256,7 +72256,7 @@
         <v>45384</v>
       </c>
       <c r="E933" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F933" t="inlineStr">
         <is>
@@ -72329,7 +72329,7 @@
         <v>45448</v>
       </c>
       <c r="E934" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F934" t="inlineStr">
         <is>
@@ -72402,7 +72402,7 @@
         <v>45294</v>
       </c>
       <c r="E935" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F935" t="inlineStr">
         <is>
@@ -72475,7 +72475,7 @@
         <v>46260</v>
       </c>
       <c r="E936" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F936" t="inlineStr">
         <is>
@@ -72548,7 +72548,7 @@
         <v>46261</v>
       </c>
       <c r="E937" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F937" t="inlineStr">
         <is>
@@ -72621,7 +72621,7 @@
         <v>45219</v>
       </c>
       <c r="E938" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F938" t="inlineStr">
         <is>
@@ -72694,7 +72694,7 @@
         <v>45147</v>
       </c>
       <c r="E939" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F939" t="inlineStr">
         <is>
@@ -72767,7 +72767,7 @@
         <v>44536</v>
       </c>
       <c r="E940" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F940" t="inlineStr">
         <is>
@@ -72840,7 +72840,7 @@
         <v>44732</v>
       </c>
       <c r="E941" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F941" t="inlineStr">
         <is>
@@ -72913,7 +72913,7 @@
         <v>46170</v>
       </c>
       <c r="E942" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F942" t="inlineStr">
         <is>
@@ -72986,7 +72986,7 @@
         <v>46262</v>
       </c>
       <c r="E943" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F943" t="inlineStr">
         <is>
@@ -73059,7 +73059,7 @@
         <v>45198</v>
       </c>
       <c r="E944" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F944" t="inlineStr">
         <is>
@@ -73132,7 +73132,7 @@
         <v>45644</v>
       </c>
       <c r="E945" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F945" t="inlineStr">
         <is>
@@ -73205,7 +73205,7 @@
         <v>45014</v>
       </c>
       <c r="E946" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F946" t="inlineStr">
         <is>
@@ -73283,7 +73283,7 @@
         <v>44897</v>
       </c>
       <c r="E947" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F947" t="inlineStr">
         <is>
@@ -73356,7 +73356,7 @@
         <v>46183</v>
       </c>
       <c r="E948" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F948" t="inlineStr">
         <is>
@@ -73429,7 +73429,7 @@
         <v>45014</v>
       </c>
       <c r="E949" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F949" t="inlineStr">
         <is>
@@ -73502,7 +73502,7 @@
         <v>45743</v>
       </c>
       <c r="E950" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F950" t="inlineStr">
         <is>
@@ -73575,7 +73575,7 @@
         <v>45534</v>
       </c>
       <c r="E951" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F951" t="inlineStr">
         <is>
@@ -73648,7 +73648,7 @@
         <v>45702</v>
       </c>
       <c r="E952" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F952" t="inlineStr">
         <is>
@@ -73721,7 +73721,7 @@
         <v>45219</v>
       </c>
       <c r="E953" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F953" t="inlineStr">
         <is>
@@ -73794,7 +73794,7 @@
         <v>44676</v>
       </c>
       <c r="E954" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F954" t="inlineStr">
         <is>
@@ -73872,7 +73872,7 @@
         <v>46269</v>
       </c>
       <c r="E955" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F955" t="inlineStr">
         <is>
@@ -73945,7 +73945,7 @@
         <v>45121</v>
       </c>
       <c r="E956" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F956" t="inlineStr">
         <is>
@@ -74018,7 +74018,7 @@
         <v>45121</v>
       </c>
       <c r="E957" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F957" t="inlineStr">
         <is>
@@ -74091,7 +74091,7 @@
         <v>45121</v>
       </c>
       <c r="E958" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F958" t="inlineStr">
         <is>
@@ -74164,7 +74164,7 @@
         <v>45440</v>
       </c>
       <c r="E959" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F959" t="inlineStr">
         <is>
@@ -74237,7 +74237,7 @@
         <v>46230</v>
       </c>
       <c r="E960" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F960" t="inlineStr">
         <is>
@@ -74310,7 +74310,7 @@
         <v>45645</v>
       </c>
       <c r="E961" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F961" t="inlineStr">
         <is>
@@ -74383,7 +74383,7 @@
         <v>45692</v>
       </c>
       <c r="E962" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F962" t="inlineStr">
         <is>
@@ -74456,7 +74456,7 @@
         <v>45028</v>
       </c>
       <c r="E963" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F963" t="inlineStr">
         <is>
@@ -74529,7 +74529,7 @@
         <v>45777</v>
       </c>
       <c r="E964" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F964" t="inlineStr">
         <is>
@@ -74607,7 +74607,7 @@
         <v>45777</v>
       </c>
       <c r="E965" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F965" t="inlineStr">
         <is>
@@ -74685,7 +74685,7 @@
         <v>45194</v>
       </c>
       <c r="E966" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F966" t="inlineStr">
         <is>
@@ -74758,7 +74758,7 @@
         <v>45547</v>
       </c>
       <c r="E967" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F967" t="inlineStr">
         <is>
@@ -74831,7 +74831,7 @@
         <v>45777</v>
       </c>
       <c r="E968" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F968" t="inlineStr">
         <is>
@@ -74909,7 +74909,7 @@
         <v>46216</v>
       </c>
       <c r="E969" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F969" t="inlineStr">
         <is>
@@ -74982,7 +74982,7 @@
         <v>46216</v>
       </c>
       <c r="E970" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F970" t="inlineStr">
         <is>
@@ -75055,7 +75055,7 @@
         <v>45519</v>
       </c>
       <c r="E971" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F971" t="inlineStr">
         <is>
@@ -75128,7 +75128,7 @@
         <v>45780</v>
       </c>
       <c r="E972" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F972" t="inlineStr">
         <is>
@@ -75201,7 +75201,7 @@
         <v>45780</v>
       </c>
       <c r="E973" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F973" t="inlineStr">
         <is>
@@ -75274,7 +75274,7 @@
         <v>45478</v>
       </c>
       <c r="E974" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F974" t="inlineStr">
         <is>
@@ -75347,7 +75347,7 @@
         <v>45546</v>
       </c>
       <c r="E975" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F975" t="inlineStr">
         <is>
@@ -75420,7 +75420,7 @@
         <v>45783</v>
       </c>
       <c r="E976" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F976" t="inlineStr">
         <is>
@@ -75493,7 +75493,7 @@
         <v>45782</v>
       </c>
       <c r="E977" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F977" t="inlineStr">
         <is>
@@ -75566,7 +75566,7 @@
         <v>46272</v>
       </c>
       <c r="E978" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F978" t="inlineStr">
         <is>
@@ -75639,7 +75639,7 @@
         <v>46272</v>
       </c>
       <c r="E979" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F979" t="inlineStr">
         <is>
@@ -75712,7 +75712,7 @@
         <v>46216</v>
       </c>
       <c r="E980" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F980" t="inlineStr">
         <is>
@@ -75785,7 +75785,7 @@
         <v>46232</v>
       </c>
       <c r="E981" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F981" t="inlineStr">
         <is>
@@ -75858,7 +75858,7 @@
         <v>46232</v>
       </c>
       <c r="E982" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F982" t="inlineStr">
         <is>
@@ -75931,7 +75931,7 @@
         <v>46237</v>
       </c>
       <c r="E983" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F983" t="inlineStr">
         <is>
@@ -76004,7 +76004,7 @@
         <v>45534</v>
       </c>
       <c r="E984" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F984" t="inlineStr">
         <is>
@@ -76077,7 +76077,7 @@
         <v>45108</v>
       </c>
       <c r="E985" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F985" t="inlineStr">
         <is>
@@ -76150,7 +76150,7 @@
         <v>44781</v>
       </c>
       <c r="E986" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F986" t="inlineStr">
         <is>
@@ -76228,7 +76228,7 @@
         <v>46276</v>
       </c>
       <c r="E987" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F987" t="inlineStr">
         <is>
@@ -76301,7 +76301,7 @@
         <v>45642</v>
       </c>
       <c r="E988" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F988" t="inlineStr">
         <is>
@@ -76374,7 +76374,7 @@
         <v>46276</v>
       </c>
       <c r="E989" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F989" t="inlineStr">
         <is>
@@ -76447,7 +76447,7 @@
         <v>45614</v>
       </c>
       <c r="E990" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F990" t="inlineStr">
         <is>
@@ -76520,7 +76520,7 @@
         <v>45716</v>
       </c>
       <c r="E991" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F991" t="inlineStr">
         <is>
@@ -76593,7 +76593,7 @@
         <v>45608</v>
       </c>
       <c r="E992" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F992" t="inlineStr">
         <is>
@@ -76666,7 +76666,7 @@
         <v>46237</v>
       </c>
       <c r="E993" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F993" t="inlineStr">
         <is>
@@ -76739,7 +76739,7 @@
         <v>46279</v>
       </c>
       <c r="E994" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F994" t="inlineStr">
         <is>
@@ -76812,7 +76812,7 @@
         <v>46279</v>
       </c>
       <c r="E995" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F995" t="inlineStr">
         <is>
@@ -76885,7 +76885,7 @@
         <v>46281</v>
       </c>
       <c r="E996" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F996" t="inlineStr">
         <is>
@@ -76958,7 +76958,7 @@
         <v>45716</v>
       </c>
       <c r="E997" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F997" t="inlineStr">
         <is>
@@ -77031,7 +77031,7 @@
         <v>45791</v>
       </c>
       <c r="E998" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F998" t="inlineStr">
         <is>
@@ -77104,7 +77104,7 @@
         <v>45796</v>
       </c>
       <c r="E999" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F999" t="inlineStr">
         <is>
@@ -77177,7 +77177,7 @@
         <v>44824</v>
       </c>
       <c r="E1000" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1000" t="inlineStr">
         <is>
@@ -77250,7 +77250,7 @@
         <v>45574</v>
       </c>
       <c r="E1001" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1001" t="inlineStr">
         <is>
@@ -77323,7 +77323,7 @@
         <v>45764</v>
       </c>
       <c r="E1002" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1002" t="inlineStr">
         <is>
@@ -77396,7 +77396,7 @@
         <v>46239</v>
       </c>
       <c r="E1003" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1003" t="inlineStr">
         <is>
@@ -77469,7 +77469,7 @@
         <v>45803</v>
       </c>
       <c r="E1004" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1004" t="inlineStr">
         <is>
@@ -77542,7 +77542,7 @@
         <v>46245</v>
       </c>
       <c r="E1005" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1005" t="inlineStr">
         <is>
@@ -77615,7 +77615,7 @@
         <v>45665</v>
       </c>
       <c r="E1006" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1006" t="inlineStr">
         <is>
@@ -77688,7 +77688,7 @@
         <v>45749</v>
       </c>
       <c r="E1007" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1007" t="inlineStr">
         <is>
@@ -77761,7 +77761,7 @@
         <v>45805</v>
       </c>
       <c r="E1008" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1008" t="inlineStr">
         <is>
@@ -77834,7 +77834,7 @@
         <v>45763</v>
       </c>
       <c r="E1009" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1009" t="inlineStr">
         <is>
@@ -77907,7 +77907,7 @@
         <v>45447</v>
       </c>
       <c r="E1010" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1010" t="inlineStr">
         <is>
@@ -77980,7 +77980,7 @@
         <v>45817</v>
       </c>
       <c r="E1011" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1011" t="inlineStr">
         <is>
@@ -78053,7 +78053,7 @@
         <v>45769</v>
       </c>
       <c r="E1012" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1012" t="inlineStr">
         <is>
@@ -78126,7 +78126,7 @@
         <v>45820</v>
       </c>
       <c r="E1013" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1013" t="inlineStr">
         <is>
@@ -78199,7 +78199,7 @@
         <v>45820</v>
       </c>
       <c r="E1014" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1014" t="inlineStr">
         <is>
@@ -78272,7 +78272,7 @@
         <v>45820</v>
       </c>
       <c r="E1015" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1015" t="inlineStr">
         <is>
@@ -78345,7 +78345,7 @@
         <v>45818</v>
       </c>
       <c r="E1016" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1016" t="inlineStr">
         <is>
@@ -78418,7 +78418,7 @@
         <v>45825</v>
       </c>
       <c r="E1017" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1017" t="inlineStr">
         <is>
@@ -78491,7 +78491,7 @@
         <v>45824</v>
       </c>
       <c r="E1018" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1018" t="inlineStr">
         <is>
@@ -78564,7 +78564,7 @@
         <v>45824</v>
       </c>
       <c r="E1019" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1019" t="inlineStr">
         <is>
@@ -78637,7 +78637,7 @@
         <v>45827</v>
       </c>
       <c r="E1020" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1020" t="inlineStr">
         <is>
@@ -78710,7 +78710,7 @@
         <v>45831</v>
       </c>
       <c r="E1021" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1021" t="inlineStr">
         <is>
@@ -78783,7 +78783,7 @@
         <v>45831</v>
       </c>
       <c r="E1022" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1022" t="inlineStr">
         <is>
@@ -78856,7 +78856,7 @@
         <v>45832</v>
       </c>
       <c r="E1023" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1023" t="inlineStr">
         <is>
@@ -78929,7 +78929,7 @@
         <v>45805</v>
       </c>
       <c r="E1024" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1024" t="inlineStr">
         <is>
@@ -79002,7 +79002,7 @@
         <v>45835</v>
       </c>
       <c r="E1025" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1025" t="inlineStr">
         <is>
@@ -79075,7 +79075,7 @@
         <v>45835</v>
       </c>
       <c r="E1026" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1026" t="inlineStr">
         <is>
@@ -79148,7 +79148,7 @@
         <v>45835</v>
       </c>
       <c r="E1027" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1027" t="inlineStr">
         <is>
@@ -79221,7 +79221,7 @@
         <v>45840</v>
       </c>
       <c r="E1028" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1028" t="inlineStr">
         <is>
@@ -79294,7 +79294,7 @@
         <v>45540</v>
       </c>
       <c r="E1029" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1029" t="inlineStr">
         <is>
@@ -79367,7 +79367,7 @@
         <v>45846</v>
       </c>
       <c r="E1030" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1030" t="inlineStr">
         <is>
@@ -79440,7 +79440,7 @@
         <v>45847</v>
       </c>
       <c r="E1031" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1031" t="inlineStr">
         <is>
@@ -79513,7 +79513,7 @@
         <v>45390</v>
       </c>
       <c r="E1032" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1032" t="inlineStr">
         <is>
@@ -79586,7 +79586,7 @@
         <v>45853</v>
       </c>
       <c r="E1033" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1033" t="inlineStr">
         <is>
@@ -79659,7 +79659,7 @@
         <v>45740</v>
       </c>
       <c r="E1034" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1034" t="inlineStr">
         <is>
@@ -79732,7 +79732,7 @@
         <v>45267</v>
       </c>
       <c r="E1035" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1035" t="inlineStr">
         <is>
@@ -79805,7 +79805,7 @@
         <v>45384</v>
       </c>
       <c r="E1036" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1036" t="inlineStr">
         <is>
@@ -79878,7 +79878,7 @@
         <v>45097</v>
       </c>
       <c r="E1037" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1037" t="inlineStr">
         <is>
@@ -79956,7 +79956,7 @@
         <v>45782</v>
       </c>
       <c r="E1038" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1038" t="inlineStr">
         <is>
@@ -80029,7 +80029,7 @@
         <v>45874</v>
       </c>
       <c r="E1039" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1039" t="inlineStr">
         <is>
@@ -80102,7 +80102,7 @@
         <v>45855</v>
       </c>
       <c r="E1040" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1040" t="inlineStr">
         <is>
@@ -80175,7 +80175,7 @@
         <v>45883</v>
       </c>
       <c r="E1041" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1041" t="inlineStr">
         <is>
@@ -80248,7 +80248,7 @@
         <v>45054</v>
       </c>
       <c r="E1042" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1042" t="inlineStr">
         <is>
@@ -80321,7 +80321,7 @@
         <v>45230</v>
       </c>
       <c r="E1043" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1043" t="inlineStr">
         <is>
@@ -80399,7 +80399,7 @@
         <v>44498</v>
       </c>
       <c r="E1044" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1044" t="inlineStr">
         <is>
@@ -80472,7 +80472,7 @@
         <v>45622</v>
       </c>
       <c r="E1045" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1045" t="inlineStr">
         <is>
@@ -80545,7 +80545,7 @@
         <v>45054</v>
       </c>
       <c r="E1046" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1046" t="inlineStr">
         <is>
@@ -80618,7 +80618,7 @@
         <v>45054</v>
       </c>
       <c r="E1047" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1047" t="inlineStr">
         <is>
@@ -80691,7 +80691,7 @@
         <v>45056</v>
       </c>
       <c r="E1048" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1048" t="inlineStr">
         <is>
@@ -80764,7 +80764,7 @@
         <v>44715</v>
       </c>
       <c r="E1049" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1049" t="inlineStr">
         <is>
@@ -80837,7 +80837,7 @@
         <v>44722</v>
       </c>
       <c r="E1050" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1050" t="inlineStr">
         <is>
@@ -80910,7 +80910,7 @@
         <v>45434</v>
       </c>
       <c r="E1051" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1051" t="inlineStr">
         <is>
@@ -80983,7 +80983,7 @@
         <v>44468</v>
       </c>
       <c r="E1052" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1052" t="inlineStr">
         <is>
@@ -81056,7 +81056,7 @@
         <v>45054</v>
       </c>
       <c r="E1053" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1053" t="inlineStr">
         <is>
@@ -81129,7 +81129,7 @@
         <v>45407</v>
       </c>
       <c r="E1054" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1054" t="inlineStr">
         <is>
@@ -81202,7 +81202,7 @@
         <v>44802</v>
       </c>
       <c r="E1055" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1055" t="inlineStr">
         <is>
@@ -81275,7 +81275,7 @@
         <v>45071</v>
       </c>
       <c r="E1056" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1056" t="inlineStr">
         <is>
@@ -81348,7 +81348,7 @@
         <v>44495</v>
       </c>
       <c r="E1057" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1057" t="inlineStr">
         <is>
@@ -81421,7 +81421,7 @@
         <v>44588</v>
       </c>
       <c r="E1058" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1058" t="inlineStr">
         <is>
@@ -81494,7 +81494,7 @@
         <v>44727</v>
       </c>
       <c r="E1059" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1059" t="inlineStr">
         <is>
@@ -81567,7 +81567,7 @@
         <v>44474</v>
       </c>
       <c r="E1060" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1060" t="inlineStr">
         <is>
@@ -81640,7 +81640,7 @@
         <v>45224</v>
       </c>
       <c r="E1061" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1061" t="inlineStr">
         <is>
@@ -81718,7 +81718,7 @@
         <v>44722</v>
       </c>
       <c r="E1062" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1062" t="inlineStr">
         <is>
@@ -81791,7 +81791,7 @@
         <v>44972</v>
       </c>
       <c r="E1063" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1063" t="inlineStr">
         <is>
@@ -81864,7 +81864,7 @@
         <v>44487</v>
       </c>
       <c r="E1064" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1064" t="inlineStr">
         <is>
@@ -81937,7 +81937,7 @@
         <v>45230</v>
       </c>
       <c r="E1065" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1065" t="inlineStr">
         <is>
@@ -82010,7 +82010,7 @@
         <v>44939</v>
       </c>
       <c r="E1066" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1066" t="inlineStr">
         <is>
@@ -82083,7 +82083,7 @@
         <v>45468</v>
       </c>
       <c r="E1067" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1067" t="inlineStr">
         <is>
@@ -82156,7 +82156,7 @@
         <v>45218</v>
       </c>
       <c r="E1068" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1068" t="inlineStr">
         <is>
@@ -82229,7 +82229,7 @@
         <v>45054</v>
       </c>
       <c r="E1069" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1069" t="inlineStr">
         <is>
@@ -82302,7 +82302,7 @@
         <v>44603</v>
       </c>
       <c r="E1070" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1070" t="inlineStr">
         <is>
@@ -82375,7 +82375,7 @@
         <v>44930</v>
       </c>
       <c r="E1071" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1071" t="inlineStr">
         <is>
@@ -82453,7 +82453,7 @@
         <v>44973</v>
       </c>
       <c r="E1072" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1072" t="inlineStr">
         <is>
@@ -82526,7 +82526,7 @@
         <v>44908</v>
       </c>
       <c r="E1073" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1073" t="inlineStr">
         <is>
@@ -82619,7 +82619,7 @@
         <v>44693</v>
       </c>
       <c r="E1074" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1074" t="inlineStr">
         <is>
@@ -82692,7 +82692,7 @@
         <v>44726</v>
       </c>
       <c r="E1075" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1075" t="inlineStr">
         <is>
@@ -82765,7 +82765,7 @@
         <v>45583</v>
       </c>
       <c r="E1076" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1076" t="inlineStr">
         <is>
@@ -82838,7 +82838,7 @@
         <v>45054</v>
       </c>
       <c r="E1077" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1077" t="inlineStr">
         <is>
@@ -82911,7 +82911,7 @@
         <v>44712</v>
       </c>
       <c r="E1078" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1078" t="inlineStr">
         <is>
@@ -82984,7 +82984,7 @@
         <v>45054</v>
       </c>
       <c r="E1079" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1079" t="inlineStr">
         <is>
@@ -83057,7 +83057,7 @@
         <v>44722</v>
       </c>
       <c r="E1080" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1080" t="inlineStr">
         <is>
@@ -83130,7 +83130,7 @@
         <v>44908</v>
       </c>
       <c r="E1081" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1081" t="inlineStr">
         <is>
@@ -83203,7 +83203,7 @@
         <v>44972</v>
       </c>
       <c r="E1082" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1082" t="inlineStr">
         <is>
@@ -83276,7 +83276,7 @@
         <v>44978</v>
       </c>
       <c r="E1083" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1083" t="inlineStr">
         <is>
@@ -83349,7 +83349,7 @@
         <v>44712</v>
       </c>
       <c r="E1084" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1084" t="inlineStr">
         <is>
@@ -83422,7 +83422,7 @@
         <v>44887</v>
       </c>
       <c r="E1085" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1085" t="inlineStr">
         <is>
@@ -83495,7 +83495,7 @@
         <v>44704</v>
       </c>
       <c r="E1086" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1086" t="inlineStr">
         <is>
@@ -83568,7 +83568,7 @@
         <v>44909</v>
       </c>
       <c r="E1087" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1087" t="inlineStr">
         <is>
@@ -83641,7 +83641,7 @@
         <v>45408</v>
       </c>
       <c r="E1088" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1088" t="inlineStr">
         <is>
@@ -83714,7 +83714,7 @@
         <v>44596</v>
       </c>
       <c r="E1089" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1089" t="inlineStr">
         <is>
@@ -83787,7 +83787,7 @@
         <v>44908</v>
       </c>
       <c r="E1090" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1090" t="inlineStr">
         <is>
@@ -83860,7 +83860,7 @@
         <v>44704</v>
       </c>
       <c r="E1091" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1091" t="inlineStr">
         <is>
@@ -83933,7 +83933,7 @@
         <v>45054</v>
       </c>
       <c r="E1092" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1092" t="inlineStr">
         <is>
@@ -84006,7 +84006,7 @@
         <v>45526</v>
       </c>
       <c r="E1093" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1093" t="inlineStr">
         <is>
@@ -84079,7 +84079,7 @@
         <v>45436</v>
       </c>
       <c r="E1094" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1094" t="inlineStr">
         <is>
@@ -84152,7 +84152,7 @@
         <v>45485</v>
       </c>
       <c r="E1095" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1095" t="inlineStr">
         <is>
@@ -84225,7 +84225,7 @@
         <v>44588</v>
       </c>
       <c r="E1096" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1096" t="inlineStr">
         <is>
@@ -84298,7 +84298,7 @@
         <v>45727</v>
       </c>
       <c r="E1097" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1097" t="inlineStr">
         <is>
@@ -84371,7 +84371,7 @@
         <v>45740</v>
       </c>
       <c r="E1098" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1098" t="inlineStr">
         <is>
@@ -84444,7 +84444,7 @@
         <v>45726</v>
       </c>
       <c r="E1099" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1099" t="inlineStr">
         <is>
@@ -84517,7 +84517,7 @@
         <v>45797</v>
       </c>
       <c r="E1100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1100" t="inlineStr">
         <is>
@@ -84590,7 +84590,7 @@
         <v>45805</v>
       </c>
       <c r="E1101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1101" t="inlineStr">
         <is>
@@ -84663,7 +84663,7 @@
         <v>45831</v>
       </c>
       <c r="E1102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1102" t="inlineStr">
         <is>
@@ -84736,7 +84736,7 @@
         <v>45951</v>
       </c>
       <c r="E1103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1103" t="inlineStr">
         <is>
@@ -84809,7 +84809,7 @@
         <v>45958</v>
       </c>
       <c r="E1104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1104" t="inlineStr">
         <is>
@@ -84882,7 +84882,7 @@
         <v>45964</v>
       </c>
       <c r="E1105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1105" t="inlineStr">
         <is>
@@ -84955,7 +84955,7 @@
         <v>45965</v>
       </c>
       <c r="E1106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1106" t="inlineStr">
         <is>
@@ -85028,7 +85028,7 @@
         <v>45981</v>
       </c>
       <c r="E1107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1107" t="inlineStr">
         <is>
@@ -85106,7 +85106,7 @@
         <v>45988</v>
       </c>
       <c r="E1108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1108" t="inlineStr">
         <is>
@@ -85179,7 +85179,7 @@
         <v>46092</v>
       </c>
       <c r="E1109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1109" t="inlineStr">
         <is>
@@ -85257,7 +85257,7 @@
         <v>46202</v>
       </c>
       <c r="E1110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1110" t="inlineStr">
         <is>
@@ -85330,7 +85330,7 @@
         <v>46262</v>
       </c>
       <c r="E1111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1111" t="inlineStr">
         <is>

--- a/Översikt VÄXJÖ.xlsx
+++ b/Översikt VÄXJÖ.xlsx
@@ -601,7 +601,7 @@
         <v>44974</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         <v>45895</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -859,7 +859,7 @@
         <v>45770</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -976,7 +976,7 @@
         <v>45888</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v>45127</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
         <v>45812</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1317,7 +1317,7 @@
         <v>45384</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         <v>46175</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>45468</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
         <v>45964</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
         <v>46188</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1882,7 +1882,7 @@
         <v>46188</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1996,7 +1996,7 @@
         <v>46199</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2110,7 +2110,7 @@
         <v>45081</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2223,7 +2223,7 @@
         <v>44958</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2336,7 +2336,7 @@
         <v>45995</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2448,7 +2448,7 @@
         <v>45294</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2565,7 +2565,7 @@
         <v>46247</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
         <v>45490</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2790,7 +2790,7 @@
         <v>45356</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2901,7 +2901,7 @@
         <v>46204</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3017,7 +3017,7 @@
         <v>46244</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3128,7 +3128,7 @@
         <v>45344</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3239,7 +3239,7 @@
         <v>46098</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3346,7 +3346,7 @@
         <v>46286</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3453,7 +3453,7 @@
         <v>45649</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3559,7 +3559,7 @@
         <v>45874</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3670,7 +3670,7 @@
         <v>44532</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3785,7 +3785,7 @@
         <v>46147</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3891,7 +3891,7 @@
         <v>46161</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4001,7 +4001,7 @@
         <v>45447</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4107,7 +4107,7 @@
         <v>45554</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4213,7 +4213,7 @@
         <v>46182</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4328,7 +4328,7 @@
         <v>45883</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4434,7 +4434,7 @@
         <v>45687</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4540,7 +4540,7 @@
         <v>45587</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
         <v>45190</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4756,7 +4756,7 @@
         <v>45093</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4866,7 +4866,7 @@
         <v>45545</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4972,7 +4972,7 @@
         <v>44704</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5078,7 +5078,7 @@
         <v>44704</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5188,7 +5188,7 @@
         <v>45460</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5294,7 +5294,7 @@
         <v>45348</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5400,7 +5400,7 @@
         <v>45351</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5506,7 +5506,7 @@
         <v>45674</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5617,7 +5617,7 @@
         <v>46100</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5723,7 +5723,7 @@
         <v>44721</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5828,7 +5828,7 @@
         <v>44704</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5933,7 +5933,7 @@
         <v>44468</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6038,7 +6038,7 @@
         <v>44645</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6143,7 +6143,7 @@
         <v>44490</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6248,7 +6248,7 @@
         <v>45754</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6353,7 +6353,7 @@
         <v>45392</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6463,7 +6463,7 @@
         <v>45280</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6568,7 +6568,7 @@
         <v>44673</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6673,7 +6673,7 @@
         <v>45617</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6783,7 +6783,7 @@
         <v>46045</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6888,7 +6888,7 @@
         <v>44872</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6993,7 +6993,7 @@
         <v>45606</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7098,7 +7098,7 @@
         <v>45688</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7203,7 +7203,7 @@
         <v>45594</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         <v>45964</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7426,7 +7426,7 @@
         <v>45643</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7531,7 +7531,7 @@
         <v>45978</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7640,7 +7640,7 @@
         <v>45327</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7745,7 +7745,7 @@
         <v>45824</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7850,7 +7850,7 @@
         <v>46161</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7955,7 +7955,7 @@
         <v>46161</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8060,7 +8060,7 @@
         <v>45428</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8170,7 +8170,7 @@
         <v>45273</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8275,7 +8275,7 @@
         <v>45280</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8380,7 +8380,7 @@
         <v>46199</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8485,7 +8485,7 @@
         <v>44705</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8594,7 +8594,7 @@
         <v>44746</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8699,7 +8699,7 @@
         <v>46281</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8804,7 +8804,7 @@
         <v>46288</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8909,7 +8909,7 @@
         <v>44741</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9014,7 +9014,7 @@
         <v>46246</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9119,7 +9119,7 @@
         <v>45098</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9224,7 +9224,7 @@
         <v>45533</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9329,7 +9329,7 @@
         <v>45369</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9434,7 +9434,7 @@
         <v>45279</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9539,7 +9539,7 @@
         <v>45594</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9649,7 +9649,7 @@
         <v>45594</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9759,7 +9759,7 @@
         <v>44894</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9864,7 +9864,7 @@
         <v>44634</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9969,7 +9969,7 @@
         <v>44712</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10074,7 +10074,7 @@
         <v>44950</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10179,7 +10179,7 @@
         <v>45436</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10284,7 +10284,7 @@
         <v>45726</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10389,7 +10389,7 @@
         <v>45805</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10494,7 +10494,7 @@
         <v>45939</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10603,7 +10603,7 @@
         <v>46100</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10708,7 +10708,7 @@
         <v>44693</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10781,7 +10781,7 @@
         <v>44812</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10854,7 +10854,7 @@
         <v>44518</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10927,7 +10927,7 @@
         <v>44536</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11000,7 +11000,7 @@
         <v>44764</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11073,7 +11073,7 @@
         <v>44519</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11146,7 +11146,7 @@
         <v>44501</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11219,7 +11219,7 @@
         <v>44814</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11292,7 +11292,7 @@
         <v>44645</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11365,7 +11365,7 @@
         <v>44643</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11438,7 +11438,7 @@
         <v>44515</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11511,7 +11511,7 @@
         <v>44814</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11584,7 +11584,7 @@
         <v>44480</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11657,7 +11657,7 @@
         <v>44525</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11730,7 +11730,7 @@
         <v>44578</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11803,7 +11803,7 @@
         <v>44516</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11881,7 +11881,7 @@
         <v>44803</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11954,7 +11954,7 @@
         <v>44466</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12027,7 +12027,7 @@
         <v>44470</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12100,7 +12100,7 @@
         <v>44691</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12173,7 +12173,7 @@
         <v>44739</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12246,7 +12246,7 @@
         <v>44590</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12324,7 +12324,7 @@
         <v>44820</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12402,7 +12402,7 @@
         <v>44814</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12475,7 +12475,7 @@
         <v>44769</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12553,7 +12553,7 @@
         <v>44820</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12626,7 +12626,7 @@
         <v>44711</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12699,7 +12699,7 @@
         <v>44474</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12772,7 +12772,7 @@
         <v>44880</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12845,7 +12845,7 @@
         <v>44508</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12918,7 +12918,7 @@
         <v>44495</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12991,7 +12991,7 @@
         <v>44515</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13064,7 +13064,7 @@
         <v>44599</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13137,7 +13137,7 @@
         <v>44476</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13210,7 +13210,7 @@
         <v>44495</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13283,7 +13283,7 @@
         <v>44599</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13356,7 +13356,7 @@
         <v>44651</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13429,7 +13429,7 @@
         <v>44876</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13507,7 +13507,7 @@
         <v>44671</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13580,7 +13580,7 @@
         <v>44466</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13653,7 +13653,7 @@
         <v>44496</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13726,7 +13726,7 @@
         <v>44750</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13799,7 +13799,7 @@
         <v>44568</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13872,7 +13872,7 @@
         <v>44543</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13945,7 +13945,7 @@
         <v>44606</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14018,7 +14018,7 @@
         <v>44470</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14091,7 +14091,7 @@
         <v>44613</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14164,7 +14164,7 @@
         <v>44746</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14237,7 +14237,7 @@
         <v>44474</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14310,7 +14310,7 @@
         <v>44610</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14383,7 +14383,7 @@
         <v>44610</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14456,7 +14456,7 @@
         <v>44491</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14529,7 +14529,7 @@
         <v>44740</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14602,7 +14602,7 @@
         <v>44483</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14675,7 +14675,7 @@
         <v>44617</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14748,7 +14748,7 @@
         <v>44726</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14821,7 +14821,7 @@
         <v>44468</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14894,7 +14894,7 @@
         <v>44551</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14967,7 +14967,7 @@
         <v>44599</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15040,7 +15040,7 @@
         <v>44781</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15113,7 +15113,7 @@
         <v>44494</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15186,7 +15186,7 @@
         <v>44522</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15259,7 +15259,7 @@
         <v>44532</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15332,7 +15332,7 @@
         <v>44532</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15405,7 +15405,7 @@
         <v>44704</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15478,7 +15478,7 @@
         <v>44498</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15551,7 +15551,7 @@
         <v>44860</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15624,7 +15624,7 @@
         <v>44596</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15697,7 +15697,7 @@
         <v>44573</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15770,7 +15770,7 @@
         <v>44712</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15843,7 +15843,7 @@
         <v>44579</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15916,7 +15916,7 @@
         <v>44711</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15989,7 +15989,7 @@
         <v>44769</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16067,7 +16067,7 @@
         <v>44502</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16145,7 +16145,7 @@
         <v>44812</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16218,7 +16218,7 @@
         <v>44489</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16291,7 +16291,7 @@
         <v>44489</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16364,7 +16364,7 @@
         <v>44483</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16437,7 +16437,7 @@
         <v>44508</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16510,7 +16510,7 @@
         <v>44574</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16583,7 +16583,7 @@
         <v>44537</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16656,7 +16656,7 @@
         <v>44537</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16729,7 +16729,7 @@
         <v>44571</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16802,7 +16802,7 @@
         <v>44489</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16875,7 +16875,7 @@
         <v>44487</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16948,7 +16948,7 @@
         <v>44603</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17026,7 +17026,7 @@
         <v>44596</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17099,7 +17099,7 @@
         <v>44473</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17172,7 +17172,7 @@
         <v>44560</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17245,7 +17245,7 @@
         <v>44474</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17318,7 +17318,7 @@
         <v>44820</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17396,7 +17396,7 @@
         <v>44820</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17474,7 +17474,7 @@
         <v>45194</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17547,7 +17547,7 @@
         <v>45219</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17620,7 +17620,7 @@
         <v>44741</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17693,7 +17693,7 @@
         <v>45715</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17766,7 +17766,7 @@
         <v>44814</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17839,7 +17839,7 @@
         <v>44814</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17912,7 +17912,7 @@
         <v>45754</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17985,7 +17985,7 @@
         <v>45754</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18058,7 +18058,7 @@
         <v>44867</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18131,7 +18131,7 @@
         <v>45372</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18204,7 +18204,7 @@
         <v>45412</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18277,7 +18277,7 @@
         <v>44741</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18350,7 +18350,7 @@
         <v>44741</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18423,7 +18423,7 @@
         <v>45219</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18496,7 +18496,7 @@
         <v>45259</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18569,7 +18569,7 @@
         <v>44874</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18642,7 +18642,7 @@
         <v>45392</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18720,7 +18720,7 @@
         <v>45300</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18793,7 +18793,7 @@
         <v>45302</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18866,7 +18866,7 @@
         <v>44894</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18944,7 +18944,7 @@
         <v>45302</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19017,7 +19017,7 @@
         <v>45386</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19090,7 +19090,7 @@
         <v>45432</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19163,7 +19163,7 @@
         <v>44986</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19236,7 +19236,7 @@
         <v>45392</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19314,7 +19314,7 @@
         <v>45392</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19392,7 +19392,7 @@
         <v>45446</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19470,7 +19470,7 @@
         <v>45317</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19543,7 +19543,7 @@
         <v>45236</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19616,7 +19616,7 @@
         <v>45112</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19689,7 +19689,7 @@
         <v>45446</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19762,7 +19762,7 @@
         <v>45477</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19840,7 +19840,7 @@
         <v>44904</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19913,7 +19913,7 @@
         <v>44904</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19986,7 +19986,7 @@
         <v>45280</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20059,7 +20059,7 @@
         <v>44963</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20132,7 +20132,7 @@
         <v>44963</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20205,7 +20205,7 @@
         <v>44963</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20278,7 +20278,7 @@
         <v>45468</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20351,7 +20351,7 @@
         <v>44880</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20424,7 +20424,7 @@
         <v>45127</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20497,7 +20497,7 @@
         <v>45127</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20570,7 +20570,7 @@
         <v>45551</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20643,7 +20643,7 @@
         <v>44573</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20716,7 +20716,7 @@
         <v>45796</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20789,7 +20789,7 @@
         <v>45201</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20862,7 +20862,7 @@
         <v>45281</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20935,7 +20935,7 @@
         <v>45622</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21008,7 +21008,7 @@
         <v>45240</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21081,7 +21081,7 @@
         <v>46019</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21154,7 +21154,7 @@
         <v>44854</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21227,7 +21227,7 @@
         <v>46019</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21300,7 +21300,7 @@
         <v>45244</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21373,7 +21373,7 @@
         <v>45883</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21446,7 +21446,7 @@
         <v>44894</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21519,7 +21519,7 @@
         <v>45111</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21592,7 +21592,7 @@
         <v>45154</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21665,7 +21665,7 @@
         <v>46029</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21738,7 +21738,7 @@
         <v>45145</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21811,7 +21811,7 @@
         <v>45294</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21884,7 +21884,7 @@
         <v>45342</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21957,7 +21957,7 @@
         <v>45330</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22030,7 +22030,7 @@
         <v>45225</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22103,7 +22103,7 @@
         <v>44950</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22176,7 +22176,7 @@
         <v>45477</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22254,7 +22254,7 @@
         <v>44545</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22327,7 +22327,7 @@
         <v>45488</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22400,7 +22400,7 @@
         <v>45127</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22473,7 +22473,7 @@
         <v>46029</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22546,7 +22546,7 @@
         <v>46031</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22624,7 +22624,7 @@
         <v>45124</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22697,7 +22697,7 @@
         <v>45764</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22770,7 +22770,7 @@
         <v>44880</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22843,7 +22843,7 @@
         <v>46031</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22921,7 +22921,7 @@
         <v>44922</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22994,7 +22994,7 @@
         <v>46036</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23067,7 +23067,7 @@
         <v>46035</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23145,7 +23145,7 @@
         <v>46035</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23223,7 +23223,7 @@
         <v>45754</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23296,7 +23296,7 @@
         <v>45574</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23369,7 +23369,7 @@
         <v>45921</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23442,7 +23442,7 @@
         <v>44537</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23515,7 +23515,7 @@
         <v>46036</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23588,7 +23588,7 @@
         <v>46035</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23666,7 +23666,7 @@
         <v>46036</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23739,7 +23739,7 @@
         <v>44547</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23812,7 +23812,7 @@
         <v>45665</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23885,7 +23885,7 @@
         <v>45894</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23958,7 +23958,7 @@
         <v>45890</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24031,7 +24031,7 @@
         <v>45856</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24104,7 +24104,7 @@
         <v>46041</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24177,7 +24177,7 @@
         <v>45895</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24250,7 +24250,7 @@
         <v>44896</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24323,7 +24323,7 @@
         <v>45897</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24401,7 +24401,7 @@
         <v>46043</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24474,7 +24474,7 @@
         <v>46048</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24547,7 +24547,7 @@
         <v>45148</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24620,7 +24620,7 @@
         <v>45148</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24693,7 +24693,7 @@
         <v>46045</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24766,7 +24766,7 @@
         <v>45645</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24839,7 +24839,7 @@
         <v>45719</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24912,7 +24912,7 @@
         <v>45902</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24985,7 +24985,7 @@
         <v>45902</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25058,7 +25058,7 @@
         <v>46045</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25131,7 +25131,7 @@
         <v>44824</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25204,7 +25204,7 @@
         <v>45902</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25277,7 +25277,7 @@
         <v>45810</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25355,7 +25355,7 @@
         <v>45190</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25428,7 +25428,7 @@
         <v>45835</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25501,7 +25501,7 @@
         <v>46049</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25574,7 +25574,7 @@
         <v>46049</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25647,7 +25647,7 @@
         <v>46049</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25720,7 +25720,7 @@
         <v>46049</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25793,7 +25793,7 @@
         <v>45905</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25866,7 +25866,7 @@
         <v>45573</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25939,7 +25939,7 @@
         <v>44867</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26012,7 +26012,7 @@
         <v>46051</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26085,7 +26085,7 @@
         <v>44599</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26158,7 +26158,7 @@
         <v>45910</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26231,7 +26231,7 @@
         <v>45672</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26304,7 +26304,7 @@
         <v>45056</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26377,7 +26377,7 @@
         <v>44896</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26450,7 +26450,7 @@
         <v>45909</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26523,7 +26523,7 @@
         <v>46056</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26596,7 +26596,7 @@
         <v>46056</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26669,7 +26669,7 @@
         <v>45559</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26742,7 +26742,7 @@
         <v>45787</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26815,7 +26815,7 @@
         <v>44532</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26888,7 +26888,7 @@
         <v>45911</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26961,7 +26961,7 @@
         <v>46057</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27034,7 +27034,7 @@
         <v>45916</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27107,7 +27107,7 @@
         <v>46059</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27180,7 +27180,7 @@
         <v>45540</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27253,7 +27253,7 @@
         <v>46061</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27326,7 +27326,7 @@
         <v>45749</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27399,7 +27399,7 @@
         <v>45390</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27472,7 +27472,7 @@
         <v>46059</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27545,7 +27545,7 @@
         <v>46059</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27618,7 +27618,7 @@
         <v>45918</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27691,7 +27691,7 @@
         <v>44595</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27764,7 +27764,7 @@
         <v>45555</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27837,7 +27837,7 @@
         <v>44903</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27910,7 +27910,7 @@
         <v>44938</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27983,7 +27983,7 @@
         <v>45803</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28056,7 +28056,7 @@
         <v>45014</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28129,7 +28129,7 @@
         <v>45924</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28202,7 +28202,7 @@
         <v>46072</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28275,7 +28275,7 @@
         <v>46073</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28348,7 +28348,7 @@
         <v>46073</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28421,7 +28421,7 @@
         <v>46075</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28494,7 +28494,7 @@
         <v>45412</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28567,7 +28567,7 @@
         <v>45412</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28640,7 +28640,7 @@
         <v>45925</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28713,7 +28713,7 @@
         <v>45140</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28786,7 +28786,7 @@
         <v>45552</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28859,7 +28859,7 @@
         <v>45378</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28932,7 +28932,7 @@
         <v>46079</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29005,7 +29005,7 @@
         <v>45534</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29078,7 +29078,7 @@
         <v>45560</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29151,7 +29151,7 @@
         <v>46079</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29224,7 +29224,7 @@
         <v>45369</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29297,7 +29297,7 @@
         <v>44599</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29370,7 +29370,7 @@
         <v>44869</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29443,7 +29443,7 @@
         <v>46083</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29516,7 +29516,7 @@
         <v>46083</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29589,7 +29589,7 @@
         <v>46083</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29662,7 +29662,7 @@
         <v>45338</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29735,7 +29735,7 @@
         <v>45244</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29808,7 +29808,7 @@
         <v>45408</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29881,7 +29881,7 @@
         <v>46083</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29954,7 +29954,7 @@
         <v>46083</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30027,7 +30027,7 @@
         <v>45805</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30100,7 +30100,7 @@
         <v>45763</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30173,7 +30173,7 @@
         <v>45447</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30246,7 +30246,7 @@
         <v>45222</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30319,7 +30319,7 @@
         <v>45169</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30392,7 +30392,7 @@
         <v>45583</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30470,7 +30470,7 @@
         <v>46084</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30543,7 +30543,7 @@
         <v>45392</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30621,7 +30621,7 @@
         <v>44670</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30694,7 +30694,7 @@
         <v>46087</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30767,7 +30767,7 @@
         <v>45937</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30840,7 +30840,7 @@
         <v>45937</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30913,7 +30913,7 @@
         <v>44711</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30986,7 +30986,7 @@
         <v>45071</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31064,7 +31064,7 @@
         <v>45583</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31137,7 +31137,7 @@
         <v>45757</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31210,7 +31210,7 @@
         <v>45384</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31283,7 +31283,7 @@
         <v>45345</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31356,7 +31356,7 @@
         <v>45896</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31429,7 +31429,7 @@
         <v>45579</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31502,7 +31502,7 @@
         <v>44970</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31575,7 +31575,7 @@
         <v>46099</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31648,7 +31648,7 @@
         <v>46100</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31721,7 +31721,7 @@
         <v>46100</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31794,7 +31794,7 @@
         <v>46100</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31867,7 +31867,7 @@
         <v>46100</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31940,7 +31940,7 @@
         <v>45764</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32013,7 +32013,7 @@
         <v>45189</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32086,7 +32086,7 @@
         <v>45189</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32159,7 +32159,7 @@
         <v>45722</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32232,7 +32232,7 @@
         <v>44963</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32305,7 +32305,7 @@
         <v>45463</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32378,7 +32378,7 @@
         <v>46107</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32451,7 +32451,7 @@
         <v>44960</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32524,7 +32524,7 @@
         <v>45594</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32602,7 +32602,7 @@
         <v>45594</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32680,7 +32680,7 @@
         <v>45594</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32758,7 +32758,7 @@
         <v>45594</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32836,7 +32836,7 @@
         <v>45594</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32914,7 +32914,7 @@
         <v>45594</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32992,7 +32992,7 @@
         <v>45594</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33070,7 +33070,7 @@
         <v>45594</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33148,7 +33148,7 @@
         <v>45586</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33221,7 +33221,7 @@
         <v>45952</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33294,7 +33294,7 @@
         <v>45923</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33367,7 +33367,7 @@
         <v>44769</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33445,7 +33445,7 @@
         <v>44769</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33523,7 +33523,7 @@
         <v>46108</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33596,7 +33596,7 @@
         <v>45281</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33669,7 +33669,7 @@
         <v>46113</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33742,7 +33742,7 @@
         <v>45180</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33815,7 +33815,7 @@
         <v>46112</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33888,7 +33888,7 @@
         <v>45714</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33961,7 +33961,7 @@
         <v>46112</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34034,7 +34034,7 @@
         <v>45670</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34107,7 +34107,7 @@
         <v>45250</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34180,7 +34180,7 @@
         <v>45946</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34253,7 +34253,7 @@
         <v>45953</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34326,7 +34326,7 @@
         <v>45594</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34404,7 +34404,7 @@
         <v>46119</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34477,7 +34477,7 @@
         <v>45629</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34550,7 +34550,7 @@
         <v>45328</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34623,7 +34623,7 @@
         <v>45328</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34696,7 +34696,7 @@
         <v>44494</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34769,7 +34769,7 @@
         <v>45594</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34847,7 +34847,7 @@
         <v>45924</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34920,7 +34920,7 @@
         <v>45964</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34993,7 +34993,7 @@
         <v>45638</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35066,7 +35066,7 @@
         <v>45611</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35139,7 +35139,7 @@
         <v>44743</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35212,7 +35212,7 @@
         <v>44711</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35285,7 +35285,7 @@
         <v>45224</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35363,7 +35363,7 @@
         <v>44966</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35436,7 +35436,7 @@
         <v>45089</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35509,7 +35509,7 @@
         <v>44972</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35582,7 +35582,7 @@
         <v>45971</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35655,7 +35655,7 @@
         <v>44972</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35728,7 +35728,7 @@
         <v>45519</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35801,7 +35801,7 @@
         <v>45702</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35874,7 +35874,7 @@
         <v>45973</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35947,7 +35947,7 @@
         <v>44967</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36020,7 +36020,7 @@
         <v>45973</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36093,7 +36093,7 @@
         <v>45012</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36166,7 +36166,7 @@
         <v>44981</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36239,7 +36239,7 @@
         <v>45166</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36312,7 +36312,7 @@
         <v>44998</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36385,7 +36385,7 @@
         <v>45979</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36458,7 +36458,7 @@
         <v>46129</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36531,7 +36531,7 @@
         <v>45979</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36604,7 +36604,7 @@
         <v>45385</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36682,7 +36682,7 @@
         <v>45385</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36760,7 +36760,7 @@
         <v>45980</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36833,7 +36833,7 @@
         <v>45495</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36906,7 +36906,7 @@
         <v>45103</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36979,7 +36979,7 @@
         <v>45103</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37052,7 +37052,7 @@
         <v>45103</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37125,7 +37125,7 @@
         <v>45558</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37198,7 +37198,7 @@
         <v>45538</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37271,7 +37271,7 @@
         <v>45114</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37344,7 +37344,7 @@
         <v>45114</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37417,7 +37417,7 @@
         <v>44739</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37490,7 +37490,7 @@
         <v>45881</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37563,7 +37563,7 @@
         <v>45638</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37636,7 +37636,7 @@
         <v>45677</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37709,7 +37709,7 @@
         <v>45128</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37782,7 +37782,7 @@
         <v>45835</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37855,7 +37855,7 @@
         <v>45743</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37928,7 +37928,7 @@
         <v>45827</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38001,7 +38001,7 @@
         <v>45698</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38074,7 +38074,7 @@
         <v>45568</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38147,7 +38147,7 @@
         <v>45810</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38225,7 +38225,7 @@
         <v>45826</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38303,7 +38303,7 @@
         <v>44774</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38376,7 +38376,7 @@
         <v>45692</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38449,7 +38449,7 @@
         <v>45670</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38522,7 +38522,7 @@
         <v>45905</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38595,7 +38595,7 @@
         <v>45923</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38668,7 +38668,7 @@
         <v>45833</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38741,7 +38741,7 @@
         <v>45883</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38814,7 +38814,7 @@
         <v>45883</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38887,7 +38887,7 @@
         <v>45775</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38960,7 +38960,7 @@
         <v>45846</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39033,7 +39033,7 @@
         <v>45782</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39106,7 +39106,7 @@
         <v>45033</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39184,7 +39184,7 @@
         <v>45923</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39257,7 +39257,7 @@
         <v>45426</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39330,7 +39330,7 @@
         <v>45121</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39403,7 +39403,7 @@
         <v>45939</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39476,7 +39476,7 @@
         <v>44782</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39554,7 +39554,7 @@
         <v>45827</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39627,7 +39627,7 @@
         <v>45645</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39700,7 +39700,7 @@
         <v>45127</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39773,7 +39773,7 @@
         <v>45168</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39846,7 +39846,7 @@
         <v>45993</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39919,7 +39919,7 @@
         <v>45993</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -39992,7 +39992,7 @@
         <v>45988</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40065,7 +40065,7 @@
         <v>45841</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40138,7 +40138,7 @@
         <v>45686</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40211,7 +40211,7 @@
         <v>45460</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40284,7 +40284,7 @@
         <v>45999</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40357,7 +40357,7 @@
         <v>44468</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40430,7 +40430,7 @@
         <v>44995</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40503,7 +40503,7 @@
         <v>45113</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40576,7 +40576,7 @@
         <v>45113</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40649,7 +40649,7 @@
         <v>44536</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40722,7 +40722,7 @@
         <v>45877</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -40795,7 +40795,7 @@
         <v>46000</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40868,7 +40868,7 @@
         <v>45818</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -40941,7 +40941,7 @@
         <v>46001</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41014,7 +41014,7 @@
         <v>45692</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41087,7 +41087,7 @@
         <v>45769</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41160,7 +41160,7 @@
         <v>45791</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41233,7 +41233,7 @@
         <v>45714</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41306,7 +41306,7 @@
         <v>44858</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41379,7 +41379,7 @@
         <v>44502</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41452,7 +41452,7 @@
         <v>45091</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41525,7 +41525,7 @@
         <v>45030</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -41598,7 +41598,7 @@
         <v>45419</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -41671,7 +41671,7 @@
         <v>45960</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -41744,7 +41744,7 @@
         <v>45820</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -41817,7 +41817,7 @@
         <v>46008</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -41890,7 +41890,7 @@
         <v>45820</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -41963,7 +41963,7 @@
         <v>46007</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42036,7 +42036,7 @@
         <v>45820</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42109,7 +42109,7 @@
         <v>45817</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42182,7 +42182,7 @@
         <v>45691</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42255,7 +42255,7 @@
         <v>46010</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42328,7 +42328,7 @@
         <v>45909</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42401,7 +42401,7 @@
         <v>44812</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42474,7 +42474,7 @@
         <v>46010</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42547,7 +42547,7 @@
         <v>45715</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42625,7 +42625,7 @@
         <v>46010</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -42698,7 +42698,7 @@
         <v>45048</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -42771,7 +42771,7 @@
         <v>45582</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -42844,7 +42844,7 @@
         <v>45190</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -42917,7 +42917,7 @@
         <v>45818</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -42990,7 +42990,7 @@
         <v>44991</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43063,7 +43063,7 @@
         <v>45513</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43136,7 +43136,7 @@
         <v>45824</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43209,7 +43209,7 @@
         <v>45894</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43282,7 +43282,7 @@
         <v>44522</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -43355,7 +43355,7 @@
         <v>45824</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -43428,7 +43428,7 @@
         <v>45210</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -43501,7 +43501,7 @@
         <v>44909</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -43574,7 +43574,7 @@
         <v>45825</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -43647,7 +43647,7 @@
         <v>44922</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -43720,7 +43720,7 @@
         <v>45753</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -43793,7 +43793,7 @@
         <v>44552</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -43866,7 +43866,7 @@
         <v>45250</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -43939,7 +43939,7 @@
         <v>45141</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44012,7 +44012,7 @@
         <v>45614</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44085,7 +44085,7 @@
         <v>45533</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44158,7 +44158,7 @@
         <v>44529</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44231,7 +44231,7 @@
         <v>44641</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -44304,7 +44304,7 @@
         <v>45329</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -44377,7 +44377,7 @@
         <v>44577</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -44450,7 +44450,7 @@
         <v>45827</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -44523,7 +44523,7 @@
         <v>44874</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -44596,7 +44596,7 @@
         <v>45715</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -44674,7 +44674,7 @@
         <v>45111</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -44747,7 +44747,7 @@
         <v>45831</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -44820,7 +44820,7 @@
         <v>45714</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -44893,7 +44893,7 @@
         <v>45267</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -44966,7 +44966,7 @@
         <v>44894</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45039,7 +45039,7 @@
         <v>45036</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45112,7 +45112,7 @@
         <v>46146</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -45185,7 +45185,7 @@
         <v>46146</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -45258,7 +45258,7 @@
         <v>45599</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -45331,7 +45331,7 @@
         <v>44523</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -45404,7 +45404,7 @@
         <v>46146</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -45477,7 +45477,7 @@
         <v>45233</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -45550,7 +45550,7 @@
         <v>44600</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -45628,7 +45628,7 @@
         <v>46147</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -45701,7 +45701,7 @@
         <v>46147</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -45774,7 +45774,7 @@
         <v>46148</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -45847,7 +45847,7 @@
         <v>46147</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -45920,7 +45920,7 @@
         <v>46147</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -45993,7 +45993,7 @@
         <v>45397</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -46066,7 +46066,7 @@
         <v>46147</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -46139,7 +46139,7 @@
         <v>45632</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -46212,7 +46212,7 @@
         <v>44473</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -46285,7 +46285,7 @@
         <v>45831</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -46358,7 +46358,7 @@
         <v>45153</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -46431,7 +46431,7 @@
         <v>44713</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -46504,7 +46504,7 @@
         <v>46149</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -46577,7 +46577,7 @@
         <v>46021</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -46650,7 +46650,7 @@
         <v>44908</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -46723,7 +46723,7 @@
         <v>46153</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -46796,7 +46796,7 @@
         <v>44897</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -46869,7 +46869,7 @@
         <v>45204</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -46942,7 +46942,7 @@
         <v>45737</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47015,7 +47015,7 @@
         <v>45805</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -47088,7 +47088,7 @@
         <v>45995</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -47161,7 +47161,7 @@
         <v>45832</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -47234,7 +47234,7 @@
         <v>45517</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -47307,7 +47307,7 @@
         <v>45557</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -47380,7 +47380,7 @@
         <v>44928</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -47453,7 +47453,7 @@
         <v>45631</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -47526,7 +47526,7 @@
         <v>45789</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -47599,7 +47599,7 @@
         <v>45279</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -47672,7 +47672,7 @@
         <v>45273</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -47745,7 +47745,7 @@
         <v>45436</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -47818,7 +47818,7 @@
         <v>45835</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -47891,7 +47891,7 @@
         <v>45106</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -47964,7 +47964,7 @@
         <v>45623</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -48037,7 +48037,7 @@
         <v>45090</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -48110,7 +48110,7 @@
         <v>45835</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -48183,7 +48183,7 @@
         <v>45561</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -48256,7 +48256,7 @@
         <v>46162</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -48329,7 +48329,7 @@
         <v>45835</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -48402,7 +48402,7 @@
         <v>45392</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -48475,7 +48475,7 @@
         <v>46162</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -48548,7 +48548,7 @@
         <v>46162</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -48621,7 +48621,7 @@
         <v>45447</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -48694,7 +48694,7 @@
         <v>45211</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -48767,7 +48767,7 @@
         <v>45104</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -48840,7 +48840,7 @@
         <v>45840</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -48913,7 +48913,7 @@
         <v>45078</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -48991,7 +48991,7 @@
         <v>45726</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -49064,7 +49064,7 @@
         <v>45780</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -49137,7 +49137,7 @@
         <v>45341</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -49210,7 +49210,7 @@
         <v>46162</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -49283,7 +49283,7 @@
         <v>45127</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -49356,7 +49356,7 @@
         <v>45719</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -49429,7 +49429,7 @@
         <v>45538</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -49507,7 +49507,7 @@
         <v>45128</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -49580,7 +49580,7 @@
         <v>45128</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -49653,7 +49653,7 @@
         <v>45540</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -49726,7 +49726,7 @@
         <v>45846</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -49799,7 +49799,7 @@
         <v>46163</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -49872,7 +49872,7 @@
         <v>46163</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -49945,7 +49945,7 @@
         <v>46163</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -50018,7 +50018,7 @@
         <v>46163</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -50091,7 +50091,7 @@
         <v>45387</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -50164,7 +50164,7 @@
         <v>45812</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -50237,7 +50237,7 @@
         <v>46163</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -50310,7 +50310,7 @@
         <v>46163</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -50383,7 +50383,7 @@
         <v>45240</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -50456,7 +50456,7 @@
         <v>45847</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -50529,7 +50529,7 @@
         <v>46168</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -50602,7 +50602,7 @@
         <v>45933</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -50675,7 +50675,7 @@
         <v>45121</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -50748,7 +50748,7 @@
         <v>45121</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -50821,7 +50821,7 @@
         <v>45121</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -50894,7 +50894,7 @@
         <v>45390</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -50967,7 +50967,7 @@
         <v>46167</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -51040,7 +51040,7 @@
         <v>46168</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -51113,7 +51113,7 @@
         <v>45853</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -51186,7 +51186,7 @@
         <v>45387</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -51259,7 +51259,7 @@
         <v>44959</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -51332,7 +51332,7 @@
         <v>45740</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -51405,7 +51405,7 @@
         <v>46100</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -51478,7 +51478,7 @@
         <v>45216</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -51551,7 +51551,7 @@
         <v>46112</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -51624,7 +51624,7 @@
         <v>46171</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -51697,7 +51697,7 @@
         <v>46099</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -51770,7 +51770,7 @@
         <v>45030</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -51843,7 +51843,7 @@
         <v>45236</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -51916,7 +51916,7 @@
         <v>45166</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -51989,7 +51989,7 @@
         <v>46171</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -52062,7 +52062,7 @@
         <v>46170</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -52135,7 +52135,7 @@
         <v>46010</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -52208,7 +52208,7 @@
         <v>46171</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -52281,7 +52281,7 @@
         <v>45446</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -52354,7 +52354,7 @@
         <v>45384</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -52427,7 +52427,7 @@
         <v>45097</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -52505,7 +52505,7 @@
         <v>45392</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -52583,7 +52583,7 @@
         <v>45324</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -52656,7 +52656,7 @@
         <v>45267</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -52729,7 +52729,7 @@
         <v>45782</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -52802,7 +52802,7 @@
         <v>45558</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -52875,7 +52875,7 @@
         <v>45309</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -52948,7 +52948,7 @@
         <v>45309</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -53021,7 +53021,7 @@
         <v>46134</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -53094,7 +53094,7 @@
         <v>46134</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -53167,7 +53167,7 @@
         <v>45113</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -53240,7 +53240,7 @@
         <v>45037</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -53313,7 +53313,7 @@
         <v>45037</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -53386,7 +53386,7 @@
         <v>45222</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -53459,7 +53459,7 @@
         <v>44988</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -53532,7 +53532,7 @@
         <v>45127</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -53605,7 +53605,7 @@
         <v>46134</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -53678,7 +53678,7 @@
         <v>46183</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -53751,7 +53751,7 @@
         <v>46170</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -53824,7 +53824,7 @@
         <v>46183</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -53897,7 +53897,7 @@
         <v>45048</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -53970,7 +53970,7 @@
         <v>45874</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -54043,7 +54043,7 @@
         <v>46183</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -54116,7 +54116,7 @@
         <v>46183</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -54189,7 +54189,7 @@
         <v>46183</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -54262,7 +54262,7 @@
         <v>45638</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -54335,7 +54335,7 @@
         <v>45685</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -54408,7 +54408,7 @@
         <v>45611</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -54481,7 +54481,7 @@
         <v>45161</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -54554,7 +54554,7 @@
         <v>44866</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -54627,7 +54627,7 @@
         <v>46188</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -54700,7 +54700,7 @@
         <v>46189</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -54773,7 +54773,7 @@
         <v>45139</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -54846,7 +54846,7 @@
         <v>45112</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -54919,7 +54919,7 @@
         <v>46188</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -54992,7 +54992,7 @@
         <v>46188</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -55065,7 +55065,7 @@
         <v>45580</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -55138,7 +55138,7 @@
         <v>46191</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -55211,7 +55211,7 @@
         <v>45014</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -55289,7 +55289,7 @@
         <v>46191</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -55362,7 +55362,7 @@
         <v>46191</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -55435,7 +55435,7 @@
         <v>45316</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -55508,7 +55508,7 @@
         <v>46190</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -55581,7 +55581,7 @@
         <v>46191</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -55654,7 +55654,7 @@
         <v>45330</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -55732,7 +55732,7 @@
         <v>46195</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -55805,7 +55805,7 @@
         <v>45219</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -55878,7 +55878,7 @@
         <v>46108</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -55951,7 +55951,7 @@
         <v>45330</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -56024,7 +56024,7 @@
         <v>45924</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -56097,7 +56097,7 @@
         <v>45644</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -56170,7 +56170,7 @@
         <v>45198</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -56243,7 +56243,7 @@
         <v>45008</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -56316,7 +56316,7 @@
         <v>45855</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -56389,7 +56389,7 @@
         <v>45000</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -56462,7 +56462,7 @@
         <v>44609</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -56535,7 +56535,7 @@
         <v>45733</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -56608,7 +56608,7 @@
         <v>45722</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -56681,7 +56681,7 @@
         <v>45036</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -56754,7 +56754,7 @@
         <v>46199</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -56827,7 +56827,7 @@
         <v>45065</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -56900,7 +56900,7 @@
         <v>46199</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -56973,7 +56973,7 @@
         <v>46198</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -57046,7 +57046,7 @@
         <v>46198</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -57119,7 +57119,7 @@
         <v>45028</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -57192,7 +57192,7 @@
         <v>45594</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -57270,7 +57270,7 @@
         <v>45594</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -57348,7 +57348,7 @@
         <v>45594</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -57426,7 +57426,7 @@
         <v>45594</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -57504,7 +57504,7 @@
         <v>46198</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -57577,7 +57577,7 @@
         <v>46198</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -57650,7 +57650,7 @@
         <v>45509</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -57723,7 +57723,7 @@
         <v>45541</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -57796,7 +57796,7 @@
         <v>46199</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -57869,7 +57869,7 @@
         <v>46199</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -57942,7 +57942,7 @@
         <v>45644</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -58015,7 +58015,7 @@
         <v>45594</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -58093,7 +58093,7 @@
         <v>45594</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -58171,7 +58171,7 @@
         <v>45594</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -58249,7 +58249,7 @@
         <v>45601</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -58322,7 +58322,7 @@
         <v>46199</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -58395,7 +58395,7 @@
         <v>45278</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -58468,7 +58468,7 @@
         <v>45316</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -58541,7 +58541,7 @@
         <v>45316</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -58614,7 +58614,7 @@
         <v>45056</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -58687,7 +58687,7 @@
         <v>46205</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -58760,7 +58760,7 @@
         <v>45161</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -58833,7 +58833,7 @@
         <v>45288</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -58906,7 +58906,7 @@
         <v>46205</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -58979,7 +58979,7 @@
         <v>45229</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -59052,7 +59052,7 @@
         <v>45222</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -59125,7 +59125,7 @@
         <v>44858</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -59198,7 +59198,7 @@
         <v>44487</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -59271,7 +59271,7 @@
         <v>46252</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -59344,7 +59344,7 @@
         <v>45372</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -59417,7 +59417,7 @@
         <v>44764</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -59490,7 +59490,7 @@
         <v>45091</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -59568,7 +59568,7 @@
         <v>45579</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -59641,7 +59641,7 @@
         <v>45385</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -59719,7 +59719,7 @@
         <v>45385</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -59797,7 +59797,7 @@
         <v>45440</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -59870,7 +59870,7 @@
         <v>46206</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -59948,7 +59948,7 @@
         <v>45679</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -60021,7 +60021,7 @@
         <v>46252</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -60094,7 +60094,7 @@
         <v>46210</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -60172,7 +60172,7 @@
         <v>45215</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -60245,7 +60245,7 @@
         <v>44876</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -60323,7 +60323,7 @@
         <v>45495</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -60396,7 +60396,7 @@
         <v>46253</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -60469,7 +60469,7 @@
         <v>46210</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -60547,7 +60547,7 @@
         <v>45210</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -60620,7 +60620,7 @@
         <v>45754</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -60693,7 +60693,7 @@
         <v>45244</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -60766,7 +60766,7 @@
         <v>44679</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -60839,7 +60839,7 @@
         <v>44678</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -60912,7 +60912,7 @@
         <v>45775</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -60985,7 +60985,7 @@
         <v>46258</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -61058,7 +61058,7 @@
         <v>44802</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -61131,7 +61131,7 @@
         <v>45420</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -61204,7 +61204,7 @@
         <v>45140</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -61277,7 +61277,7 @@
         <v>45686</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -61350,7 +61350,7 @@
         <v>45686</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -61423,7 +61423,7 @@
         <v>45085</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -61496,7 +61496,7 @@
         <v>44676</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -61574,7 +61574,7 @@
         <v>44620</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -61647,7 +61647,7 @@
         <v>46260</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -61720,7 +61720,7 @@
         <v>45253</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -61793,7 +61793,7 @@
         <v>45247</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -61866,7 +61866,7 @@
         <v>44676</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -61944,7 +61944,7 @@
         <v>45236</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -62017,7 +62017,7 @@
         <v>45236</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -62090,7 +62090,7 @@
         <v>46170</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -62163,7 +62163,7 @@
         <v>45114</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -62236,7 +62236,7 @@
         <v>46261</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -62309,7 +62309,7 @@
         <v>45679</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -62382,7 +62382,7 @@
         <v>44690</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -62455,7 +62455,7 @@
         <v>44705</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -62528,7 +62528,7 @@
         <v>44651</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -62601,7 +62601,7 @@
         <v>45460</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -62674,7 +62674,7 @@
         <v>46262</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -62747,7 +62747,7 @@
         <v>45421</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -62820,7 +62820,7 @@
         <v>45188</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -62893,7 +62893,7 @@
         <v>45176</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -62966,7 +62966,7 @@
         <v>45121</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -63039,7 +63039,7 @@
         <v>45250</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -63112,7 +63112,7 @@
         <v>44746</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -63185,7 +63185,7 @@
         <v>45753</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -63258,7 +63258,7 @@
         <v>45288</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -63331,7 +63331,7 @@
         <v>44686</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -63404,7 +63404,7 @@
         <v>45260</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -63477,7 +63477,7 @@
         <v>44915</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -63550,7 +63550,7 @@
         <v>44651</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -63623,7 +63623,7 @@
         <v>44831</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -63696,7 +63696,7 @@
         <v>46230</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -63769,7 +63769,7 @@
         <v>46183</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -63842,7 +63842,7 @@
         <v>45301</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -63915,7 +63915,7 @@
         <v>45247</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -63988,7 +63988,7 @@
         <v>45309</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -64061,7 +64061,7 @@
         <v>45121</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -64134,7 +64134,7 @@
         <v>44677</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -64207,7 +64207,7 @@
         <v>44811</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -64280,7 +64280,7 @@
         <v>46269</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -64353,7 +64353,7 @@
         <v>44749</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -64426,7 +64426,7 @@
         <v>45104</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -64499,7 +64499,7 @@
         <v>44496</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -64572,7 +64572,7 @@
         <v>44858</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -64645,7 +64645,7 @@
         <v>46272</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -64718,7 +64718,7 @@
         <v>46272</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -64791,7 +64791,7 @@
         <v>46216</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -64864,7 +64864,7 @@
         <v>46216</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -64937,7 +64937,7 @@
         <v>46216</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -65010,7 +65010,7 @@
         <v>45274</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -65083,7 +65083,7 @@
         <v>45246</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -65156,7 +65156,7 @@
         <v>45743</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -65229,7 +65229,7 @@
         <v>46276</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -65302,7 +65302,7 @@
         <v>45198</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -65375,7 +65375,7 @@
         <v>45644</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -65448,7 +65448,7 @@
         <v>45128</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -65521,7 +65521,7 @@
         <v>46232</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -65594,7 +65594,7 @@
         <v>46232</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -65667,7 +65667,7 @@
         <v>46276</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -65740,7 +65740,7 @@
         <v>45686</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -65813,7 +65813,7 @@
         <v>46279</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -65886,7 +65886,7 @@
         <v>46279</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -65959,7 +65959,7 @@
         <v>45278</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -66032,7 +66032,7 @@
         <v>45559</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -66105,7 +66105,7 @@
         <v>45181</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -66178,7 +66178,7 @@
         <v>45141</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -66251,7 +66251,7 @@
         <v>45194</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -66324,7 +66324,7 @@
         <v>46237</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -66397,7 +66397,7 @@
         <v>46237</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -66470,7 +66470,7 @@
         <v>45302</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -66543,7 +66543,7 @@
         <v>45726</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -66616,7 +66616,7 @@
         <v>45401</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -66689,7 +66689,7 @@
         <v>45244</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -66762,7 +66762,7 @@
         <v>45152</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -66835,7 +66835,7 @@
         <v>45702</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -66908,7 +66908,7 @@
         <v>46281</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -66981,7 +66981,7 @@
         <v>46239</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -67054,7 +67054,7 @@
         <v>45541</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -67127,7 +67127,7 @@
         <v>45300</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -67200,7 +67200,7 @@
         <v>45300</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -67273,7 +67273,7 @@
         <v>46244</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -67351,7 +67351,7 @@
         <v>46244</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -67429,7 +67429,7 @@
         <v>46244</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -67507,7 +67507,7 @@
         <v>45342</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -67580,7 +67580,7 @@
         <v>45302</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -67653,7 +67653,7 @@
         <v>45322</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -67726,7 +67726,7 @@
         <v>46244</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -67804,7 +67804,7 @@
         <v>46244</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -67882,7 +67882,7 @@
         <v>45511</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -67955,7 +67955,7 @@
         <v>44915</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -68028,7 +68028,7 @@
         <v>46244</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -68101,7 +68101,7 @@
         <v>46244</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -68179,7 +68179,7 @@
         <v>44652</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -68252,7 +68252,7 @@
         <v>46288</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -68325,7 +68325,7 @@
         <v>44537</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -68398,7 +68398,7 @@
         <v>46245</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -68471,7 +68471,7 @@
         <v>44609</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -68544,7 +68544,7 @@
         <v>46245</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -68617,7 +68617,7 @@
         <v>45183</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -68690,7 +68690,7 @@
         <v>46288</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -68763,7 +68763,7 @@
         <v>45121</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -68836,7 +68836,7 @@
         <v>45420</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -68909,7 +68909,7 @@
         <v>45253</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -68982,7 +68982,7 @@
         <v>44845</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -69055,7 +69055,7 @@
         <v>44915</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -69128,7 +69128,7 @@
         <v>44552</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -69201,7 +69201,7 @@
         <v>45070</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -69274,7 +69274,7 @@
         <v>46244</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -69347,7 +69347,7 @@
         <v>46245</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -69420,7 +69420,7 @@
         <v>44998</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -69493,7 +69493,7 @@
         <v>44592</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -69566,7 +69566,7 @@
         <v>45103</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -69639,7 +69639,7 @@
         <v>45058</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -69712,7 +69712,7 @@
         <v>46289</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -69785,7 +69785,7 @@
         <v>46021</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -69858,7 +69858,7 @@
         <v>45315</v>
       </c>
       <c r="E900" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -69931,7 +69931,7 @@
         <v>45315</v>
       </c>
       <c r="E901" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>
@@ -70004,7 +70004,7 @@
         <v>46056</v>
       </c>
       <c r="E902" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F902" t="inlineStr">
         <is>
@@ -70077,7 +70077,7 @@
         <v>46289</v>
       </c>
       <c r="E903" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F903" t="inlineStr">
         <is>
@@ -70150,7 +70150,7 @@
         <v>44979</v>
       </c>
       <c r="E904" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F904" t="inlineStr">
         <is>
@@ -70223,7 +70223,7 @@
         <v>45386</v>
       </c>
       <c r="E905" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F905" t="inlineStr">
         <is>
@@ -70296,7 +70296,7 @@
         <v>45359</v>
       </c>
       <c r="E906" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F906" t="inlineStr">
         <is>
@@ -70369,7 +70369,7 @@
         <v>44959</v>
       </c>
       <c r="E907" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F907" t="inlineStr">
         <is>
@@ -70442,7 +70442,7 @@
         <v>46246</v>
       </c>
       <c r="E908" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F908" t="inlineStr">
         <is>
@@ -70520,7 +70520,7 @@
         <v>45594</v>
       </c>
       <c r="E909" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F909" t="inlineStr">
         <is>
@@ -70598,7 +70598,7 @@
         <v>45594</v>
       </c>
       <c r="E910" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F910" t="inlineStr">
         <is>
@@ -70676,7 +70676,7 @@
         <v>45594</v>
       </c>
       <c r="E911" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F911" t="inlineStr">
         <is>
@@ -70754,7 +70754,7 @@
         <v>45230</v>
       </c>
       <c r="E912" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F912" t="inlineStr">
         <is>
@@ -70827,7 +70827,7 @@
         <v>44843</v>
       </c>
       <c r="E913" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F913" t="inlineStr">
         <is>
@@ -70900,7 +70900,7 @@
         <v>44894</v>
       </c>
       <c r="E914" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F914" t="inlineStr">
         <is>
@@ -70973,7 +70973,7 @@
         <v>45245</v>
       </c>
       <c r="E915" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F915" t="inlineStr">
         <is>
@@ -71046,7 +71046,7 @@
         <v>44963</v>
       </c>
       <c r="E916" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F916" t="inlineStr">
         <is>
@@ -71119,7 +71119,7 @@
         <v>45597</v>
       </c>
       <c r="E917" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F917" t="inlineStr">
         <is>
@@ -71192,7 +71192,7 @@
         <v>45219</v>
       </c>
       <c r="E918" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F918" t="inlineStr">
         <is>
@@ -71265,7 +71265,7 @@
         <v>45061</v>
       </c>
       <c r="E919" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F919" t="inlineStr">
         <is>
@@ -71338,7 +71338,7 @@
         <v>45572</v>
       </c>
       <c r="E920" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F920" t="inlineStr">
         <is>
@@ -71411,7 +71411,7 @@
         <v>45304</v>
       </c>
       <c r="E921" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F921" t="inlineStr">
         <is>
@@ -71484,7 +71484,7 @@
         <v>45029</v>
       </c>
       <c r="E922" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F922" t="inlineStr">
         <is>
@@ -71557,7 +71557,7 @@
         <v>44992</v>
       </c>
       <c r="E923" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F923" t="inlineStr">
         <is>
@@ -71630,7 +71630,7 @@
         <v>45552</v>
       </c>
       <c r="E924" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F924" t="inlineStr">
         <is>
@@ -71703,7 +71703,7 @@
         <v>45199</v>
       </c>
       <c r="E925" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F925" t="inlineStr">
         <is>
@@ -71776,7 +71776,7 @@
         <v>45181</v>
       </c>
       <c r="E926" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F926" t="inlineStr">
         <is>
@@ -71849,7 +71849,7 @@
         <v>45147</v>
       </c>
       <c r="E927" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F927" t="inlineStr">
         <is>
@@ -71922,7 +71922,7 @@
         <v>45105</v>
       </c>
       <c r="E928" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F928" t="inlineStr">
         <is>
@@ -71995,7 +71995,7 @@
         <v>44501</v>
       </c>
       <c r="E929" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F929" t="inlineStr">
         <is>
@@ -72068,7 +72068,7 @@
         <v>45557</v>
       </c>
       <c r="E930" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F930" t="inlineStr">
         <is>
@@ -72141,7 +72141,7 @@
         <v>45324</v>
       </c>
       <c r="E931" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F931" t="inlineStr">
         <is>
@@ -72214,7 +72214,7 @@
         <v>45554</v>
       </c>
       <c r="E932" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F932" t="inlineStr">
         <is>
@@ -72287,7 +72287,7 @@
         <v>44761</v>
       </c>
       <c r="E933" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F933" t="inlineStr">
         <is>
@@ -72365,7 +72365,7 @@
         <v>45468</v>
       </c>
       <c r="E934" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F934" t="inlineStr">
         <is>
@@ -72438,7 +72438,7 @@
         <v>45057</v>
       </c>
       <c r="E935" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F935" t="inlineStr">
         <is>
@@ -72511,7 +72511,7 @@
         <v>45427</v>
       </c>
       <c r="E936" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F936" t="inlineStr">
         <is>
@@ -72584,7 +72584,7 @@
         <v>45400</v>
       </c>
       <c r="E937" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F937" t="inlineStr">
         <is>
@@ -72657,7 +72657,7 @@
         <v>45594</v>
       </c>
       <c r="E938" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F938" t="inlineStr">
         <is>
@@ -72735,7 +72735,7 @@
         <v>45446</v>
       </c>
       <c r="E939" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F939" t="inlineStr">
         <is>
@@ -72808,7 +72808,7 @@
         <v>44977</v>
       </c>
       <c r="E940" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F940" t="inlineStr">
         <is>
@@ -72881,7 +72881,7 @@
         <v>45009</v>
       </c>
       <c r="E941" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F941" t="inlineStr">
         <is>
@@ -72959,7 +72959,7 @@
         <v>45679</v>
       </c>
       <c r="E942" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F942" t="inlineStr">
         <is>
@@ -73032,7 +73032,7 @@
         <v>44602</v>
       </c>
       <c r="E943" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F943" t="inlineStr">
         <is>
@@ -73105,7 +73105,7 @@
         <v>44732</v>
       </c>
       <c r="E944" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F944" t="inlineStr">
         <is>
@@ -73178,7 +73178,7 @@
         <v>45176</v>
       </c>
       <c r="E945" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F945" t="inlineStr">
         <is>
@@ -73251,7 +73251,7 @@
         <v>44956</v>
       </c>
       <c r="E946" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F946" t="inlineStr">
         <is>
@@ -73324,7 +73324,7 @@
         <v>45281</v>
       </c>
       <c r="E947" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F947" t="inlineStr">
         <is>
@@ -73397,7 +73397,7 @@
         <v>45090</v>
       </c>
       <c r="E948" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F948" t="inlineStr">
         <is>
@@ -73470,7 +73470,7 @@
         <v>45019</v>
       </c>
       <c r="E949" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F949" t="inlineStr">
         <is>
@@ -73543,7 +73543,7 @@
         <v>45611</v>
       </c>
       <c r="E950" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F950" t="inlineStr">
         <is>
@@ -73616,7 +73616,7 @@
         <v>45676</v>
       </c>
       <c r="E951" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F951" t="inlineStr">
         <is>
@@ -73694,7 +73694,7 @@
         <v>45162</v>
       </c>
       <c r="E952" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F952" t="inlineStr">
         <is>
@@ -73767,7 +73767,7 @@
         <v>45162</v>
       </c>
       <c r="E953" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F953" t="inlineStr">
         <is>
@@ -73840,7 +73840,7 @@
         <v>45581</v>
       </c>
       <c r="E954" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F954" t="inlineStr">
         <is>
@@ -73913,7 +73913,7 @@
         <v>45504</v>
       </c>
       <c r="E955" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F955" t="inlineStr">
         <is>
@@ -73986,7 +73986,7 @@
         <v>44502</v>
       </c>
       <c r="E956" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F956" t="inlineStr">
         <is>
@@ -74064,7 +74064,7 @@
         <v>45049</v>
       </c>
       <c r="E957" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F957" t="inlineStr">
         <is>
@@ -74137,7 +74137,7 @@
         <v>44896</v>
       </c>
       <c r="E958" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F958" t="inlineStr">
         <is>
@@ -74210,7 +74210,7 @@
         <v>45665</v>
       </c>
       <c r="E959" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F959" t="inlineStr">
         <is>
@@ -74283,7 +74283,7 @@
         <v>45762</v>
       </c>
       <c r="E960" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F960" t="inlineStr">
         <is>
@@ -74361,7 +74361,7 @@
         <v>45153</v>
       </c>
       <c r="E961" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F961" t="inlineStr">
         <is>
@@ -74434,7 +74434,7 @@
         <v>45679</v>
       </c>
       <c r="E962" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F962" t="inlineStr">
         <is>
@@ -74507,7 +74507,7 @@
         <v>45296</v>
       </c>
       <c r="E963" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F963" t="inlineStr">
         <is>
@@ -74580,7 +74580,7 @@
         <v>45617</v>
       </c>
       <c r="E964" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F964" t="inlineStr">
         <is>
@@ -74653,7 +74653,7 @@
         <v>45769</v>
       </c>
       <c r="E965" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F965" t="inlineStr">
         <is>
@@ -74726,7 +74726,7 @@
         <v>44687</v>
       </c>
       <c r="E966" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F966" t="inlineStr">
         <is>
@@ -74799,7 +74799,7 @@
         <v>45211</v>
       </c>
       <c r="E967" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F967" t="inlineStr">
         <is>
@@ -74872,7 +74872,7 @@
         <v>45632</v>
       </c>
       <c r="E968" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F968" t="inlineStr">
         <is>
@@ -74945,7 +74945,7 @@
         <v>45232</v>
       </c>
       <c r="E969" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F969" t="inlineStr">
         <is>
@@ -75018,7 +75018,7 @@
         <v>45139</v>
       </c>
       <c r="E970" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F970" t="inlineStr">
         <is>
@@ -75091,7 +75091,7 @@
         <v>45373</v>
       </c>
       <c r="E971" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F971" t="inlineStr">
         <is>
@@ -75164,7 +75164,7 @@
         <v>45448</v>
       </c>
       <c r="E972" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F972" t="inlineStr">
         <is>
@@ -75237,7 +75237,7 @@
         <v>45022</v>
       </c>
       <c r="E973" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F973" t="inlineStr">
         <is>
@@ -75310,7 +75310,7 @@
         <v>45693</v>
       </c>
       <c r="E974" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F974" t="inlineStr">
         <is>
@@ -75383,7 +75383,7 @@
         <v>45555</v>
       </c>
       <c r="E975" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F975" t="inlineStr">
         <is>
@@ -75456,7 +75456,7 @@
         <v>45309</v>
       </c>
       <c r="E976" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F976" t="inlineStr">
         <is>
@@ -75529,7 +75529,7 @@
         <v>45309</v>
       </c>
       <c r="E977" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F977" t="inlineStr">
         <is>
@@ -75602,7 +75602,7 @@
         <v>45108</v>
       </c>
       <c r="E978" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F978" t="inlineStr">
         <is>
@@ -75675,7 +75675,7 @@
         <v>45169</v>
       </c>
       <c r="E979" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F979" t="inlineStr">
         <is>
@@ -75748,7 +75748,7 @@
         <v>45608</v>
       </c>
       <c r="E980" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F980" t="inlineStr">
         <is>
@@ -75821,7 +75821,7 @@
         <v>45205</v>
       </c>
       <c r="E981" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F981" t="inlineStr">
         <is>
@@ -75894,7 +75894,7 @@
         <v>45070</v>
       </c>
       <c r="E982" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F982" t="inlineStr">
         <is>
@@ -75967,7 +75967,7 @@
         <v>44900</v>
       </c>
       <c r="E983" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F983" t="inlineStr">
         <is>
@@ -76040,7 +76040,7 @@
         <v>44900</v>
       </c>
       <c r="E984" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F984" t="inlineStr">
         <is>
@@ -76113,7 +76113,7 @@
         <v>44532</v>
       </c>
       <c r="E985" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F985" t="inlineStr">
         <is>
@@ -76186,7 +76186,7 @@
         <v>45181</v>
       </c>
       <c r="E986" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F986" t="inlineStr">
         <is>
@@ -76259,7 +76259,7 @@
         <v>44929</v>
       </c>
       <c r="E987" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F987" t="inlineStr">
         <is>
@@ -76337,7 +76337,7 @@
         <v>44656</v>
       </c>
       <c r="E988" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F988" t="inlineStr">
         <is>
@@ -76410,7 +76410,7 @@
         <v>45443</v>
       </c>
       <c r="E989" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F989" t="inlineStr">
         <is>
@@ -76483,7 +76483,7 @@
         <v>45147</v>
       </c>
       <c r="E990" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F990" t="inlineStr">
         <is>
@@ -76556,7 +76556,7 @@
         <v>45217</v>
       </c>
       <c r="E991" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F991" t="inlineStr">
         <is>
@@ -76629,7 +76629,7 @@
         <v>44831</v>
       </c>
       <c r="E992" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F992" t="inlineStr">
         <is>
@@ -76702,7 +76702,7 @@
         <v>45194</v>
       </c>
       <c r="E993" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F993" t="inlineStr">
         <is>
@@ -76775,7 +76775,7 @@
         <v>45219</v>
       </c>
       <c r="E994" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F994" t="inlineStr">
         <is>
@@ -76848,7 +76848,7 @@
         <v>45280</v>
       </c>
       <c r="E995" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F995" t="inlineStr">
         <is>
@@ -76921,7 +76921,7 @@
         <v>45705</v>
       </c>
       <c r="E996" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F996" t="inlineStr">
         <is>
@@ -76999,7 +76999,7 @@
         <v>45016</v>
       </c>
       <c r="E997" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F997" t="inlineStr">
         <is>
@@ -77072,7 +77072,7 @@
         <v>45061</v>
       </c>
       <c r="E998" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F998" t="inlineStr">
         <is>
@@ -77145,7 +77145,7 @@
         <v>45560</v>
       </c>
       <c r="E999" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F999" t="inlineStr">
         <is>
@@ -77218,7 +77218,7 @@
         <v>44909</v>
       </c>
       <c r="E1000" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1000" t="inlineStr">
         <is>
@@ -77296,7 +77296,7 @@
         <v>44986</v>
       </c>
       <c r="E1001" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1001" t="inlineStr">
         <is>
@@ -77369,7 +77369,7 @@
         <v>45686</v>
       </c>
       <c r="E1002" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1002" t="inlineStr">
         <is>
@@ -77442,7 +77442,7 @@
         <v>45737</v>
       </c>
       <c r="E1003" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1003" t="inlineStr">
         <is>
@@ -77515,7 +77515,7 @@
         <v>45224</v>
       </c>
       <c r="E1004" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1004" t="inlineStr">
         <is>
@@ -77588,7 +77588,7 @@
         <v>45304</v>
       </c>
       <c r="E1005" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1005" t="inlineStr">
         <is>
@@ -77661,7 +77661,7 @@
         <v>45244</v>
       </c>
       <c r="E1006" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1006" t="inlineStr">
         <is>
@@ -77734,7 +77734,7 @@
         <v>45250</v>
       </c>
       <c r="E1007" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1007" t="inlineStr">
         <is>
@@ -77807,7 +77807,7 @@
         <v>45557</v>
       </c>
       <c r="E1008" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1008" t="inlineStr">
         <is>
@@ -77880,7 +77880,7 @@
         <v>45579</v>
       </c>
       <c r="E1009" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1009" t="inlineStr">
         <is>
@@ -77953,7 +77953,7 @@
         <v>45533</v>
       </c>
       <c r="E1010" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1010" t="inlineStr">
         <is>
@@ -78026,7 +78026,7 @@
         <v>45579</v>
       </c>
       <c r="E1011" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1011" t="inlineStr">
         <is>
@@ -78099,7 +78099,7 @@
         <v>45702</v>
       </c>
       <c r="E1012" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1012" t="inlineStr">
         <is>
@@ -78172,7 +78172,7 @@
         <v>45165</v>
       </c>
       <c r="E1013" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1013" t="inlineStr">
         <is>
@@ -78245,7 +78245,7 @@
         <v>45397</v>
       </c>
       <c r="E1014" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1014" t="inlineStr">
         <is>
@@ -78318,7 +78318,7 @@
         <v>45194</v>
       </c>
       <c r="E1015" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1015" t="inlineStr">
         <is>
@@ -78391,7 +78391,7 @@
         <v>45547</v>
       </c>
       <c r="E1016" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1016" t="inlineStr">
         <is>
@@ -78464,7 +78464,7 @@
         <v>45777</v>
       </c>
       <c r="E1017" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1017" t="inlineStr">
         <is>
@@ -78542,7 +78542,7 @@
         <v>45519</v>
       </c>
       <c r="E1018" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1018" t="inlineStr">
         <is>
@@ -78615,7 +78615,7 @@
         <v>45777</v>
       </c>
       <c r="E1019" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1019" t="inlineStr">
         <is>
@@ -78693,7 +78693,7 @@
         <v>45777</v>
       </c>
       <c r="E1020" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1020" t="inlineStr">
         <is>
@@ -78771,7 +78771,7 @@
         <v>45780</v>
       </c>
       <c r="E1021" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1021" t="inlineStr">
         <is>
@@ -78844,7 +78844,7 @@
         <v>45780</v>
       </c>
       <c r="E1022" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1022" t="inlineStr">
         <is>
@@ -78917,7 +78917,7 @@
         <v>45782</v>
       </c>
       <c r="E1023" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1023" t="inlineStr">
         <is>
@@ -78990,7 +78990,7 @@
         <v>45546</v>
       </c>
       <c r="E1024" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1024" t="inlineStr">
         <is>
@@ -79063,7 +79063,7 @@
         <v>45783</v>
       </c>
       <c r="E1025" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1025" t="inlineStr">
         <is>
@@ -79136,7 +79136,7 @@
         <v>45534</v>
       </c>
       <c r="E1026" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1026" t="inlineStr">
         <is>
@@ -79209,7 +79209,7 @@
         <v>45478</v>
       </c>
       <c r="E1027" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1027" t="inlineStr">
         <is>
@@ -79282,7 +79282,7 @@
         <v>45642</v>
       </c>
       <c r="E1028" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1028" t="inlineStr">
         <is>
@@ -79355,7 +79355,7 @@
         <v>44781</v>
       </c>
       <c r="E1029" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1029" t="inlineStr">
         <is>
@@ -79433,7 +79433,7 @@
         <v>45608</v>
       </c>
       <c r="E1030" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1030" t="inlineStr">
         <is>
@@ -79506,7 +79506,7 @@
         <v>45108</v>
       </c>
       <c r="E1031" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1031" t="inlineStr">
         <is>
@@ -79579,7 +79579,7 @@
         <v>45716</v>
       </c>
       <c r="E1032" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1032" t="inlineStr">
         <is>
@@ -79652,7 +79652,7 @@
         <v>45614</v>
       </c>
       <c r="E1033" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1033" t="inlineStr">
         <is>
@@ -79725,7 +79725,7 @@
         <v>45716</v>
       </c>
       <c r="E1034" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1034" t="inlineStr">
         <is>
@@ -79798,7 +79798,7 @@
         <v>45791</v>
       </c>
       <c r="E1035" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1035" t="inlineStr">
         <is>
@@ -79871,7 +79871,7 @@
         <v>44715</v>
       </c>
       <c r="E1036" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1036" t="inlineStr">
         <is>
@@ -79944,7 +79944,7 @@
         <v>44722</v>
       </c>
       <c r="E1037" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1037" t="inlineStr">
         <is>
@@ -80017,7 +80017,7 @@
         <v>44588</v>
       </c>
       <c r="E1038" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1038" t="inlineStr">
         <is>
@@ -80090,7 +80090,7 @@
         <v>44727</v>
       </c>
       <c r="E1039" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1039" t="inlineStr">
         <is>
@@ -80163,7 +80163,7 @@
         <v>44722</v>
       </c>
       <c r="E1040" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1040" t="inlineStr">
         <is>
@@ -80236,7 +80236,7 @@
         <v>44603</v>
       </c>
       <c r="E1041" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1041" t="inlineStr">
         <is>
@@ -80309,7 +80309,7 @@
         <v>44693</v>
       </c>
       <c r="E1042" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1042" t="inlineStr">
         <is>
@@ -80382,7 +80382,7 @@
         <v>44726</v>
       </c>
       <c r="E1043" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1043" t="inlineStr">
         <is>
@@ -80455,7 +80455,7 @@
         <v>44712</v>
       </c>
       <c r="E1044" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1044" t="inlineStr">
         <is>
@@ -80528,7 +80528,7 @@
         <v>44722</v>
       </c>
       <c r="E1045" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1045" t="inlineStr">
         <is>
@@ -80601,7 +80601,7 @@
         <v>44712</v>
       </c>
       <c r="E1046" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1046" t="inlineStr">
         <is>
@@ -80674,7 +80674,7 @@
         <v>44704</v>
       </c>
       <c r="E1047" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1047" t="inlineStr">
         <is>
@@ -80747,7 +80747,7 @@
         <v>44596</v>
       </c>
       <c r="E1048" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1048" t="inlineStr">
         <is>
@@ -80820,7 +80820,7 @@
         <v>44704</v>
       </c>
       <c r="E1049" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1049" t="inlineStr">
         <is>
@@ -80893,7 +80893,7 @@
         <v>44588</v>
       </c>
       <c r="E1050" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1050" t="inlineStr">
         <is>
@@ -80966,7 +80966,7 @@
         <v>45054</v>
       </c>
       <c r="E1051" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1051" t="inlineStr">
         <is>
@@ -81039,7 +81039,7 @@
         <v>45230</v>
       </c>
       <c r="E1052" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1052" t="inlineStr">
         <is>
@@ -81117,7 +81117,7 @@
         <v>44498</v>
       </c>
       <c r="E1053" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1053" t="inlineStr">
         <is>
@@ -81190,7 +81190,7 @@
         <v>45622</v>
       </c>
       <c r="E1054" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1054" t="inlineStr">
         <is>
@@ -81263,7 +81263,7 @@
         <v>45054</v>
       </c>
       <c r="E1055" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1055" t="inlineStr">
         <is>
@@ -81336,7 +81336,7 @@
         <v>45054</v>
       </c>
       <c r="E1056" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1056" t="inlineStr">
         <is>
@@ -81409,7 +81409,7 @@
         <v>45056</v>
       </c>
       <c r="E1057" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1057" t="inlineStr">
         <is>
@@ -81482,7 +81482,7 @@
         <v>45434</v>
       </c>
       <c r="E1058" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1058" t="inlineStr">
         <is>
@@ -81555,7 +81555,7 @@
         <v>44468</v>
       </c>
       <c r="E1059" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1059" t="inlineStr">
         <is>
@@ -81628,7 +81628,7 @@
         <v>45054</v>
       </c>
       <c r="E1060" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1060" t="inlineStr">
         <is>
@@ -81701,7 +81701,7 @@
         <v>45407</v>
       </c>
       <c r="E1061" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1061" t="inlineStr">
         <is>
@@ -81774,7 +81774,7 @@
         <v>44802</v>
       </c>
       <c r="E1062" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1062" t="inlineStr">
         <is>
@@ -81847,7 +81847,7 @@
         <v>45071</v>
       </c>
       <c r="E1063" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1063" t="inlineStr">
         <is>
@@ -81920,7 +81920,7 @@
         <v>44495</v>
       </c>
       <c r="E1064" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1064" t="inlineStr">
         <is>
@@ -81993,7 +81993,7 @@
         <v>44474</v>
       </c>
       <c r="E1065" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1065" t="inlineStr">
         <is>
@@ -82066,7 +82066,7 @@
         <v>45224</v>
       </c>
       <c r="E1066" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1066" t="inlineStr">
         <is>
@@ -82144,7 +82144,7 @@
         <v>44972</v>
       </c>
       <c r="E1067" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1067" t="inlineStr">
         <is>
@@ -82217,7 +82217,7 @@
         <v>44487</v>
       </c>
       <c r="E1068" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1068" t="inlineStr">
         <is>
@@ -82290,7 +82290,7 @@
         <v>45230</v>
       </c>
       <c r="E1069" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1069" t="inlineStr">
         <is>
@@ -82363,7 +82363,7 @@
         <v>44939</v>
       </c>
       <c r="E1070" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1070" t="inlineStr">
         <is>
@@ -82436,7 +82436,7 @@
         <v>45468</v>
       </c>
       <c r="E1071" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1071" t="inlineStr">
         <is>
@@ -82509,7 +82509,7 @@
         <v>45218</v>
       </c>
       <c r="E1072" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1072" t="inlineStr">
         <is>
@@ -82582,7 +82582,7 @@
         <v>45054</v>
       </c>
       <c r="E1073" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1073" t="inlineStr">
         <is>
@@ -82655,7 +82655,7 @@
         <v>44930</v>
       </c>
       <c r="E1074" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1074" t="inlineStr">
         <is>
@@ -82733,7 +82733,7 @@
         <v>44973</v>
       </c>
       <c r="E1075" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1075" t="inlineStr">
         <is>
@@ -82806,7 +82806,7 @@
         <v>44908</v>
       </c>
       <c r="E1076" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1076" t="inlineStr">
         <is>
@@ -82899,7 +82899,7 @@
         <v>45583</v>
       </c>
       <c r="E1077" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1077" t="inlineStr">
         <is>
@@ -82972,7 +82972,7 @@
         <v>45054</v>
       </c>
       <c r="E1078" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1078" t="inlineStr">
         <is>
@@ -83045,7 +83045,7 @@
         <v>45054</v>
       </c>
       <c r="E1079" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1079" t="inlineStr">
         <is>
@@ -83118,7 +83118,7 @@
         <v>44908</v>
       </c>
       <c r="E1080" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1080" t="inlineStr">
         <is>
@@ -83191,7 +83191,7 @@
         <v>44972</v>
       </c>
       <c r="E1081" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1081" t="inlineStr">
         <is>
@@ -83264,7 +83264,7 @@
         <v>44978</v>
       </c>
       <c r="E1082" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1082" t="inlineStr">
         <is>
@@ -83337,7 +83337,7 @@
         <v>44887</v>
       </c>
       <c r="E1083" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1083" t="inlineStr">
         <is>
@@ -83410,7 +83410,7 @@
         <v>44909</v>
       </c>
       <c r="E1084" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1084" t="inlineStr">
         <is>
@@ -83483,7 +83483,7 @@
         <v>45408</v>
       </c>
       <c r="E1085" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1085" t="inlineStr">
         <is>
@@ -83556,7 +83556,7 @@
         <v>44908</v>
       </c>
       <c r="E1086" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1086" t="inlineStr">
         <is>
@@ -83629,7 +83629,7 @@
         <v>45054</v>
       </c>
       <c r="E1087" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1087" t="inlineStr">
         <is>
@@ -83702,7 +83702,7 @@
         <v>45526</v>
       </c>
       <c r="E1088" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1088" t="inlineStr">
         <is>
@@ -83775,7 +83775,7 @@
         <v>45436</v>
       </c>
       <c r="E1089" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1089" t="inlineStr">
         <is>
@@ -83848,7 +83848,7 @@
         <v>45485</v>
       </c>
       <c r="E1090" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1090" t="inlineStr">
         <is>
@@ -83921,7 +83921,7 @@
         <v>45727</v>
       </c>
       <c r="E1091" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1091" t="inlineStr">
         <is>
@@ -83994,7 +83994,7 @@
         <v>45740</v>
       </c>
       <c r="E1092" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1092" t="inlineStr">
         <is>
@@ -84067,7 +84067,7 @@
         <v>45726</v>
       </c>
       <c r="E1093" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1093" t="inlineStr">
         <is>
@@ -84140,7 +84140,7 @@
         <v>45797</v>
       </c>
       <c r="E1094" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1094" t="inlineStr">
         <is>
@@ -84213,7 +84213,7 @@
         <v>45805</v>
       </c>
       <c r="E1095" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1095" t="inlineStr">
         <is>
@@ -84286,7 +84286,7 @@
         <v>45831</v>
       </c>
       <c r="E1096" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1096" t="inlineStr">
         <is>
@@ -84359,7 +84359,7 @@
         <v>45951</v>
       </c>
       <c r="E1097" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1097" t="inlineStr">
         <is>
@@ -84432,7 +84432,7 @@
         <v>45958</v>
       </c>
       <c r="E1098" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1098" t="inlineStr">
         <is>
@@ -84505,7 +84505,7 @@
         <v>45964</v>
       </c>
       <c r="E1099" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1099" t="inlineStr">
         <is>
@@ -84578,7 +84578,7 @@
         <v>45965</v>
       </c>
       <c r="E1100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1100" t="inlineStr">
         <is>
@@ -84651,7 +84651,7 @@
         <v>45981</v>
       </c>
       <c r="E1101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1101" t="inlineStr">
         <is>
@@ -84729,7 +84729,7 @@
         <v>45988</v>
       </c>
       <c r="E1102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1102" t="inlineStr">
         <is>
@@ -84802,7 +84802,7 @@
         <v>46092</v>
       </c>
       <c r="E1103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1103" t="inlineStr">
         <is>
@@ -84880,7 +84880,7 @@
         <v>46202</v>
       </c>
       <c r="E1104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1104" t="inlineStr">
         <is>
@@ -84953,7 +84953,7 @@
         <v>46262</v>
       </c>
       <c r="E1105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1105" t="inlineStr">
         <is>

--- a/Översikt VÄXJÖ.xlsx
+++ b/Översikt VÄXJÖ.xlsx
@@ -601,7 +601,7 @@
         <v>44974</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         <v>45895</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -859,7 +859,7 @@
         <v>45770</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -976,7 +976,7 @@
         <v>45468</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         <v>45384</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
         <v>45888</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>45812</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         <v>45127</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>46175</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
         <v>45964</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1769,7 +1769,7 @@
         <v>46188</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
         <v>46188</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         <v>46199</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>45081</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2224,7 +2224,7 @@
         <v>44958</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2337,7 +2337,7 @@
         <v>45490</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2454,7 +2454,7 @@
         <v>45294</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2571,7 +2571,7 @@
         <v>45995</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2683,7 +2683,7 @@
         <v>46247</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2791,7 +2791,7 @@
         <v>45356</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2902,7 +2902,7 @@
         <v>46204</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3018,7 +3018,7 @@
         <v>46244</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3129,7 +3129,7 @@
         <v>45344</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         <v>46098</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3347,7 +3347,7 @@
         <v>46286</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3454,7 +3454,7 @@
         <v>45883</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3560,7 +3560,7 @@
         <v>45447</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3666,7 +3666,7 @@
         <v>45093</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3776,7 +3776,7 @@
         <v>45545</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3882,7 +3882,7 @@
         <v>45649</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3988,7 +3988,7 @@
         <v>45687</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4094,7 +4094,7 @@
         <v>45554</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4200,7 +4200,7 @@
         <v>45587</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4310,7 +4310,7 @@
         <v>44532</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4425,7 +4425,7 @@
         <v>45190</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4531,7 +4531,7 @@
         <v>45874</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4642,7 +4642,7 @@
         <v>46147</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4748,7 +4748,7 @@
         <v>46161</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4858,7 +4858,7 @@
         <v>46182</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4973,7 +4973,7 @@
         <v>46296</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5079,7 +5079,7 @@
         <v>44704</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5185,7 +5185,7 @@
         <v>44704</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5295,7 +5295,7 @@
         <v>45460</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5401,7 +5401,7 @@
         <v>45348</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         <v>45351</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5613,7 +5613,7 @@
         <v>45674</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5724,7 +5724,7 @@
         <v>46100</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5830,7 +5830,7 @@
         <v>44721</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5935,7 +5935,7 @@
         <v>44704</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6040,7 +6040,7 @@
         <v>44490</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6145,7 +6145,7 @@
         <v>44645</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6250,7 +6250,7 @@
         <v>45754</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6355,7 +6355,7 @@
         <v>45392</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6465,7 +6465,7 @@
         <v>45280</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6570,7 +6570,7 @@
         <v>44673</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6675,7 +6675,7 @@
         <v>45428</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6785,7 +6785,7 @@
         <v>45273</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6890,7 +6890,7 @@
         <v>45280</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6995,7 +6995,7 @@
         <v>44872</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7100,7 +7100,7 @@
         <v>44894</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7205,7 +7205,7 @@
         <v>45688</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7310,7 +7310,7 @@
         <v>45617</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7420,7 +7420,7 @@
         <v>45606</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7525,7 +7525,7 @@
         <v>44705</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7634,7 +7634,7 @@
         <v>45820</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7739,7 +7739,7 @@
         <v>45643</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7844,7 +7844,7 @@
         <v>45964</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7953,7 +7953,7 @@
         <v>44746</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8058,7 +8058,7 @@
         <v>45978</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8167,7 +8167,7 @@
         <v>45594</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8281,7 +8281,7 @@
         <v>44741</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8386,7 +8386,7 @@
         <v>45327</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8491,7 +8491,7 @@
         <v>45824</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8596,7 +8596,7 @@
         <v>45098</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8701,7 +8701,7 @@
         <v>46045</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8806,7 +8806,7 @@
         <v>45533</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8911,7 +8911,7 @@
         <v>45369</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9016,7 +9016,7 @@
         <v>45279</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         <v>45594</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9231,7 +9231,7 @@
         <v>45594</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9341,7 +9341,7 @@
         <v>46161</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9446,7 +9446,7 @@
         <v>46161</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9551,7 +9551,7 @@
         <v>46199</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9656,7 +9656,7 @@
         <v>46281</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9761,7 +9761,7 @@
         <v>46288</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9866,7 +9866,7 @@
         <v>46246</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9971,7 +9971,7 @@
         <v>46296</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10076,7 +10076,7 @@
         <v>46303</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10181,7 +10181,7 @@
         <v>44634</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10286,7 +10286,7 @@
         <v>44712</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10391,7 +10391,7 @@
         <v>44950</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10496,7 +10496,7 @@
         <v>45436</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10601,7 +10601,7 @@
         <v>45726</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10706,7 +10706,7 @@
         <v>45805</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10811,7 +10811,7 @@
         <v>45939</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10920,7 +10920,7 @@
         <v>46100</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11025,7 +11025,7 @@
         <v>44693</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11098,7 +11098,7 @@
         <v>44812</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11171,7 +11171,7 @@
         <v>44518</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11244,7 +11244,7 @@
         <v>44536</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11317,7 +11317,7 @@
         <v>44764</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11390,7 +11390,7 @@
         <v>44519</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11463,7 +11463,7 @@
         <v>44501</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11536,7 +11536,7 @@
         <v>44814</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11609,7 +11609,7 @@
         <v>44645</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11682,7 +11682,7 @@
         <v>44643</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11755,7 +11755,7 @@
         <v>44515</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11828,7 +11828,7 @@
         <v>44814</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11901,7 +11901,7 @@
         <v>44480</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11974,7 +11974,7 @@
         <v>44525</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12047,7 +12047,7 @@
         <v>44578</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12120,7 +12120,7 @@
         <v>44516</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12198,7 +12198,7 @@
         <v>44803</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12271,7 +12271,7 @@
         <v>44691</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12344,7 +12344,7 @@
         <v>44739</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12417,7 +12417,7 @@
         <v>44590</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12495,7 +12495,7 @@
         <v>44820</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12573,7 +12573,7 @@
         <v>44814</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12646,7 +12646,7 @@
         <v>44769</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12724,7 +12724,7 @@
         <v>44711</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12797,7 +12797,7 @@
         <v>44820</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12870,7 +12870,7 @@
         <v>44508</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12943,7 +12943,7 @@
         <v>44880</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13016,7 +13016,7 @@
         <v>44495</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13089,7 +13089,7 @@
         <v>44515</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13162,7 +13162,7 @@
         <v>44599</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13235,7 +13235,7 @@
         <v>44495</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13308,7 +13308,7 @@
         <v>44599</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13381,7 +13381,7 @@
         <v>44651</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13454,7 +13454,7 @@
         <v>44876</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13532,7 +13532,7 @@
         <v>44671</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13605,7 +13605,7 @@
         <v>44491</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13678,7 +13678,7 @@
         <v>44502</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13756,7 +13756,7 @@
         <v>44812</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13829,7 +13829,7 @@
         <v>44740</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13902,7 +13902,7 @@
         <v>44483</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13975,7 +13975,7 @@
         <v>44496</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14048,7 +14048,7 @@
         <v>44489</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14121,7 +14121,7 @@
         <v>44489</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14194,7 +14194,7 @@
         <v>44617</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14267,7 +14267,7 @@
         <v>44483</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14340,7 +14340,7 @@
         <v>44750</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14413,7 +14413,7 @@
         <v>44498</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14486,7 +14486,7 @@
         <v>44508</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14559,7 +14559,7 @@
         <v>44726</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14632,7 +14632,7 @@
         <v>44568</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14705,7 +14705,7 @@
         <v>44537</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14778,7 +14778,7 @@
         <v>44574</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14851,7 +14851,7 @@
         <v>44860</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14924,7 +14924,7 @@
         <v>44551</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14997,7 +14997,7 @@
         <v>44537</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15070,7 +15070,7 @@
         <v>44543</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15143,7 +15143,7 @@
         <v>44599</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15216,7 +15216,7 @@
         <v>44596</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15289,7 +15289,7 @@
         <v>44606</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15362,7 +15362,7 @@
         <v>44573</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15435,7 +15435,7 @@
         <v>44571</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15508,7 +15508,7 @@
         <v>44712</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15581,7 +15581,7 @@
         <v>44489</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15654,7 +15654,7 @@
         <v>44613</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15727,7 +15727,7 @@
         <v>44579</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15800,7 +15800,7 @@
         <v>44746</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15873,7 +15873,7 @@
         <v>44487</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15946,7 +15946,7 @@
         <v>44711</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16019,7 +16019,7 @@
         <v>44610</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16092,7 +16092,7 @@
         <v>44781</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16165,7 +16165,7 @@
         <v>44769</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16243,7 +16243,7 @@
         <v>44603</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16321,7 +16321,7 @@
         <v>44494</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16394,7 +16394,7 @@
         <v>44610</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16467,7 +16467,7 @@
         <v>44704</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16540,7 +16540,7 @@
         <v>44596</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16613,7 +16613,7 @@
         <v>44522</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16686,7 +16686,7 @@
         <v>44867</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16759,7 +16759,7 @@
         <v>44532</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16832,7 +16832,7 @@
         <v>44532</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16905,7 +16905,7 @@
         <v>44560</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16978,7 +16978,7 @@
         <v>44602</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17051,7 +17051,7 @@
         <v>44732</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17124,7 +17124,7 @@
         <v>45372</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17197,7 +17197,7 @@
         <v>45176</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17270,7 +17270,7 @@
         <v>44820</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17348,7 +17348,7 @@
         <v>44820</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17426,7 +17426,7 @@
         <v>44956</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17499,7 +17499,7 @@
         <v>45281</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17572,7 +17572,7 @@
         <v>45632</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17645,7 +17645,7 @@
         <v>45153</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17718,7 +17718,7 @@
         <v>44713</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17791,7 +17791,7 @@
         <v>45090</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17864,7 +17864,7 @@
         <v>45019</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17937,7 +17937,7 @@
         <v>45219</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18010,7 +18010,7 @@
         <v>44908</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18083,7 +18083,7 @@
         <v>44897</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18156,7 +18156,7 @@
         <v>45611</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18229,7 +18229,7 @@
         <v>45204</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18302,7 +18302,7 @@
         <v>45737</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18375,7 +18375,7 @@
         <v>45676</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18453,7 +18453,7 @@
         <v>45162</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18526,7 +18526,7 @@
         <v>45162</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18599,7 +18599,7 @@
         <v>45581</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18672,7 +18672,7 @@
         <v>45504</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18745,7 +18745,7 @@
         <v>44502</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18823,7 +18823,7 @@
         <v>45259</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18896,7 +18896,7 @@
         <v>44874</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18969,7 +18969,7 @@
         <v>45049</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19042,7 +19042,7 @@
         <v>45392</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19120,7 +19120,7 @@
         <v>45412</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19193,7 +19193,7 @@
         <v>44741</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19266,7 +19266,7 @@
         <v>44741</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19339,7 +19339,7 @@
         <v>44896</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19412,7 +19412,7 @@
         <v>45194</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19485,7 +19485,7 @@
         <v>45557</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19558,7 +19558,7 @@
         <v>44928</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19631,7 +19631,7 @@
         <v>45219</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19704,7 +19704,7 @@
         <v>44814</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19777,7 +19777,7 @@
         <v>44814</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19850,7 +19850,7 @@
         <v>45665</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19923,7 +19923,7 @@
         <v>45762</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20001,7 +20001,7 @@
         <v>45279</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20074,7 +20074,7 @@
         <v>45153</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20147,7 +20147,7 @@
         <v>45679</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20220,7 +20220,7 @@
         <v>45273</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20293,7 +20293,7 @@
         <v>45296</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20366,7 +20366,7 @@
         <v>45436</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20439,7 +20439,7 @@
         <v>45106</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20512,7 +20512,7 @@
         <v>44741</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20585,7 +20585,7 @@
         <v>45715</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20658,7 +20658,7 @@
         <v>45617</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20731,7 +20731,7 @@
         <v>44894</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20809,7 +20809,7 @@
         <v>45090</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20882,7 +20882,7 @@
         <v>45769</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20955,7 +20955,7 @@
         <v>45561</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21028,7 +21028,7 @@
         <v>45392</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21101,7 +21101,7 @@
         <v>45300</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21174,7 +21174,7 @@
         <v>45302</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21247,7 +21247,7 @@
         <v>45447</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21320,7 +21320,7 @@
         <v>44687</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21393,7 +21393,7 @@
         <v>45211</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21466,7 +21466,7 @@
         <v>45211</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21539,7 +21539,7 @@
         <v>45632</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21612,7 +21612,7 @@
         <v>45104</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21685,7 +21685,7 @@
         <v>45232</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21758,7 +21758,7 @@
         <v>45078</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21836,7 +21836,7 @@
         <v>45726</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21909,7 +21909,7 @@
         <v>45302</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21982,7 +21982,7 @@
         <v>45386</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22055,7 +22055,7 @@
         <v>45341</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22128,7 +22128,7 @@
         <v>45127</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22201,7 +22201,7 @@
         <v>45139</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22274,7 +22274,7 @@
         <v>45392</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22352,7 +22352,7 @@
         <v>45392</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22430,7 +22430,7 @@
         <v>45446</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22508,7 +22508,7 @@
         <v>44986</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22581,7 +22581,7 @@
         <v>45373</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22654,7 +22654,7 @@
         <v>45448</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22727,7 +22727,7 @@
         <v>45538</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22805,7 +22805,7 @@
         <v>45128</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22878,7 +22878,7 @@
         <v>45128</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22951,7 +22951,7 @@
         <v>45432</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23024,7 +23024,7 @@
         <v>45387</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23097,7 +23097,7 @@
         <v>45022</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23170,7 +23170,7 @@
         <v>45754</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23243,7 +23243,7 @@
         <v>45754</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23316,7 +23316,7 @@
         <v>45693</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23389,7 +23389,7 @@
         <v>45240</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23462,7 +23462,7 @@
         <v>45555</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23535,7 +23535,7 @@
         <v>45317</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23608,7 +23608,7 @@
         <v>45278</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23681,7 +23681,7 @@
         <v>45309</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23754,7 +23754,7 @@
         <v>45309</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23827,7 +23827,7 @@
         <v>45121</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23900,7 +23900,7 @@
         <v>45121</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23973,7 +23973,7 @@
         <v>45121</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24046,7 +24046,7 @@
         <v>45236</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24119,7 +24119,7 @@
         <v>45161</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24192,7 +24192,7 @@
         <v>45112</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24265,7 +24265,7 @@
         <v>45288</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24338,7 +24338,7 @@
         <v>45108</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24411,7 +24411,7 @@
         <v>45387</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24484,7 +24484,7 @@
         <v>45477</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24562,7 +24562,7 @@
         <v>44959</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24635,7 +24635,7 @@
         <v>45229</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24708,7 +24708,7 @@
         <v>45222</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24781,7 +24781,7 @@
         <v>45169</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24854,7 +24854,7 @@
         <v>44487</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24927,7 +24927,7 @@
         <v>45446</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25000,7 +25000,7 @@
         <v>45280</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25073,7 +25073,7 @@
         <v>44880</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25146,7 +25146,7 @@
         <v>44904</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25219,7 +25219,7 @@
         <v>44904</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25292,7 +25292,7 @@
         <v>45608</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25365,7 +25365,7 @@
         <v>45205</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25438,7 +25438,7 @@
         <v>45201</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25511,7 +25511,7 @@
         <v>45281</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25584,7 +25584,7 @@
         <v>44963</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25657,7 +25657,7 @@
         <v>44963</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25730,7 +25730,7 @@
         <v>44963</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25803,7 +25803,7 @@
         <v>45070</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25876,7 +25876,7 @@
         <v>45622</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25949,7 +25949,7 @@
         <v>45240</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26022,7 +26022,7 @@
         <v>45468</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26095,7 +26095,7 @@
         <v>44900</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26168,7 +26168,7 @@
         <v>44900</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26241,7 +26241,7 @@
         <v>45127</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26314,7 +26314,7 @@
         <v>45127</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26387,7 +26387,7 @@
         <v>45883</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26460,7 +26460,7 @@
         <v>45551</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26533,7 +26533,7 @@
         <v>44573</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26606,7 +26606,7 @@
         <v>44532</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26679,7 +26679,7 @@
         <v>45225</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26752,7 +26752,7 @@
         <v>45181</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26825,7 +26825,7 @@
         <v>44854</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26898,7 +26898,7 @@
         <v>45244</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26971,7 +26971,7 @@
         <v>45127</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27044,7 +27044,7 @@
         <v>44894</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27117,7 +27117,7 @@
         <v>44929</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27195,7 +27195,7 @@
         <v>45111</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27268,7 +27268,7 @@
         <v>44656</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27341,7 +27341,7 @@
         <v>45154</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27414,7 +27414,7 @@
         <v>45030</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27487,7 +27487,7 @@
         <v>45443</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27560,7 +27560,7 @@
         <v>45145</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27633,7 +27633,7 @@
         <v>45147</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27706,7 +27706,7 @@
         <v>45217</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27779,7 +27779,7 @@
         <v>45294</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27852,7 +27852,7 @@
         <v>45236</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27925,7 +27925,7 @@
         <v>44831</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27998,7 +27998,7 @@
         <v>45166</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28071,7 +28071,7 @@
         <v>45194</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28144,7 +28144,7 @@
         <v>45219</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28217,7 +28217,7 @@
         <v>45342</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28290,7 +28290,7 @@
         <v>45754</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28363,7 +28363,7 @@
         <v>45330</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28436,7 +28436,7 @@
         <v>44950</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28509,7 +28509,7 @@
         <v>45280</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28582,7 +28582,7 @@
         <v>45705</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28660,7 +28660,7 @@
         <v>45446</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28733,7 +28733,7 @@
         <v>45477</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28811,7 +28811,7 @@
         <v>45392</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28889,7 +28889,7 @@
         <v>44547</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28962,7 +28962,7 @@
         <v>44545</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29035,7 +29035,7 @@
         <v>45324</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29108,7 +29108,7 @@
         <v>45016</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29181,7 +29181,7 @@
         <v>45488</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29254,7 +29254,7 @@
         <v>45061</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29327,7 +29327,7 @@
         <v>45124</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29400,7 +29400,7 @@
         <v>45894</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29473,7 +29473,7 @@
         <v>45890</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29546,7 +29546,7 @@
         <v>45856</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29619,7 +29619,7 @@
         <v>45895</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29692,7 +29692,7 @@
         <v>45897</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29770,7 +29770,7 @@
         <v>44880</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29843,7 +29843,7 @@
         <v>45560</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29916,7 +29916,7 @@
         <v>44909</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29994,7 +29994,7 @@
         <v>44922</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30067,7 +30067,7 @@
         <v>45645</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30140,7 +30140,7 @@
         <v>45719</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30213,7 +30213,7 @@
         <v>44986</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30286,7 +30286,7 @@
         <v>45902</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30359,7 +30359,7 @@
         <v>45902</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30432,7 +30432,7 @@
         <v>45686</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30505,7 +30505,7 @@
         <v>45737</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30578,7 +30578,7 @@
         <v>45224</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30651,7 +30651,7 @@
         <v>45304</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30724,7 +30724,7 @@
         <v>44537</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30797,7 +30797,7 @@
         <v>45902</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30870,7 +30870,7 @@
         <v>45244</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30943,7 +30943,7 @@
         <v>45810</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31021,7 +31021,7 @@
         <v>45835</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31094,7 +31094,7 @@
         <v>45250</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31167,7 +31167,7 @@
         <v>45557</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31240,7 +31240,7 @@
         <v>45579</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31313,7 +31313,7 @@
         <v>45558</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31386,7 +31386,7 @@
         <v>45309</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31459,7 +31459,7 @@
         <v>45533</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31532,7 +31532,7 @@
         <v>45309</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31605,7 +31605,7 @@
         <v>45579</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31678,7 +31678,7 @@
         <v>45702</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31751,7 +31751,7 @@
         <v>44896</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31824,7 +31824,7 @@
         <v>45905</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31897,7 +31897,7 @@
         <v>45165</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31970,7 +31970,7 @@
         <v>45910</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32043,7 +32043,7 @@
         <v>45113</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32116,7 +32116,7 @@
         <v>45148</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32189,7 +32189,7 @@
         <v>45148</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32262,7 +32262,7 @@
         <v>45037</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32335,7 +32335,7 @@
         <v>45037</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32408,7 +32408,7 @@
         <v>45194</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32481,7 +32481,7 @@
         <v>45547</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32554,7 +32554,7 @@
         <v>45909</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32627,7 +32627,7 @@
         <v>45777</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32705,7 +32705,7 @@
         <v>45519</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32778,7 +32778,7 @@
         <v>45777</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32856,7 +32856,7 @@
         <v>45190</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32929,7 +32929,7 @@
         <v>45777</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33007,7 +33007,7 @@
         <v>45222</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33080,7 +33080,7 @@
         <v>45787</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33153,7 +33153,7 @@
         <v>44988</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33226,7 +33226,7 @@
         <v>45127</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33299,7 +33299,7 @@
         <v>45780</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33372,7 +33372,7 @@
         <v>45780</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33445,7 +33445,7 @@
         <v>45911</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33518,7 +33518,7 @@
         <v>45782</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33591,7 +33591,7 @@
         <v>45573</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33664,7 +33664,7 @@
         <v>44867</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33737,7 +33737,7 @@
         <v>45048</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33810,7 +33810,7 @@
         <v>45546</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33883,7 +33883,7 @@
         <v>45540</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33956,7 +33956,7 @@
         <v>44599</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34029,7 +34029,7 @@
         <v>45783</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34102,7 +34102,7 @@
         <v>45672</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34175,7 +34175,7 @@
         <v>45056</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34248,7 +34248,7 @@
         <v>45534</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34321,7 +34321,7 @@
         <v>45478</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34394,7 +34394,7 @@
         <v>45638</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34467,7 +34467,7 @@
         <v>44896</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34540,7 +34540,7 @@
         <v>45685</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34613,7 +34613,7 @@
         <v>45642</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34686,7 +34686,7 @@
         <v>45559</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34759,7 +34759,7 @@
         <v>44781</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34837,7 +34837,7 @@
         <v>45611</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34910,7 +34910,7 @@
         <v>44532</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34983,7 +34983,7 @@
         <v>45161</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35056,7 +35056,7 @@
         <v>45608</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35129,7 +35129,7 @@
         <v>44866</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35202,7 +35202,7 @@
         <v>45918</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35275,7 +35275,7 @@
         <v>45108</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35348,7 +35348,7 @@
         <v>45716</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35421,7 +35421,7 @@
         <v>45390</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35494,7 +35494,7 @@
         <v>45139</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35567,7 +35567,7 @@
         <v>45112</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35640,7 +35640,7 @@
         <v>45614</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35713,7 +35713,7 @@
         <v>44595</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35786,7 +35786,7 @@
         <v>45555</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35859,7 +35859,7 @@
         <v>45580</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35932,7 +35932,7 @@
         <v>44903</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36005,7 +36005,7 @@
         <v>44938</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36078,7 +36078,7 @@
         <v>45014</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36156,7 +36156,7 @@
         <v>45716</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36229,7 +36229,7 @@
         <v>45316</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36302,7 +36302,7 @@
         <v>45924</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36375,7 +36375,7 @@
         <v>45330</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36453,7 +36453,7 @@
         <v>45014</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36526,7 +36526,7 @@
         <v>45219</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36599,7 +36599,7 @@
         <v>45925</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36672,7 +36672,7 @@
         <v>45330</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36745,7 +36745,7 @@
         <v>45644</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36818,7 +36818,7 @@
         <v>45198</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36891,7 +36891,7 @@
         <v>45008</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36964,7 +36964,7 @@
         <v>45412</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37037,7 +37037,7 @@
         <v>45412</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37110,7 +37110,7 @@
         <v>45140</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37183,7 +37183,7 @@
         <v>45791</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37256,7 +37256,7 @@
         <v>45000</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37329,7 +37329,7 @@
         <v>44609</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37402,7 +37402,7 @@
         <v>45733</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37475,7 +37475,7 @@
         <v>45552</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37548,7 +37548,7 @@
         <v>45722</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37621,7 +37621,7 @@
         <v>45036</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37694,7 +37694,7 @@
         <v>45378</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37767,7 +37767,7 @@
         <v>45796</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37840,7 +37840,7 @@
         <v>45534</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37913,7 +37913,7 @@
         <v>45560</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37986,7 +37986,7 @@
         <v>45369</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38059,7 +38059,7 @@
         <v>44599</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38132,7 +38132,7 @@
         <v>44869</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38205,7 +38205,7 @@
         <v>45338</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38278,7 +38278,7 @@
         <v>45065</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38351,7 +38351,7 @@
         <v>45244</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38424,7 +38424,7 @@
         <v>45408</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38497,7 +38497,7 @@
         <v>45028</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38570,7 +38570,7 @@
         <v>45222</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38643,7 +38643,7 @@
         <v>45594</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38721,7 +38721,7 @@
         <v>45594</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38799,7 +38799,7 @@
         <v>45594</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38877,7 +38877,7 @@
         <v>45594</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38955,7 +38955,7 @@
         <v>45169</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39028,7 +39028,7 @@
         <v>45583</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39106,7 +39106,7 @@
         <v>45392</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39184,7 +39184,7 @@
         <v>44670</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39257,7 +39257,7 @@
         <v>45509</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39330,7 +39330,7 @@
         <v>45644</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39403,7 +39403,7 @@
         <v>45594</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39481,7 +39481,7 @@
         <v>45594</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39559,7 +39559,7 @@
         <v>45594</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39637,7 +39637,7 @@
         <v>45764</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39710,7 +39710,7 @@
         <v>45574</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39783,7 +39783,7 @@
         <v>45601</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39856,7 +39856,7 @@
         <v>45665</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39929,7 +39929,7 @@
         <v>44711</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40002,7 +40002,7 @@
         <v>45071</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40080,7 +40080,7 @@
         <v>45316</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40153,7 +40153,7 @@
         <v>45583</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40226,7 +40226,7 @@
         <v>44824</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40299,7 +40299,7 @@
         <v>45316</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40372,7 +40372,7 @@
         <v>45056</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40445,7 +40445,7 @@
         <v>45757</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40518,7 +40518,7 @@
         <v>45384</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40591,7 +40591,7 @@
         <v>45345</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40664,7 +40664,7 @@
         <v>44858</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40737,7 +40737,7 @@
         <v>45579</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40810,7 +40810,7 @@
         <v>45749</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -40883,7 +40883,7 @@
         <v>44970</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40956,7 +40956,7 @@
         <v>45937</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41029,7 +41029,7 @@
         <v>45803</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41102,7 +41102,7 @@
         <v>45937</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41175,7 +41175,7 @@
         <v>45372</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41248,7 +41248,7 @@
         <v>44764</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41321,7 +41321,7 @@
         <v>45091</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41399,7 +41399,7 @@
         <v>45579</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41472,7 +41472,7 @@
         <v>45805</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41545,7 +41545,7 @@
         <v>45385</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41623,7 +41623,7 @@
         <v>45385</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -41701,7 +41701,7 @@
         <v>45763</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -41774,7 +41774,7 @@
         <v>45447</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -41847,7 +41847,7 @@
         <v>45764</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -41920,7 +41920,7 @@
         <v>45440</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -41993,7 +41993,7 @@
         <v>45189</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42066,7 +42066,7 @@
         <v>45189</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42139,7 +42139,7 @@
         <v>45722</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42212,7 +42212,7 @@
         <v>45679</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42285,7 +42285,7 @@
         <v>44963</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42358,7 +42358,7 @@
         <v>45463</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42431,7 +42431,7 @@
         <v>45896</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42504,7 +42504,7 @@
         <v>44960</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42577,7 +42577,7 @@
         <v>45594</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42655,7 +42655,7 @@
         <v>45594</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42733,7 +42733,7 @@
         <v>45594</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -42811,7 +42811,7 @@
         <v>45594</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -42889,7 +42889,7 @@
         <v>45594</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -42967,7 +42967,7 @@
         <v>45594</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43045,7 +43045,7 @@
         <v>45594</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43123,7 +43123,7 @@
         <v>45586</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43196,7 +43196,7 @@
         <v>45215</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43269,7 +43269,7 @@
         <v>44876</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43347,7 +43347,7 @@
         <v>45495</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43420,7 +43420,7 @@
         <v>45210</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -43493,7 +43493,7 @@
         <v>45281</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -43566,7 +43566,7 @@
         <v>45754</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -43639,7 +43639,7 @@
         <v>45244</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -43712,7 +43712,7 @@
         <v>45180</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -43785,7 +43785,7 @@
         <v>44679</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -43858,7 +43858,7 @@
         <v>44678</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -43931,7 +43931,7 @@
         <v>45714</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44004,7 +44004,7 @@
         <v>45775</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44077,7 +44077,7 @@
         <v>45670</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44150,7 +44150,7 @@
         <v>45250</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44223,7 +44223,7 @@
         <v>45769</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44296,7 +44296,7 @@
         <v>45820</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44369,7 +44369,7 @@
         <v>44802</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -44442,7 +44442,7 @@
         <v>45420</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -44515,7 +44515,7 @@
         <v>45140</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -44588,7 +44588,7 @@
         <v>45820</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -44661,7 +44661,7 @@
         <v>45817</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -44734,7 +44734,7 @@
         <v>45818</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -44807,7 +44807,7 @@
         <v>45629</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -44880,7 +44880,7 @@
         <v>45328</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -44953,7 +44953,7 @@
         <v>45328</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45026,7 +45026,7 @@
         <v>44494</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45099,7 +45099,7 @@
         <v>45824</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45172,7 +45172,7 @@
         <v>45824</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45245,7 +45245,7 @@
         <v>45686</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -45318,7 +45318,7 @@
         <v>45686</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -45391,7 +45391,7 @@
         <v>45638</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -45464,7 +45464,7 @@
         <v>45825</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -45537,7 +45537,7 @@
         <v>45611</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -45610,7 +45610,7 @@
         <v>45085</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -45683,7 +45683,7 @@
         <v>44676</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -45761,7 +45761,7 @@
         <v>44743</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -45834,7 +45834,7 @@
         <v>44711</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -45907,7 +45907,7 @@
         <v>44620</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -45980,7 +45980,7 @@
         <v>45827</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46053,7 +46053,7 @@
         <v>45831</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46126,7 +46126,7 @@
         <v>45224</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -46204,7 +46204,7 @@
         <v>44966</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -46277,7 +46277,7 @@
         <v>45089</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -46350,7 +46350,7 @@
         <v>44972</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -46423,7 +46423,7 @@
         <v>44972</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -46496,7 +46496,7 @@
         <v>45519</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -46569,7 +46569,7 @@
         <v>45253</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -46642,7 +46642,7 @@
         <v>45247</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -46715,7 +46715,7 @@
         <v>45702</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -46788,7 +46788,7 @@
         <v>45831</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -46861,7 +46861,7 @@
         <v>45952</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -46934,7 +46934,7 @@
         <v>45923</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47007,7 +47007,7 @@
         <v>44676</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47085,7 +47085,7 @@
         <v>45946</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47158,7 +47158,7 @@
         <v>45953</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -47231,7 +47231,7 @@
         <v>45236</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -47304,7 +47304,7 @@
         <v>45236</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -47377,7 +47377,7 @@
         <v>44967</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -47450,7 +47450,7 @@
         <v>45805</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -47523,7 +47523,7 @@
         <v>45832</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -47596,7 +47596,7 @@
         <v>45114</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -47669,7 +47669,7 @@
         <v>45012</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -47742,7 +47742,7 @@
         <v>45679</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -47815,7 +47815,7 @@
         <v>44690</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -47888,7 +47888,7 @@
         <v>44981</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -47961,7 +47961,7 @@
         <v>45924</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48034,7 +48034,7 @@
         <v>44705</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48107,7 +48107,7 @@
         <v>45835</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -48180,7 +48180,7 @@
         <v>45166</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -48253,7 +48253,7 @@
         <v>45835</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -48326,7 +48326,7 @@
         <v>44651</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -48399,7 +48399,7 @@
         <v>45964</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -48472,7 +48472,7 @@
         <v>44998</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -48545,7 +48545,7 @@
         <v>45460</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -48618,7 +48618,7 @@
         <v>45835</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -48691,7 +48691,7 @@
         <v>45421</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -48764,7 +48764,7 @@
         <v>45188</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -48837,7 +48837,7 @@
         <v>45385</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -48915,7 +48915,7 @@
         <v>45385</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -48993,7 +48993,7 @@
         <v>45495</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -49066,7 +49066,7 @@
         <v>45176</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -49139,7 +49139,7 @@
         <v>45103</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -49212,7 +49212,7 @@
         <v>45103</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -49285,7 +49285,7 @@
         <v>45103</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -49358,7 +49358,7 @@
         <v>45121</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -49431,7 +49431,7 @@
         <v>45558</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -49504,7 +49504,7 @@
         <v>45538</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -49577,7 +49577,7 @@
         <v>45840</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -49650,7 +49650,7 @@
         <v>45114</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -49723,7 +49723,7 @@
         <v>45114</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -49796,7 +49796,7 @@
         <v>44739</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -49869,7 +49869,7 @@
         <v>45250</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -49942,7 +49942,7 @@
         <v>44746</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -50015,7 +50015,7 @@
         <v>45128</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -50088,7 +50088,7 @@
         <v>45753</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -50161,7 +50161,7 @@
         <v>45971</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -50234,7 +50234,7 @@
         <v>45540</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -50307,7 +50307,7 @@
         <v>45568</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -50380,7 +50380,7 @@
         <v>45846</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -50453,7 +50453,7 @@
         <v>44774</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -50526,7 +50526,7 @@
         <v>45692</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -50599,7 +50599,7 @@
         <v>45288</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -50672,7 +50672,7 @@
         <v>44686</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -50745,7 +50745,7 @@
         <v>45033</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -50823,7 +50823,7 @@
         <v>45847</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -50896,7 +50896,7 @@
         <v>45260</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -50969,7 +50969,7 @@
         <v>44915</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -51042,7 +51042,7 @@
         <v>45121</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -51115,7 +51115,7 @@
         <v>44782</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -51193,7 +51193,7 @@
         <v>44651</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -51266,7 +51266,7 @@
         <v>45390</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -51339,7 +51339,7 @@
         <v>45973</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -51412,7 +51412,7 @@
         <v>45645</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -51485,7 +51485,7 @@
         <v>45127</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -51558,7 +51558,7 @@
         <v>45168</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -51631,7 +51631,7 @@
         <v>45853</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -51704,7 +51704,7 @@
         <v>45460</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -51777,7 +51777,7 @@
         <v>45740</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -51850,7 +51850,7 @@
         <v>44995</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -51923,7 +51923,7 @@
         <v>45113</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -51996,7 +51996,7 @@
         <v>45113</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -52069,7 +52069,7 @@
         <v>44536</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -52142,7 +52142,7 @@
         <v>44831</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -52215,7 +52215,7 @@
         <v>45301</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -52288,7 +52288,7 @@
         <v>45384</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -52361,7 +52361,7 @@
         <v>45247</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -52434,7 +52434,7 @@
         <v>45097</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -52512,7 +52512,7 @@
         <v>45267</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -52585,7 +52585,7 @@
         <v>45309</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -52658,7 +52658,7 @@
         <v>45121</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -52731,7 +52731,7 @@
         <v>45692</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -52804,7 +52804,7 @@
         <v>44677</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -52877,7 +52877,7 @@
         <v>45782</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -52950,7 +52950,7 @@
         <v>44811</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -53023,7 +53023,7 @@
         <v>44749</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -53096,7 +53096,7 @@
         <v>45714</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -53169,7 +53169,7 @@
         <v>45104</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -53242,7 +53242,7 @@
         <v>44858</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -53315,7 +53315,7 @@
         <v>44502</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -53388,7 +53388,7 @@
         <v>45091</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -53461,7 +53461,7 @@
         <v>45030</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -53534,7 +53534,7 @@
         <v>45979</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -53607,7 +53607,7 @@
         <v>45874</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -53680,7 +53680,7 @@
         <v>45979</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -53753,7 +53753,7 @@
         <v>44496</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -53826,7 +53826,7 @@
         <v>45691</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -53899,7 +53899,7 @@
         <v>44858</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -53972,7 +53972,7 @@
         <v>45980</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -54045,7 +54045,7 @@
         <v>44812</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -54118,7 +54118,7 @@
         <v>45715</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -54196,7 +54196,7 @@
         <v>45048</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -54269,7 +54269,7 @@
         <v>45190</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -54342,7 +54342,7 @@
         <v>44991</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -54415,7 +54415,7 @@
         <v>45513</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -54488,7 +54488,7 @@
         <v>45274</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -54561,7 +54561,7 @@
         <v>45246</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -54634,7 +54634,7 @@
         <v>45743</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -54707,7 +54707,7 @@
         <v>45198</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -54780,7 +54780,7 @@
         <v>45644</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -54853,7 +54853,7 @@
         <v>45128</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -54926,7 +54926,7 @@
         <v>45210</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -54999,7 +54999,7 @@
         <v>45686</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -55072,7 +55072,7 @@
         <v>45278</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -55145,7 +55145,7 @@
         <v>45559</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -55218,7 +55218,7 @@
         <v>46099</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -55291,7 +55291,7 @@
         <v>44909</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -55364,7 +55364,7 @@
         <v>45181</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -55437,7 +55437,7 @@
         <v>46100</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -55510,7 +55510,7 @@
         <v>45141</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -55583,7 +55583,7 @@
         <v>46100</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -55656,7 +55656,7 @@
         <v>45194</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -55729,7 +55729,7 @@
         <v>46100</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -55802,7 +55802,7 @@
         <v>44922</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -55875,7 +55875,7 @@
         <v>45302</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -55948,7 +55948,7 @@
         <v>45753</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -56021,7 +56021,7 @@
         <v>45726</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -56094,7 +56094,7 @@
         <v>45401</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -56167,7 +56167,7 @@
         <v>45244</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -56240,7 +56240,7 @@
         <v>44552</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -56313,7 +56313,7 @@
         <v>45152</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -56386,7 +56386,7 @@
         <v>45250</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -56459,7 +56459,7 @@
         <v>45141</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -56532,7 +56532,7 @@
         <v>45702</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -56605,7 +56605,7 @@
         <v>45614</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -56678,7 +56678,7 @@
         <v>45533</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -56751,7 +56751,7 @@
         <v>44529</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -56824,7 +56824,7 @@
         <v>46107</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -56897,7 +56897,7 @@
         <v>44641</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -56970,7 +56970,7 @@
         <v>44769</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -57048,7 +57048,7 @@
         <v>44769</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -57126,7 +57126,7 @@
         <v>46108</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -57199,7 +57199,7 @@
         <v>45541</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -57272,7 +57272,7 @@
         <v>44874</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -57345,7 +57345,7 @@
         <v>45715</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -57423,7 +57423,7 @@
         <v>45111</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -57496,7 +57496,7 @@
         <v>45714</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -57569,7 +57569,7 @@
         <v>45300</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -57642,7 +57642,7 @@
         <v>45300</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -57715,7 +57715,7 @@
         <v>45267</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -57788,7 +57788,7 @@
         <v>46113</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -57861,7 +57861,7 @@
         <v>44894</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -57934,7 +57934,7 @@
         <v>46112</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -58007,7 +58007,7 @@
         <v>45036</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -58080,7 +58080,7 @@
         <v>45342</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -58153,7 +58153,7 @@
         <v>46112</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -58226,7 +58226,7 @@
         <v>45599</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -58299,7 +58299,7 @@
         <v>45302</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -58372,7 +58372,7 @@
         <v>45322</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -58445,7 +58445,7 @@
         <v>44523</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -58518,7 +58518,7 @@
         <v>45233</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -58591,7 +58591,7 @@
         <v>44600</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -58669,7 +58669,7 @@
         <v>44915</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -58742,7 +58742,7 @@
         <v>45993</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -58815,7 +58815,7 @@
         <v>45594</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -58893,7 +58893,7 @@
         <v>46119</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -58966,7 +58966,7 @@
         <v>45993</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -59039,7 +59039,7 @@
         <v>45594</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -59117,7 +59117,7 @@
         <v>45988</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -59190,7 +59190,7 @@
         <v>44652</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -59263,7 +59263,7 @@
         <v>45999</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -59336,7 +59336,7 @@
         <v>46000</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -59409,7 +59409,7 @@
         <v>46001</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -59482,7 +59482,7 @@
         <v>44537</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -59555,7 +59555,7 @@
         <v>44609</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -59628,7 +59628,7 @@
         <v>45183</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -59701,7 +59701,7 @@
         <v>45121</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -59774,7 +59774,7 @@
         <v>46129</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -59847,7 +59847,7 @@
         <v>45420</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -59920,7 +59920,7 @@
         <v>45253</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -59993,7 +59993,7 @@
         <v>44845</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -60066,7 +60066,7 @@
         <v>44915</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -60139,7 +60139,7 @@
         <v>44552</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -60212,7 +60212,7 @@
         <v>45070</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -60285,7 +60285,7 @@
         <v>44998</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -60358,7 +60358,7 @@
         <v>44592</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -60431,7 +60431,7 @@
         <v>45881</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -60504,7 +60504,7 @@
         <v>45103</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -60577,7 +60577,7 @@
         <v>45638</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -60650,7 +60650,7 @@
         <v>45677</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -60723,7 +60723,7 @@
         <v>45835</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -60796,7 +60796,7 @@
         <v>46008</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -60869,7 +60869,7 @@
         <v>45743</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -60942,7 +60942,7 @@
         <v>45058</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -61015,7 +61015,7 @@
         <v>45827</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -61088,7 +61088,7 @@
         <v>46007</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -61161,7 +61161,7 @@
         <v>45698</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -61234,7 +61234,7 @@
         <v>45810</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -61312,7 +61312,7 @@
         <v>45826</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -61390,7 +61390,7 @@
         <v>45670</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -61463,7 +61463,7 @@
         <v>45905</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -61536,7 +61536,7 @@
         <v>45923</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -61609,7 +61609,7 @@
         <v>45833</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -61682,7 +61682,7 @@
         <v>45883</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -61755,7 +61755,7 @@
         <v>45883</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -61828,7 +61828,7 @@
         <v>45775</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -61901,7 +61901,7 @@
         <v>45846</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -61974,7 +61974,7 @@
         <v>45315</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -62047,7 +62047,7 @@
         <v>45315</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -62120,7 +62120,7 @@
         <v>45782</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -62193,7 +62193,7 @@
         <v>46010</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -62266,7 +62266,7 @@
         <v>45923</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -62339,7 +62339,7 @@
         <v>45426</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -62412,7 +62412,7 @@
         <v>46010</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -62485,7 +62485,7 @@
         <v>45939</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -62558,7 +62558,7 @@
         <v>45827</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -62631,7 +62631,7 @@
         <v>46010</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -62704,7 +62704,7 @@
         <v>44979</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -62777,7 +62777,7 @@
         <v>45386</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -62850,7 +62850,7 @@
         <v>45359</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -62923,7 +62923,7 @@
         <v>46019</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -62996,7 +62996,7 @@
         <v>46019</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -63069,7 +63069,7 @@
         <v>44959</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -63142,7 +63142,7 @@
         <v>45841</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -63215,7 +63215,7 @@
         <v>45686</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -63288,7 +63288,7 @@
         <v>45594</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -63366,7 +63366,7 @@
         <v>45594</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -63444,7 +63444,7 @@
         <v>45230</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -63517,7 +63517,7 @@
         <v>45877</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -63590,7 +63590,7 @@
         <v>44843</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -63663,7 +63663,7 @@
         <v>44894</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -63736,7 +63736,7 @@
         <v>45818</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -63809,7 +63809,7 @@
         <v>46029</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -63882,7 +63882,7 @@
         <v>45245</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -63955,7 +63955,7 @@
         <v>44963</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -64028,7 +64028,7 @@
         <v>46029</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -64101,7 +64101,7 @@
         <v>46031</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -64179,7 +64179,7 @@
         <v>45791</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -64252,7 +64252,7 @@
         <v>46031</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -64330,7 +64330,7 @@
         <v>45597</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -64403,7 +64403,7 @@
         <v>45219</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -64476,7 +64476,7 @@
         <v>45061</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -64549,7 +64549,7 @@
         <v>45419</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -64622,7 +64622,7 @@
         <v>45960</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -64695,7 +64695,7 @@
         <v>45572</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -64768,7 +64768,7 @@
         <v>45304</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -64841,7 +64841,7 @@
         <v>46036</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -64914,7 +64914,7 @@
         <v>46035</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -64992,7 +64992,7 @@
         <v>46035</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -65070,7 +65070,7 @@
         <v>45921</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -65143,7 +65143,7 @@
         <v>46036</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -65216,7 +65216,7 @@
         <v>45029</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -65289,7 +65289,7 @@
         <v>46035</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -65367,7 +65367,7 @@
         <v>44992</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -65440,7 +65440,7 @@
         <v>46036</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -65513,7 +65513,7 @@
         <v>45552</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -65586,7 +65586,7 @@
         <v>45199</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -65659,7 +65659,7 @@
         <v>45909</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -65732,7 +65732,7 @@
         <v>45181</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -65805,7 +65805,7 @@
         <v>46041</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -65878,7 +65878,7 @@
         <v>45147</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -65951,7 +65951,7 @@
         <v>45582</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -66024,7 +66024,7 @@
         <v>45105</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -66097,7 +66097,7 @@
         <v>44501</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -66170,7 +66170,7 @@
         <v>45557</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -66243,7 +66243,7 @@
         <v>45894</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -66316,7 +66316,7 @@
         <v>46043</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -66389,7 +66389,7 @@
         <v>45324</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -66462,7 +66462,7 @@
         <v>46048</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -66535,7 +66535,7 @@
         <v>44522</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -66608,7 +66608,7 @@
         <v>46045</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -66681,7 +66681,7 @@
         <v>45554</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -66754,7 +66754,7 @@
         <v>46045</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -66827,7 +66827,7 @@
         <v>44761</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -66905,7 +66905,7 @@
         <v>45468</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -66978,7 +66978,7 @@
         <v>45057</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -67051,7 +67051,7 @@
         <v>45427</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -67124,7 +67124,7 @@
         <v>45400</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -67197,7 +67197,7 @@
         <v>46049</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -67270,7 +67270,7 @@
         <v>45594</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -67348,7 +67348,7 @@
         <v>45446</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -67421,7 +67421,7 @@
         <v>44977</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -67494,7 +67494,7 @@
         <v>45009</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -67572,7 +67572,7 @@
         <v>46049</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -67645,7 +67645,7 @@
         <v>45679</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -67718,7 +67718,7 @@
         <v>46049</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -67791,7 +67791,7 @@
         <v>46051</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -67864,7 +67864,7 @@
         <v>46056</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -67937,7 +67937,7 @@
         <v>46056</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -68010,7 +68010,7 @@
         <v>46057</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -68083,7 +68083,7 @@
         <v>46059</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -68156,7 +68156,7 @@
         <v>46061</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -68229,7 +68229,7 @@
         <v>45329</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -68302,7 +68302,7 @@
         <v>44577</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -68375,7 +68375,7 @@
         <v>46059</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -68448,7 +68448,7 @@
         <v>46059</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -68521,7 +68521,7 @@
         <v>46146</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -68594,7 +68594,7 @@
         <v>46146</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -68667,7 +68667,7 @@
         <v>46146</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -68740,7 +68740,7 @@
         <v>46147</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -68813,7 +68813,7 @@
         <v>46147</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -68886,7 +68886,7 @@
         <v>46148</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -68959,7 +68959,7 @@
         <v>46147</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -69032,7 +69032,7 @@
         <v>46147</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -69105,7 +69105,7 @@
         <v>45397</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -69178,7 +69178,7 @@
         <v>46147</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -69251,7 +69251,7 @@
         <v>46149</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -69324,7 +69324,7 @@
         <v>46021</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -69397,7 +69397,7 @@
         <v>46072</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -69470,7 +69470,7 @@
         <v>46073</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -69543,7 +69543,7 @@
         <v>46073</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -69616,7 +69616,7 @@
         <v>46153</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -69689,7 +69689,7 @@
         <v>46075</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -69762,7 +69762,7 @@
         <v>46079</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -69835,7 +69835,7 @@
         <v>46079</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -69908,7 +69908,7 @@
         <v>46083</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -69981,7 +69981,7 @@
         <v>46083</v>
       </c>
       <c r="E900" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -70054,7 +70054,7 @@
         <v>46083</v>
       </c>
       <c r="E901" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>
@@ -70127,7 +70127,7 @@
         <v>45995</v>
       </c>
       <c r="E902" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F902" t="inlineStr">
         <is>
@@ -70200,7 +70200,7 @@
         <v>46083</v>
       </c>
       <c r="E903" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F903" t="inlineStr">
         <is>
@@ -70273,7 +70273,7 @@
         <v>46083</v>
       </c>
       <c r="E904" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F904" t="inlineStr">
         <is>
@@ -70346,7 +70346,7 @@
         <v>45517</v>
       </c>
       <c r="E905" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F905" t="inlineStr">
         <is>
@@ -70419,7 +70419,7 @@
         <v>46084</v>
       </c>
       <c r="E906" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F906" t="inlineStr">
         <is>
@@ -70492,7 +70492,7 @@
         <v>45631</v>
       </c>
       <c r="E907" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F907" t="inlineStr">
         <is>
@@ -70565,7 +70565,7 @@
         <v>45789</v>
       </c>
       <c r="E908" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F908" t="inlineStr">
         <is>
@@ -70638,7 +70638,7 @@
         <v>46087</v>
       </c>
       <c r="E909" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F909" t="inlineStr">
         <is>
@@ -70711,7 +70711,7 @@
         <v>45623</v>
       </c>
       <c r="E910" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F910" t="inlineStr">
         <is>
@@ -70784,7 +70784,7 @@
         <v>46162</v>
       </c>
       <c r="E911" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F911" t="inlineStr">
         <is>
@@ -70857,7 +70857,7 @@
         <v>46162</v>
       </c>
       <c r="E912" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F912" t="inlineStr">
         <is>
@@ -70930,7 +70930,7 @@
         <v>45780</v>
       </c>
       <c r="E913" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F913" t="inlineStr">
         <is>
@@ -71003,7 +71003,7 @@
         <v>46162</v>
       </c>
       <c r="E914" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F914" t="inlineStr">
         <is>
@@ -71076,7 +71076,7 @@
         <v>45719</v>
       </c>
       <c r="E915" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F915" t="inlineStr">
         <is>
@@ -71149,7 +71149,7 @@
         <v>46163</v>
       </c>
       <c r="E916" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F916" t="inlineStr">
         <is>
@@ -71222,7 +71222,7 @@
         <v>46163</v>
       </c>
       <c r="E917" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F917" t="inlineStr">
         <is>
@@ -71295,7 +71295,7 @@
         <v>46163</v>
       </c>
       <c r="E918" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F918" t="inlineStr">
         <is>
@@ -71368,7 +71368,7 @@
         <v>46163</v>
       </c>
       <c r="E919" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F919" t="inlineStr">
         <is>
@@ -71441,7 +71441,7 @@
         <v>45812</v>
       </c>
       <c r="E920" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F920" t="inlineStr">
         <is>
@@ -71514,7 +71514,7 @@
         <v>46163</v>
       </c>
       <c r="E921" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F921" t="inlineStr">
         <is>
@@ -71587,7 +71587,7 @@
         <v>46163</v>
       </c>
       <c r="E922" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F922" t="inlineStr">
         <is>
@@ -71660,7 +71660,7 @@
         <v>46168</v>
       </c>
       <c r="E923" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F923" t="inlineStr">
         <is>
@@ -71733,7 +71733,7 @@
         <v>45933</v>
       </c>
       <c r="E924" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F924" t="inlineStr">
         <is>
@@ -71806,7 +71806,7 @@
         <v>46167</v>
       </c>
       <c r="E925" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F925" t="inlineStr">
         <is>
@@ -71879,7 +71879,7 @@
         <v>46168</v>
       </c>
       <c r="E926" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F926" t="inlineStr">
         <is>
@@ -71952,7 +71952,7 @@
         <v>46100</v>
       </c>
       <c r="E927" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F927" t="inlineStr">
         <is>
@@ -72025,7 +72025,7 @@
         <v>45216</v>
       </c>
       <c r="E928" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F928" t="inlineStr">
         <is>
@@ -72098,7 +72098,7 @@
         <v>46112</v>
       </c>
       <c r="E929" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F929" t="inlineStr">
         <is>
@@ -72171,7 +72171,7 @@
         <v>46171</v>
       </c>
       <c r="E930" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F930" t="inlineStr">
         <is>
@@ -72244,7 +72244,7 @@
         <v>46171</v>
       </c>
       <c r="E931" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F931" t="inlineStr">
         <is>
@@ -72317,7 +72317,7 @@
         <v>46170</v>
       </c>
       <c r="E932" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F932" t="inlineStr">
         <is>
@@ -72390,7 +72390,7 @@
         <v>46010</v>
       </c>
       <c r="E933" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F933" t="inlineStr">
         <is>
@@ -72463,7 +72463,7 @@
         <v>46171</v>
       </c>
       <c r="E934" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F934" t="inlineStr">
         <is>
@@ -72536,7 +72536,7 @@
         <v>46134</v>
       </c>
       <c r="E935" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F935" t="inlineStr">
         <is>
@@ -72609,7 +72609,7 @@
         <v>46134</v>
       </c>
       <c r="E936" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F936" t="inlineStr">
         <is>
@@ -72682,7 +72682,7 @@
         <v>46134</v>
       </c>
       <c r="E937" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F937" t="inlineStr">
         <is>
@@ -72755,7 +72755,7 @@
         <v>46170</v>
       </c>
       <c r="E938" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F938" t="inlineStr">
         <is>
@@ -72828,7 +72828,7 @@
         <v>46183</v>
       </c>
       <c r="E939" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F939" t="inlineStr">
         <is>
@@ -72901,7 +72901,7 @@
         <v>46183</v>
       </c>
       <c r="E940" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F940" t="inlineStr">
         <is>
@@ -72974,7 +72974,7 @@
         <v>46183</v>
       </c>
       <c r="E941" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F941" t="inlineStr">
         <is>
@@ -73047,7 +73047,7 @@
         <v>46183</v>
       </c>
       <c r="E942" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F942" t="inlineStr">
         <is>
@@ -73120,7 +73120,7 @@
         <v>46189</v>
       </c>
       <c r="E943" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F943" t="inlineStr">
         <is>
@@ -73193,7 +73193,7 @@
         <v>46188</v>
       </c>
       <c r="E944" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F944" t="inlineStr">
         <is>
@@ -73266,7 +73266,7 @@
         <v>46191</v>
       </c>
       <c r="E945" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F945" t="inlineStr">
         <is>
@@ -73339,7 +73339,7 @@
         <v>46190</v>
       </c>
       <c r="E946" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F946" t="inlineStr">
         <is>
@@ -73412,7 +73412,7 @@
         <v>46191</v>
       </c>
       <c r="E947" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F947" t="inlineStr">
         <is>
@@ -73485,7 +73485,7 @@
         <v>46108</v>
       </c>
       <c r="E948" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F948" t="inlineStr">
         <is>
@@ -73558,7 +73558,7 @@
         <v>45924</v>
       </c>
       <c r="E949" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F949" t="inlineStr">
         <is>
@@ -73631,7 +73631,7 @@
         <v>46199</v>
       </c>
       <c r="E950" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F950" t="inlineStr">
         <is>
@@ -73704,7 +73704,7 @@
         <v>46199</v>
       </c>
       <c r="E951" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F951" t="inlineStr">
         <is>
@@ -73777,7 +73777,7 @@
         <v>46198</v>
       </c>
       <c r="E952" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F952" t="inlineStr">
         <is>
@@ -73850,7 +73850,7 @@
         <v>46198</v>
       </c>
       <c r="E953" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F953" t="inlineStr">
         <is>
@@ -73923,7 +73923,7 @@
         <v>46198</v>
       </c>
       <c r="E954" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F954" t="inlineStr">
         <is>
@@ -73996,7 +73996,7 @@
         <v>46198</v>
       </c>
       <c r="E955" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F955" t="inlineStr">
         <is>
@@ -74069,7 +74069,7 @@
         <v>45541</v>
       </c>
       <c r="E956" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F956" t="inlineStr">
         <is>
@@ -74142,7 +74142,7 @@
         <v>46199</v>
       </c>
       <c r="E957" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F957" t="inlineStr">
         <is>
@@ -74215,7 +74215,7 @@
         <v>46199</v>
       </c>
       <c r="E958" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F958" t="inlineStr">
         <is>
@@ -74288,7 +74288,7 @@
         <v>46205</v>
       </c>
       <c r="E959" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F959" t="inlineStr">
         <is>
@@ -74361,7 +74361,7 @@
         <v>46205</v>
       </c>
       <c r="E960" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F960" t="inlineStr">
         <is>
@@ -74434,7 +74434,7 @@
         <v>46206</v>
       </c>
       <c r="E961" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F961" t="inlineStr">
         <is>
@@ -74512,7 +74512,7 @@
         <v>46210</v>
       </c>
       <c r="E962" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F962" t="inlineStr">
         <is>
@@ -74590,7 +74590,7 @@
         <v>46210</v>
       </c>
       <c r="E963" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F963" t="inlineStr">
         <is>
@@ -74668,7 +74668,7 @@
         <v>46170</v>
       </c>
       <c r="E964" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F964" t="inlineStr">
         <is>
@@ -74741,7 +74741,7 @@
         <v>46230</v>
       </c>
       <c r="E965" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F965" t="inlineStr">
         <is>
@@ -74814,7 +74814,7 @@
         <v>46269</v>
       </c>
       <c r="E966" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F966" t="inlineStr">
         <is>
@@ -74887,7 +74887,7 @@
         <v>46272</v>
       </c>
       <c r="E967" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F967" t="inlineStr">
         <is>
@@ -74960,7 +74960,7 @@
         <v>46272</v>
       </c>
       <c r="E968" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F968" t="inlineStr">
         <is>
@@ -75033,7 +75033,7 @@
         <v>46216</v>
       </c>
       <c r="E969" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F969" t="inlineStr">
         <is>
@@ -75106,7 +75106,7 @@
         <v>46216</v>
       </c>
       <c r="E970" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F970" t="inlineStr">
         <is>
@@ -75179,7 +75179,7 @@
         <v>46216</v>
       </c>
       <c r="E971" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F971" t="inlineStr">
         <is>
@@ -75252,7 +75252,7 @@
         <v>46276</v>
       </c>
       <c r="E972" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F972" t="inlineStr">
         <is>
@@ -75325,7 +75325,7 @@
         <v>46232</v>
       </c>
       <c r="E973" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F973" t="inlineStr">
         <is>
@@ -75398,7 +75398,7 @@
         <v>46232</v>
       </c>
       <c r="E974" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F974" t="inlineStr">
         <is>
@@ -75471,7 +75471,7 @@
         <v>46276</v>
       </c>
       <c r="E975" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F975" t="inlineStr">
         <is>
@@ -75544,7 +75544,7 @@
         <v>46279</v>
       </c>
       <c r="E976" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F976" t="inlineStr">
         <is>
@@ -75617,7 +75617,7 @@
         <v>46279</v>
       </c>
       <c r="E977" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F977" t="inlineStr">
         <is>
@@ -75690,7 +75690,7 @@
         <v>46237</v>
       </c>
       <c r="E978" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F978" t="inlineStr">
         <is>
@@ -75763,7 +75763,7 @@
         <v>46237</v>
       </c>
       <c r="E979" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F979" t="inlineStr">
         <is>
@@ -75836,7 +75836,7 @@
         <v>46281</v>
       </c>
       <c r="E980" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F980" t="inlineStr">
         <is>
@@ -75909,7 +75909,7 @@
         <v>46239</v>
       </c>
       <c r="E981" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F981" t="inlineStr">
         <is>
@@ -75982,7 +75982,7 @@
         <v>46244</v>
       </c>
       <c r="E982" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F982" t="inlineStr">
         <is>
@@ -76060,7 +76060,7 @@
         <v>46244</v>
       </c>
       <c r="E983" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F983" t="inlineStr">
         <is>
@@ -76138,7 +76138,7 @@
         <v>46244</v>
       </c>
       <c r="E984" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F984" t="inlineStr">
         <is>
@@ -76216,7 +76216,7 @@
         <v>46244</v>
       </c>
       <c r="E985" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F985" t="inlineStr">
         <is>
@@ -76294,7 +76294,7 @@
         <v>46244</v>
       </c>
       <c r="E986" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F986" t="inlineStr">
         <is>
@@ -76372,7 +76372,7 @@
         <v>46244</v>
       </c>
       <c r="E987" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F987" t="inlineStr">
         <is>
@@ -76445,7 +76445,7 @@
         <v>46244</v>
       </c>
       <c r="E988" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F988" t="inlineStr">
         <is>
@@ -76523,7 +76523,7 @@
         <v>46288</v>
       </c>
       <c r="E989" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F989" t="inlineStr">
         <is>
@@ -76596,7 +76596,7 @@
         <v>46245</v>
       </c>
       <c r="E990" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F990" t="inlineStr">
         <is>
@@ -76669,7 +76669,7 @@
         <v>46288</v>
       </c>
       <c r="E991" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F991" t="inlineStr">
         <is>
@@ -76742,7 +76742,7 @@
         <v>46244</v>
       </c>
       <c r="E992" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F992" t="inlineStr">
         <is>
@@ -76815,7 +76815,7 @@
         <v>46245</v>
       </c>
       <c r="E993" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F993" t="inlineStr">
         <is>
@@ -76888,7 +76888,7 @@
         <v>46289</v>
       </c>
       <c r="E994" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F994" t="inlineStr">
         <is>
@@ -76961,7 +76961,7 @@
         <v>46021</v>
       </c>
       <c r="E995" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F995" t="inlineStr">
         <is>
@@ -77034,7 +77034,7 @@
         <v>46056</v>
       </c>
       <c r="E996" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F996" t="inlineStr">
         <is>
@@ -77107,7 +77107,7 @@
         <v>46289</v>
       </c>
       <c r="E997" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F997" t="inlineStr">
         <is>
@@ -77180,7 +77180,7 @@
         <v>46246</v>
       </c>
       <c r="E998" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F998" t="inlineStr">
         <is>
@@ -77258,7 +77258,7 @@
         <v>46294</v>
       </c>
       <c r="E999" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F999" t="inlineStr">
         <is>
@@ -77331,7 +77331,7 @@
         <v>46294</v>
       </c>
       <c r="E1000" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1000" t="inlineStr">
         <is>
@@ -77404,7 +77404,7 @@
         <v>46294</v>
       </c>
       <c r="E1001" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1001" t="inlineStr">
         <is>
@@ -77477,7 +77477,7 @@
         <v>46294</v>
       </c>
       <c r="E1002" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1002" t="inlineStr">
         <is>
@@ -77550,7 +77550,7 @@
         <v>46237</v>
       </c>
       <c r="E1003" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1003" t="inlineStr">
         <is>
@@ -77623,7 +77623,7 @@
         <v>46294</v>
       </c>
       <c r="E1004" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1004" t="inlineStr">
         <is>
@@ -77696,7 +77696,7 @@
         <v>46294</v>
       </c>
       <c r="E1005" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1005" t="inlineStr">
         <is>
@@ -77769,7 +77769,7 @@
         <v>46245</v>
       </c>
       <c r="E1006" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1006" t="inlineStr">
         <is>
@@ -77842,7 +77842,7 @@
         <v>46296</v>
       </c>
       <c r="E1007" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1007" t="inlineStr">
         <is>
@@ -77915,7 +77915,7 @@
         <v>46296</v>
       </c>
       <c r="E1008" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1008" t="inlineStr">
         <is>
@@ -77988,7 +77988,7 @@
         <v>46296</v>
       </c>
       <c r="E1009" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1009" t="inlineStr">
         <is>
@@ -78061,7 +78061,7 @@
         <v>46296</v>
       </c>
       <c r="E1010" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1010" t="inlineStr">
         <is>
@@ -78134,7 +78134,7 @@
         <v>46252</v>
       </c>
       <c r="E1011" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1011" t="inlineStr">
         <is>
@@ -78207,7 +78207,7 @@
         <v>46296</v>
       </c>
       <c r="E1012" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1012" t="inlineStr">
         <is>
@@ -78280,7 +78280,7 @@
         <v>46296</v>
       </c>
       <c r="E1013" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1013" t="inlineStr">
         <is>
@@ -78353,7 +78353,7 @@
         <v>46253</v>
       </c>
       <c r="E1014" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1014" t="inlineStr">
         <is>
@@ -78426,7 +78426,7 @@
         <v>46295</v>
       </c>
       <c r="E1015" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1015" t="inlineStr">
         <is>
@@ -78504,7 +78504,7 @@
         <v>46296</v>
       </c>
       <c r="E1016" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1016" t="inlineStr">
         <is>
@@ -78577,7 +78577,7 @@
         <v>46252</v>
       </c>
       <c r="E1017" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1017" t="inlineStr">
         <is>
@@ -78650,7 +78650,7 @@
         <v>46300</v>
       </c>
       <c r="E1018" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1018" t="inlineStr">
         <is>
@@ -78723,7 +78723,7 @@
         <v>45594</v>
       </c>
       <c r="E1019" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1019" t="inlineStr">
         <is>
@@ -78801,7 +78801,7 @@
         <v>46300</v>
       </c>
       <c r="E1020" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1020" t="inlineStr">
         <is>
@@ -78874,7 +78874,7 @@
         <v>46301</v>
       </c>
       <c r="E1021" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1021" t="inlineStr">
         <is>
@@ -78947,7 +78947,7 @@
         <v>46199</v>
       </c>
       <c r="E1022" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1022" t="inlineStr">
         <is>
@@ -79020,7 +79020,7 @@
         <v>46258</v>
       </c>
       <c r="E1023" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1023" t="inlineStr">
         <is>
@@ -79093,7 +79093,7 @@
         <v>45916</v>
       </c>
       <c r="E1024" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1024" t="inlineStr">
         <is>
@@ -79166,7 +79166,7 @@
         <v>46261</v>
       </c>
       <c r="E1025" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1025" t="inlineStr">
         <is>
@@ -79239,7 +79239,7 @@
         <v>46304</v>
       </c>
       <c r="E1026" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1026" t="inlineStr">
         <is>
@@ -79312,7 +79312,7 @@
         <v>46262</v>
       </c>
       <c r="E1027" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1027" t="inlineStr">
         <is>
@@ -79385,7 +79385,7 @@
         <v>46183</v>
       </c>
       <c r="E1028" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1028" t="inlineStr">
         <is>
@@ -79458,7 +79458,7 @@
         <v>46260</v>
       </c>
       <c r="E1029" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1029" t="inlineStr">
         <is>
@@ -79531,7 +79531,7 @@
         <v>46304</v>
       </c>
       <c r="E1030" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1030" t="inlineStr">
         <is>
@@ -79604,7 +79604,7 @@
         <v>46183</v>
       </c>
       <c r="E1031" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1031" t="inlineStr">
         <is>
@@ -79677,7 +79677,7 @@
         <v>44715</v>
       </c>
       <c r="E1032" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1032" t="inlineStr">
         <is>
@@ -79750,7 +79750,7 @@
         <v>44722</v>
       </c>
       <c r="E1033" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1033" t="inlineStr">
         <is>
@@ -79823,7 +79823,7 @@
         <v>44588</v>
       </c>
       <c r="E1034" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1034" t="inlineStr">
         <is>
@@ -79896,7 +79896,7 @@
         <v>44727</v>
       </c>
       <c r="E1035" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1035" t="inlineStr">
         <is>
@@ -79969,7 +79969,7 @@
         <v>44722</v>
       </c>
       <c r="E1036" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1036" t="inlineStr">
         <is>
@@ -80042,7 +80042,7 @@
         <v>44603</v>
       </c>
       <c r="E1037" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1037" t="inlineStr">
         <is>
@@ -80115,7 +80115,7 @@
         <v>44693</v>
       </c>
       <c r="E1038" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1038" t="inlineStr">
         <is>
@@ -80188,7 +80188,7 @@
         <v>44726</v>
       </c>
       <c r="E1039" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1039" t="inlineStr">
         <is>
@@ -80261,7 +80261,7 @@
         <v>44712</v>
       </c>
       <c r="E1040" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1040" t="inlineStr">
         <is>
@@ -80334,7 +80334,7 @@
         <v>44722</v>
       </c>
       <c r="E1041" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1041" t="inlineStr">
         <is>
@@ -80407,7 +80407,7 @@
         <v>44712</v>
       </c>
       <c r="E1042" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1042" t="inlineStr">
         <is>
@@ -80480,7 +80480,7 @@
         <v>44704</v>
       </c>
       <c r="E1043" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1043" t="inlineStr">
         <is>
@@ -80553,7 +80553,7 @@
         <v>44596</v>
       </c>
       <c r="E1044" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1044" t="inlineStr">
         <is>
@@ -80626,7 +80626,7 @@
         <v>44704</v>
       </c>
       <c r="E1045" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1045" t="inlineStr">
         <is>
@@ -80699,7 +80699,7 @@
         <v>44588</v>
       </c>
       <c r="E1046" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1046" t="inlineStr">
         <is>
@@ -80772,7 +80772,7 @@
         <v>45054</v>
       </c>
       <c r="E1047" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1047" t="inlineStr">
         <is>
@@ -80845,7 +80845,7 @@
         <v>45230</v>
       </c>
       <c r="E1048" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1048" t="inlineStr">
         <is>
@@ -80923,7 +80923,7 @@
         <v>44498</v>
       </c>
       <c r="E1049" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1049" t="inlineStr">
         <is>
@@ -80996,7 +80996,7 @@
         <v>45622</v>
       </c>
       <c r="E1050" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1050" t="inlineStr">
         <is>
@@ -81069,7 +81069,7 @@
         <v>45054</v>
       </c>
       <c r="E1051" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1051" t="inlineStr">
         <is>
@@ -81142,7 +81142,7 @@
         <v>45054</v>
       </c>
       <c r="E1052" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1052" t="inlineStr">
         <is>
@@ -81215,7 +81215,7 @@
         <v>45056</v>
       </c>
       <c r="E1053" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1053" t="inlineStr">
         <is>
@@ -81288,7 +81288,7 @@
         <v>45434</v>
       </c>
       <c r="E1054" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1054" t="inlineStr">
         <is>
@@ -81361,7 +81361,7 @@
         <v>45054</v>
       </c>
       <c r="E1055" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1055" t="inlineStr">
         <is>
@@ -81434,7 +81434,7 @@
         <v>45407</v>
       </c>
       <c r="E1056" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1056" t="inlineStr">
         <is>
@@ -81507,7 +81507,7 @@
         <v>44802</v>
       </c>
       <c r="E1057" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1057" t="inlineStr">
         <is>
@@ -81580,7 +81580,7 @@
         <v>45071</v>
       </c>
       <c r="E1058" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1058" t="inlineStr">
         <is>
@@ -81653,7 +81653,7 @@
         <v>44495</v>
       </c>
       <c r="E1059" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1059" t="inlineStr">
         <is>
@@ -81726,7 +81726,7 @@
         <v>45224</v>
       </c>
       <c r="E1060" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1060" t="inlineStr">
         <is>
@@ -81804,7 +81804,7 @@
         <v>44972</v>
       </c>
       <c r="E1061" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1061" t="inlineStr">
         <is>
@@ -81877,7 +81877,7 @@
         <v>44487</v>
       </c>
       <c r="E1062" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1062" t="inlineStr">
         <is>
@@ -81950,7 +81950,7 @@
         <v>45230</v>
       </c>
       <c r="E1063" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1063" t="inlineStr">
         <is>
@@ -82023,7 +82023,7 @@
         <v>44939</v>
       </c>
       <c r="E1064" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1064" t="inlineStr">
         <is>
@@ -82096,7 +82096,7 @@
         <v>45468</v>
       </c>
       <c r="E1065" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1065" t="inlineStr">
         <is>
@@ -82169,7 +82169,7 @@
         <v>45218</v>
       </c>
       <c r="E1066" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1066" t="inlineStr">
         <is>
@@ -82242,7 +82242,7 @@
         <v>45054</v>
       </c>
       <c r="E1067" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1067" t="inlineStr">
         <is>
@@ -82315,7 +82315,7 @@
         <v>44930</v>
       </c>
       <c r="E1068" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1068" t="inlineStr">
         <is>
@@ -82393,7 +82393,7 @@
         <v>44973</v>
       </c>
       <c r="E1069" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1069" t="inlineStr">
         <is>
@@ -82466,7 +82466,7 @@
         <v>44908</v>
       </c>
       <c r="E1070" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1070" t="inlineStr">
         <is>
@@ -82559,7 +82559,7 @@
         <v>45583</v>
       </c>
       <c r="E1071" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1071" t="inlineStr">
         <is>
@@ -82632,7 +82632,7 @@
         <v>45054</v>
       </c>
       <c r="E1072" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1072" t="inlineStr">
         <is>
@@ -82705,7 +82705,7 @@
         <v>45054</v>
       </c>
       <c r="E1073" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1073" t="inlineStr">
         <is>
@@ -82778,7 +82778,7 @@
         <v>44908</v>
       </c>
       <c r="E1074" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1074" t="inlineStr">
         <is>
@@ -82851,7 +82851,7 @@
         <v>44972</v>
       </c>
       <c r="E1075" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1075" t="inlineStr">
         <is>
@@ -82924,7 +82924,7 @@
         <v>44978</v>
       </c>
       <c r="E1076" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1076" t="inlineStr">
         <is>
@@ -82997,7 +82997,7 @@
         <v>44887</v>
       </c>
       <c r="E1077" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1077" t="inlineStr">
         <is>
@@ -83070,7 +83070,7 @@
         <v>44909</v>
       </c>
       <c r="E1078" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1078" t="inlineStr">
         <is>
@@ -83143,7 +83143,7 @@
         <v>45408</v>
       </c>
       <c r="E1079" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1079" t="inlineStr">
         <is>
@@ -83216,7 +83216,7 @@
         <v>44908</v>
       </c>
       <c r="E1080" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1080" t="inlineStr">
         <is>
@@ -83289,7 +83289,7 @@
         <v>45054</v>
       </c>
       <c r="E1081" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1081" t="inlineStr">
         <is>
@@ -83362,7 +83362,7 @@
         <v>45526</v>
       </c>
       <c r="E1082" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1082" t="inlineStr">
         <is>
@@ -83435,7 +83435,7 @@
         <v>45436</v>
       </c>
       <c r="E1083" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1083" t="inlineStr">
         <is>
@@ -83508,7 +83508,7 @@
         <v>45485</v>
       </c>
       <c r="E1084" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1084" t="inlineStr">
         <is>
@@ -83581,7 +83581,7 @@
         <v>45727</v>
       </c>
       <c r="E1085" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1085" t="inlineStr">
         <is>
@@ -83654,7 +83654,7 @@
         <v>45740</v>
       </c>
       <c r="E1086" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1086" t="inlineStr">
         <is>
@@ -83727,7 +83727,7 @@
         <v>45726</v>
       </c>
       <c r="E1087" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1087" t="inlineStr">
         <is>
@@ -83800,7 +83800,7 @@
         <v>45797</v>
       </c>
       <c r="E1088" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1088" t="inlineStr">
         <is>
@@ -83873,7 +83873,7 @@
         <v>45805</v>
       </c>
       <c r="E1089" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1089" t="inlineStr">
         <is>
@@ -83946,7 +83946,7 @@
         <v>45831</v>
       </c>
       <c r="E1090" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1090" t="inlineStr">
         <is>
@@ -84019,7 +84019,7 @@
         <v>45951</v>
       </c>
       <c r="E1091" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1091" t="inlineStr">
         <is>
@@ -84092,7 +84092,7 @@
         <v>45958</v>
       </c>
       <c r="E1092" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1092" t="inlineStr">
         <is>
@@ -84165,7 +84165,7 @@
         <v>45964</v>
       </c>
       <c r="E1093" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1093" t="inlineStr">
         <is>
@@ -84238,7 +84238,7 @@
         <v>45965</v>
       </c>
       <c r="E1094" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1094" t="inlineStr">
         <is>
@@ -84311,7 +84311,7 @@
         <v>45981</v>
       </c>
       <c r="E1095" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1095" t="inlineStr">
         <is>
@@ -84389,7 +84389,7 @@
         <v>45988</v>
       </c>
       <c r="E1096" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1096" t="inlineStr">
         <is>
@@ -84462,7 +84462,7 @@
         <v>46092</v>
       </c>
       <c r="E1097" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1097" t="inlineStr">
         <is>
@@ -84540,7 +84540,7 @@
         <v>46202</v>
       </c>
       <c r="E1098" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1098" t="inlineStr">
         <is>
@@ -84613,7 +84613,7 @@
         <v>46300</v>
       </c>
       <c r="E1099" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1099" t="inlineStr">
         <is>
@@ -84686,7 +84686,7 @@
         <v>46262</v>
       </c>
       <c r="E1100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1100" t="inlineStr">
         <is>
@@ -84759,7 +84759,7 @@
         <v>46304</v>
       </c>
       <c r="E1101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1101" t="inlineStr">
         <is>

--- a/Översikt VÄXJÖ.xlsx
+++ b/Översikt VÄXJÖ.xlsx
@@ -601,7 +601,7 @@
         <v>44974</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         <v>45895</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -859,7 +859,7 @@
         <v>45770</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -976,7 +976,7 @@
         <v>45468</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         <v>45384</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
         <v>45888</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>45812</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         <v>45127</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>46175</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
         <v>45964</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1769,7 +1769,7 @@
         <v>46188</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
         <v>46188</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         <v>46199</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>45081</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2224,7 +2224,7 @@
         <v>44958</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2337,7 +2337,7 @@
         <v>45490</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2454,7 +2454,7 @@
         <v>45294</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2571,7 +2571,7 @@
         <v>45995</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2683,7 +2683,7 @@
         <v>46247</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2791,7 +2791,7 @@
         <v>45356</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2902,7 +2902,7 @@
         <v>46204</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3018,7 +3018,7 @@
         <v>46244</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3129,7 +3129,7 @@
         <v>45344</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         <v>46098</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3347,7 +3347,7 @@
         <v>46286</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3454,7 +3454,7 @@
         <v>45883</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3560,7 +3560,7 @@
         <v>45447</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3666,7 +3666,7 @@
         <v>45093</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3776,7 +3776,7 @@
         <v>45545</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3882,7 +3882,7 @@
         <v>45649</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3988,7 +3988,7 @@
         <v>45687</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4094,7 +4094,7 @@
         <v>45554</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4200,7 +4200,7 @@
         <v>45587</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4310,7 +4310,7 @@
         <v>44532</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4425,7 +4425,7 @@
         <v>45190</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4531,7 +4531,7 @@
         <v>45874</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4642,7 +4642,7 @@
         <v>46147</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4748,7 +4748,7 @@
         <v>46161</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4858,7 +4858,7 @@
         <v>46182</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4973,7 +4973,7 @@
         <v>46296</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5079,7 +5079,7 @@
         <v>44704</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5185,7 +5185,7 @@
         <v>44704</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5295,7 +5295,7 @@
         <v>45460</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5401,7 +5401,7 @@
         <v>45348</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         <v>45351</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5613,7 +5613,7 @@
         <v>45674</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5724,7 +5724,7 @@
         <v>46100</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5830,7 +5830,7 @@
         <v>44721</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5935,7 +5935,7 @@
         <v>44704</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6040,7 +6040,7 @@
         <v>44490</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6145,7 +6145,7 @@
         <v>44645</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6250,7 +6250,7 @@
         <v>45754</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6355,7 +6355,7 @@
         <v>45392</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6465,7 +6465,7 @@
         <v>45280</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6570,7 +6570,7 @@
         <v>44673</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6675,7 +6675,7 @@
         <v>45428</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6785,7 +6785,7 @@
         <v>45273</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6890,7 +6890,7 @@
         <v>45280</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6995,7 +6995,7 @@
         <v>44872</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7100,7 +7100,7 @@
         <v>44894</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7205,7 +7205,7 @@
         <v>45688</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7310,7 +7310,7 @@
         <v>45617</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7420,7 +7420,7 @@
         <v>45606</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7525,7 +7525,7 @@
         <v>44705</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7634,7 +7634,7 @@
         <v>45820</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7739,7 +7739,7 @@
         <v>45643</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7844,7 +7844,7 @@
         <v>45964</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7953,7 +7953,7 @@
         <v>44746</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8058,7 +8058,7 @@
         <v>45978</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8167,7 +8167,7 @@
         <v>45594</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8281,7 +8281,7 @@
         <v>44741</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8386,7 +8386,7 @@
         <v>45327</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8491,7 +8491,7 @@
         <v>45824</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8596,7 +8596,7 @@
         <v>45098</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8701,7 +8701,7 @@
         <v>46045</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8806,7 +8806,7 @@
         <v>45533</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8911,7 +8911,7 @@
         <v>45369</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9016,7 +9016,7 @@
         <v>45279</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         <v>45594</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9231,7 +9231,7 @@
         <v>45594</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9341,7 +9341,7 @@
         <v>46161</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9446,7 +9446,7 @@
         <v>46161</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9551,7 +9551,7 @@
         <v>46199</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9656,7 +9656,7 @@
         <v>46281</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9761,7 +9761,7 @@
         <v>46288</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9866,7 +9866,7 @@
         <v>46246</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9971,7 +9971,7 @@
         <v>46296</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10076,7 +10076,7 @@
         <v>46303</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10181,7 +10181,7 @@
         <v>44634</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10286,7 +10286,7 @@
         <v>44712</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10391,7 +10391,7 @@
         <v>44950</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10496,7 +10496,7 @@
         <v>45436</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10601,7 +10601,7 @@
         <v>45726</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10706,7 +10706,7 @@
         <v>45805</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10811,7 +10811,7 @@
         <v>45939</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10920,7 +10920,7 @@
         <v>46100</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11025,7 +11025,7 @@
         <v>44693</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11098,7 +11098,7 @@
         <v>44812</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11171,7 +11171,7 @@
         <v>44518</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11244,7 +11244,7 @@
         <v>44536</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11317,7 +11317,7 @@
         <v>44764</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11390,7 +11390,7 @@
         <v>44519</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11463,7 +11463,7 @@
         <v>44501</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11536,7 +11536,7 @@
         <v>44814</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11609,7 +11609,7 @@
         <v>44645</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11682,7 +11682,7 @@
         <v>44643</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11755,7 +11755,7 @@
         <v>44515</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11828,7 +11828,7 @@
         <v>44814</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11901,7 +11901,7 @@
         <v>44480</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11974,7 +11974,7 @@
         <v>44525</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12047,7 +12047,7 @@
         <v>44578</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12120,7 +12120,7 @@
         <v>44516</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12198,7 +12198,7 @@
         <v>44803</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12271,7 +12271,7 @@
         <v>44691</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12344,7 +12344,7 @@
         <v>44739</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12417,7 +12417,7 @@
         <v>44590</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12495,7 +12495,7 @@
         <v>44820</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12573,7 +12573,7 @@
         <v>44814</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12646,7 +12646,7 @@
         <v>44769</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12724,7 +12724,7 @@
         <v>44711</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12797,7 +12797,7 @@
         <v>44820</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12870,7 +12870,7 @@
         <v>44508</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12943,7 +12943,7 @@
         <v>44880</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13016,7 +13016,7 @@
         <v>44495</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13089,7 +13089,7 @@
         <v>44515</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13162,7 +13162,7 @@
         <v>44599</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13235,7 +13235,7 @@
         <v>44495</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13308,7 +13308,7 @@
         <v>44599</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13381,7 +13381,7 @@
         <v>44651</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13454,7 +13454,7 @@
         <v>44876</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13532,7 +13532,7 @@
         <v>44671</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13605,7 +13605,7 @@
         <v>44491</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13678,7 +13678,7 @@
         <v>44502</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13756,7 +13756,7 @@
         <v>44812</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13829,7 +13829,7 @@
         <v>44740</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13902,7 +13902,7 @@
         <v>44483</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13975,7 +13975,7 @@
         <v>44496</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14048,7 +14048,7 @@
         <v>44489</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14121,7 +14121,7 @@
         <v>44489</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14194,7 +14194,7 @@
         <v>44617</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14267,7 +14267,7 @@
         <v>44483</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14340,7 +14340,7 @@
         <v>44750</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14413,7 +14413,7 @@
         <v>44498</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14486,7 +14486,7 @@
         <v>44508</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14559,7 +14559,7 @@
         <v>44726</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14632,7 +14632,7 @@
         <v>44568</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14705,7 +14705,7 @@
         <v>44537</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14778,7 +14778,7 @@
         <v>44574</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14851,7 +14851,7 @@
         <v>44860</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14924,7 +14924,7 @@
         <v>44551</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14997,7 +14997,7 @@
         <v>44537</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15070,7 +15070,7 @@
         <v>44543</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15143,7 +15143,7 @@
         <v>44599</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15216,7 +15216,7 @@
         <v>44596</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15289,7 +15289,7 @@
         <v>44606</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15362,7 +15362,7 @@
         <v>44573</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15435,7 +15435,7 @@
         <v>44571</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15508,7 +15508,7 @@
         <v>44712</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15581,7 +15581,7 @@
         <v>44489</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15654,7 +15654,7 @@
         <v>44613</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15727,7 +15727,7 @@
         <v>44579</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15800,7 +15800,7 @@
         <v>44746</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15873,7 +15873,7 @@
         <v>44487</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15946,7 +15946,7 @@
         <v>44711</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16019,7 +16019,7 @@
         <v>44610</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16092,7 +16092,7 @@
         <v>44781</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16165,7 +16165,7 @@
         <v>44769</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16243,7 +16243,7 @@
         <v>44603</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16321,7 +16321,7 @@
         <v>44494</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16394,7 +16394,7 @@
         <v>44610</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16467,7 +16467,7 @@
         <v>44704</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16540,7 +16540,7 @@
         <v>44596</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16613,7 +16613,7 @@
         <v>44522</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16686,7 +16686,7 @@
         <v>44867</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16759,7 +16759,7 @@
         <v>44532</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16832,7 +16832,7 @@
         <v>44532</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16905,7 +16905,7 @@
         <v>44560</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16978,7 +16978,7 @@
         <v>44602</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17051,7 +17051,7 @@
         <v>44732</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17124,7 +17124,7 @@
         <v>45372</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17197,7 +17197,7 @@
         <v>45176</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17270,7 +17270,7 @@
         <v>44820</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17348,7 +17348,7 @@
         <v>44820</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17426,7 +17426,7 @@
         <v>44956</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17499,7 +17499,7 @@
         <v>45281</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17572,7 +17572,7 @@
         <v>45632</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17645,7 +17645,7 @@
         <v>45153</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17718,7 +17718,7 @@
         <v>44713</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17791,7 +17791,7 @@
         <v>45090</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17864,7 +17864,7 @@
         <v>45019</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17937,7 +17937,7 @@
         <v>45219</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18010,7 +18010,7 @@
         <v>44908</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18083,7 +18083,7 @@
         <v>44897</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18156,7 +18156,7 @@
         <v>45611</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18229,7 +18229,7 @@
         <v>45204</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18302,7 +18302,7 @@
         <v>45737</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18375,7 +18375,7 @@
         <v>45676</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18453,7 +18453,7 @@
         <v>45162</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18526,7 +18526,7 @@
         <v>45162</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18599,7 +18599,7 @@
         <v>45581</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18672,7 +18672,7 @@
         <v>45504</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18745,7 +18745,7 @@
         <v>44502</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18823,7 +18823,7 @@
         <v>45259</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18896,7 +18896,7 @@
         <v>44874</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18969,7 +18969,7 @@
         <v>45049</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19042,7 +19042,7 @@
         <v>45392</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19120,7 +19120,7 @@
         <v>45412</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19193,7 +19193,7 @@
         <v>44741</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19266,7 +19266,7 @@
         <v>44741</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19339,7 +19339,7 @@
         <v>44896</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19412,7 +19412,7 @@
         <v>45194</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19485,7 +19485,7 @@
         <v>45557</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19558,7 +19558,7 @@
         <v>44928</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19631,7 +19631,7 @@
         <v>45219</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19704,7 +19704,7 @@
         <v>44814</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19777,7 +19777,7 @@
         <v>44814</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19850,7 +19850,7 @@
         <v>45665</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19923,7 +19923,7 @@
         <v>45762</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20001,7 +20001,7 @@
         <v>45279</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20074,7 +20074,7 @@
         <v>45153</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20147,7 +20147,7 @@
         <v>45679</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20220,7 +20220,7 @@
         <v>45273</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20293,7 +20293,7 @@
         <v>45296</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20366,7 +20366,7 @@
         <v>45436</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20439,7 +20439,7 @@
         <v>45106</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20512,7 +20512,7 @@
         <v>44741</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20585,7 +20585,7 @@
         <v>45715</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20658,7 +20658,7 @@
         <v>45617</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20731,7 +20731,7 @@
         <v>44894</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20809,7 +20809,7 @@
         <v>45090</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20882,7 +20882,7 @@
         <v>45769</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20955,7 +20955,7 @@
         <v>45561</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21028,7 +21028,7 @@
         <v>45392</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21101,7 +21101,7 @@
         <v>45300</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21174,7 +21174,7 @@
         <v>45302</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21247,7 +21247,7 @@
         <v>45447</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21320,7 +21320,7 @@
         <v>44687</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21393,7 +21393,7 @@
         <v>45211</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21466,7 +21466,7 @@
         <v>45211</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21539,7 +21539,7 @@
         <v>45632</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21612,7 +21612,7 @@
         <v>45104</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21685,7 +21685,7 @@
         <v>45232</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21758,7 +21758,7 @@
         <v>45078</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21836,7 +21836,7 @@
         <v>45726</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21909,7 +21909,7 @@
         <v>45302</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21982,7 +21982,7 @@
         <v>45386</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22055,7 +22055,7 @@
         <v>45341</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22128,7 +22128,7 @@
         <v>45127</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22201,7 +22201,7 @@
         <v>45139</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22274,7 +22274,7 @@
         <v>45392</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22352,7 +22352,7 @@
         <v>45392</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22430,7 +22430,7 @@
         <v>45446</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22508,7 +22508,7 @@
         <v>44986</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22581,7 +22581,7 @@
         <v>45373</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22654,7 +22654,7 @@
         <v>45448</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22727,7 +22727,7 @@
         <v>45538</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22805,7 +22805,7 @@
         <v>45128</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22878,7 +22878,7 @@
         <v>45128</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22951,7 +22951,7 @@
         <v>45432</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23024,7 +23024,7 @@
         <v>45387</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23097,7 +23097,7 @@
         <v>45022</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23170,7 +23170,7 @@
         <v>45754</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23243,7 +23243,7 @@
         <v>45754</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23316,7 +23316,7 @@
         <v>45693</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23389,7 +23389,7 @@
         <v>45240</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23462,7 +23462,7 @@
         <v>45555</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23535,7 +23535,7 @@
         <v>45317</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23608,7 +23608,7 @@
         <v>45278</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23681,7 +23681,7 @@
         <v>45309</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23754,7 +23754,7 @@
         <v>45309</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23827,7 +23827,7 @@
         <v>45121</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23900,7 +23900,7 @@
         <v>45121</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23973,7 +23973,7 @@
         <v>45121</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24046,7 +24046,7 @@
         <v>45236</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24119,7 +24119,7 @@
         <v>45161</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24192,7 +24192,7 @@
         <v>45112</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24265,7 +24265,7 @@
         <v>45288</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24338,7 +24338,7 @@
         <v>45108</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24411,7 +24411,7 @@
         <v>45387</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24484,7 +24484,7 @@
         <v>45477</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24562,7 +24562,7 @@
         <v>44959</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24635,7 +24635,7 @@
         <v>45229</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24708,7 +24708,7 @@
         <v>45222</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24781,7 +24781,7 @@
         <v>45169</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24854,7 +24854,7 @@
         <v>44487</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24927,7 +24927,7 @@
         <v>45446</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25000,7 +25000,7 @@
         <v>45280</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25073,7 +25073,7 @@
         <v>44880</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25146,7 +25146,7 @@
         <v>44904</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25219,7 +25219,7 @@
         <v>44904</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25292,7 +25292,7 @@
         <v>45608</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25365,7 +25365,7 @@
         <v>45205</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25438,7 +25438,7 @@
         <v>45201</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25511,7 +25511,7 @@
         <v>45281</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25584,7 +25584,7 @@
         <v>44963</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25657,7 +25657,7 @@
         <v>44963</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25730,7 +25730,7 @@
         <v>44963</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25803,7 +25803,7 @@
         <v>45070</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25876,7 +25876,7 @@
         <v>45622</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25949,7 +25949,7 @@
         <v>45240</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26022,7 +26022,7 @@
         <v>45468</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26095,7 +26095,7 @@
         <v>44900</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26168,7 +26168,7 @@
         <v>44900</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26241,7 +26241,7 @@
         <v>45127</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26314,7 +26314,7 @@
         <v>45127</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26387,7 +26387,7 @@
         <v>45883</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26460,7 +26460,7 @@
         <v>45551</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26533,7 +26533,7 @@
         <v>44573</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26606,7 +26606,7 @@
         <v>44532</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26679,7 +26679,7 @@
         <v>45225</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26752,7 +26752,7 @@
         <v>45181</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26825,7 +26825,7 @@
         <v>44854</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26898,7 +26898,7 @@
         <v>45244</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26971,7 +26971,7 @@
         <v>45127</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27044,7 +27044,7 @@
         <v>44894</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27117,7 +27117,7 @@
         <v>44929</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27195,7 +27195,7 @@
         <v>45111</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27268,7 +27268,7 @@
         <v>44656</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27341,7 +27341,7 @@
         <v>45154</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27414,7 +27414,7 @@
         <v>45030</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27487,7 +27487,7 @@
         <v>45443</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27560,7 +27560,7 @@
         <v>45145</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27633,7 +27633,7 @@
         <v>45147</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27706,7 +27706,7 @@
         <v>45217</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27779,7 +27779,7 @@
         <v>45294</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27852,7 +27852,7 @@
         <v>45236</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27925,7 +27925,7 @@
         <v>44831</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27998,7 +27998,7 @@
         <v>45166</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28071,7 +28071,7 @@
         <v>45194</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28144,7 +28144,7 @@
         <v>45219</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28217,7 +28217,7 @@
         <v>45342</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28290,7 +28290,7 @@
         <v>45754</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28363,7 +28363,7 @@
         <v>45330</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28436,7 +28436,7 @@
         <v>44950</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28509,7 +28509,7 @@
         <v>45280</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28582,7 +28582,7 @@
         <v>45705</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28660,7 +28660,7 @@
         <v>45446</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28733,7 +28733,7 @@
         <v>45477</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28811,7 +28811,7 @@
         <v>45392</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28889,7 +28889,7 @@
         <v>44547</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28962,7 +28962,7 @@
         <v>44545</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29035,7 +29035,7 @@
         <v>45324</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29108,7 +29108,7 @@
         <v>45016</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29181,7 +29181,7 @@
         <v>45488</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29254,7 +29254,7 @@
         <v>45061</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29327,7 +29327,7 @@
         <v>45124</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29400,7 +29400,7 @@
         <v>45894</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29473,7 +29473,7 @@
         <v>45890</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29546,7 +29546,7 @@
         <v>45856</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29619,7 +29619,7 @@
         <v>45895</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29692,7 +29692,7 @@
         <v>45897</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29770,7 +29770,7 @@
         <v>44880</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29843,7 +29843,7 @@
         <v>45560</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29916,7 +29916,7 @@
         <v>44909</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29994,7 +29994,7 @@
         <v>44922</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30067,7 +30067,7 @@
         <v>45645</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30140,7 +30140,7 @@
         <v>45719</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30213,7 +30213,7 @@
         <v>44986</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30286,7 +30286,7 @@
         <v>45902</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30359,7 +30359,7 @@
         <v>45902</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30432,7 +30432,7 @@
         <v>45686</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30505,7 +30505,7 @@
         <v>45737</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30578,7 +30578,7 @@
         <v>45224</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30651,7 +30651,7 @@
         <v>45304</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30724,7 +30724,7 @@
         <v>44537</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30797,7 +30797,7 @@
         <v>45902</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30870,7 +30870,7 @@
         <v>45244</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30943,7 +30943,7 @@
         <v>45810</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31021,7 +31021,7 @@
         <v>45835</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31094,7 +31094,7 @@
         <v>45250</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31167,7 +31167,7 @@
         <v>45557</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31240,7 +31240,7 @@
         <v>45579</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31313,7 +31313,7 @@
         <v>45558</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31386,7 +31386,7 @@
         <v>45309</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31459,7 +31459,7 @@
         <v>45533</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31532,7 +31532,7 @@
         <v>45309</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31605,7 +31605,7 @@
         <v>45579</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31678,7 +31678,7 @@
         <v>45702</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31751,7 +31751,7 @@
         <v>44896</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31824,7 +31824,7 @@
         <v>45905</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31897,7 +31897,7 @@
         <v>45165</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31970,7 +31970,7 @@
         <v>45910</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32043,7 +32043,7 @@
         <v>45113</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32116,7 +32116,7 @@
         <v>45148</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32189,7 +32189,7 @@
         <v>45148</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32262,7 +32262,7 @@
         <v>45037</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32335,7 +32335,7 @@
         <v>45037</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32408,7 +32408,7 @@
         <v>45194</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32481,7 +32481,7 @@
         <v>45547</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32554,7 +32554,7 @@
         <v>45909</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32627,7 +32627,7 @@
         <v>45777</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32705,7 +32705,7 @@
         <v>45519</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32778,7 +32778,7 @@
         <v>45777</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32856,7 +32856,7 @@
         <v>45190</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32929,7 +32929,7 @@
         <v>45777</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33007,7 +33007,7 @@
         <v>45222</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33080,7 +33080,7 @@
         <v>45787</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33153,7 +33153,7 @@
         <v>44988</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33226,7 +33226,7 @@
         <v>45127</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33299,7 +33299,7 @@
         <v>45780</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33372,7 +33372,7 @@
         <v>45780</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33445,7 +33445,7 @@
         <v>45911</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33518,7 +33518,7 @@
         <v>45782</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33591,7 +33591,7 @@
         <v>45573</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33664,7 +33664,7 @@
         <v>44867</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33737,7 +33737,7 @@
         <v>45048</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33810,7 +33810,7 @@
         <v>45546</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33883,7 +33883,7 @@
         <v>45540</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33956,7 +33956,7 @@
         <v>44599</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34029,7 +34029,7 @@
         <v>45783</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34102,7 +34102,7 @@
         <v>45672</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34175,7 +34175,7 @@
         <v>45056</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34248,7 +34248,7 @@
         <v>45534</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34321,7 +34321,7 @@
         <v>45478</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34394,7 +34394,7 @@
         <v>45638</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34467,7 +34467,7 @@
         <v>44896</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34540,7 +34540,7 @@
         <v>45685</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34613,7 +34613,7 @@
         <v>45642</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34686,7 +34686,7 @@
         <v>45559</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34759,7 +34759,7 @@
         <v>44781</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34837,7 +34837,7 @@
         <v>45611</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34910,7 +34910,7 @@
         <v>44532</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34983,7 +34983,7 @@
         <v>45161</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35056,7 +35056,7 @@
         <v>45608</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35129,7 +35129,7 @@
         <v>44866</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35202,7 +35202,7 @@
         <v>45918</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35275,7 +35275,7 @@
         <v>45108</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35348,7 +35348,7 @@
         <v>45716</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35421,7 +35421,7 @@
         <v>45390</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35494,7 +35494,7 @@
         <v>45139</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35567,7 +35567,7 @@
         <v>45112</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35640,7 +35640,7 @@
         <v>45614</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35713,7 +35713,7 @@
         <v>44595</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35786,7 +35786,7 @@
         <v>45555</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35859,7 +35859,7 @@
         <v>45580</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35932,7 +35932,7 @@
         <v>44903</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36005,7 +36005,7 @@
         <v>44938</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36078,7 +36078,7 @@
         <v>45014</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36156,7 +36156,7 @@
         <v>45716</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36229,7 +36229,7 @@
         <v>45316</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36302,7 +36302,7 @@
         <v>45924</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36375,7 +36375,7 @@
         <v>45330</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36453,7 +36453,7 @@
         <v>45014</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36526,7 +36526,7 @@
         <v>45219</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36599,7 +36599,7 @@
         <v>45925</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36672,7 +36672,7 @@
         <v>45330</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36745,7 +36745,7 @@
         <v>45644</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36818,7 +36818,7 @@
         <v>45198</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36891,7 +36891,7 @@
         <v>45008</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36964,7 +36964,7 @@
         <v>45412</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37037,7 +37037,7 @@
         <v>45412</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37110,7 +37110,7 @@
         <v>45140</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37183,7 +37183,7 @@
         <v>45791</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37256,7 +37256,7 @@
         <v>45000</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37329,7 +37329,7 @@
         <v>44609</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37402,7 +37402,7 @@
         <v>45733</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37475,7 +37475,7 @@
         <v>45552</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37548,7 +37548,7 @@
         <v>45722</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37621,7 +37621,7 @@
         <v>45036</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37694,7 +37694,7 @@
         <v>45378</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37767,7 +37767,7 @@
         <v>45796</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37840,7 +37840,7 @@
         <v>45534</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37913,7 +37913,7 @@
         <v>45560</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37986,7 +37986,7 @@
         <v>45369</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38059,7 +38059,7 @@
         <v>44599</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38132,7 +38132,7 @@
         <v>44869</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38205,7 +38205,7 @@
         <v>45338</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38278,7 +38278,7 @@
         <v>45065</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38351,7 +38351,7 @@
         <v>45244</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38424,7 +38424,7 @@
         <v>45408</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38497,7 +38497,7 @@
         <v>45028</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38570,7 +38570,7 @@
         <v>45222</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38643,7 +38643,7 @@
         <v>45594</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38721,7 +38721,7 @@
         <v>45594</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38799,7 +38799,7 @@
         <v>45594</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38877,7 +38877,7 @@
         <v>45594</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38955,7 +38955,7 @@
         <v>45169</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39028,7 +39028,7 @@
         <v>45583</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39106,7 +39106,7 @@
         <v>45392</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39184,7 +39184,7 @@
         <v>44670</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39257,7 +39257,7 @@
         <v>45509</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39330,7 +39330,7 @@
         <v>45644</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39403,7 +39403,7 @@
         <v>45594</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39481,7 +39481,7 @@
         <v>45594</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39559,7 +39559,7 @@
         <v>45594</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39637,7 +39637,7 @@
         <v>45764</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39710,7 +39710,7 @@
         <v>45574</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39783,7 +39783,7 @@
         <v>45601</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39856,7 +39856,7 @@
         <v>45665</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39929,7 +39929,7 @@
         <v>44711</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40002,7 +40002,7 @@
         <v>45071</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40080,7 +40080,7 @@
         <v>45316</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40153,7 +40153,7 @@
         <v>45583</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40226,7 +40226,7 @@
         <v>44824</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40299,7 +40299,7 @@
         <v>45316</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40372,7 +40372,7 @@
         <v>45056</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40445,7 +40445,7 @@
         <v>45757</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40518,7 +40518,7 @@
         <v>45384</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40591,7 +40591,7 @@
         <v>45345</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40664,7 +40664,7 @@
         <v>44858</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40737,7 +40737,7 @@
         <v>45579</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40810,7 +40810,7 @@
         <v>45749</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -40883,7 +40883,7 @@
         <v>44970</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40956,7 +40956,7 @@
         <v>45937</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41029,7 +41029,7 @@
         <v>45803</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41102,7 +41102,7 @@
         <v>45937</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41175,7 +41175,7 @@
         <v>45372</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41248,7 +41248,7 @@
         <v>44764</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41321,7 +41321,7 @@
         <v>45091</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41399,7 +41399,7 @@
         <v>45579</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41472,7 +41472,7 @@
         <v>45805</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41545,7 +41545,7 @@
         <v>45385</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41623,7 +41623,7 @@
         <v>45385</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -41701,7 +41701,7 @@
         <v>45763</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -41774,7 +41774,7 @@
         <v>45447</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -41847,7 +41847,7 @@
         <v>45764</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -41920,7 +41920,7 @@
         <v>45440</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -41993,7 +41993,7 @@
         <v>45189</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42066,7 +42066,7 @@
         <v>45189</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42139,7 +42139,7 @@
         <v>45722</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42212,7 +42212,7 @@
         <v>45679</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42285,7 +42285,7 @@
         <v>44963</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42358,7 +42358,7 @@
         <v>45463</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42431,7 +42431,7 @@
         <v>45896</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42504,7 +42504,7 @@
         <v>44960</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42577,7 +42577,7 @@
         <v>45594</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42655,7 +42655,7 @@
         <v>45594</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42733,7 +42733,7 @@
         <v>45594</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -42811,7 +42811,7 @@
         <v>45594</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -42889,7 +42889,7 @@
         <v>45594</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -42967,7 +42967,7 @@
         <v>45594</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43045,7 +43045,7 @@
         <v>45594</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43123,7 +43123,7 @@
         <v>45586</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43196,7 +43196,7 @@
         <v>45215</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43269,7 +43269,7 @@
         <v>44876</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43347,7 +43347,7 @@
         <v>45495</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43420,7 +43420,7 @@
         <v>45210</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -43493,7 +43493,7 @@
         <v>45281</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -43566,7 +43566,7 @@
         <v>45754</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -43639,7 +43639,7 @@
         <v>45244</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -43712,7 +43712,7 @@
         <v>45180</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -43785,7 +43785,7 @@
         <v>44679</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -43858,7 +43858,7 @@
         <v>44678</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -43931,7 +43931,7 @@
         <v>45714</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44004,7 +44004,7 @@
         <v>45775</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44077,7 +44077,7 @@
         <v>45670</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44150,7 +44150,7 @@
         <v>45250</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44223,7 +44223,7 @@
         <v>45769</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44296,7 +44296,7 @@
         <v>45820</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44369,7 +44369,7 @@
         <v>44802</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -44442,7 +44442,7 @@
         <v>45420</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -44515,7 +44515,7 @@
         <v>45140</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -44588,7 +44588,7 @@
         <v>45820</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -44661,7 +44661,7 @@
         <v>45817</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -44734,7 +44734,7 @@
         <v>45818</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -44807,7 +44807,7 @@
         <v>45629</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -44880,7 +44880,7 @@
         <v>45328</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -44953,7 +44953,7 @@
         <v>45328</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45026,7 +45026,7 @@
         <v>44494</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45099,7 +45099,7 @@
         <v>45824</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45172,7 +45172,7 @@
         <v>45824</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45245,7 +45245,7 @@
         <v>45686</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -45318,7 +45318,7 @@
         <v>45686</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -45391,7 +45391,7 @@
         <v>45638</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -45464,7 +45464,7 @@
         <v>45825</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -45537,7 +45537,7 @@
         <v>45611</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -45610,7 +45610,7 @@
         <v>45085</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -45683,7 +45683,7 @@
         <v>44676</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -45761,7 +45761,7 @@
         <v>44743</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -45834,7 +45834,7 @@
         <v>44711</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -45907,7 +45907,7 @@
         <v>44620</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -45980,7 +45980,7 @@
         <v>45827</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46053,7 +46053,7 @@
         <v>45831</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46126,7 +46126,7 @@
         <v>45224</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -46204,7 +46204,7 @@
         <v>44966</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -46277,7 +46277,7 @@
         <v>45089</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -46350,7 +46350,7 @@
         <v>44972</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -46423,7 +46423,7 @@
         <v>44972</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -46496,7 +46496,7 @@
         <v>45519</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -46569,7 +46569,7 @@
         <v>45253</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -46642,7 +46642,7 @@
         <v>45247</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -46715,7 +46715,7 @@
         <v>45702</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -46788,7 +46788,7 @@
         <v>45831</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -46861,7 +46861,7 @@
         <v>45952</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -46934,7 +46934,7 @@
         <v>45923</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47007,7 +47007,7 @@
         <v>44676</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47085,7 +47085,7 @@
         <v>45946</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47158,7 +47158,7 @@
         <v>45953</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -47231,7 +47231,7 @@
         <v>45236</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -47304,7 +47304,7 @@
         <v>45236</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -47377,7 +47377,7 @@
         <v>44967</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -47450,7 +47450,7 @@
         <v>45805</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -47523,7 +47523,7 @@
         <v>45832</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -47596,7 +47596,7 @@
         <v>45114</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -47669,7 +47669,7 @@
         <v>45012</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -47742,7 +47742,7 @@
         <v>45679</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -47815,7 +47815,7 @@
         <v>44690</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -47888,7 +47888,7 @@
         <v>44981</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -47961,7 +47961,7 @@
         <v>45924</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48034,7 +48034,7 @@
         <v>44705</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48107,7 +48107,7 @@
         <v>45835</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -48180,7 +48180,7 @@
         <v>45166</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -48253,7 +48253,7 @@
         <v>45835</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -48326,7 +48326,7 @@
         <v>44651</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -48399,7 +48399,7 @@
         <v>45964</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -48472,7 +48472,7 @@
         <v>44998</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -48545,7 +48545,7 @@
         <v>45460</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -48618,7 +48618,7 @@
         <v>45835</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -48691,7 +48691,7 @@
         <v>45421</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -48764,7 +48764,7 @@
         <v>45188</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -48837,7 +48837,7 @@
         <v>45385</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -48915,7 +48915,7 @@
         <v>45385</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -48993,7 +48993,7 @@
         <v>45495</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -49066,7 +49066,7 @@
         <v>45176</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -49139,7 +49139,7 @@
         <v>45103</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -49212,7 +49212,7 @@
         <v>45103</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -49285,7 +49285,7 @@
         <v>45103</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -49358,7 +49358,7 @@
         <v>45121</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -49431,7 +49431,7 @@
         <v>45558</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -49504,7 +49504,7 @@
         <v>45538</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -49577,7 +49577,7 @@
         <v>45840</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -49650,7 +49650,7 @@
         <v>45114</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -49723,7 +49723,7 @@
         <v>45114</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -49796,7 +49796,7 @@
         <v>44739</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -49869,7 +49869,7 @@
         <v>45250</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -49942,7 +49942,7 @@
         <v>44746</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -50015,7 +50015,7 @@
         <v>45128</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -50088,7 +50088,7 @@
         <v>45753</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -50161,7 +50161,7 @@
         <v>45971</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -50234,7 +50234,7 @@
         <v>45540</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -50307,7 +50307,7 @@
         <v>45568</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -50380,7 +50380,7 @@
         <v>45846</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -50453,7 +50453,7 @@
         <v>44774</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -50526,7 +50526,7 @@
         <v>45692</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -50599,7 +50599,7 @@
         <v>45288</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -50672,7 +50672,7 @@
         <v>44686</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -50745,7 +50745,7 @@
         <v>45033</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -50823,7 +50823,7 @@
         <v>45847</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -50896,7 +50896,7 @@
         <v>45260</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -50969,7 +50969,7 @@
         <v>44915</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -51042,7 +51042,7 @@
         <v>45121</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -51115,7 +51115,7 @@
         <v>44782</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -51193,7 +51193,7 @@
         <v>44651</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -51266,7 +51266,7 @@
         <v>45390</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -51339,7 +51339,7 @@
         <v>45973</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -51412,7 +51412,7 @@
         <v>45645</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -51485,7 +51485,7 @@
         <v>45127</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -51558,7 +51558,7 @@
         <v>45168</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -51631,7 +51631,7 @@
         <v>45853</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -51704,7 +51704,7 @@
         <v>45460</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -51777,7 +51777,7 @@
         <v>45740</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -51850,7 +51850,7 @@
         <v>44995</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -51923,7 +51923,7 @@
         <v>45113</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -51996,7 +51996,7 @@
         <v>45113</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -52069,7 +52069,7 @@
         <v>44536</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -52142,7 +52142,7 @@
         <v>44831</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -52215,7 +52215,7 @@
         <v>45301</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -52288,7 +52288,7 @@
         <v>45384</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -52361,7 +52361,7 @@
         <v>45247</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -52434,7 +52434,7 @@
         <v>45097</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -52512,7 +52512,7 @@
         <v>45267</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -52585,7 +52585,7 @@
         <v>45309</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -52658,7 +52658,7 @@
         <v>45121</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -52731,7 +52731,7 @@
         <v>45692</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -52804,7 +52804,7 @@
         <v>44677</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -52877,7 +52877,7 @@
         <v>45782</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -52950,7 +52950,7 @@
         <v>44811</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -53023,7 +53023,7 @@
         <v>44749</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -53096,7 +53096,7 @@
         <v>45714</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -53169,7 +53169,7 @@
         <v>45104</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -53242,7 +53242,7 @@
         <v>44858</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -53315,7 +53315,7 @@
         <v>44502</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -53388,7 +53388,7 @@
         <v>45091</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -53461,7 +53461,7 @@
         <v>45030</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -53534,7 +53534,7 @@
         <v>45979</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -53607,7 +53607,7 @@
         <v>45874</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -53680,7 +53680,7 @@
         <v>45979</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -53753,7 +53753,7 @@
         <v>44496</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -53826,7 +53826,7 @@
         <v>45691</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -53899,7 +53899,7 @@
         <v>44858</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -53972,7 +53972,7 @@
         <v>45980</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -54045,7 +54045,7 @@
         <v>44812</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -54118,7 +54118,7 @@
         <v>45715</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -54196,7 +54196,7 @@
         <v>45048</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -54269,7 +54269,7 @@
         <v>45190</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -54342,7 +54342,7 @@
         <v>44991</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -54415,7 +54415,7 @@
         <v>45513</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -54488,7 +54488,7 @@
         <v>45274</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -54561,7 +54561,7 @@
         <v>45246</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -54634,7 +54634,7 @@
         <v>45743</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -54707,7 +54707,7 @@
         <v>45198</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -54780,7 +54780,7 @@
         <v>45644</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -54853,7 +54853,7 @@
         <v>45128</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -54926,7 +54926,7 @@
         <v>45210</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -54999,7 +54999,7 @@
         <v>45686</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -55072,7 +55072,7 @@
         <v>45278</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -55145,7 +55145,7 @@
         <v>45559</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -55218,7 +55218,7 @@
         <v>46099</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -55291,7 +55291,7 @@
         <v>44909</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -55364,7 +55364,7 @@
         <v>45181</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -55437,7 +55437,7 @@
         <v>46100</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -55510,7 +55510,7 @@
         <v>45141</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -55583,7 +55583,7 @@
         <v>46100</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -55656,7 +55656,7 @@
         <v>45194</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -55729,7 +55729,7 @@
         <v>46100</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -55802,7 +55802,7 @@
         <v>44922</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -55875,7 +55875,7 @@
         <v>45302</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -55948,7 +55948,7 @@
         <v>45753</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -56021,7 +56021,7 @@
         <v>45726</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -56094,7 +56094,7 @@
         <v>45401</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -56167,7 +56167,7 @@
         <v>45244</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -56240,7 +56240,7 @@
         <v>44552</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -56313,7 +56313,7 @@
         <v>45152</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -56386,7 +56386,7 @@
         <v>45250</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -56459,7 +56459,7 @@
         <v>45141</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -56532,7 +56532,7 @@
         <v>45702</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -56605,7 +56605,7 @@
         <v>45614</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -56678,7 +56678,7 @@
         <v>45533</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -56751,7 +56751,7 @@
         <v>44529</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -56824,7 +56824,7 @@
         <v>46107</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -56897,7 +56897,7 @@
         <v>44641</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -56970,7 +56970,7 @@
         <v>44769</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -57048,7 +57048,7 @@
         <v>44769</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -57126,7 +57126,7 @@
         <v>46108</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -57199,7 +57199,7 @@
         <v>45541</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -57272,7 +57272,7 @@
         <v>44874</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -57345,7 +57345,7 @@
         <v>45715</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -57423,7 +57423,7 @@
         <v>45111</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -57496,7 +57496,7 @@
         <v>45714</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -57569,7 +57569,7 @@
         <v>45300</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -57642,7 +57642,7 @@
         <v>45300</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -57715,7 +57715,7 @@
         <v>45267</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -57788,7 +57788,7 @@
         <v>46113</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -57861,7 +57861,7 @@
         <v>44894</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -57934,7 +57934,7 @@
         <v>46112</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -58007,7 +58007,7 @@
         <v>45036</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -58080,7 +58080,7 @@
         <v>45342</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -58153,7 +58153,7 @@
         <v>46112</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -58226,7 +58226,7 @@
         <v>45599</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -58299,7 +58299,7 @@
         <v>45302</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -58372,7 +58372,7 @@
         <v>45322</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -58445,7 +58445,7 @@
         <v>44523</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -58518,7 +58518,7 @@
         <v>45233</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -58591,7 +58591,7 @@
         <v>44600</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -58669,7 +58669,7 @@
         <v>44915</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -58742,7 +58742,7 @@
         <v>45993</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -58815,7 +58815,7 @@
         <v>45594</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -58893,7 +58893,7 @@
         <v>46119</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -58966,7 +58966,7 @@
         <v>45993</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -59039,7 +59039,7 @@
         <v>45594</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -59117,7 +59117,7 @@
         <v>45988</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -59190,7 +59190,7 @@
         <v>44652</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -59263,7 +59263,7 @@
         <v>45999</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -59336,7 +59336,7 @@
         <v>46000</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -59409,7 +59409,7 @@
         <v>46001</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -59482,7 +59482,7 @@
         <v>44537</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -59555,7 +59555,7 @@
         <v>44609</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -59628,7 +59628,7 @@
         <v>45183</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -59701,7 +59701,7 @@
         <v>45121</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -59774,7 +59774,7 @@
         <v>46129</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -59847,7 +59847,7 @@
         <v>45420</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -59920,7 +59920,7 @@
         <v>45253</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -59993,7 +59993,7 @@
         <v>44845</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -60066,7 +60066,7 @@
         <v>44915</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -60139,7 +60139,7 @@
         <v>44552</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -60212,7 +60212,7 @@
         <v>45070</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -60285,7 +60285,7 @@
         <v>44998</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -60358,7 +60358,7 @@
         <v>44592</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -60431,7 +60431,7 @@
         <v>45881</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -60504,7 +60504,7 @@
         <v>45103</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -60577,7 +60577,7 @@
         <v>45638</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -60650,7 +60650,7 @@
         <v>45677</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -60723,7 +60723,7 @@
         <v>45835</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -60796,7 +60796,7 @@
         <v>46008</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -60869,7 +60869,7 @@
         <v>45743</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -60942,7 +60942,7 @@
         <v>45058</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -61015,7 +61015,7 @@
         <v>45827</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -61088,7 +61088,7 @@
         <v>46007</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -61161,7 +61161,7 @@
         <v>45698</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -61234,7 +61234,7 @@
         <v>45810</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -61312,7 +61312,7 @@
         <v>45826</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -61390,7 +61390,7 @@
         <v>45670</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -61463,7 +61463,7 @@
         <v>45905</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -61536,7 +61536,7 @@
         <v>45923</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -61609,7 +61609,7 @@
         <v>45833</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -61682,7 +61682,7 @@
         <v>45883</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -61755,7 +61755,7 @@
         <v>45883</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -61828,7 +61828,7 @@
         <v>45775</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -61901,7 +61901,7 @@
         <v>45846</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -61974,7 +61974,7 @@
         <v>45315</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -62047,7 +62047,7 @@
         <v>45315</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -62120,7 +62120,7 @@
         <v>45782</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -62193,7 +62193,7 @@
         <v>46010</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -62266,7 +62266,7 @@
         <v>45923</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -62339,7 +62339,7 @@
         <v>45426</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -62412,7 +62412,7 @@
         <v>46010</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -62485,7 +62485,7 @@
         <v>45939</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -62558,7 +62558,7 @@
         <v>45827</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -62631,7 +62631,7 @@
         <v>46010</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -62704,7 +62704,7 @@
         <v>44979</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -62777,7 +62777,7 @@
         <v>45386</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -62850,7 +62850,7 @@
         <v>45359</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -62923,7 +62923,7 @@
         <v>46019</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -62996,7 +62996,7 @@
         <v>46019</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -63069,7 +63069,7 @@
         <v>44959</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -63142,7 +63142,7 @@
         <v>45841</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -63215,7 +63215,7 @@
         <v>45686</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -63288,7 +63288,7 @@
         <v>45594</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -63366,7 +63366,7 @@
         <v>45594</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -63444,7 +63444,7 @@
         <v>45230</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -63517,7 +63517,7 @@
         <v>45877</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -63590,7 +63590,7 @@
         <v>44843</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -63663,7 +63663,7 @@
         <v>44894</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -63736,7 +63736,7 @@
         <v>45818</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -63809,7 +63809,7 @@
         <v>46029</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -63882,7 +63882,7 @@
         <v>45245</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -63955,7 +63955,7 @@
         <v>44963</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -64028,7 +64028,7 @@
         <v>46029</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -64101,7 +64101,7 @@
         <v>46031</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -64179,7 +64179,7 @@
         <v>45791</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -64252,7 +64252,7 @@
         <v>46031</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -64330,7 +64330,7 @@
         <v>45597</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -64403,7 +64403,7 @@
         <v>45219</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -64476,7 +64476,7 @@
         <v>45061</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -64549,7 +64549,7 @@
         <v>45419</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -64622,7 +64622,7 @@
         <v>45960</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -64695,7 +64695,7 @@
         <v>45572</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -64768,7 +64768,7 @@
         <v>45304</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -64841,7 +64841,7 @@
         <v>46036</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -64914,7 +64914,7 @@
         <v>46035</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -64992,7 +64992,7 @@
         <v>46035</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -65070,7 +65070,7 @@
         <v>45921</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -65143,7 +65143,7 @@
         <v>46036</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -65216,7 +65216,7 @@
         <v>45029</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -65289,7 +65289,7 @@
         <v>46035</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -65367,7 +65367,7 @@
         <v>44992</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -65440,7 +65440,7 @@
         <v>46036</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -65513,7 +65513,7 @@
         <v>45552</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -65586,7 +65586,7 @@
         <v>45199</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -65659,7 +65659,7 @@
         <v>45909</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -65732,7 +65732,7 @@
         <v>45181</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -65805,7 +65805,7 @@
         <v>46041</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -65878,7 +65878,7 @@
         <v>45147</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -65951,7 +65951,7 @@
         <v>45582</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -66024,7 +66024,7 @@
         <v>45105</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -66097,7 +66097,7 @@
         <v>44501</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -66170,7 +66170,7 @@
         <v>45557</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -66243,7 +66243,7 @@
         <v>45894</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -66316,7 +66316,7 @@
         <v>46043</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -66389,7 +66389,7 @@
         <v>45324</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -66462,7 +66462,7 @@
         <v>46048</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -66535,7 +66535,7 @@
         <v>44522</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -66608,7 +66608,7 @@
         <v>46045</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -66681,7 +66681,7 @@
         <v>45554</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -66754,7 +66754,7 @@
         <v>46045</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -66827,7 +66827,7 @@
         <v>44761</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -66905,7 +66905,7 @@
         <v>45468</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -66978,7 +66978,7 @@
         <v>45057</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -67051,7 +67051,7 @@
         <v>45427</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -67124,7 +67124,7 @@
         <v>45400</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -67197,7 +67197,7 @@
         <v>46049</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -67270,7 +67270,7 @@
         <v>45594</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -67348,7 +67348,7 @@
         <v>45446</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -67421,7 +67421,7 @@
         <v>44977</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -67494,7 +67494,7 @@
         <v>45009</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -67572,7 +67572,7 @@
         <v>46049</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -67645,7 +67645,7 @@
         <v>45679</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -67718,7 +67718,7 @@
         <v>46049</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -67791,7 +67791,7 @@
         <v>46051</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -67864,7 +67864,7 @@
         <v>46056</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -67937,7 +67937,7 @@
         <v>46056</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -68010,7 +68010,7 @@
         <v>46057</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -68083,7 +68083,7 @@
         <v>46059</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -68156,7 +68156,7 @@
         <v>46061</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -68229,7 +68229,7 @@
         <v>45329</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -68302,7 +68302,7 @@
         <v>44577</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -68375,7 +68375,7 @@
         <v>46059</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -68448,7 +68448,7 @@
         <v>46059</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -68521,7 +68521,7 @@
         <v>46146</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -68594,7 +68594,7 @@
         <v>46146</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -68667,7 +68667,7 @@
         <v>46146</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -68740,7 +68740,7 @@
         <v>46147</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -68813,7 +68813,7 @@
         <v>46147</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -68886,7 +68886,7 @@
         <v>46148</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -68959,7 +68959,7 @@
         <v>46147</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -69032,7 +69032,7 @@
         <v>46147</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -69105,7 +69105,7 @@
         <v>45397</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -69178,7 +69178,7 @@
         <v>46147</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -69251,7 +69251,7 @@
         <v>46149</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -69324,7 +69324,7 @@
         <v>46021</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -69397,7 +69397,7 @@
         <v>46072</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -69470,7 +69470,7 @@
         <v>46073</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -69543,7 +69543,7 @@
         <v>46073</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -69616,7 +69616,7 @@
         <v>46153</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -69689,7 +69689,7 @@
         <v>46075</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -69762,7 +69762,7 @@
         <v>46079</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -69835,7 +69835,7 @@
         <v>46079</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -69908,7 +69908,7 @@
         <v>46083</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -69981,7 +69981,7 @@
         <v>46083</v>
       </c>
       <c r="E900" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -70054,7 +70054,7 @@
         <v>46083</v>
       </c>
       <c r="E901" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>
@@ -70127,7 +70127,7 @@
         <v>45995</v>
       </c>
       <c r="E902" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F902" t="inlineStr">
         <is>
@@ -70200,7 +70200,7 @@
         <v>46083</v>
       </c>
       <c r="E903" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F903" t="inlineStr">
         <is>
@@ -70273,7 +70273,7 @@
         <v>46083</v>
       </c>
       <c r="E904" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F904" t="inlineStr">
         <is>
@@ -70346,7 +70346,7 @@
         <v>45517</v>
       </c>
       <c r="E905" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F905" t="inlineStr">
         <is>
@@ -70419,7 +70419,7 @@
         <v>46084</v>
       </c>
       <c r="E906" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F906" t="inlineStr">
         <is>
@@ -70492,7 +70492,7 @@
         <v>45631</v>
       </c>
       <c r="E907" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F907" t="inlineStr">
         <is>
@@ -70565,7 +70565,7 @@
         <v>45789</v>
       </c>
       <c r="E908" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F908" t="inlineStr">
         <is>
@@ -70638,7 +70638,7 @@
         <v>46087</v>
       </c>
       <c r="E909" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F909" t="inlineStr">
         <is>
@@ -70711,7 +70711,7 @@
         <v>45623</v>
       </c>
       <c r="E910" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F910" t="inlineStr">
         <is>
@@ -70784,7 +70784,7 @@
         <v>46162</v>
       </c>
       <c r="E911" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F911" t="inlineStr">
         <is>
@@ -70857,7 +70857,7 @@
         <v>46162</v>
       </c>
       <c r="E912" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F912" t="inlineStr">
         <is>
@@ -70930,7 +70930,7 @@
         <v>45780</v>
       </c>
       <c r="E913" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F913" t="inlineStr">
         <is>
@@ -71003,7 +71003,7 @@
         <v>46162</v>
       </c>
       <c r="E914" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F914" t="inlineStr">
         <is>
@@ -71076,7 +71076,7 @@
         <v>45719</v>
       </c>
       <c r="E915" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F915" t="inlineStr">
         <is>
@@ -71149,7 +71149,7 @@
         <v>46163</v>
       </c>
       <c r="E916" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F916" t="inlineStr">
         <is>
@@ -71222,7 +71222,7 @@
         <v>46163</v>
       </c>
       <c r="E917" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F917" t="inlineStr">
         <is>
@@ -71295,7 +71295,7 @@
         <v>46163</v>
       </c>
       <c r="E918" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F918" t="inlineStr">
         <is>
@@ -71368,7 +71368,7 @@
         <v>46163</v>
       </c>
       <c r="E919" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F919" t="inlineStr">
         <is>
@@ -71441,7 +71441,7 @@
         <v>45812</v>
       </c>
       <c r="E920" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F920" t="inlineStr">
         <is>
@@ -71514,7 +71514,7 @@
         <v>46163</v>
       </c>
       <c r="E921" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F921" t="inlineStr">
         <is>
@@ -71587,7 +71587,7 @@
         <v>46163</v>
       </c>
       <c r="E922" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F922" t="inlineStr">
         <is>
@@ -71660,7 +71660,7 @@
         <v>46168</v>
       </c>
       <c r="E923" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F923" t="inlineStr">
         <is>
@@ -71733,7 +71733,7 @@
         <v>45933</v>
       </c>
       <c r="E924" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F924" t="inlineStr">
         <is>
@@ -71806,7 +71806,7 @@
         <v>46167</v>
       </c>
       <c r="E925" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F925" t="inlineStr">
         <is>
@@ -71879,7 +71879,7 @@
         <v>46168</v>
       </c>
       <c r="E926" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F926" t="inlineStr">
         <is>
@@ -71952,7 +71952,7 @@
         <v>46100</v>
       </c>
       <c r="E927" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F927" t="inlineStr">
         <is>
@@ -72025,7 +72025,7 @@
         <v>45216</v>
       </c>
       <c r="E928" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F928" t="inlineStr">
         <is>
@@ -72098,7 +72098,7 @@
         <v>46112</v>
       </c>
       <c r="E929" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F929" t="inlineStr">
         <is>
@@ -72171,7 +72171,7 @@
         <v>46171</v>
       </c>
       <c r="E930" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F930" t="inlineStr">
         <is>
@@ -72244,7 +72244,7 @@
         <v>46171</v>
       </c>
       <c r="E931" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F931" t="inlineStr">
         <is>
@@ -72317,7 +72317,7 @@
         <v>46170</v>
       </c>
       <c r="E932" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F932" t="inlineStr">
         <is>
@@ -72390,7 +72390,7 @@
         <v>46010</v>
       </c>
       <c r="E933" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F933" t="inlineStr">
         <is>
@@ -72463,7 +72463,7 @@
         <v>46171</v>
       </c>
       <c r="E934" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F934" t="inlineStr">
         <is>
@@ -72536,7 +72536,7 @@
         <v>46134</v>
       </c>
       <c r="E935" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F935" t="inlineStr">
         <is>
@@ -72609,7 +72609,7 @@
         <v>46134</v>
       </c>
       <c r="E936" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F936" t="inlineStr">
         <is>
@@ -72682,7 +72682,7 @@
         <v>46134</v>
       </c>
       <c r="E937" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F937" t="inlineStr">
         <is>
@@ -72755,7 +72755,7 @@
         <v>46170</v>
       </c>
       <c r="E938" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F938" t="inlineStr">
         <is>
@@ -72828,7 +72828,7 @@
         <v>46183</v>
       </c>
       <c r="E939" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F939" t="inlineStr">
         <is>
@@ -72901,7 +72901,7 @@
         <v>46183</v>
       </c>
       <c r="E940" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F940" t="inlineStr">
         <is>
@@ -72974,7 +72974,7 @@
         <v>46183</v>
       </c>
       <c r="E941" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F941" t="inlineStr">
         <is>
@@ -73047,7 +73047,7 @@
         <v>46183</v>
       </c>
       <c r="E942" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F942" t="inlineStr">
         <is>
@@ -73120,7 +73120,7 @@
         <v>46189</v>
       </c>
       <c r="E943" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F943" t="inlineStr">
         <is>
@@ -73193,7 +73193,7 @@
         <v>46188</v>
       </c>
       <c r="E944" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F944" t="inlineStr">
         <is>
@@ -73266,7 +73266,7 @@
         <v>46191</v>
       </c>
       <c r="E945" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F945" t="inlineStr">
         <is>
@@ -73339,7 +73339,7 @@
         <v>46190</v>
       </c>
       <c r="E946" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F946" t="inlineStr">
         <is>
@@ -73412,7 +73412,7 @@
         <v>46191</v>
       </c>
       <c r="E947" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F947" t="inlineStr">
         <is>
@@ -73485,7 +73485,7 @@
         <v>46108</v>
       </c>
       <c r="E948" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F948" t="inlineStr">
         <is>
@@ -73558,7 +73558,7 @@
         <v>45924</v>
       </c>
       <c r="E949" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F949" t="inlineStr">
         <is>
@@ -73631,7 +73631,7 @@
         <v>46199</v>
       </c>
       <c r="E950" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F950" t="inlineStr">
         <is>
@@ -73704,7 +73704,7 @@
         <v>46199</v>
       </c>
       <c r="E951" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F951" t="inlineStr">
         <is>
@@ -73777,7 +73777,7 @@
         <v>46198</v>
       </c>
       <c r="E952" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F952" t="inlineStr">
         <is>
@@ -73850,7 +73850,7 @@
         <v>46198</v>
       </c>
       <c r="E953" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F953" t="inlineStr">
         <is>
@@ -73923,7 +73923,7 @@
         <v>46198</v>
       </c>
       <c r="E954" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F954" t="inlineStr">
         <is>
@@ -73996,7 +73996,7 @@
         <v>46198</v>
       </c>
       <c r="E955" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F955" t="inlineStr">
         <is>
@@ -74069,7 +74069,7 @@
         <v>45541</v>
       </c>
       <c r="E956" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F956" t="inlineStr">
         <is>
@@ -74142,7 +74142,7 @@
         <v>46199</v>
       </c>
       <c r="E957" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F957" t="inlineStr">
         <is>
@@ -74215,7 +74215,7 @@
         <v>46199</v>
       </c>
       <c r="E958" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F958" t="inlineStr">
         <is>
@@ -74288,7 +74288,7 @@
         <v>46205</v>
       </c>
       <c r="E959" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F959" t="inlineStr">
         <is>
@@ -74361,7 +74361,7 @@
         <v>46205</v>
       </c>
       <c r="E960" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F960" t="inlineStr">
         <is>
@@ -74434,7 +74434,7 @@
         <v>46206</v>
       </c>
       <c r="E961" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F961" t="inlineStr">
         <is>
@@ -74512,7 +74512,7 @@
         <v>46210</v>
       </c>
       <c r="E962" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F962" t="inlineStr">
         <is>
@@ -74590,7 +74590,7 @@
         <v>46210</v>
       </c>
       <c r="E963" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F963" t="inlineStr">
         <is>
@@ -74668,7 +74668,7 @@
         <v>46170</v>
       </c>
       <c r="E964" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F964" t="inlineStr">
         <is>
@@ -74741,7 +74741,7 @@
         <v>46230</v>
       </c>
       <c r="E965" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F965" t="inlineStr">
         <is>
@@ -74814,7 +74814,7 @@
         <v>46269</v>
       </c>
       <c r="E966" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F966" t="inlineStr">
         <is>
@@ -74887,7 +74887,7 @@
         <v>46272</v>
       </c>
       <c r="E967" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F967" t="inlineStr">
         <is>
@@ -74960,7 +74960,7 @@
         <v>46272</v>
       </c>
       <c r="E968" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F968" t="inlineStr">
         <is>
@@ -75033,7 +75033,7 @@
         <v>46216</v>
       </c>
       <c r="E969" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F969" t="inlineStr">
         <is>
@@ -75106,7 +75106,7 @@
         <v>46216</v>
       </c>
       <c r="E970" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F970" t="inlineStr">
         <is>
@@ -75179,7 +75179,7 @@
         <v>46216</v>
       </c>
       <c r="E971" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F971" t="inlineStr">
         <is>
@@ -75252,7 +75252,7 @@
         <v>46276</v>
       </c>
       <c r="E972" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F972" t="inlineStr">
         <is>
@@ -75325,7 +75325,7 @@
         <v>46232</v>
       </c>
       <c r="E973" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F973" t="inlineStr">
         <is>
@@ -75398,7 +75398,7 @@
         <v>46232</v>
       </c>
       <c r="E974" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F974" t="inlineStr">
         <is>
@@ -75471,7 +75471,7 @@
         <v>46276</v>
       </c>
       <c r="E975" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F975" t="inlineStr">
         <is>
@@ -75544,7 +75544,7 @@
         <v>46279</v>
       </c>
       <c r="E976" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F976" t="inlineStr">
         <is>
@@ -75617,7 +75617,7 @@
         <v>46279</v>
       </c>
       <c r="E977" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F977" t="inlineStr">
         <is>
@@ -75690,7 +75690,7 @@
         <v>46237</v>
       </c>
       <c r="E978" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F978" t="inlineStr">
         <is>
@@ -75763,7 +75763,7 @@
         <v>46237</v>
       </c>
       <c r="E979" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F979" t="inlineStr">
         <is>
@@ -75836,7 +75836,7 @@
         <v>46281</v>
       </c>
       <c r="E980" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F980" t="inlineStr">
         <is>
@@ -75909,7 +75909,7 @@
         <v>46239</v>
       </c>
       <c r="E981" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F981" t="inlineStr">
         <is>
@@ -75982,7 +75982,7 @@
         <v>46244</v>
       </c>
       <c r="E982" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F982" t="inlineStr">
         <is>
@@ -76060,7 +76060,7 @@
         <v>46244</v>
       </c>
       <c r="E983" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F983" t="inlineStr">
         <is>
@@ -76138,7 +76138,7 @@
         <v>46244</v>
       </c>
       <c r="E984" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F984" t="inlineStr">
         <is>
@@ -76216,7 +76216,7 @@
         <v>46244</v>
       </c>
       <c r="E985" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F985" t="inlineStr">
         <is>
@@ -76294,7 +76294,7 @@
         <v>46244</v>
       </c>
       <c r="E986" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F986" t="inlineStr">
         <is>
@@ -76372,7 +76372,7 @@
         <v>46244</v>
       </c>
       <c r="E987" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F987" t="inlineStr">
         <is>
@@ -76445,7 +76445,7 @@
         <v>46244</v>
       </c>
       <c r="E988" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F988" t="inlineStr">
         <is>
@@ -76523,7 +76523,7 @@
         <v>46288</v>
       </c>
       <c r="E989" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F989" t="inlineStr">
         <is>
@@ -76596,7 +76596,7 @@
         <v>46245</v>
       </c>
       <c r="E990" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F990" t="inlineStr">
         <is>
@@ -76669,7 +76669,7 @@
         <v>46288</v>
       </c>
       <c r="E991" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F991" t="inlineStr">
         <is>
@@ -76742,7 +76742,7 @@
         <v>46244</v>
       </c>
       <c r="E992" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F992" t="inlineStr">
         <is>
@@ -76815,7 +76815,7 @@
         <v>46245</v>
       </c>
       <c r="E993" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F993" t="inlineStr">
         <is>
@@ -76888,7 +76888,7 @@
         <v>46289</v>
       </c>
       <c r="E994" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F994" t="inlineStr">
         <is>
@@ -76961,7 +76961,7 @@
         <v>46021</v>
       </c>
       <c r="E995" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F995" t="inlineStr">
         <is>
@@ -77034,7 +77034,7 @@
         <v>46056</v>
       </c>
       <c r="E996" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F996" t="inlineStr">
         <is>
@@ -77107,7 +77107,7 @@
         <v>46289</v>
       </c>
       <c r="E997" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F997" t="inlineStr">
         <is>
@@ -77180,7 +77180,7 @@
         <v>46246</v>
       </c>
       <c r="E998" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F998" t="inlineStr">
         <is>
@@ -77258,7 +77258,7 @@
         <v>46294</v>
       </c>
       <c r="E999" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F999" t="inlineStr">
         <is>
@@ -77331,7 +77331,7 @@
         <v>46294</v>
       </c>
       <c r="E1000" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1000" t="inlineStr">
         <is>
@@ -77404,7 +77404,7 @@
         <v>46294</v>
       </c>
       <c r="E1001" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1001" t="inlineStr">
         <is>
@@ -77477,7 +77477,7 @@
         <v>46294</v>
       </c>
       <c r="E1002" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1002" t="inlineStr">
         <is>
@@ -77550,7 +77550,7 @@
         <v>46237</v>
       </c>
       <c r="E1003" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1003" t="inlineStr">
         <is>
@@ -77623,7 +77623,7 @@
         <v>46294</v>
       </c>
       <c r="E1004" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1004" t="inlineStr">
         <is>
@@ -77696,7 +77696,7 @@
         <v>46294</v>
       </c>
       <c r="E1005" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1005" t="inlineStr">
         <is>
@@ -77769,7 +77769,7 @@
         <v>46245</v>
       </c>
       <c r="E1006" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1006" t="inlineStr">
         <is>
@@ -77842,7 +77842,7 @@
         <v>46296</v>
       </c>
       <c r="E1007" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1007" t="inlineStr">
         <is>
@@ -77915,7 +77915,7 @@
         <v>46296</v>
       </c>
       <c r="E1008" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1008" t="inlineStr">
         <is>
@@ -77988,7 +77988,7 @@
         <v>46296</v>
       </c>
       <c r="E1009" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1009" t="inlineStr">
         <is>
@@ -78061,7 +78061,7 @@
         <v>46296</v>
       </c>
       <c r="E1010" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1010" t="inlineStr">
         <is>
@@ -78134,7 +78134,7 @@
         <v>46252</v>
       </c>
       <c r="E1011" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1011" t="inlineStr">
         <is>
@@ -78207,7 +78207,7 @@
         <v>46296</v>
       </c>
       <c r="E1012" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1012" t="inlineStr">
         <is>
@@ -78280,7 +78280,7 @@
         <v>46296</v>
       </c>
       <c r="E1013" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1013" t="inlineStr">
         <is>
@@ -78353,7 +78353,7 @@
         <v>46253</v>
       </c>
       <c r="E1014" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1014" t="inlineStr">
         <is>
@@ -78426,7 +78426,7 @@
         <v>46295</v>
       </c>
       <c r="E1015" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1015" t="inlineStr">
         <is>
@@ -78504,7 +78504,7 @@
         <v>46296</v>
       </c>
       <c r="E1016" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1016" t="inlineStr">
         <is>
@@ -78577,7 +78577,7 @@
         <v>46252</v>
       </c>
       <c r="E1017" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1017" t="inlineStr">
         <is>
@@ -78650,7 +78650,7 @@
         <v>46300</v>
       </c>
       <c r="E1018" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1018" t="inlineStr">
         <is>
@@ -78723,7 +78723,7 @@
         <v>45594</v>
       </c>
       <c r="E1019" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1019" t="inlineStr">
         <is>
@@ -78801,7 +78801,7 @@
         <v>46300</v>
       </c>
       <c r="E1020" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1020" t="inlineStr">
         <is>
@@ -78874,7 +78874,7 @@
         <v>46301</v>
       </c>
       <c r="E1021" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1021" t="inlineStr">
         <is>
@@ -78947,7 +78947,7 @@
         <v>46199</v>
       </c>
       <c r="E1022" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1022" t="inlineStr">
         <is>
@@ -79020,7 +79020,7 @@
         <v>46258</v>
       </c>
       <c r="E1023" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1023" t="inlineStr">
         <is>
@@ -79093,7 +79093,7 @@
         <v>45916</v>
       </c>
       <c r="E1024" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1024" t="inlineStr">
         <is>
@@ -79166,7 +79166,7 @@
         <v>46261</v>
       </c>
       <c r="E1025" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1025" t="inlineStr">
         <is>
@@ -79239,7 +79239,7 @@
         <v>46304</v>
       </c>
       <c r="E1026" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1026" t="inlineStr">
         <is>
@@ -79312,7 +79312,7 @@
         <v>46262</v>
       </c>
       <c r="E1027" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1027" t="inlineStr">
         <is>
@@ -79385,7 +79385,7 @@
         <v>46183</v>
       </c>
       <c r="E1028" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1028" t="inlineStr">
         <is>
@@ -79458,7 +79458,7 @@
         <v>46260</v>
       </c>
       <c r="E1029" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1029" t="inlineStr">
         <is>
@@ -79531,7 +79531,7 @@
         <v>46304</v>
       </c>
       <c r="E1030" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1030" t="inlineStr">
         <is>
@@ -79604,7 +79604,7 @@
         <v>46183</v>
       </c>
       <c r="E1031" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1031" t="inlineStr">
         <is>
@@ -79677,7 +79677,7 @@
         <v>44715</v>
       </c>
       <c r="E1032" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1032" t="inlineStr">
         <is>
@@ -79750,7 +79750,7 @@
         <v>44722</v>
       </c>
       <c r="E1033" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1033" t="inlineStr">
         <is>
@@ -79823,7 +79823,7 @@
         <v>44588</v>
       </c>
       <c r="E1034" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1034" t="inlineStr">
         <is>
@@ -79896,7 +79896,7 @@
         <v>44727</v>
       </c>
       <c r="E1035" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1035" t="inlineStr">
         <is>
@@ -79969,7 +79969,7 @@
         <v>44722</v>
       </c>
       <c r="E1036" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1036" t="inlineStr">
         <is>
@@ -80042,7 +80042,7 @@
         <v>44603</v>
       </c>
       <c r="E1037" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1037" t="inlineStr">
         <is>
@@ -80115,7 +80115,7 @@
         <v>44693</v>
       </c>
       <c r="E1038" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1038" t="inlineStr">
         <is>
@@ -80188,7 +80188,7 @@
         <v>44726</v>
       </c>
       <c r="E1039" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1039" t="inlineStr">
         <is>
@@ -80261,7 +80261,7 @@
         <v>44712</v>
       </c>
       <c r="E1040" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1040" t="inlineStr">
         <is>
@@ -80334,7 +80334,7 @@
         <v>44722</v>
       </c>
       <c r="E1041" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1041" t="inlineStr">
         <is>
@@ -80407,7 +80407,7 @@
         <v>44712</v>
       </c>
       <c r="E1042" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1042" t="inlineStr">
         <is>
@@ -80480,7 +80480,7 @@
         <v>44704</v>
       </c>
       <c r="E1043" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1043" t="inlineStr">
         <is>
@@ -80553,7 +80553,7 @@
         <v>44596</v>
       </c>
       <c r="E1044" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1044" t="inlineStr">
         <is>
@@ -80626,7 +80626,7 @@
         <v>44704</v>
       </c>
       <c r="E1045" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1045" t="inlineStr">
         <is>
@@ -80699,7 +80699,7 @@
         <v>44588</v>
       </c>
       <c r="E1046" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1046" t="inlineStr">
         <is>
@@ -80772,7 +80772,7 @@
         <v>45054</v>
       </c>
       <c r="E1047" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1047" t="inlineStr">
         <is>
@@ -80845,7 +80845,7 @@
         <v>45230</v>
       </c>
       <c r="E1048" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1048" t="inlineStr">
         <is>
@@ -80923,7 +80923,7 @@
         <v>44498</v>
       </c>
       <c r="E1049" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1049" t="inlineStr">
         <is>
@@ -80996,7 +80996,7 @@
         <v>45622</v>
       </c>
       <c r="E1050" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1050" t="inlineStr">
         <is>
@@ -81069,7 +81069,7 @@
         <v>45054</v>
       </c>
       <c r="E1051" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1051" t="inlineStr">
         <is>
@@ -81142,7 +81142,7 @@
         <v>45054</v>
       </c>
       <c r="E1052" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1052" t="inlineStr">
         <is>
@@ -81215,7 +81215,7 @@
         <v>45056</v>
       </c>
       <c r="E1053" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1053" t="inlineStr">
         <is>
@@ -81288,7 +81288,7 @@
         <v>45434</v>
       </c>
       <c r="E1054" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1054" t="inlineStr">
         <is>
@@ -81361,7 +81361,7 @@
         <v>45054</v>
       </c>
       <c r="E1055" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1055" t="inlineStr">
         <is>
@@ -81434,7 +81434,7 @@
         <v>45407</v>
       </c>
       <c r="E1056" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1056" t="inlineStr">
         <is>
@@ -81507,7 +81507,7 @@
         <v>44802</v>
       </c>
       <c r="E1057" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1057" t="inlineStr">
         <is>
@@ -81580,7 +81580,7 @@
         <v>45071</v>
       </c>
       <c r="E1058" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1058" t="inlineStr">
         <is>
@@ -81653,7 +81653,7 @@
         <v>44495</v>
       </c>
       <c r="E1059" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1059" t="inlineStr">
         <is>
@@ -81726,7 +81726,7 @@
         <v>45224</v>
       </c>
       <c r="E1060" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1060" t="inlineStr">
         <is>
@@ -81804,7 +81804,7 @@
         <v>44972</v>
       </c>
       <c r="E1061" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1061" t="inlineStr">
         <is>
@@ -81877,7 +81877,7 @@
         <v>44487</v>
       </c>
       <c r="E1062" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1062" t="inlineStr">
         <is>
@@ -81950,7 +81950,7 @@
         <v>45230</v>
       </c>
       <c r="E1063" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1063" t="inlineStr">
         <is>
@@ -82023,7 +82023,7 @@
         <v>44939</v>
       </c>
       <c r="E1064" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1064" t="inlineStr">
         <is>
@@ -82096,7 +82096,7 @@
         <v>45468</v>
       </c>
       <c r="E1065" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1065" t="inlineStr">
         <is>
@@ -82169,7 +82169,7 @@
         <v>45218</v>
       </c>
       <c r="E1066" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1066" t="inlineStr">
         <is>
@@ -82242,7 +82242,7 @@
         <v>45054</v>
       </c>
       <c r="E1067" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1067" t="inlineStr">
         <is>
@@ -82315,7 +82315,7 @@
         <v>44930</v>
       </c>
       <c r="E1068" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1068" t="inlineStr">
         <is>
@@ -82393,7 +82393,7 @@
         <v>44973</v>
       </c>
       <c r="E1069" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1069" t="inlineStr">
         <is>
@@ -82466,7 +82466,7 @@
         <v>44908</v>
       </c>
       <c r="E1070" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1070" t="inlineStr">
         <is>
@@ -82559,7 +82559,7 @@
         <v>45583</v>
       </c>
       <c r="E1071" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1071" t="inlineStr">
         <is>
@@ -82632,7 +82632,7 @@
         <v>45054</v>
       </c>
       <c r="E1072" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1072" t="inlineStr">
         <is>
@@ -82705,7 +82705,7 @@
         <v>45054</v>
       </c>
       <c r="E1073" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1073" t="inlineStr">
         <is>
@@ -82778,7 +82778,7 @@
         <v>44908</v>
       </c>
       <c r="E1074" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1074" t="inlineStr">
         <is>
@@ -82851,7 +82851,7 @@
         <v>44972</v>
       </c>
       <c r="E1075" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1075" t="inlineStr">
         <is>
@@ -82924,7 +82924,7 @@
         <v>44978</v>
       </c>
       <c r="E1076" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1076" t="inlineStr">
         <is>
@@ -82997,7 +82997,7 @@
         <v>44887</v>
       </c>
       <c r="E1077" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1077" t="inlineStr">
         <is>
@@ -83070,7 +83070,7 @@
         <v>44909</v>
       </c>
       <c r="E1078" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1078" t="inlineStr">
         <is>
@@ -83143,7 +83143,7 @@
         <v>45408</v>
       </c>
       <c r="E1079" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1079" t="inlineStr">
         <is>
@@ -83216,7 +83216,7 @@
         <v>44908</v>
       </c>
       <c r="E1080" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1080" t="inlineStr">
         <is>
@@ -83289,7 +83289,7 @@
         <v>45054</v>
       </c>
       <c r="E1081" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1081" t="inlineStr">
         <is>
@@ -83362,7 +83362,7 @@
         <v>45526</v>
       </c>
       <c r="E1082" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1082" t="inlineStr">
         <is>
@@ -83435,7 +83435,7 @@
         <v>45436</v>
       </c>
       <c r="E1083" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1083" t="inlineStr">
         <is>
@@ -83508,7 +83508,7 @@
         <v>45485</v>
       </c>
       <c r="E1084" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1084" t="inlineStr">
         <is>
@@ -83581,7 +83581,7 @@
         <v>45727</v>
       </c>
       <c r="E1085" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1085" t="inlineStr">
         <is>
@@ -83654,7 +83654,7 @@
         <v>45740</v>
       </c>
       <c r="E1086" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1086" t="inlineStr">
         <is>
@@ -83727,7 +83727,7 @@
         <v>45726</v>
       </c>
       <c r="E1087" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1087" t="inlineStr">
         <is>
@@ -83800,7 +83800,7 @@
         <v>45797</v>
       </c>
       <c r="E1088" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1088" t="inlineStr">
         <is>
@@ -83873,7 +83873,7 @@
         <v>45805</v>
       </c>
       <c r="E1089" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1089" t="inlineStr">
         <is>
@@ -83946,7 +83946,7 @@
         <v>45831</v>
       </c>
       <c r="E1090" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1090" t="inlineStr">
         <is>
@@ -84019,7 +84019,7 @@
         <v>45951</v>
       </c>
       <c r="E1091" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1091" t="inlineStr">
         <is>
@@ -84092,7 +84092,7 @@
         <v>45958</v>
       </c>
       <c r="E1092" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1092" t="inlineStr">
         <is>
@@ -84165,7 +84165,7 @@
         <v>45964</v>
       </c>
       <c r="E1093" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1093" t="inlineStr">
         <is>
@@ -84238,7 +84238,7 @@
         <v>45965</v>
       </c>
       <c r="E1094" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1094" t="inlineStr">
         <is>
@@ -84311,7 +84311,7 @@
         <v>45981</v>
       </c>
       <c r="E1095" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1095" t="inlineStr">
         <is>
@@ -84389,7 +84389,7 @@
         <v>45988</v>
       </c>
       <c r="E1096" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1096" t="inlineStr">
         <is>
@@ -84462,7 +84462,7 @@
         <v>46092</v>
       </c>
       <c r="E1097" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1097" t="inlineStr">
         <is>
@@ -84540,7 +84540,7 @@
         <v>46202</v>
       </c>
       <c r="E1098" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1098" t="inlineStr">
         <is>
@@ -84613,7 +84613,7 @@
         <v>46300</v>
       </c>
       <c r="E1099" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1099" t="inlineStr">
         <is>
@@ -84686,7 +84686,7 @@
         <v>46262</v>
       </c>
       <c r="E1100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1100" t="inlineStr">
         <is>
@@ -84759,7 +84759,7 @@
         <v>46304</v>
       </c>
       <c r="E1101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1101" t="inlineStr">
         <is>

--- a/Översikt VÄXJÖ.xlsx
+++ b/Översikt VÄXJÖ.xlsx
@@ -601,7 +601,7 @@
         <v>44974</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         <v>45895</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -859,7 +859,7 @@
         <v>45770</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -976,7 +976,7 @@
         <v>45468</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         <v>45384</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
         <v>45888</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>46175</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>45127</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
         <v>45812</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
         <v>45964</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1769,7 +1769,7 @@
         <v>46188</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
         <v>46188</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         <v>46199</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>44958</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2224,7 +2224,7 @@
         <v>45081</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2337,7 +2337,7 @@
         <v>45294</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2454,7 +2454,7 @@
         <v>45995</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2566,7 +2566,7 @@
         <v>45490</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2683,7 +2683,7 @@
         <v>46247</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2791,7 +2791,7 @@
         <v>46204</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2907,7 +2907,7 @@
         <v>46244</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3018,7 +3018,7 @@
         <v>45356</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3129,7 +3129,7 @@
         <v>45344</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         <v>46098</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3347,7 +3347,7 @@
         <v>46286</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3454,7 +3454,7 @@
         <v>44532</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3569,7 +3569,7 @@
         <v>45874</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3680,7 +3680,7 @@
         <v>46147</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3786,7 +3786,7 @@
         <v>46161</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3896,7 +3896,7 @@
         <v>45190</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4002,7 +4002,7 @@
         <v>46182</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4117,7 +4117,7 @@
         <v>45687</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4223,7 +4223,7 @@
         <v>45093</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4333,7 +4333,7 @@
         <v>45587</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4443,7 +4443,7 @@
         <v>45447</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4549,7 +4549,7 @@
         <v>45649</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4655,7 +4655,7 @@
         <v>46296</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4761,7 +4761,7 @@
         <v>45545</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4867,7 +4867,7 @@
         <v>45820</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4977,7 +4977,7 @@
         <v>45554</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5083,7 +5083,7 @@
         <v>45883</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5189,7 +5189,7 @@
         <v>44704</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5295,7 +5295,7 @@
         <v>45460</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5401,7 +5401,7 @@
         <v>44704</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5511,7 +5511,7 @@
         <v>45348</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5617,7 +5617,7 @@
         <v>45351</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5723,7 +5723,7 @@
         <v>45674</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5834,7 +5834,7 @@
         <v>46100</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5940,7 +5940,7 @@
         <v>44721</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6045,7 +6045,7 @@
         <v>44704</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6150,7 +6150,7 @@
         <v>44645</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6255,7 +6255,7 @@
         <v>44490</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6360,7 +6360,7 @@
         <v>45594</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6470,7 +6470,7 @@
         <v>45594</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6580,7 +6580,7 @@
         <v>45392</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6690,7 +6690,7 @@
         <v>44705</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6799,7 +6799,7 @@
         <v>45643</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6904,7 +6904,7 @@
         <v>44741</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7009,7 +7009,7 @@
         <v>45279</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7114,7 +7114,7 @@
         <v>45280</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7219,7 +7219,7 @@
         <v>45327</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7324,7 +7324,7 @@
         <v>45824</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7429,7 +7429,7 @@
         <v>44673</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7534,7 +7534,7 @@
         <v>45428</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7644,7 +7644,7 @@
         <v>44746</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7749,7 +7749,7 @@
         <v>46161</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7854,7 +7854,7 @@
         <v>45964</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7963,7 +7963,7 @@
         <v>46161</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8068,7 +8068,7 @@
         <v>45978</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8177,7 +8177,7 @@
         <v>44872</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8282,7 +8282,7 @@
         <v>45754</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8387,7 +8387,7 @@
         <v>46045</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8492,7 +8492,7 @@
         <v>45688</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8597,7 +8597,7 @@
         <v>45273</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8702,7 +8702,7 @@
         <v>45594</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8816,7 +8816,7 @@
         <v>46199</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8921,7 +8921,7 @@
         <v>45533</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9026,7 +9026,7 @@
         <v>45098</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9131,7 +9131,7 @@
         <v>45280</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9236,7 +9236,7 @@
         <v>45369</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9341,7 +9341,7 @@
         <v>46281</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9446,7 +9446,7 @@
         <v>46288</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9551,7 +9551,7 @@
         <v>46246</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9656,7 +9656,7 @@
         <v>46296</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9761,7 +9761,7 @@
         <v>44894</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9866,7 +9866,7 @@
         <v>46303</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9971,7 +9971,7 @@
         <v>45617</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10081,7 +10081,7 @@
         <v>45606</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10186,7 +10186,7 @@
         <v>44634</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10291,7 +10291,7 @@
         <v>44712</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10396,7 +10396,7 @@
         <v>44950</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10501,7 +10501,7 @@
         <v>45436</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10606,7 +10606,7 @@
         <v>45726</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10711,7 +10711,7 @@
         <v>45805</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10816,7 +10816,7 @@
         <v>45939</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10925,7 +10925,7 @@
         <v>46100</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11030,7 +11030,7 @@
         <v>44693</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11103,7 +11103,7 @@
         <v>44812</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11176,7 +11176,7 @@
         <v>44518</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11249,7 +11249,7 @@
         <v>44536</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11322,7 +11322,7 @@
         <v>44764</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11395,7 +11395,7 @@
         <v>44519</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11468,7 +11468,7 @@
         <v>44501</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11541,7 +11541,7 @@
         <v>44814</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11614,7 +11614,7 @@
         <v>44645</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11687,7 +11687,7 @@
         <v>44643</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11760,7 +11760,7 @@
         <v>44515</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11833,7 +11833,7 @@
         <v>44814</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11906,7 +11906,7 @@
         <v>44525</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11979,7 +11979,7 @@
         <v>44578</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12052,7 +12052,7 @@
         <v>44516</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12130,7 +12130,7 @@
         <v>44803</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12203,7 +12203,7 @@
         <v>44691</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12276,7 +12276,7 @@
         <v>44739</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12349,7 +12349,7 @@
         <v>44590</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12427,7 +12427,7 @@
         <v>44820</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12505,7 +12505,7 @@
         <v>44814</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12578,7 +12578,7 @@
         <v>44769</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12656,7 +12656,7 @@
         <v>44820</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12729,7 +12729,7 @@
         <v>44711</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12802,7 +12802,7 @@
         <v>44880</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12875,7 +12875,7 @@
         <v>44495</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12948,7 +12948,7 @@
         <v>44508</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13021,7 +13021,7 @@
         <v>44515</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13094,7 +13094,7 @@
         <v>44599</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13167,7 +13167,7 @@
         <v>44495</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13240,7 +13240,7 @@
         <v>44599</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13313,7 +13313,7 @@
         <v>44651</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13386,7 +13386,7 @@
         <v>44876</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13464,7 +13464,7 @@
         <v>44671</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13537,7 +13537,7 @@
         <v>44496</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13610,7 +13610,7 @@
         <v>44750</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13683,7 +13683,7 @@
         <v>44568</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13756,7 +13756,7 @@
         <v>44543</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13829,7 +13829,7 @@
         <v>44606</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13902,7 +13902,7 @@
         <v>44613</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13975,7 +13975,7 @@
         <v>44746</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14048,7 +14048,7 @@
         <v>44610</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14121,7 +14121,7 @@
         <v>44610</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14194,7 +14194,7 @@
         <v>44491</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14267,7 +14267,7 @@
         <v>44740</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14340,7 +14340,7 @@
         <v>44617</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14413,7 +14413,7 @@
         <v>44726</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14486,7 +14486,7 @@
         <v>44551</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14559,7 +14559,7 @@
         <v>44599</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14632,7 +14632,7 @@
         <v>44781</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14705,7 +14705,7 @@
         <v>44494</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14778,7 +14778,7 @@
         <v>44704</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14851,7 +14851,7 @@
         <v>44522</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14924,7 +14924,7 @@
         <v>44532</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14997,7 +14997,7 @@
         <v>44532</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15070,7 +15070,7 @@
         <v>44498</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15143,7 +15143,7 @@
         <v>44860</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15216,7 +15216,7 @@
         <v>44596</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15289,7 +15289,7 @@
         <v>44573</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15362,7 +15362,7 @@
         <v>44712</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15435,7 +15435,7 @@
         <v>44579</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15508,7 +15508,7 @@
         <v>44711</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15581,7 +15581,7 @@
         <v>44769</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15659,7 +15659,7 @@
         <v>44502</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15737,7 +15737,7 @@
         <v>44812</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15810,7 +15810,7 @@
         <v>44489</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15883,7 +15883,7 @@
         <v>44489</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15956,7 +15956,7 @@
         <v>44508</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16029,7 +16029,7 @@
         <v>44574</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16102,7 +16102,7 @@
         <v>44537</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16175,7 +16175,7 @@
         <v>44537</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16248,7 +16248,7 @@
         <v>44571</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16321,7 +16321,7 @@
         <v>44489</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16394,7 +16394,7 @@
         <v>44487</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16467,7 +16467,7 @@
         <v>44603</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16545,7 +16545,7 @@
         <v>44596</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16618,7 +16618,7 @@
         <v>44560</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16691,7 +16691,7 @@
         <v>44820</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16769,7 +16769,7 @@
         <v>44820</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16847,7 +16847,7 @@
         <v>44802</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16920,7 +16920,7 @@
         <v>45386</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16993,7 +16993,7 @@
         <v>44894</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17071,7 +17071,7 @@
         <v>44915</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17144,7 +17144,7 @@
         <v>44523</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17217,7 +17217,7 @@
         <v>44573</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17290,7 +17290,7 @@
         <v>45420</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17363,7 +17363,7 @@
         <v>45477</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17441,7 +17441,7 @@
         <v>45236</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17514,7 +17514,7 @@
         <v>45594</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17592,7 +17592,7 @@
         <v>45594</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17670,7 +17670,7 @@
         <v>45594</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17748,7 +17748,7 @@
         <v>45594</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17826,7 +17826,7 @@
         <v>44967</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17899,7 +17899,7 @@
         <v>45460</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17972,7 +17972,7 @@
         <v>45324</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18045,7 +18045,7 @@
         <v>44502</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18123,7 +18123,7 @@
         <v>45715</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18201,7 +18201,7 @@
         <v>45672</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18274,7 +18274,7 @@
         <v>45594</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18352,7 +18352,7 @@
         <v>45594</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18430,7 +18430,7 @@
         <v>45554</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18503,7 +18503,7 @@
         <v>44537</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18576,7 +18576,7 @@
         <v>44764</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18649,7 +18649,7 @@
         <v>45775</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18722,7 +18722,7 @@
         <v>45762</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18800,7 +18800,7 @@
         <v>45056</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18873,7 +18873,7 @@
         <v>45558</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18946,7 +18946,7 @@
         <v>45679</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19019,7 +19019,7 @@
         <v>44656</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19092,7 +19092,7 @@
         <v>44970</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19165,7 +19165,7 @@
         <v>44988</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19238,7 +19238,7 @@
         <v>45181</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19311,7 +19311,7 @@
         <v>45152</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19384,7 +19384,7 @@
         <v>45057</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19457,7 +19457,7 @@
         <v>45330</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19530,7 +19530,7 @@
         <v>44991</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19603,7 +19603,7 @@
         <v>44900</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19676,7 +19676,7 @@
         <v>45322</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19749,7 +19749,7 @@
         <v>44713</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19822,7 +19822,7 @@
         <v>44979</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19895,7 +19895,7 @@
         <v>45033</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19973,7 +19973,7 @@
         <v>44532</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20046,7 +20046,7 @@
         <v>44602</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20119,7 +20119,7 @@
         <v>44620</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20192,7 +20192,7 @@
         <v>45561</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20265,7 +20265,7 @@
         <v>44894</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20338,7 +20338,7 @@
         <v>45541</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20411,7 +20411,7 @@
         <v>45726</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20484,7 +20484,7 @@
         <v>44599</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20557,7 +20557,7 @@
         <v>45114</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20630,7 +20630,7 @@
         <v>45341</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20703,7 +20703,7 @@
         <v>45359</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20776,7 +20776,7 @@
         <v>45555</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20849,7 +20849,7 @@
         <v>45330</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20922,7 +20922,7 @@
         <v>45105</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20995,7 +20995,7 @@
         <v>45691</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21068,7 +21068,7 @@
         <v>45714</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21141,7 +21141,7 @@
         <v>45579</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21214,7 +21214,7 @@
         <v>45557</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21287,7 +21287,7 @@
         <v>45219</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21360,7 +21360,7 @@
         <v>45557</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21433,7 +21433,7 @@
         <v>45583</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21506,7 +21506,7 @@
         <v>45309</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21579,7 +21579,7 @@
         <v>45737</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21652,7 +21652,7 @@
         <v>45408</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21725,7 +21725,7 @@
         <v>45586</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21798,7 +21798,7 @@
         <v>45392</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21876,7 +21876,7 @@
         <v>45309</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21949,7 +21949,7 @@
         <v>44854</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22022,7 +22022,7 @@
         <v>45253</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22095,7 +22095,7 @@
         <v>45460</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22168,7 +22168,7 @@
         <v>44552</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22241,7 +22241,7 @@
         <v>45309</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22314,7 +22314,7 @@
         <v>45244</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22387,7 +22387,7 @@
         <v>45244</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22460,7 +22460,7 @@
         <v>44909</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22533,7 +22533,7 @@
         <v>45211</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22606,7 +22606,7 @@
         <v>45686</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22679,7 +22679,7 @@
         <v>45233</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22752,7 +22752,7 @@
         <v>44814</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22825,7 +22825,7 @@
         <v>44814</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22898,7 +22898,7 @@
         <v>45061</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22971,7 +22971,7 @@
         <v>45280</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23044,7 +23044,7 @@
         <v>45300</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23117,7 +23117,7 @@
         <v>44858</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23190,7 +23190,7 @@
         <v>45412</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23263,7 +23263,7 @@
         <v>45194</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23336,7 +23336,7 @@
         <v>44929</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23414,7 +23414,7 @@
         <v>44981</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23487,7 +23487,7 @@
         <v>45372</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23560,7 +23560,7 @@
         <v>44746</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23633,7 +23633,7 @@
         <v>44896</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23706,7 +23706,7 @@
         <v>45714</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23779,7 +23779,7 @@
         <v>45246</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23852,7 +23852,7 @@
         <v>45019</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23925,7 +23925,7 @@
         <v>45140</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23998,7 +23998,7 @@
         <v>44959</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24071,7 +24071,7 @@
         <v>45112</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24144,7 +24144,7 @@
         <v>45219</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24217,7 +24217,7 @@
         <v>45315</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24290,7 +24290,7 @@
         <v>45168</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24363,7 +24363,7 @@
         <v>45166</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24436,7 +24436,7 @@
         <v>45222</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24509,7 +24509,7 @@
         <v>45244</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24582,7 +24582,7 @@
         <v>45611</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24655,7 +24655,7 @@
         <v>45162</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24728,7 +24728,7 @@
         <v>45162</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24801,7 +24801,7 @@
         <v>45194</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24874,7 +24874,7 @@
         <v>45090</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24947,7 +24947,7 @@
         <v>44679</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25020,7 +25020,7 @@
         <v>45128</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25093,7 +25093,7 @@
         <v>44963</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25166,7 +25166,7 @@
         <v>44963</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25239,7 +25239,7 @@
         <v>44963</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25312,7 +25312,7 @@
         <v>45278</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25385,7 +25385,7 @@
         <v>45304</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25458,7 +25458,7 @@
         <v>44866</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25531,7 +25531,7 @@
         <v>44529</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25604,7 +25604,7 @@
         <v>45686</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25677,7 +25677,7 @@
         <v>45686</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25750,7 +25750,7 @@
         <v>45111</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25823,7 +25823,7 @@
         <v>44678</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25896,7 +25896,7 @@
         <v>44915</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25969,7 +25969,7 @@
         <v>45245</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26042,7 +26042,7 @@
         <v>45279</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26115,7 +26115,7 @@
         <v>45753</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26188,7 +26188,7 @@
         <v>45304</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26261,7 +26261,7 @@
         <v>45190</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26334,7 +26334,7 @@
         <v>45104</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26407,7 +26407,7 @@
         <v>44537</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26480,7 +26480,7 @@
         <v>45236</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26553,7 +26553,7 @@
         <v>45236</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26626,7 +26626,7 @@
         <v>45121</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26699,7 +26699,7 @@
         <v>45121</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26772,7 +26772,7 @@
         <v>45121</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26845,7 +26845,7 @@
         <v>45317</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26918,7 +26918,7 @@
         <v>44950</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26991,7 +26991,7 @@
         <v>45638</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27064,7 +27064,7 @@
         <v>45169</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27137,7 +27137,7 @@
         <v>45036</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27210,7 +27210,7 @@
         <v>45048</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27283,7 +27283,7 @@
         <v>45240</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27356,7 +27356,7 @@
         <v>45463</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27429,7 +27429,7 @@
         <v>45154</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27502,7 +27502,7 @@
         <v>45230</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27575,7 +27575,7 @@
         <v>45715</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27648,7 +27648,7 @@
         <v>45769</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27721,7 +27721,7 @@
         <v>45328</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27794,7 +27794,7 @@
         <v>45328</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27867,7 +27867,7 @@
         <v>45194</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27940,7 +27940,7 @@
         <v>44922</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28013,7 +28013,7 @@
         <v>45632</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28086,7 +28086,7 @@
         <v>45446</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28159,7 +28159,7 @@
         <v>45058</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28232,7 +28232,7 @@
         <v>44908</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28305,7 +28305,7 @@
         <v>45611</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28378,7 +28378,7 @@
         <v>45594</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28456,7 +28456,7 @@
         <v>45281</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28529,7 +28529,7 @@
         <v>45883</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28602,7 +28602,7 @@
         <v>45274</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28675,7 +28675,7 @@
         <v>45883</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28748,7 +28748,7 @@
         <v>45883</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28821,7 +28821,7 @@
         <v>45827</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28894,7 +28894,7 @@
         <v>45638</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28967,7 +28967,7 @@
         <v>45743</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29040,7 +29040,7 @@
         <v>45791</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29113,7 +29113,7 @@
         <v>45670</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29186,7 +29186,7 @@
         <v>45833</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29259,7 +29259,7 @@
         <v>45201</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29332,7 +29332,7 @@
         <v>45782</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29405,7 +29405,7 @@
         <v>45280</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29478,7 +29478,7 @@
         <v>45909</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29551,7 +29551,7 @@
         <v>45281</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29624,7 +29624,7 @@
         <v>45225</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29697,7 +29697,7 @@
         <v>45127</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29770,7 +29770,7 @@
         <v>45775</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29843,7 +29843,7 @@
         <v>45835</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29916,7 +29916,7 @@
         <v>45030</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29989,7 +29989,7 @@
         <v>45210</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30062,7 +30062,7 @@
         <v>44880</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30135,7 +30135,7 @@
         <v>45841</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30208,7 +30208,7 @@
         <v>45826</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30286,7 +30286,7 @@
         <v>45960</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30359,7 +30359,7 @@
         <v>45112</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30432,7 +30432,7 @@
         <v>44966</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30505,7 +30505,7 @@
         <v>45426</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30578,7 +30578,7 @@
         <v>45387</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30651,7 +30651,7 @@
         <v>45560</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30724,7 +30724,7 @@
         <v>45091</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30802,7 +30802,7 @@
         <v>44487</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30875,7 +30875,7 @@
         <v>44741</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30948,7 +30948,7 @@
         <v>44741</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31021,7 +31021,7 @@
         <v>45281</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31094,7 +31094,7 @@
         <v>45905</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31167,7 +31167,7 @@
         <v>45715</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31245,7 +31245,7 @@
         <v>44687</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31318,7 +31318,7 @@
         <v>45846</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31391,7 +31391,7 @@
         <v>44547</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31464,7 +31464,7 @@
         <v>45890</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31537,7 +31537,7 @@
         <v>45895</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31610,7 +31610,7 @@
         <v>45894</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31683,7 +31683,7 @@
         <v>45161</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31756,7 +31756,7 @@
         <v>45436</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31829,7 +31829,7 @@
         <v>45260</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31902,7 +31902,7 @@
         <v>45240</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31975,7 +31975,7 @@
         <v>45856</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32048,7 +32048,7 @@
         <v>45148</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32121,7 +32121,7 @@
         <v>45148</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32194,7 +32194,7 @@
         <v>45698</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32267,7 +32267,7 @@
         <v>44545</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32340,7 +32340,7 @@
         <v>45897</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32418,7 +32418,7 @@
         <v>45091</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32491,7 +32491,7 @@
         <v>45222</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32564,7 +32564,7 @@
         <v>45754</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32637,7 +32637,7 @@
         <v>45622</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32710,7 +32710,7 @@
         <v>45288</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32783,7 +32783,7 @@
         <v>45229</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32856,7 +32856,7 @@
         <v>45390</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32929,7 +32929,7 @@
         <v>45827</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33002,7 +33002,7 @@
         <v>45278</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33075,7 +33075,7 @@
         <v>45124</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33148,7 +33148,7 @@
         <v>45818</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33221,7 +33221,7 @@
         <v>45385</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33299,7 +33299,7 @@
         <v>45810</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33377,7 +33377,7 @@
         <v>44522</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33450,7 +33450,7 @@
         <v>45329</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33523,7 +33523,7 @@
         <v>45686</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33596,7 +33596,7 @@
         <v>44577</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33669,7 +33669,7 @@
         <v>45419</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33742,7 +33742,7 @@
         <v>45902</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33815,7 +33815,7 @@
         <v>45877</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33888,7 +33888,7 @@
         <v>45810</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33966,7 +33966,7 @@
         <v>45719</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34039,7 +34039,7 @@
         <v>45645</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34112,7 +34112,7 @@
         <v>45835</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34185,7 +34185,7 @@
         <v>45342</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34258,7 +34258,7 @@
         <v>45902</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34331,7 +34331,7 @@
         <v>45902</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34404,7 +34404,7 @@
         <v>45905</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34477,7 +34477,7 @@
         <v>45049</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34550,7 +34550,7 @@
         <v>45244</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34623,7 +34623,7 @@
         <v>45909</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34696,7 +34696,7 @@
         <v>45629</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34769,7 +34769,7 @@
         <v>45599</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34842,7 +34842,7 @@
         <v>45145</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34915,7 +34915,7 @@
         <v>45911</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34988,7 +34988,7 @@
         <v>45910</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35061,7 +35061,7 @@
         <v>44845</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35134,7 +35134,7 @@
         <v>45787</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35207,7 +35207,7 @@
         <v>45169</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35280,7 +35280,7 @@
         <v>44711</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35353,7 +35353,7 @@
         <v>45153</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35426,7 +35426,7 @@
         <v>44938</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35499,7 +35499,7 @@
         <v>45540</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35572,7 +35572,7 @@
         <v>45918</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35645,7 +35645,7 @@
         <v>45104</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35718,7 +35718,7 @@
         <v>45702</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35791,7 +35791,7 @@
         <v>46146</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35864,7 +35864,7 @@
         <v>46146</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35937,7 +35937,7 @@
         <v>45387</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36010,7 +36010,7 @@
         <v>46146</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36083,7 +36083,7 @@
         <v>46147</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36156,7 +36156,7 @@
         <v>46147</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36229,7 +36229,7 @@
         <v>46147</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36302,7 +36302,7 @@
         <v>45924</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36375,7 +36375,7 @@
         <v>46147</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36448,7 +36448,7 @@
         <v>46147</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36521,7 +36521,7 @@
         <v>45113</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36594,7 +36594,7 @@
         <v>45925</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36667,7 +36667,7 @@
         <v>45579</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36740,7 +36740,7 @@
         <v>45513</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36813,7 +36813,7 @@
         <v>45215</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36886,7 +36886,7 @@
         <v>44532</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36959,7 +36959,7 @@
         <v>46149</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37032,7 +37032,7 @@
         <v>45397</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37105,7 +37105,7 @@
         <v>46148</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37178,7 +37178,7 @@
         <v>46021</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37251,7 +37251,7 @@
         <v>45224</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37329,7 +37329,7 @@
         <v>44641</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37402,7 +37402,7 @@
         <v>46153</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37475,7 +37475,7 @@
         <v>45070</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37548,7 +37548,7 @@
         <v>45937</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37621,7 +37621,7 @@
         <v>45128</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37694,7 +37694,7 @@
         <v>45259</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37767,7 +37767,7 @@
         <v>45937</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37840,7 +37840,7 @@
         <v>45309</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37913,7 +37913,7 @@
         <v>45309</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37986,7 +37986,7 @@
         <v>45488</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38059,7 +38059,7 @@
         <v>45009</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38137,7 +38137,7 @@
         <v>45896</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38210,7 +38210,7 @@
         <v>45686</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38283,7 +38283,7 @@
         <v>45103</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38356,7 +38356,7 @@
         <v>44858</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38429,7 +38429,7 @@
         <v>45253</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38502,7 +38502,7 @@
         <v>45250</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38575,7 +38575,7 @@
         <v>45016</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38648,7 +38648,7 @@
         <v>45670</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38721,7 +38721,7 @@
         <v>45250</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38794,7 +38794,7 @@
         <v>45995</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38867,7 +38867,7 @@
         <v>45789</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38940,7 +38940,7 @@
         <v>45923</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39013,7 +39013,7 @@
         <v>44986</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39086,7 +39086,7 @@
         <v>45952</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39159,7 +39159,7 @@
         <v>45517</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39232,7 +39232,7 @@
         <v>45631</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39305,7 +39305,7 @@
         <v>45183</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39378,7 +39378,7 @@
         <v>45946</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39451,7 +39451,7 @@
         <v>44977</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39524,7 +39524,7 @@
         <v>45953</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39597,7 +39597,7 @@
         <v>45114</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39670,7 +39670,7 @@
         <v>45114</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39743,7 +39743,7 @@
         <v>45296</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39816,7 +39816,7 @@
         <v>45181</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39889,7 +39889,7 @@
         <v>45090</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39962,7 +39962,7 @@
         <v>45964</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40035,7 +40035,7 @@
         <v>44867</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40108,7 +40108,7 @@
         <v>45597</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40181,7 +40181,7 @@
         <v>45401</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40254,7 +40254,7 @@
         <v>45924</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40327,7 +40327,7 @@
         <v>45685</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40400,7 +40400,7 @@
         <v>44972</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40473,7 +40473,7 @@
         <v>45623</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40546,7 +40546,7 @@
         <v>45971</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40619,7 +40619,7 @@
         <v>44928</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40692,7 +40692,7 @@
         <v>45568</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40765,7 +40765,7 @@
         <v>46162</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -40838,7 +40838,7 @@
         <v>46163</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40911,7 +40911,7 @@
         <v>46163</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -40984,7 +40984,7 @@
         <v>45780</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41057,7 +41057,7 @@
         <v>46163</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41130,7 +41130,7 @@
         <v>46163</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41203,7 +41203,7 @@
         <v>45061</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41276,7 +41276,7 @@
         <v>45973</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41349,7 +41349,7 @@
         <v>46163</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41422,7 +41422,7 @@
         <v>46162</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41495,7 +41495,7 @@
         <v>46163</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41568,7 +41568,7 @@
         <v>44904</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -41641,7 +41641,7 @@
         <v>44904</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -41714,7 +41714,7 @@
         <v>45719</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -41787,7 +41787,7 @@
         <v>45420</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -41860,7 +41860,7 @@
         <v>45504</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -41933,7 +41933,7 @@
         <v>45583</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42011,7 +42011,7 @@
         <v>45979</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42084,7 +42084,7 @@
         <v>45979</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42157,7 +42157,7 @@
         <v>45753</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42230,7 +42230,7 @@
         <v>46162</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42303,7 +42303,7 @@
         <v>45980</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42376,7 +42376,7 @@
         <v>45617</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42449,7 +42449,7 @@
         <v>44670</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42522,7 +42522,7 @@
         <v>45324</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42595,7 +42595,7 @@
         <v>45029</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42668,7 +42668,7 @@
         <v>44651</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -42741,7 +42741,7 @@
         <v>45533</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -42814,7 +42814,7 @@
         <v>46167</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -42887,7 +42887,7 @@
         <v>45147</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -42960,7 +42960,7 @@
         <v>45392</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43038,7 +43038,7 @@
         <v>45392</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43111,7 +43111,7 @@
         <v>45812</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43184,7 +43184,7 @@
         <v>45103</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43257,7 +43257,7 @@
         <v>45103</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43330,7 +43330,7 @@
         <v>45103</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -43403,7 +43403,7 @@
         <v>45247</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -43476,7 +43476,7 @@
         <v>45559</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -43549,7 +43549,7 @@
         <v>45579</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -43622,7 +43622,7 @@
         <v>46168</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -43695,7 +43695,7 @@
         <v>45427</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -43768,7 +43768,7 @@
         <v>45250</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -43841,7 +43841,7 @@
         <v>45733</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -43914,7 +43914,7 @@
         <v>45993</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -43987,7 +43987,7 @@
         <v>45993</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44060,7 +44060,7 @@
         <v>44552</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44133,7 +44133,7 @@
         <v>45988</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44206,7 +44206,7 @@
         <v>45180</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44279,7 +44279,7 @@
         <v>45580</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -44352,7 +44352,7 @@
         <v>45999</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -44425,7 +44425,7 @@
         <v>44761</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -44503,7 +44503,7 @@
         <v>46168</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -44576,7 +44576,7 @@
         <v>45933</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -44649,7 +44649,7 @@
         <v>45477</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -44727,7 +44727,7 @@
         <v>46000</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -44800,7 +44800,7 @@
         <v>45559</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -44873,7 +44873,7 @@
         <v>45153</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -44946,7 +44946,7 @@
         <v>45421</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45019,7 +45019,7 @@
         <v>46001</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45092,7 +45092,7 @@
         <v>46100</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45165,7 +45165,7 @@
         <v>46170</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -45238,7 +45238,7 @@
         <v>44811</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -45311,7 +45311,7 @@
         <v>46171</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -45384,7 +45384,7 @@
         <v>45216</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -45457,7 +45457,7 @@
         <v>45113</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -45530,7 +45530,7 @@
         <v>45113</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -45603,7 +45603,7 @@
         <v>46007</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -45676,7 +45676,7 @@
         <v>44896</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -45749,7 +45749,7 @@
         <v>46008</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -45822,7 +45822,7 @@
         <v>46010</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -45895,7 +45895,7 @@
         <v>46010</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -45968,7 +45968,7 @@
         <v>45538</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46046,7 +46046,7 @@
         <v>46010</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -46119,7 +46119,7 @@
         <v>44903</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -46192,7 +46192,7 @@
         <v>44502</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -46265,7 +46265,7 @@
         <v>46112</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -46338,7 +46338,7 @@
         <v>46171</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -46411,7 +46411,7 @@
         <v>45538</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -46484,7 +46484,7 @@
         <v>46010</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -46557,7 +46557,7 @@
         <v>45301</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -46630,7 +46630,7 @@
         <v>46171</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -46703,7 +46703,7 @@
         <v>44595</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -46776,7 +46776,7 @@
         <v>45330</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -46854,7 +46854,7 @@
         <v>45250</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -46927,7 +46927,7 @@
         <v>46019</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47000,7 +47000,7 @@
         <v>44592</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47073,7 +47073,7 @@
         <v>45722</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -47146,7 +47146,7 @@
         <v>46019</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -47219,7 +47219,7 @@
         <v>45557</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -47292,7 +47292,7 @@
         <v>46029</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -47365,7 +47365,7 @@
         <v>46029</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -47438,7 +47438,7 @@
         <v>45432</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -47511,7 +47511,7 @@
         <v>44686</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -47584,7 +47584,7 @@
         <v>46031</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -47662,7 +47662,7 @@
         <v>46031</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -47740,7 +47740,7 @@
         <v>46035</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -47818,7 +47818,7 @@
         <v>45400</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -47891,7 +47891,7 @@
         <v>44705</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -47964,7 +47964,7 @@
         <v>45315</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48037,7 +48037,7 @@
         <v>46035</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -48115,7 +48115,7 @@
         <v>46035</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -48193,7 +48193,7 @@
         <v>46036</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -48266,7 +48266,7 @@
         <v>46036</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -48339,7 +48339,7 @@
         <v>46036</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -48412,7 +48412,7 @@
         <v>46134</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -48485,7 +48485,7 @@
         <v>46134</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -48558,7 +48558,7 @@
         <v>45921</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -48631,7 +48631,7 @@
         <v>46041</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -48704,7 +48704,7 @@
         <v>45065</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -48777,7 +48777,7 @@
         <v>44743</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -48850,7 +48850,7 @@
         <v>45121</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -48923,7 +48923,7 @@
         <v>44831</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -48996,7 +48996,7 @@
         <v>45302</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -49069,7 +49069,7 @@
         <v>45573</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -49142,7 +49142,7 @@
         <v>44676</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -49220,7 +49220,7 @@
         <v>46043</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -49293,7 +49293,7 @@
         <v>46045</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -49366,7 +49366,7 @@
         <v>45036</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -49439,7 +49439,7 @@
         <v>46045</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -49512,7 +49512,7 @@
         <v>45302</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -49585,7 +49585,7 @@
         <v>46134</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -49658,7 +49658,7 @@
         <v>46049</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -49731,7 +49731,7 @@
         <v>46048</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -49804,7 +49804,7 @@
         <v>45632</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -49877,7 +49877,7 @@
         <v>45188</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -49950,7 +49950,7 @@
         <v>45552</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -50023,7 +50023,7 @@
         <v>46049</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -50096,7 +50096,7 @@
         <v>46170</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -50169,7 +50169,7 @@
         <v>45181</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -50242,7 +50242,7 @@
         <v>46049</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -50315,7 +50315,7 @@
         <v>46051</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -50388,7 +50388,7 @@
         <v>45071</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -50466,7 +50466,7 @@
         <v>45558</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -50539,7 +50539,7 @@
         <v>45594</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -50617,7 +50617,7 @@
         <v>45594</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -50695,7 +50695,7 @@
         <v>45594</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -50773,7 +50773,7 @@
         <v>46056</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -50846,7 +50846,7 @@
         <v>46183</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -50919,7 +50919,7 @@
         <v>46183</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -50992,7 +50992,7 @@
         <v>46183</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -51065,7 +51065,7 @@
         <v>46056</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -51138,7 +51138,7 @@
         <v>46057</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -51211,7 +51211,7 @@
         <v>45693</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -51284,7 +51284,7 @@
         <v>46183</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -51357,7 +51357,7 @@
         <v>46059</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -51430,7 +51430,7 @@
         <v>46059</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -51503,7 +51503,7 @@
         <v>46059</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -51576,7 +51576,7 @@
         <v>45764</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -51649,7 +51649,7 @@
         <v>45644</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -51722,7 +51722,7 @@
         <v>45056</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -51795,7 +51795,7 @@
         <v>45037</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -51868,7 +51868,7 @@
         <v>45037</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -51941,7 +51941,7 @@
         <v>45581</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -52014,7 +52014,7 @@
         <v>46061</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -52087,7 +52087,7 @@
         <v>44609</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -52160,7 +52160,7 @@
         <v>44652</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -52233,7 +52233,7 @@
         <v>44956</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -52306,7 +52306,7 @@
         <v>45300</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -52379,7 +52379,7 @@
         <v>45211</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -52452,7 +52452,7 @@
         <v>46188</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -52525,7 +52525,7 @@
         <v>46073</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -52598,7 +52598,7 @@
         <v>45210</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -52671,7 +52671,7 @@
         <v>46073</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -52744,7 +52744,7 @@
         <v>46072</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -52817,7 +52817,7 @@
         <v>45533</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -52890,7 +52890,7 @@
         <v>44986</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -52963,7 +52963,7 @@
         <v>44741</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -53036,7 +53036,7 @@
         <v>45338</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -53109,7 +53109,7 @@
         <v>44960</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -53182,7 +53182,7 @@
         <v>44843</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -53255,7 +53255,7 @@
         <v>46075</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -53328,7 +53328,7 @@
         <v>46079</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -53401,7 +53401,7 @@
         <v>46079</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -53474,7 +53474,7 @@
         <v>45665</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -53547,7 +53547,7 @@
         <v>46084</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -53620,7 +53620,7 @@
         <v>46083</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -53693,7 +53693,7 @@
         <v>44874</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -53766,7 +53766,7 @@
         <v>44874</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -53839,7 +53839,7 @@
         <v>46083</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -53912,7 +53912,7 @@
         <v>46083</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -53985,7 +53985,7 @@
         <v>46083</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -54058,7 +54058,7 @@
         <v>46083</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -54131,7 +54131,7 @@
         <v>44963</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -54204,7 +54204,7 @@
         <v>44600</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -54282,7 +54282,7 @@
         <v>46189</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -54355,7 +54355,7 @@
         <v>45412</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -54428,7 +54428,7 @@
         <v>45412</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -54501,7 +54501,7 @@
         <v>46190</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -54574,7 +54574,7 @@
         <v>46087</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -54647,7 +54647,7 @@
         <v>45757</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -54720,7 +54720,7 @@
         <v>45316</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -54793,7 +54793,7 @@
         <v>45316</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -54866,7 +54866,7 @@
         <v>46191</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -54939,7 +54939,7 @@
         <v>45551</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -55012,7 +55012,7 @@
         <v>45924</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -55085,7 +55085,7 @@
         <v>46108</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -55158,7 +55158,7 @@
         <v>44896</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -55231,7 +55231,7 @@
         <v>45601</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -55304,7 +55304,7 @@
         <v>46191</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -55377,7 +55377,7 @@
         <v>45679</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -55450,7 +55450,7 @@
         <v>45316</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -55523,7 +55523,7 @@
         <v>46100</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -55596,7 +55596,7 @@
         <v>46099</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -55669,7 +55669,7 @@
         <v>46100</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -55742,7 +55742,7 @@
         <v>46100</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -55815,7 +55815,7 @@
         <v>45140</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -55888,7 +55888,7 @@
         <v>45446</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -55966,7 +55966,7 @@
         <v>45392</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -56044,7 +56044,7 @@
         <v>45166</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -56117,7 +56117,7 @@
         <v>45345</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -56190,7 +56190,7 @@
         <v>44915</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -56263,7 +56263,7 @@
         <v>44972</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -56336,7 +56336,7 @@
         <v>44998</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -56409,7 +56409,7 @@
         <v>46198</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -56482,7 +56482,7 @@
         <v>45468</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -56555,7 +56555,7 @@
         <v>46198</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -56628,7 +56628,7 @@
         <v>46107</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -56701,7 +56701,7 @@
         <v>46198</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -56774,7 +56774,7 @@
         <v>46108</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -56847,7 +56847,7 @@
         <v>44880</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -56920,7 +56920,7 @@
         <v>46112</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -56993,7 +56993,7 @@
         <v>44769</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -57071,7 +57071,7 @@
         <v>45676</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -57149,7 +57149,7 @@
         <v>44769</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -57227,7 +57227,7 @@
         <v>46112</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -57300,7 +57300,7 @@
         <v>46198</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -57373,7 +57373,7 @@
         <v>45127</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -57446,7 +57446,7 @@
         <v>45288</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -57519,7 +57519,7 @@
         <v>45022</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -57592,7 +57592,7 @@
         <v>44869</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -57665,7 +57665,7 @@
         <v>46113</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -57738,7 +57738,7 @@
         <v>45594</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -57816,7 +57816,7 @@
         <v>45594</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -57894,7 +57894,7 @@
         <v>46119</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -57967,7 +57967,7 @@
         <v>44998</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -58040,7 +58040,7 @@
         <v>45217</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -58113,7 +58113,7 @@
         <v>46199</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -58186,7 +58186,7 @@
         <v>45085</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -58259,7 +58259,7 @@
         <v>44609</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -58332,7 +58332,7 @@
         <v>46199</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -58405,7 +58405,7 @@
         <v>45722</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -58478,7 +58478,7 @@
         <v>45560</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -58551,7 +58551,7 @@
         <v>46129</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -58624,7 +58624,7 @@
         <v>44831</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -58697,7 +58697,7 @@
         <v>45611</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -58770,7 +58770,7 @@
         <v>45679</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -58843,7 +58843,7 @@
         <v>45679</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -58916,7 +58916,7 @@
         <v>45030</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -58989,7 +58989,7 @@
         <v>45881</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -59062,7 +59062,7 @@
         <v>45300</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -59135,7 +59135,7 @@
         <v>44774</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -59208,7 +59208,7 @@
         <v>45128</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -59281,7 +59281,7 @@
         <v>45128</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -59354,7 +59354,7 @@
         <v>45111</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -59427,7 +59427,7 @@
         <v>46199</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -59500,7 +59500,7 @@
         <v>45541</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -59573,7 +59573,7 @@
         <v>45677</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -59646,7 +59646,7 @@
         <v>45638</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -59719,7 +59719,7 @@
         <v>45582</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -59792,7 +59792,7 @@
         <v>46199</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -59865,7 +59865,7 @@
         <v>45386</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -59938,7 +59938,7 @@
         <v>45923</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -60011,7 +60011,7 @@
         <v>45165</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -60084,7 +60084,7 @@
         <v>45555</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -60157,7 +60157,7 @@
         <v>45939</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -60230,7 +60230,7 @@
         <v>45141</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -60303,7 +60303,7 @@
         <v>45141</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -60376,7 +60376,7 @@
         <v>46206</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -60454,7 +60454,7 @@
         <v>44496</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -60527,7 +60527,7 @@
         <v>45894</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -60600,7 +60600,7 @@
         <v>45923</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -60673,7 +60673,7 @@
         <v>45579</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -60746,7 +60746,7 @@
         <v>46205</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -60819,7 +60819,7 @@
         <v>45754</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -60892,7 +60892,7 @@
         <v>46205</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -60965,7 +60965,7 @@
         <v>45754</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -61038,7 +61038,7 @@
         <v>46210</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -61116,7 +61116,7 @@
         <v>45012</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -61189,7 +61189,7 @@
         <v>46210</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -61267,7 +61267,7 @@
         <v>45222</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -61340,7 +61340,7 @@
         <v>45127</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -61413,7 +61413,7 @@
         <v>44867</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -61486,7 +61486,7 @@
         <v>45552</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -61559,7 +61559,7 @@
         <v>45247</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -61632,7 +61632,7 @@
         <v>44922</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -61705,7 +61705,7 @@
         <v>45048</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -61778,7 +61778,7 @@
         <v>45205</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -61851,7 +61851,7 @@
         <v>46170</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -61924,7 +61924,7 @@
         <v>44501</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -61997,7 +61997,7 @@
         <v>44995</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -62070,7 +62070,7 @@
         <v>44876</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -62148,7 +62148,7 @@
         <v>45495</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -62221,7 +62221,7 @@
         <v>44963</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -62294,7 +62294,7 @@
         <v>45106</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -62367,7 +62367,7 @@
         <v>45385</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -62445,7 +62445,7 @@
         <v>45385</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -62523,7 +62523,7 @@
         <v>44900</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -62596,7 +62596,7 @@
         <v>45199</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -62669,7 +62669,7 @@
         <v>45070</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -62742,7 +62742,7 @@
         <v>44494</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -62815,7 +62815,7 @@
         <v>45754</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -62888,7 +62888,7 @@
         <v>45224</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -62961,7 +62961,7 @@
         <v>46272</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -63034,7 +63034,7 @@
         <v>46272</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -63107,7 +63107,7 @@
         <v>45161</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -63180,7 +63180,7 @@
         <v>44711</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -63253,7 +63253,7 @@
         <v>44782</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -63331,7 +63331,7 @@
         <v>45572</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -63404,7 +63404,7 @@
         <v>45204</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -63477,7 +63477,7 @@
         <v>46232</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -63550,7 +63550,7 @@
         <v>45443</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -63623,7 +63623,7 @@
         <v>45726</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -63696,7 +63696,7 @@
         <v>45139</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -63769,7 +63769,7 @@
         <v>45373</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -63842,7 +63842,7 @@
         <v>45369</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -63915,7 +63915,7 @@
         <v>46232</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -63988,7 +63988,7 @@
         <v>45127</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -64061,7 +64061,7 @@
         <v>45127</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -64134,7 +64134,7 @@
         <v>45372</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -64207,7 +64207,7 @@
         <v>45219</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -64280,7 +64280,7 @@
         <v>45594</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -64358,7 +64358,7 @@
         <v>45594</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -64436,7 +64436,7 @@
         <v>44690</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -64509,7 +64509,7 @@
         <v>46237</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -64582,7 +64582,7 @@
         <v>45385</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -64660,7 +64660,7 @@
         <v>46276</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -64733,7 +64733,7 @@
         <v>45702</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -64806,7 +64806,7 @@
         <v>45000</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -64879,7 +64879,7 @@
         <v>45446</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -64952,7 +64952,7 @@
         <v>44858</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -65025,7 +65025,7 @@
         <v>46276</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -65098,7 +65098,7 @@
         <v>45594</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -65176,7 +65176,7 @@
         <v>45594</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -65254,7 +65254,7 @@
         <v>45594</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -65332,7 +65332,7 @@
         <v>45594</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -65410,7 +65410,7 @@
         <v>45594</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -65488,7 +65488,7 @@
         <v>45302</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -65561,7 +65561,7 @@
         <v>45302</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -65634,7 +65634,7 @@
         <v>44959</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -65707,7 +65707,7 @@
         <v>44894</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -65780,7 +65780,7 @@
         <v>45267</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -65853,7 +65853,7 @@
         <v>45198</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -65926,7 +65926,7 @@
         <v>44651</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -65999,7 +65999,7 @@
         <v>46237</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -66072,7 +66072,7 @@
         <v>46279</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -66145,7 +66145,7 @@
         <v>46279</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -66218,7 +66218,7 @@
         <v>46281</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -66291,7 +66291,7 @@
         <v>45509</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -66364,7 +66364,7 @@
         <v>45447</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -66437,7 +66437,7 @@
         <v>45378</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -66510,7 +66510,7 @@
         <v>45495</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -66583,7 +66583,7 @@
         <v>45446</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -66656,7 +66656,7 @@
         <v>45008</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -66729,7 +66729,7 @@
         <v>44739</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -66802,7 +66802,7 @@
         <v>45519</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -66875,7 +66875,7 @@
         <v>45176</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -66948,7 +66948,7 @@
         <v>45176</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -67021,7 +67021,7 @@
         <v>46239</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -67094,7 +67094,7 @@
         <v>45644</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -67167,7 +67167,7 @@
         <v>44812</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -67240,7 +67240,7 @@
         <v>44992</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -67313,7 +67313,7 @@
         <v>45139</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -67386,7 +67386,7 @@
         <v>46244</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -67459,7 +67459,7 @@
         <v>45244</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -67532,7 +67532,7 @@
         <v>45232</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -67605,7 +67605,7 @@
         <v>46244</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -67683,7 +67683,7 @@
         <v>46244</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -67761,7 +67761,7 @@
         <v>46244</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -67834,7 +67834,7 @@
         <v>45705</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -67912,7 +67912,7 @@
         <v>45078</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -67990,7 +67990,7 @@
         <v>45737</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -68063,7 +68063,7 @@
         <v>46244</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -68141,7 +68141,7 @@
         <v>46244</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -68219,7 +68219,7 @@
         <v>45108</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -68292,7 +68292,7 @@
         <v>46244</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -68370,7 +68370,7 @@
         <v>44749</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -68443,7 +68443,7 @@
         <v>46244</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -68521,7 +68521,7 @@
         <v>45468</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -68594,7 +68594,7 @@
         <v>45127</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -68667,7 +68667,7 @@
         <v>46288</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -68740,7 +68740,7 @@
         <v>46245</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -68813,7 +68813,7 @@
         <v>45273</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -68886,7 +68886,7 @@
         <v>46245</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -68959,7 +68959,7 @@
         <v>45392</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -69037,7 +69037,7 @@
         <v>45608</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -69110,7 +69110,7 @@
         <v>44894</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -69183,7 +69183,7 @@
         <v>46289</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -69256,7 +69256,7 @@
         <v>46289</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -69329,7 +69329,7 @@
         <v>46288</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -69402,7 +69402,7 @@
         <v>44677</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -69475,7 +69475,7 @@
         <v>45089</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -69548,7 +69548,7 @@
         <v>45236</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -69621,7 +69621,7 @@
         <v>45392</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -69699,7 +69699,7 @@
         <v>46246</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -69777,7 +69777,7 @@
         <v>45342</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -69850,7 +69850,7 @@
         <v>45189</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -69923,7 +69923,7 @@
         <v>45189</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -69996,7 +69996,7 @@
         <v>44909</v>
       </c>
       <c r="E900" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -70074,7 +70074,7 @@
         <v>45190</v>
       </c>
       <c r="E901" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>
@@ -70147,7 +70147,7 @@
         <v>45714</v>
       </c>
       <c r="E902" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F902" t="inlineStr">
         <is>
@@ -70220,7 +70220,7 @@
         <v>44599</v>
       </c>
       <c r="E903" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F903" t="inlineStr">
         <is>
@@ -70293,7 +70293,7 @@
         <v>45614</v>
       </c>
       <c r="E904" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F904" t="inlineStr">
         <is>
@@ -70366,7 +70366,7 @@
         <v>46056</v>
       </c>
       <c r="E905" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F905" t="inlineStr">
         <is>
@@ -70439,7 +70439,7 @@
         <v>45692</v>
       </c>
       <c r="E906" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F906" t="inlineStr">
         <is>
@@ -70512,7 +70512,7 @@
         <v>45384</v>
       </c>
       <c r="E907" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F907" t="inlineStr">
         <is>
@@ -70585,7 +70585,7 @@
         <v>45448</v>
       </c>
       <c r="E908" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F908" t="inlineStr">
         <is>
@@ -70658,7 +70658,7 @@
         <v>45294</v>
       </c>
       <c r="E909" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F909" t="inlineStr">
         <is>
@@ -70731,7 +70731,7 @@
         <v>45219</v>
       </c>
       <c r="E910" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F910" t="inlineStr">
         <is>
@@ -70804,7 +70804,7 @@
         <v>45147</v>
       </c>
       <c r="E911" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F911" t="inlineStr">
         <is>
@@ -70877,7 +70877,7 @@
         <v>44536</v>
       </c>
       <c r="E912" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F912" t="inlineStr">
         <is>
@@ -70950,7 +70950,7 @@
         <v>46021</v>
       </c>
       <c r="E913" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F913" t="inlineStr">
         <is>
@@ -71023,7 +71023,7 @@
         <v>44732</v>
       </c>
       <c r="E914" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F914" t="inlineStr">
         <is>
@@ -71096,7 +71096,7 @@
         <v>46295</v>
       </c>
       <c r="E915" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F915" t="inlineStr">
         <is>
@@ -71174,7 +71174,7 @@
         <v>46294</v>
       </c>
       <c r="E916" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F916" t="inlineStr">
         <is>
@@ -71247,7 +71247,7 @@
         <v>46252</v>
       </c>
       <c r="E917" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F917" t="inlineStr">
         <is>
@@ -71320,7 +71320,7 @@
         <v>45198</v>
       </c>
       <c r="E918" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F918" t="inlineStr">
         <is>
@@ -71393,7 +71393,7 @@
         <v>46294</v>
       </c>
       <c r="E919" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F919" t="inlineStr">
         <is>
@@ -71466,7 +71466,7 @@
         <v>46294</v>
       </c>
       <c r="E920" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F920" t="inlineStr">
         <is>
@@ -71539,7 +71539,7 @@
         <v>46294</v>
       </c>
       <c r="E921" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F921" t="inlineStr">
         <is>
@@ -71612,7 +71612,7 @@
         <v>46294</v>
       </c>
       <c r="E922" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F922" t="inlineStr">
         <is>
@@ -71685,7 +71685,7 @@
         <v>46294</v>
       </c>
       <c r="E923" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F923" t="inlineStr">
         <is>
@@ -71758,7 +71758,7 @@
         <v>46253</v>
       </c>
       <c r="E924" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F924" t="inlineStr">
         <is>
@@ -71831,7 +71831,7 @@
         <v>46237</v>
       </c>
       <c r="E925" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F925" t="inlineStr">
         <is>
@@ -71904,7 +71904,7 @@
         <v>45594</v>
       </c>
       <c r="E926" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F926" t="inlineStr">
         <is>
@@ -71982,7 +71982,7 @@
         <v>45644</v>
       </c>
       <c r="E927" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F927" t="inlineStr">
         <is>
@@ -72055,7 +72055,7 @@
         <v>45014</v>
       </c>
       <c r="E928" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F928" t="inlineStr">
         <is>
@@ -72133,7 +72133,7 @@
         <v>44897</v>
       </c>
       <c r="E929" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F929" t="inlineStr">
         <is>
@@ -72206,7 +72206,7 @@
         <v>46296</v>
       </c>
       <c r="E930" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F930" t="inlineStr">
         <is>
@@ -72279,7 +72279,7 @@
         <v>46296</v>
       </c>
       <c r="E931" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F931" t="inlineStr">
         <is>
@@ -72352,7 +72352,7 @@
         <v>46296</v>
       </c>
       <c r="E932" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F932" t="inlineStr">
         <is>
@@ -72425,7 +72425,7 @@
         <v>45014</v>
       </c>
       <c r="E933" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F933" t="inlineStr">
         <is>
@@ -72498,7 +72498,7 @@
         <v>45743</v>
       </c>
       <c r="E934" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F934" t="inlineStr">
         <is>
@@ -72571,7 +72571,7 @@
         <v>46296</v>
       </c>
       <c r="E935" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F935" t="inlineStr">
         <is>
@@ -72644,7 +72644,7 @@
         <v>46296</v>
       </c>
       <c r="E936" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F936" t="inlineStr">
         <is>
@@ -72717,7 +72717,7 @@
         <v>46252</v>
       </c>
       <c r="E937" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F937" t="inlineStr">
         <is>
@@ -72790,7 +72790,7 @@
         <v>46296</v>
       </c>
       <c r="E938" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F938" t="inlineStr">
         <is>
@@ -72863,7 +72863,7 @@
         <v>46296</v>
       </c>
       <c r="E939" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F939" t="inlineStr">
         <is>
@@ -72936,7 +72936,7 @@
         <v>45534</v>
       </c>
       <c r="E940" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F940" t="inlineStr">
         <is>
@@ -73009,7 +73009,7 @@
         <v>45702</v>
       </c>
       <c r="E941" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F941" t="inlineStr">
         <is>
@@ -73082,7 +73082,7 @@
         <v>45219</v>
       </c>
       <c r="E942" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F942" t="inlineStr">
         <is>
@@ -73155,7 +73155,7 @@
         <v>44676</v>
       </c>
       <c r="E943" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F943" t="inlineStr">
         <is>
@@ -73233,7 +73233,7 @@
         <v>45121</v>
       </c>
       <c r="E944" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F944" t="inlineStr">
         <is>
@@ -73306,7 +73306,7 @@
         <v>45121</v>
       </c>
       <c r="E945" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F945" t="inlineStr">
         <is>
@@ -73379,7 +73379,7 @@
         <v>45121</v>
       </c>
       <c r="E946" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F946" t="inlineStr">
         <is>
@@ -73452,7 +73452,7 @@
         <v>45440</v>
       </c>
       <c r="E947" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F947" t="inlineStr">
         <is>
@@ -73525,7 +73525,7 @@
         <v>45645</v>
       </c>
       <c r="E948" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F948" t="inlineStr">
         <is>
@@ -73598,7 +73598,7 @@
         <v>45692</v>
       </c>
       <c r="E949" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F949" t="inlineStr">
         <is>
@@ -73671,7 +73671,7 @@
         <v>45028</v>
       </c>
       <c r="E950" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F950" t="inlineStr">
         <is>
@@ -73744,7 +73744,7 @@
         <v>45777</v>
       </c>
       <c r="E951" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F951" t="inlineStr">
         <is>
@@ -73822,7 +73822,7 @@
         <v>45777</v>
       </c>
       <c r="E952" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F952" t="inlineStr">
         <is>
@@ -73900,7 +73900,7 @@
         <v>45194</v>
       </c>
       <c r="E953" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F953" t="inlineStr">
         <is>
@@ -73973,7 +73973,7 @@
         <v>45547</v>
       </c>
       <c r="E954" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F954" t="inlineStr">
         <is>
@@ -74046,7 +74046,7 @@
         <v>45777</v>
       </c>
       <c r="E955" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F955" t="inlineStr">
         <is>
@@ -74124,7 +74124,7 @@
         <v>45519</v>
       </c>
       <c r="E956" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F956" t="inlineStr">
         <is>
@@ -74197,7 +74197,7 @@
         <v>46301</v>
       </c>
       <c r="E957" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F957" t="inlineStr">
         <is>
@@ -74270,7 +74270,7 @@
         <v>45780</v>
       </c>
       <c r="E958" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F958" t="inlineStr">
         <is>
@@ -74343,7 +74343,7 @@
         <v>45780</v>
       </c>
       <c r="E959" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F959" t="inlineStr">
         <is>
@@ -74416,7 +74416,7 @@
         <v>45478</v>
       </c>
       <c r="E960" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F960" t="inlineStr">
         <is>
@@ -74489,7 +74489,7 @@
         <v>45546</v>
       </c>
       <c r="E961" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F961" t="inlineStr">
         <is>
@@ -74562,7 +74562,7 @@
         <v>45783</v>
       </c>
       <c r="E962" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F962" t="inlineStr">
         <is>
@@ -74635,7 +74635,7 @@
         <v>45782</v>
       </c>
       <c r="E963" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F963" t="inlineStr">
         <is>
@@ -74708,7 +74708,7 @@
         <v>46300</v>
       </c>
       <c r="E964" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F964" t="inlineStr">
         <is>
@@ -74781,7 +74781,7 @@
         <v>46199</v>
       </c>
       <c r="E965" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F965" t="inlineStr">
         <is>
@@ -74854,7 +74854,7 @@
         <v>45534</v>
       </c>
       <c r="E966" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F966" t="inlineStr">
         <is>
@@ -74927,7 +74927,7 @@
         <v>45108</v>
       </c>
       <c r="E967" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F967" t="inlineStr">
         <is>
@@ -75000,7 +75000,7 @@
         <v>46300</v>
       </c>
       <c r="E968" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F968" t="inlineStr">
         <is>
@@ -75073,7 +75073,7 @@
         <v>44781</v>
       </c>
       <c r="E969" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F969" t="inlineStr">
         <is>
@@ -75151,7 +75151,7 @@
         <v>46258</v>
       </c>
       <c r="E970" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F970" t="inlineStr">
         <is>
@@ -75224,7 +75224,7 @@
         <v>45642</v>
       </c>
       <c r="E971" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F971" t="inlineStr">
         <is>
@@ -75297,7 +75297,7 @@
         <v>45614</v>
       </c>
       <c r="E972" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F972" t="inlineStr">
         <is>
@@ -75370,7 +75370,7 @@
         <v>45716</v>
       </c>
       <c r="E973" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F973" t="inlineStr">
         <is>
@@ -75443,7 +75443,7 @@
         <v>45608</v>
       </c>
       <c r="E974" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F974" t="inlineStr">
         <is>
@@ -75516,7 +75516,7 @@
         <v>46260</v>
       </c>
       <c r="E975" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F975" t="inlineStr">
         <is>
@@ -75589,7 +75589,7 @@
         <v>46183</v>
       </c>
       <c r="E976" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F976" t="inlineStr">
         <is>
@@ -75662,7 +75662,7 @@
         <v>45716</v>
       </c>
       <c r="E977" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F977" t="inlineStr">
         <is>
@@ -75735,7 +75735,7 @@
         <v>45791</v>
       </c>
       <c r="E978" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F978" t="inlineStr">
         <is>
@@ -75808,7 +75808,7 @@
         <v>45916</v>
       </c>
       <c r="E979" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F979" t="inlineStr">
         <is>
@@ -75881,7 +75881,7 @@
         <v>46261</v>
       </c>
       <c r="E980" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F980" t="inlineStr">
         <is>
@@ -75954,7 +75954,7 @@
         <v>46183</v>
       </c>
       <c r="E981" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F981" t="inlineStr">
         <is>
@@ -76027,7 +76027,7 @@
         <v>46307</v>
       </c>
       <c r="E982" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F982" t="inlineStr">
         <is>
@@ -76100,7 +76100,7 @@
         <v>46307</v>
       </c>
       <c r="E983" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F983" t="inlineStr">
         <is>
@@ -76173,7 +76173,7 @@
         <v>45796</v>
       </c>
       <c r="E984" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F984" t="inlineStr">
         <is>
@@ -76246,7 +76246,7 @@
         <v>44824</v>
       </c>
       <c r="E985" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F985" t="inlineStr">
         <is>
@@ -76319,7 +76319,7 @@
         <v>45574</v>
       </c>
       <c r="E986" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F986" t="inlineStr">
         <is>
@@ -76392,7 +76392,7 @@
         <v>46262</v>
       </c>
       <c r="E987" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F987" t="inlineStr">
         <is>
@@ -76465,7 +76465,7 @@
         <v>46304</v>
       </c>
       <c r="E988" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F988" t="inlineStr">
         <is>
@@ -76538,7 +76538,7 @@
         <v>46307</v>
       </c>
       <c r="E989" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F989" t="inlineStr">
         <is>
@@ -76611,7 +76611,7 @@
         <v>45764</v>
       </c>
       <c r="E990" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F990" t="inlineStr">
         <is>
@@ -76684,7 +76684,7 @@
         <v>46304</v>
       </c>
       <c r="E991" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F991" t="inlineStr">
         <is>
@@ -76757,7 +76757,7 @@
         <v>45803</v>
       </c>
       <c r="E992" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F992" t="inlineStr">
         <is>
@@ -76830,7 +76830,7 @@
         <v>46216</v>
       </c>
       <c r="E993" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F993" t="inlineStr">
         <is>
@@ -76903,7 +76903,7 @@
         <v>46216</v>
       </c>
       <c r="E994" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F994" t="inlineStr">
         <is>
@@ -76976,7 +76976,7 @@
         <v>46308</v>
       </c>
       <c r="E995" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F995" t="inlineStr">
         <is>
@@ -77049,7 +77049,7 @@
         <v>45665</v>
       </c>
       <c r="E996" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F996" t="inlineStr">
         <is>
@@ -77122,7 +77122,7 @@
         <v>45749</v>
       </c>
       <c r="E997" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F997" t="inlineStr">
         <is>
@@ -77195,7 +77195,7 @@
         <v>45805</v>
       </c>
       <c r="E998" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F998" t="inlineStr">
         <is>
@@ -77268,7 +77268,7 @@
         <v>46230</v>
       </c>
       <c r="E999" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F999" t="inlineStr">
         <is>
@@ -77341,7 +77341,7 @@
         <v>45763</v>
       </c>
       <c r="E1000" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1000" t="inlineStr">
         <is>
@@ -77414,7 +77414,7 @@
         <v>45447</v>
       </c>
       <c r="E1001" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1001" t="inlineStr">
         <is>
@@ -77487,7 +77487,7 @@
         <v>46216</v>
       </c>
       <c r="E1002" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1002" t="inlineStr">
         <is>
@@ -77560,7 +77560,7 @@
         <v>46245</v>
       </c>
       <c r="E1003" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1003" t="inlineStr">
         <is>
@@ -77633,7 +77633,7 @@
         <v>45817</v>
       </c>
       <c r="E1004" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1004" t="inlineStr">
         <is>
@@ -77706,7 +77706,7 @@
         <v>45769</v>
       </c>
       <c r="E1005" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1005" t="inlineStr">
         <is>
@@ -77779,7 +77779,7 @@
         <v>45820</v>
       </c>
       <c r="E1006" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1006" t="inlineStr">
         <is>
@@ -77852,7 +77852,7 @@
         <v>45820</v>
       </c>
       <c r="E1007" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1007" t="inlineStr">
         <is>
@@ -77925,7 +77925,7 @@
         <v>45818</v>
       </c>
       <c r="E1008" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1008" t="inlineStr">
         <is>
@@ -77998,7 +77998,7 @@
         <v>45825</v>
       </c>
       <c r="E1009" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1009" t="inlineStr">
         <is>
@@ -78071,7 +78071,7 @@
         <v>45824</v>
       </c>
       <c r="E1010" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1010" t="inlineStr">
         <is>
@@ -78144,7 +78144,7 @@
         <v>45824</v>
       </c>
       <c r="E1011" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1011" t="inlineStr">
         <is>
@@ -78217,7 +78217,7 @@
         <v>46269</v>
       </c>
       <c r="E1012" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1012" t="inlineStr">
         <is>
@@ -78290,7 +78290,7 @@
         <v>45827</v>
       </c>
       <c r="E1013" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1013" t="inlineStr">
         <is>
@@ -78363,7 +78363,7 @@
         <v>45831</v>
       </c>
       <c r="E1014" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1014" t="inlineStr">
         <is>
@@ -78436,7 +78436,7 @@
         <v>45831</v>
       </c>
       <c r="E1015" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1015" t="inlineStr">
         <is>
@@ -78509,7 +78509,7 @@
         <v>45832</v>
       </c>
       <c r="E1016" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1016" t="inlineStr">
         <is>
@@ -78582,7 +78582,7 @@
         <v>45805</v>
       </c>
       <c r="E1017" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1017" t="inlineStr">
         <is>
@@ -78655,7 +78655,7 @@
         <v>45835</v>
       </c>
       <c r="E1018" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1018" t="inlineStr">
         <is>
@@ -78728,7 +78728,7 @@
         <v>45835</v>
       </c>
       <c r="E1019" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1019" t="inlineStr">
         <is>
@@ -78801,7 +78801,7 @@
         <v>45835</v>
       </c>
       <c r="E1020" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1020" t="inlineStr">
         <is>
@@ -78874,7 +78874,7 @@
         <v>45840</v>
       </c>
       <c r="E1021" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1021" t="inlineStr">
         <is>
@@ -78947,7 +78947,7 @@
         <v>45540</v>
       </c>
       <c r="E1022" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1022" t="inlineStr">
         <is>
@@ -79020,7 +79020,7 @@
         <v>45846</v>
       </c>
       <c r="E1023" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1023" t="inlineStr">
         <is>
@@ -79093,7 +79093,7 @@
         <v>45847</v>
       </c>
       <c r="E1024" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1024" t="inlineStr">
         <is>
@@ -79166,7 +79166,7 @@
         <v>45390</v>
       </c>
       <c r="E1025" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1025" t="inlineStr">
         <is>
@@ -79239,7 +79239,7 @@
         <v>45853</v>
       </c>
       <c r="E1026" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1026" t="inlineStr">
         <is>
@@ -79312,7 +79312,7 @@
         <v>45740</v>
       </c>
       <c r="E1027" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1027" t="inlineStr">
         <is>
@@ -79385,7 +79385,7 @@
         <v>45267</v>
       </c>
       <c r="E1028" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1028" t="inlineStr">
         <is>
@@ -79458,7 +79458,7 @@
         <v>45384</v>
       </c>
       <c r="E1029" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1029" t="inlineStr">
         <is>
@@ -79531,7 +79531,7 @@
         <v>45097</v>
       </c>
       <c r="E1030" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1030" t="inlineStr">
         <is>
@@ -79609,7 +79609,7 @@
         <v>45782</v>
       </c>
       <c r="E1031" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1031" t="inlineStr">
         <is>
@@ -79682,7 +79682,7 @@
         <v>45874</v>
       </c>
       <c r="E1032" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1032" t="inlineStr">
         <is>
@@ -79755,7 +79755,7 @@
         <v>45054</v>
       </c>
       <c r="E1033" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1033" t="inlineStr">
         <is>
@@ -79828,7 +79828,7 @@
         <v>45230</v>
       </c>
       <c r="E1034" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1034" t="inlineStr">
         <is>
@@ -79906,7 +79906,7 @@
         <v>44498</v>
       </c>
       <c r="E1035" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1035" t="inlineStr">
         <is>
@@ -79979,7 +79979,7 @@
         <v>45622</v>
       </c>
       <c r="E1036" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1036" t="inlineStr">
         <is>
@@ -80052,7 +80052,7 @@
         <v>45054</v>
       </c>
       <c r="E1037" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1037" t="inlineStr">
         <is>
@@ -80125,7 +80125,7 @@
         <v>45054</v>
       </c>
       <c r="E1038" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1038" t="inlineStr">
         <is>
@@ -80198,7 +80198,7 @@
         <v>45056</v>
       </c>
       <c r="E1039" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1039" t="inlineStr">
         <is>
@@ -80271,7 +80271,7 @@
         <v>44715</v>
       </c>
       <c r="E1040" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1040" t="inlineStr">
         <is>
@@ -80344,7 +80344,7 @@
         <v>44722</v>
       </c>
       <c r="E1041" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1041" t="inlineStr">
         <is>
@@ -80417,7 +80417,7 @@
         <v>45434</v>
       </c>
       <c r="E1042" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1042" t="inlineStr">
         <is>
@@ -80490,7 +80490,7 @@
         <v>45054</v>
       </c>
       <c r="E1043" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1043" t="inlineStr">
         <is>
@@ -80563,7 +80563,7 @@
         <v>45407</v>
       </c>
       <c r="E1044" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1044" t="inlineStr">
         <is>
@@ -80636,7 +80636,7 @@
         <v>44802</v>
       </c>
       <c r="E1045" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1045" t="inlineStr">
         <is>
@@ -80709,7 +80709,7 @@
         <v>45071</v>
       </c>
       <c r="E1046" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1046" t="inlineStr">
         <is>
@@ -80782,7 +80782,7 @@
         <v>44495</v>
       </c>
       <c r="E1047" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1047" t="inlineStr">
         <is>
@@ -80855,7 +80855,7 @@
         <v>44588</v>
       </c>
       <c r="E1048" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1048" t="inlineStr">
         <is>
@@ -80928,7 +80928,7 @@
         <v>44727</v>
       </c>
       <c r="E1049" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1049" t="inlineStr">
         <is>
@@ -81001,7 +81001,7 @@
         <v>45224</v>
       </c>
       <c r="E1050" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1050" t="inlineStr">
         <is>
@@ -81079,7 +81079,7 @@
         <v>44722</v>
       </c>
       <c r="E1051" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1051" t="inlineStr">
         <is>
@@ -81152,7 +81152,7 @@
         <v>44972</v>
       </c>
       <c r="E1052" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1052" t="inlineStr">
         <is>
@@ -81225,7 +81225,7 @@
         <v>44487</v>
       </c>
       <c r="E1053" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1053" t="inlineStr">
         <is>
@@ -81298,7 +81298,7 @@
         <v>45230</v>
       </c>
       <c r="E1054" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1054" t="inlineStr">
         <is>
@@ -81371,7 +81371,7 @@
         <v>44939</v>
       </c>
       <c r="E1055" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1055" t="inlineStr">
         <is>
@@ -81444,7 +81444,7 @@
         <v>45468</v>
       </c>
       <c r="E1056" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1056" t="inlineStr">
         <is>
@@ -81517,7 +81517,7 @@
         <v>45218</v>
       </c>
       <c r="E1057" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1057" t="inlineStr">
         <is>
@@ -81590,7 +81590,7 @@
         <v>45054</v>
       </c>
       <c r="E1058" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1058" t="inlineStr">
         <is>
@@ -81663,7 +81663,7 @@
         <v>44603</v>
       </c>
       <c r="E1059" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1059" t="inlineStr">
         <is>
@@ -81736,7 +81736,7 @@
         <v>44930</v>
       </c>
       <c r="E1060" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1060" t="inlineStr">
         <is>
@@ -81814,7 +81814,7 @@
         <v>44973</v>
       </c>
       <c r="E1061" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1061" t="inlineStr">
         <is>
@@ -81887,7 +81887,7 @@
         <v>44908</v>
       </c>
       <c r="E1062" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1062" t="inlineStr">
         <is>
@@ -81980,7 +81980,7 @@
         <v>44693</v>
       </c>
       <c r="E1063" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1063" t="inlineStr">
         <is>
@@ -82053,7 +82053,7 @@
         <v>44726</v>
       </c>
       <c r="E1064" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1064" t="inlineStr">
         <is>
@@ -82126,7 +82126,7 @@
         <v>45583</v>
       </c>
       <c r="E1065" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1065" t="inlineStr">
         <is>
@@ -82199,7 +82199,7 @@
         <v>45054</v>
       </c>
       <c r="E1066" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1066" t="inlineStr">
         <is>
@@ -82272,7 +82272,7 @@
         <v>44712</v>
       </c>
       <c r="E1067" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1067" t="inlineStr">
         <is>
@@ -82345,7 +82345,7 @@
         <v>45054</v>
       </c>
       <c r="E1068" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1068" t="inlineStr">
         <is>
@@ -82418,7 +82418,7 @@
         <v>44722</v>
       </c>
       <c r="E1069" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1069" t="inlineStr">
         <is>
@@ -82491,7 +82491,7 @@
         <v>44908</v>
       </c>
       <c r="E1070" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1070" t="inlineStr">
         <is>
@@ -82564,7 +82564,7 @@
         <v>44972</v>
       </c>
       <c r="E1071" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1071" t="inlineStr">
         <is>
@@ -82637,7 +82637,7 @@
         <v>44978</v>
       </c>
       <c r="E1072" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1072" t="inlineStr">
         <is>
@@ -82710,7 +82710,7 @@
         <v>44712</v>
       </c>
       <c r="E1073" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1073" t="inlineStr">
         <is>
@@ -82783,7 +82783,7 @@
         <v>44887</v>
       </c>
       <c r="E1074" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1074" t="inlineStr">
         <is>
@@ -82856,7 +82856,7 @@
         <v>44704</v>
       </c>
       <c r="E1075" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1075" t="inlineStr">
         <is>
@@ -82929,7 +82929,7 @@
         <v>44909</v>
       </c>
       <c r="E1076" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1076" t="inlineStr">
         <is>
@@ -83002,7 +83002,7 @@
         <v>45408</v>
       </c>
       <c r="E1077" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1077" t="inlineStr">
         <is>
@@ -83075,7 +83075,7 @@
         <v>44596</v>
       </c>
       <c r="E1078" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1078" t="inlineStr">
         <is>
@@ -83148,7 +83148,7 @@
         <v>44908</v>
       </c>
       <c r="E1079" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1079" t="inlineStr">
         <is>
@@ -83221,7 +83221,7 @@
         <v>44704</v>
       </c>
       <c r="E1080" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1080" t="inlineStr">
         <is>
@@ -83294,7 +83294,7 @@
         <v>45054</v>
       </c>
       <c r="E1081" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1081" t="inlineStr">
         <is>
@@ -83367,7 +83367,7 @@
         <v>45526</v>
       </c>
       <c r="E1082" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1082" t="inlineStr">
         <is>
@@ -83440,7 +83440,7 @@
         <v>45436</v>
       </c>
       <c r="E1083" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1083" t="inlineStr">
         <is>
@@ -83513,7 +83513,7 @@
         <v>45485</v>
       </c>
       <c r="E1084" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1084" t="inlineStr">
         <is>
@@ -83586,7 +83586,7 @@
         <v>44588</v>
       </c>
       <c r="E1085" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1085" t="inlineStr">
         <is>
@@ -83659,7 +83659,7 @@
         <v>45727</v>
       </c>
       <c r="E1086" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1086" t="inlineStr">
         <is>
@@ -83732,7 +83732,7 @@
         <v>45740</v>
       </c>
       <c r="E1087" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1087" t="inlineStr">
         <is>
@@ -83805,7 +83805,7 @@
         <v>45726</v>
       </c>
       <c r="E1088" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1088" t="inlineStr">
         <is>
@@ -83878,7 +83878,7 @@
         <v>45797</v>
       </c>
       <c r="E1089" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1089" t="inlineStr">
         <is>
@@ -83951,7 +83951,7 @@
         <v>45805</v>
       </c>
       <c r="E1090" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1090" t="inlineStr">
         <is>
@@ -84024,7 +84024,7 @@
         <v>45831</v>
       </c>
       <c r="E1091" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1091" t="inlineStr">
         <is>
@@ -84097,7 +84097,7 @@
         <v>45951</v>
       </c>
       <c r="E1092" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1092" t="inlineStr">
         <is>
@@ -84170,7 +84170,7 @@
         <v>45958</v>
       </c>
       <c r="E1093" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1093" t="inlineStr">
         <is>
@@ -84243,7 +84243,7 @@
         <v>45964</v>
       </c>
       <c r="E1094" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1094" t="inlineStr">
         <is>
@@ -84316,7 +84316,7 @@
         <v>45965</v>
       </c>
       <c r="E1095" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1095" t="inlineStr">
         <is>
@@ -84389,7 +84389,7 @@
         <v>45981</v>
       </c>
       <c r="E1096" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1096" t="inlineStr">
         <is>
@@ -84467,7 +84467,7 @@
         <v>45988</v>
       </c>
       <c r="E1097" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1097" t="inlineStr">
         <is>
@@ -84540,7 +84540,7 @@
         <v>46092</v>
       </c>
       <c r="E1098" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1098" t="inlineStr">
         <is>
@@ -84618,7 +84618,7 @@
         <v>46202</v>
       </c>
       <c r="E1099" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1099" t="inlineStr">
         <is>
@@ -84691,7 +84691,7 @@
         <v>46300</v>
       </c>
       <c r="E1100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1100" t="inlineStr">
         <is>
@@ -84764,7 +84764,7 @@
         <v>46262</v>
       </c>
       <c r="E1101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1101" t="inlineStr">
         <is>
@@ -84837,7 +84837,7 @@
         <v>46304</v>
       </c>
       <c r="E1102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1102" t="inlineStr">
         <is>

--- a/Översikt VÄXJÖ.xlsx
+++ b/Översikt VÄXJÖ.xlsx
@@ -601,7 +601,7 @@
         <v>44974</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         <v>45895</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -859,7 +859,7 @@
         <v>45468</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -976,7 +976,7 @@
         <v>45770</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         <v>45888</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1204,7 +1204,7 @@
         <v>46175</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
         <v>45812</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
         <v>45127</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1545,7 +1545,7 @@
         <v>45384</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         <v>45964</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1770,7 +1770,7 @@
         <v>46188</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1884,7 +1884,7 @@
         <v>46188</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1998,7 +1998,7 @@
         <v>46199</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2112,7 +2112,7 @@
         <v>44958</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
         <v>45081</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
         <v>45995</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2450,7 +2450,7 @@
         <v>45490</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2567,7 +2567,7 @@
         <v>46247</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2675,7 +2675,7 @@
         <v>45294</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2792,7 +2792,7 @@
         <v>46204</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2908,7 +2908,7 @@
         <v>46244</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3019,7 +3019,7 @@
         <v>45356</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3130,7 +3130,7 @@
         <v>45344</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3241,7 +3241,7 @@
         <v>46098</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3348,7 +3348,7 @@
         <v>46286</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3455,7 +3455,7 @@
         <v>45190</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3561,7 +3561,7 @@
         <v>46161</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3671,7 +3671,7 @@
         <v>46182</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3786,7 +3786,7 @@
         <v>45093</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3896,7 +3896,7 @@
         <v>45545</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4002,7 +4002,7 @@
         <v>45820</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4112,7 +4112,7 @@
         <v>46296</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4218,7 +4218,7 @@
         <v>45554</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4324,7 +4324,7 @@
         <v>45883</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4430,7 +4430,7 @@
         <v>45874</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4541,7 +4541,7 @@
         <v>45649</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4647,7 +4647,7 @@
         <v>46147</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4753,7 +4753,7 @@
         <v>44532</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4868,7 +4868,7 @@
         <v>45447</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4974,7 +4974,7 @@
         <v>45687</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5080,7 +5080,7 @@
         <v>45587</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5190,7 +5190,7 @@
         <v>44704</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5296,7 +5296,7 @@
         <v>44704</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5406,7 +5406,7 @@
         <v>45460</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5512,7 +5512,7 @@
         <v>45348</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5618,7 +5618,7 @@
         <v>45351</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5724,7 +5724,7 @@
         <v>45674</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         <v>46100</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5941,7 +5941,7 @@
         <v>44721</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6046,7 +6046,7 @@
         <v>44704</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6151,7 +6151,7 @@
         <v>44645</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6256,7 +6256,7 @@
         <v>44673</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6361,7 +6361,7 @@
         <v>46161</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6466,7 +6466,7 @@
         <v>46161</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6571,7 +6571,7 @@
         <v>45098</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6676,7 +6676,7 @@
         <v>45533</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6781,7 +6781,7 @@
         <v>45369</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6886,7 +6886,7 @@
         <v>45279</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6991,7 +6991,7 @@
         <v>45594</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7101,7 +7101,7 @@
         <v>45594</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7211,7 +7211,7 @@
         <v>45754</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7316,7 +7316,7 @@
         <v>45392</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7426,7 +7426,7 @@
         <v>45964</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7535,7 +7535,7 @@
         <v>45978</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7644,7 +7644,7 @@
         <v>46199</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7749,7 +7749,7 @@
         <v>45280</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7854,7 +7854,7 @@
         <v>44894</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7959,7 +7959,7 @@
         <v>46281</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8064,7 +8064,7 @@
         <v>46288</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8169,7 +8169,7 @@
         <v>46045</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8274,7 +8274,7 @@
         <v>45617</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8384,7 +8384,7 @@
         <v>45606</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8489,7 +8489,7 @@
         <v>46246</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8594,7 +8594,7 @@
         <v>46296</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8699,7 +8699,7 @@
         <v>46303</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8804,7 +8804,7 @@
         <v>45594</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8918,7 +8918,7 @@
         <v>45327</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9023,7 +9023,7 @@
         <v>44872</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9128,7 +9128,7 @@
         <v>45824</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9233,7 +9233,7 @@
         <v>45688</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9338,7 +9338,7 @@
         <v>45643</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         <v>45428</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9553,7 +9553,7 @@
         <v>45273</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9658,7 +9658,7 @@
         <v>45280</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9763,7 +9763,7 @@
         <v>44705</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9872,7 +9872,7 @@
         <v>44746</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9977,7 +9977,7 @@
         <v>44741</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10082,7 +10082,7 @@
         <v>44634</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10187,7 +10187,7 @@
         <v>44712</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10292,7 +10292,7 @@
         <v>44950</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10397,7 +10397,7 @@
         <v>45436</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10502,7 +10502,7 @@
         <v>45726</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10607,7 +10607,7 @@
         <v>45805</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10712,7 +10712,7 @@
         <v>45939</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10821,7 +10821,7 @@
         <v>46100</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10926,7 +10926,7 @@
         <v>44812</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10999,7 +10999,7 @@
         <v>44693</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11072,7 +11072,7 @@
         <v>44518</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11145,7 +11145,7 @@
         <v>44536</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11218,7 +11218,7 @@
         <v>44764</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11291,7 +11291,7 @@
         <v>44519</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11364,7 +11364,7 @@
         <v>44501</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11437,7 +11437,7 @@
         <v>44645</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11510,7 +11510,7 @@
         <v>44814</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11583,7 +11583,7 @@
         <v>44643</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11656,7 +11656,7 @@
         <v>44515</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11729,7 +11729,7 @@
         <v>44814</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11802,7 +11802,7 @@
         <v>44525</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11875,7 +11875,7 @@
         <v>44578</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11948,7 +11948,7 @@
         <v>44516</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12026,7 +12026,7 @@
         <v>44803</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12099,7 +12099,7 @@
         <v>44691</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12172,7 +12172,7 @@
         <v>44739</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12245,7 +12245,7 @@
         <v>44590</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12323,7 +12323,7 @@
         <v>44820</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12401,7 +12401,7 @@
         <v>44814</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12474,7 +12474,7 @@
         <v>44769</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12552,7 +12552,7 @@
         <v>44820</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12625,7 +12625,7 @@
         <v>44711</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12698,7 +12698,7 @@
         <v>44880</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12771,7 +12771,7 @@
         <v>44508</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12844,7 +12844,7 @@
         <v>44495</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12917,7 +12917,7 @@
         <v>44515</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12990,7 +12990,7 @@
         <v>44599</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13063,7 +13063,7 @@
         <v>44599</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13136,7 +13136,7 @@
         <v>44495</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13209,7 +13209,7 @@
         <v>44651</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13282,7 +13282,7 @@
         <v>44876</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13360,7 +13360,7 @@
         <v>44671</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13433,7 +13433,7 @@
         <v>44496</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13506,7 +13506,7 @@
         <v>44750</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13579,7 +13579,7 @@
         <v>44568</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13652,7 +13652,7 @@
         <v>44543</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13725,7 +13725,7 @@
         <v>44606</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13798,7 +13798,7 @@
         <v>44613</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13871,7 +13871,7 @@
         <v>44746</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13944,7 +13944,7 @@
         <v>44610</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14017,7 +14017,7 @@
         <v>44610</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14090,7 +14090,7 @@
         <v>44740</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14163,7 +14163,7 @@
         <v>44617</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14236,7 +14236,7 @@
         <v>44726</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14309,7 +14309,7 @@
         <v>44551</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14382,7 +14382,7 @@
         <v>44599</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14455,7 +14455,7 @@
         <v>44781</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14528,7 +14528,7 @@
         <v>44494</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14601,7 +14601,7 @@
         <v>44704</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14674,7 +14674,7 @@
         <v>44522</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14747,7 +14747,7 @@
         <v>44532</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14820,7 +14820,7 @@
         <v>44532</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14893,7 +14893,7 @@
         <v>44498</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14966,7 +14966,7 @@
         <v>44860</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15039,7 +15039,7 @@
         <v>44596</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15112,7 +15112,7 @@
         <v>44573</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15185,7 +15185,7 @@
         <v>44712</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15258,7 +15258,7 @@
         <v>44579</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15331,7 +15331,7 @@
         <v>44711</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15404,7 +15404,7 @@
         <v>44769</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15482,7 +15482,7 @@
         <v>44502</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15560,7 +15560,7 @@
         <v>44812</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15633,7 +15633,7 @@
         <v>44508</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15706,7 +15706,7 @@
         <v>44574</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15779,7 +15779,7 @@
         <v>44537</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15852,7 +15852,7 @@
         <v>44537</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15925,7 +15925,7 @@
         <v>44571</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15998,7 +15998,7 @@
         <v>44603</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16076,7 +16076,7 @@
         <v>44596</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16149,7 +16149,7 @@
         <v>44560</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16222,7 +16222,7 @@
         <v>44998</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16295,7 +16295,7 @@
         <v>44592</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16368,7 +16368,7 @@
         <v>44820</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16446,7 +16446,7 @@
         <v>44820</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16524,7 +16524,7 @@
         <v>45229</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16597,7 +16597,7 @@
         <v>45103</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16670,7 +16670,7 @@
         <v>45222</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16743,7 +16743,7 @@
         <v>45754</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16816,7 +16816,7 @@
         <v>45412</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16889,7 +16889,7 @@
         <v>44741</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16962,7 +16962,7 @@
         <v>44741</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17035,7 +17035,7 @@
         <v>45194</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17108,7 +17108,7 @@
         <v>45058</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17181,7 +17181,7 @@
         <v>45219</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17254,7 +17254,7 @@
         <v>44814</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17327,7 +17327,7 @@
         <v>44814</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17400,7 +17400,7 @@
         <v>44547</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17473,7 +17473,7 @@
         <v>44741</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17546,7 +17546,7 @@
         <v>45715</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17619,7 +17619,7 @@
         <v>45280</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17692,7 +17692,7 @@
         <v>45894</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17765,7 +17765,7 @@
         <v>45890</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17838,7 +17838,7 @@
         <v>44880</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17911,7 +17911,7 @@
         <v>45856</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17984,7 +17984,7 @@
         <v>45895</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18057,7 +18057,7 @@
         <v>45201</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18130,7 +18130,7 @@
         <v>45281</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18203,7 +18203,7 @@
         <v>45315</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18276,7 +18276,7 @@
         <v>45315</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18349,7 +18349,7 @@
         <v>45897</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18427,7 +18427,7 @@
         <v>45622</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18500,7 +18500,7 @@
         <v>45240</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18573,7 +18573,7 @@
         <v>45883</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18646,7 +18646,7 @@
         <v>45754</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18719,7 +18719,7 @@
         <v>45754</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18792,7 +18792,7 @@
         <v>44979</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18865,7 +18865,7 @@
         <v>45645</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18938,7 +18938,7 @@
         <v>45719</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19011,7 +19011,7 @@
         <v>45386</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19084,7 +19084,7 @@
         <v>45902</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19157,7 +19157,7 @@
         <v>45902</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19230,7 +19230,7 @@
         <v>45359</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19303,7 +19303,7 @@
         <v>45225</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19376,7 +19376,7 @@
         <v>45902</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19449,7 +19449,7 @@
         <v>45810</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19527,7 +19527,7 @@
         <v>45835</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19600,7 +19600,7 @@
         <v>44959</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19673,7 +19673,7 @@
         <v>44867</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19746,7 +19746,7 @@
         <v>45372</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19819,7 +19819,7 @@
         <v>45594</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19897,7 +19897,7 @@
         <v>45594</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19975,7 +19975,7 @@
         <v>45905</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20048,7 +20048,7 @@
         <v>45127</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20121,7 +20121,7 @@
         <v>45230</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20194,7 +20194,7 @@
         <v>45623</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20267,7 +20267,7 @@
         <v>44843</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20340,7 +20340,7 @@
         <v>45910</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20413,7 +20413,7 @@
         <v>44894</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20486,7 +20486,7 @@
         <v>46162</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20559,7 +20559,7 @@
         <v>45909</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20632,7 +20632,7 @@
         <v>46162</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20705,7 +20705,7 @@
         <v>45245</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20778,7 +20778,7 @@
         <v>44963</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20851,7 +20851,7 @@
         <v>45780</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20924,7 +20924,7 @@
         <v>45787</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20997,7 +20997,7 @@
         <v>46162</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21070,7 +21070,7 @@
         <v>45719</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21143,7 +21143,7 @@
         <v>45911</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21216,7 +21216,7 @@
         <v>46163</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21289,7 +21289,7 @@
         <v>45540</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21362,7 +21362,7 @@
         <v>46163</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21435,7 +21435,7 @@
         <v>45597</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21508,7 +21508,7 @@
         <v>46163</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21581,7 +21581,7 @@
         <v>46163</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21654,7 +21654,7 @@
         <v>45219</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21727,7 +21727,7 @@
         <v>45061</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21800,7 +21800,7 @@
         <v>45812</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21873,7 +21873,7 @@
         <v>45572</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21946,7 +21946,7 @@
         <v>46163</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22019,7 +22019,7 @@
         <v>45304</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22092,7 +22092,7 @@
         <v>45918</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22165,7 +22165,7 @@
         <v>46163</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22238,7 +22238,7 @@
         <v>46168</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22311,7 +22311,7 @@
         <v>45029</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22384,7 +22384,7 @@
         <v>44992</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22457,7 +22457,7 @@
         <v>45933</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22530,7 +22530,7 @@
         <v>45552</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22603,7 +22603,7 @@
         <v>45199</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22676,7 +22676,7 @@
         <v>45181</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22749,7 +22749,7 @@
         <v>46167</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22822,7 +22822,7 @@
         <v>45924</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22895,7 +22895,7 @@
         <v>45147</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22968,7 +22968,7 @@
         <v>46168</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23041,7 +23041,7 @@
         <v>45105</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23114,7 +23114,7 @@
         <v>44501</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23187,7 +23187,7 @@
         <v>45925</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23260,7 +23260,7 @@
         <v>45557</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23333,7 +23333,7 @@
         <v>46100</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23406,7 +23406,7 @@
         <v>45216</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23479,7 +23479,7 @@
         <v>46112</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23552,7 +23552,7 @@
         <v>46171</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23625,7 +23625,7 @@
         <v>46171</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23698,7 +23698,7 @@
         <v>45324</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23771,7 +23771,7 @@
         <v>46170</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23844,7 +23844,7 @@
         <v>45219</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23917,7 +23917,7 @@
         <v>46010</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23990,7 +23990,7 @@
         <v>46171</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24063,7 +24063,7 @@
         <v>45554</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24136,7 +24136,7 @@
         <v>44761</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24214,7 +24214,7 @@
         <v>45468</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24287,7 +24287,7 @@
         <v>45937</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24360,7 +24360,7 @@
         <v>45057</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24433,7 +24433,7 @@
         <v>45937</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24506,7 +24506,7 @@
         <v>45427</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24579,7 +24579,7 @@
         <v>45400</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24652,7 +24652,7 @@
         <v>45594</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24730,7 +24730,7 @@
         <v>45446</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24803,7 +24803,7 @@
         <v>44977</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24876,7 +24876,7 @@
         <v>45009</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24954,7 +24954,7 @@
         <v>45679</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25027,7 +25027,7 @@
         <v>44602</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25100,7 +25100,7 @@
         <v>44732</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25173,7 +25173,7 @@
         <v>45176</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25246,7 +25246,7 @@
         <v>45896</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25319,7 +25319,7 @@
         <v>45259</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25392,7 +25392,7 @@
         <v>44874</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25465,7 +25465,7 @@
         <v>44956</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25538,7 +25538,7 @@
         <v>45281</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25611,7 +25611,7 @@
         <v>45392</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25689,7 +25689,7 @@
         <v>44894</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25767,7 +25767,7 @@
         <v>45090</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25840,7 +25840,7 @@
         <v>45300</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25913,7 +25913,7 @@
         <v>45302</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25986,7 +25986,7 @@
         <v>45019</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26059,7 +26059,7 @@
         <v>45611</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26132,7 +26132,7 @@
         <v>46134</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26205,7 +26205,7 @@
         <v>45386</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26278,7 +26278,7 @@
         <v>45676</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26356,7 +26356,7 @@
         <v>45162</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26429,7 +26429,7 @@
         <v>45162</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26502,7 +26502,7 @@
         <v>46134</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26575,7 +26575,7 @@
         <v>45392</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26653,7 +26653,7 @@
         <v>45392</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26731,7 +26731,7 @@
         <v>45446</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26809,7 +26809,7 @@
         <v>44986</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26882,7 +26882,7 @@
         <v>45581</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26955,7 +26955,7 @@
         <v>45504</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27028,7 +27028,7 @@
         <v>45432</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27101,7 +27101,7 @@
         <v>44502</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27179,7 +27179,7 @@
         <v>45049</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27252,7 +27252,7 @@
         <v>44896</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27325,7 +27325,7 @@
         <v>45665</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27398,7 +27398,7 @@
         <v>45762</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27476,7 +27476,7 @@
         <v>46134</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27549,7 +27549,7 @@
         <v>46170</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27622,7 +27622,7 @@
         <v>45153</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27695,7 +27695,7 @@
         <v>46183</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27768,7 +27768,7 @@
         <v>45952</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27841,7 +27841,7 @@
         <v>45923</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27914,7 +27914,7 @@
         <v>45679</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27987,7 +27987,7 @@
         <v>45296</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28060,7 +28060,7 @@
         <v>46183</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28133,7 +28133,7 @@
         <v>46183</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28206,7 +28206,7 @@
         <v>45617</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28279,7 +28279,7 @@
         <v>45769</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28352,7 +28352,7 @@
         <v>46183</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28425,7 +28425,7 @@
         <v>44687</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28498,7 +28498,7 @@
         <v>45211</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28571,7 +28571,7 @@
         <v>45632</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28644,7 +28644,7 @@
         <v>45946</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28717,7 +28717,7 @@
         <v>45232</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28790,7 +28790,7 @@
         <v>45953</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28863,7 +28863,7 @@
         <v>45139</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28936,7 +28936,7 @@
         <v>45924</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29009,7 +29009,7 @@
         <v>46189</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29082,7 +29082,7 @@
         <v>45964</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29155,7 +29155,7 @@
         <v>45373</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29228,7 +29228,7 @@
         <v>45448</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29301,7 +29301,7 @@
         <v>46188</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29374,7 +29374,7 @@
         <v>45022</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29447,7 +29447,7 @@
         <v>46191</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29520,7 +29520,7 @@
         <v>45693</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29593,7 +29593,7 @@
         <v>45317</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29666,7 +29666,7 @@
         <v>45555</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29739,7 +29739,7 @@
         <v>46190</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29812,7 +29812,7 @@
         <v>45309</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29885,7 +29885,7 @@
         <v>45309</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29958,7 +29958,7 @@
         <v>46191</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30031,7 +30031,7 @@
         <v>46108</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30104,7 +30104,7 @@
         <v>45971</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30177,7 +30177,7 @@
         <v>45924</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30250,7 +30250,7 @@
         <v>45108</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30323,7 +30323,7 @@
         <v>45169</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30396,7 +30396,7 @@
         <v>45608</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30469,7 +30469,7 @@
         <v>45205</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30542,7 +30542,7 @@
         <v>45070</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30615,7 +30615,7 @@
         <v>46199</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30688,7 +30688,7 @@
         <v>44900</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30761,7 +30761,7 @@
         <v>45973</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30834,7 +30834,7 @@
         <v>44900</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30907,7 +30907,7 @@
         <v>46199</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30980,7 +30980,7 @@
         <v>46198</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31053,7 +31053,7 @@
         <v>44532</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31126,7 +31126,7 @@
         <v>46198</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31199,7 +31199,7 @@
         <v>45181</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31272,7 +31272,7 @@
         <v>45236</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31345,7 +31345,7 @@
         <v>45112</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31418,7 +31418,7 @@
         <v>46198</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31491,7 +31491,7 @@
         <v>46198</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31564,7 +31564,7 @@
         <v>45979</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31637,7 +31637,7 @@
         <v>44929</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31715,7 +31715,7 @@
         <v>45979</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31788,7 +31788,7 @@
         <v>45541</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31861,7 +31861,7 @@
         <v>46199</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31934,7 +31934,7 @@
         <v>44656</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32007,7 +32007,7 @@
         <v>45980</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32080,7 +32080,7 @@
         <v>45443</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32153,7 +32153,7 @@
         <v>45147</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32226,7 +32226,7 @@
         <v>45217</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32299,7 +32299,7 @@
         <v>44831</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32372,7 +32372,7 @@
         <v>46199</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32445,7 +32445,7 @@
         <v>45194</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32518,7 +32518,7 @@
         <v>45219</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32591,7 +32591,7 @@
         <v>45477</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32669,7 +32669,7 @@
         <v>45280</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32742,7 +32742,7 @@
         <v>46205</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32815,7 +32815,7 @@
         <v>45705</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32893,7 +32893,7 @@
         <v>46205</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32966,7 +32966,7 @@
         <v>45016</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33039,7 +33039,7 @@
         <v>45061</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33112,7 +33112,7 @@
         <v>45560</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33185,7 +33185,7 @@
         <v>44909</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33263,7 +33263,7 @@
         <v>44986</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33336,7 +33336,7 @@
         <v>46206</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33414,7 +33414,7 @@
         <v>45686</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33487,7 +33487,7 @@
         <v>45737</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33560,7 +33560,7 @@
         <v>45224</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33633,7 +33633,7 @@
         <v>46210</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33711,7 +33711,7 @@
         <v>45304</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33784,7 +33784,7 @@
         <v>45244</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33857,7 +33857,7 @@
         <v>45250</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33930,7 +33930,7 @@
         <v>46210</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34008,7 +34008,7 @@
         <v>45446</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34081,7 +34081,7 @@
         <v>44904</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34154,7 +34154,7 @@
         <v>44904</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34227,7 +34227,7 @@
         <v>44963</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34300,7 +34300,7 @@
         <v>44963</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34373,7 +34373,7 @@
         <v>44963</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34446,7 +34446,7 @@
         <v>45993</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34519,7 +34519,7 @@
         <v>45468</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34592,7 +34592,7 @@
         <v>45127</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34665,7 +34665,7 @@
         <v>45127</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34738,7 +34738,7 @@
         <v>45993</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34811,7 +34811,7 @@
         <v>45551</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34884,7 +34884,7 @@
         <v>45988</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34957,7 +34957,7 @@
         <v>45557</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35030,7 +35030,7 @@
         <v>44573</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35103,7 +35103,7 @@
         <v>45579</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35176,7 +35176,7 @@
         <v>45533</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35249,7 +35249,7 @@
         <v>45579</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35322,7 +35322,7 @@
         <v>45702</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35395,7 +35395,7 @@
         <v>45999</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35468,7 +35468,7 @@
         <v>46170</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35541,7 +35541,7 @@
         <v>45165</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35614,7 +35614,7 @@
         <v>46000</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35687,7 +35687,7 @@
         <v>45194</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35760,7 +35760,7 @@
         <v>46001</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35833,7 +35833,7 @@
         <v>45547</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35906,7 +35906,7 @@
         <v>45777</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35984,7 +35984,7 @@
         <v>45519</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36057,7 +36057,7 @@
         <v>45777</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36135,7 +36135,7 @@
         <v>45777</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36213,7 +36213,7 @@
         <v>45780</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36286,7 +36286,7 @@
         <v>45780</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36359,7 +36359,7 @@
         <v>44854</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36432,7 +36432,7 @@
         <v>45782</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36505,7 +36505,7 @@
         <v>45546</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36578,7 +36578,7 @@
         <v>45783</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36651,7 +36651,7 @@
         <v>46008</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36724,7 +36724,7 @@
         <v>45534</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36797,7 +36797,7 @@
         <v>46007</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36870,7 +36870,7 @@
         <v>45478</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36943,7 +36943,7 @@
         <v>46232</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37016,7 +37016,7 @@
         <v>46232</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37089,7 +37089,7 @@
         <v>46279</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37162,7 +37162,7 @@
         <v>46279</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37235,7 +37235,7 @@
         <v>45642</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37308,7 +37308,7 @@
         <v>44781</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37386,7 +37386,7 @@
         <v>46010</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37459,7 +37459,7 @@
         <v>45608</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37532,7 +37532,7 @@
         <v>46010</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37605,7 +37605,7 @@
         <v>46010</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37678,7 +37678,7 @@
         <v>45108</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37751,7 +37751,7 @@
         <v>46237</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37824,7 +37824,7 @@
         <v>46237</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37897,7 +37897,7 @@
         <v>45716</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37970,7 +37970,7 @@
         <v>45244</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38043,7 +38043,7 @@
         <v>45614</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38116,7 +38116,7 @@
         <v>46019</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38189,7 +38189,7 @@
         <v>46019</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38262,7 +38262,7 @@
         <v>45716</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38335,7 +38335,7 @@
         <v>46281</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38408,7 +38408,7 @@
         <v>46239</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38481,7 +38481,7 @@
         <v>44894</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38554,7 +38554,7 @@
         <v>46029</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38627,7 +38627,7 @@
         <v>46244</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38705,7 +38705,7 @@
         <v>46244</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38783,7 +38783,7 @@
         <v>46029</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38856,7 +38856,7 @@
         <v>46244</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38934,7 +38934,7 @@
         <v>46031</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39012,7 +39012,7 @@
         <v>46031</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39090,7 +39090,7 @@
         <v>46244</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39168,7 +39168,7 @@
         <v>45791</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39241,7 +39241,7 @@
         <v>46036</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39314,7 +39314,7 @@
         <v>46035</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39392,7 +39392,7 @@
         <v>46035</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39470,7 +39470,7 @@
         <v>46244</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39548,7 +39548,7 @@
         <v>45921</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39621,7 +39621,7 @@
         <v>46036</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39694,7 +39694,7 @@
         <v>45796</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39767,7 +39767,7 @@
         <v>46035</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39845,7 +39845,7 @@
         <v>46036</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39918,7 +39918,7 @@
         <v>46244</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39991,7 +39991,7 @@
         <v>45111</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40064,7 +40064,7 @@
         <v>46244</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40142,7 +40142,7 @@
         <v>46041</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40215,7 +40215,7 @@
         <v>46288</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40288,7 +40288,7 @@
         <v>46245</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40361,7 +40361,7 @@
         <v>46288</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40434,7 +40434,7 @@
         <v>46043</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40507,7 +40507,7 @@
         <v>46048</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40580,7 +40580,7 @@
         <v>46045</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40653,7 +40653,7 @@
         <v>45764</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40726,7 +40726,7 @@
         <v>46244</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40799,7 +40799,7 @@
         <v>46245</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -40872,7 +40872,7 @@
         <v>46045</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40945,7 +40945,7 @@
         <v>45574</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41018,7 +41018,7 @@
         <v>45665</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41091,7 +41091,7 @@
         <v>46049</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41164,7 +41164,7 @@
         <v>45154</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41237,7 +41237,7 @@
         <v>44824</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41310,7 +41310,7 @@
         <v>46289</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41383,7 +41383,7 @@
         <v>46049</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41456,7 +41456,7 @@
         <v>46049</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41529,7 +41529,7 @@
         <v>45749</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41602,7 +41602,7 @@
         <v>46051</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -41675,7 +41675,7 @@
         <v>45803</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -41748,7 +41748,7 @@
         <v>45145</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -41821,7 +41821,7 @@
         <v>46021</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -41894,7 +41894,7 @@
         <v>45294</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -41967,7 +41967,7 @@
         <v>46056</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42040,7 +42040,7 @@
         <v>45805</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42113,7 +42113,7 @@
         <v>46289</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42186,7 +42186,7 @@
         <v>45763</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42259,7 +42259,7 @@
         <v>46056</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42332,7 +42332,7 @@
         <v>46056</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42405,7 +42405,7 @@
         <v>45447</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42478,7 +42478,7 @@
         <v>46057</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42551,7 +42551,7 @@
         <v>46246</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42629,7 +42629,7 @@
         <v>46059</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42702,7 +42702,7 @@
         <v>46061</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -42775,7 +42775,7 @@
         <v>45342</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -42848,7 +42848,7 @@
         <v>46059</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -42921,7 +42921,7 @@
         <v>46059</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -42994,7 +42994,7 @@
         <v>45330</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43067,7 +43067,7 @@
         <v>44950</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43140,7 +43140,7 @@
         <v>46294</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43213,7 +43213,7 @@
         <v>46294</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43286,7 +43286,7 @@
         <v>46294</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43359,7 +43359,7 @@
         <v>46294</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -43432,7 +43432,7 @@
         <v>46237</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -43505,7 +43505,7 @@
         <v>46294</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -43578,7 +43578,7 @@
         <v>45769</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -43651,7 +43651,7 @@
         <v>45820</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -43724,7 +43724,7 @@
         <v>46294</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -43797,7 +43797,7 @@
         <v>46072</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -43870,7 +43870,7 @@
         <v>45820</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -43943,7 +43943,7 @@
         <v>46296</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44016,7 +44016,7 @@
         <v>46296</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44089,7 +44089,7 @@
         <v>46073</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44162,7 +44162,7 @@
         <v>45817</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44235,7 +44235,7 @@
         <v>46073</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44308,7 +44308,7 @@
         <v>45818</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -44381,7 +44381,7 @@
         <v>46075</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -44454,7 +44454,7 @@
         <v>46296</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -44527,7 +44527,7 @@
         <v>46296</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -44600,7 +44600,7 @@
         <v>45824</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -44673,7 +44673,7 @@
         <v>46252</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -44746,7 +44746,7 @@
         <v>45824</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -44819,7 +44819,7 @@
         <v>46296</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -44892,7 +44892,7 @@
         <v>46296</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -44965,7 +44965,7 @@
         <v>45825</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45038,7 +45038,7 @@
         <v>46253</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45111,7 +45111,7 @@
         <v>46079</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45184,7 +45184,7 @@
         <v>46079</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -45257,7 +45257,7 @@
         <v>46083</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -45330,7 +45330,7 @@
         <v>46083</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -45403,7 +45403,7 @@
         <v>46083</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -45476,7 +45476,7 @@
         <v>45827</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -45549,7 +45549,7 @@
         <v>45831</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -45622,7 +45622,7 @@
         <v>46295</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -45700,7 +45700,7 @@
         <v>46083</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -45773,7 +45773,7 @@
         <v>46083</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -45846,7 +45846,7 @@
         <v>46296</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -45919,7 +45919,7 @@
         <v>46084</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -45992,7 +45992,7 @@
         <v>45831</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46065,7 +46065,7 @@
         <v>46252</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -46138,7 +46138,7 @@
         <v>46300</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -46211,7 +46211,7 @@
         <v>45477</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -46289,7 +46289,7 @@
         <v>46087</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -46362,7 +46362,7 @@
         <v>45805</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -46435,7 +46435,7 @@
         <v>45832</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -46508,7 +46508,7 @@
         <v>45835</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -46581,7 +46581,7 @@
         <v>45835</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -46654,7 +46654,7 @@
         <v>45594</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -46732,7 +46732,7 @@
         <v>46300</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -46805,7 +46805,7 @@
         <v>45835</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -46878,7 +46878,7 @@
         <v>44545</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -46951,7 +46951,7 @@
         <v>45840</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47024,7 +47024,7 @@
         <v>45488</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47097,7 +47097,7 @@
         <v>45540</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -47170,7 +47170,7 @@
         <v>46099</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -47243,7 +47243,7 @@
         <v>46100</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -47316,7 +47316,7 @@
         <v>45846</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -47389,7 +47389,7 @@
         <v>45124</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -47462,7 +47462,7 @@
         <v>46100</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -47535,7 +47535,7 @@
         <v>46100</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -47608,7 +47608,7 @@
         <v>44880</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -47681,7 +47681,7 @@
         <v>46301</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -47754,7 +47754,7 @@
         <v>45847</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -47827,7 +47827,7 @@
         <v>44922</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -47900,7 +47900,7 @@
         <v>45390</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -47973,7 +47973,7 @@
         <v>46107</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48046,7 +48046,7 @@
         <v>46199</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -48119,7 +48119,7 @@
         <v>45853</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -48192,7 +48192,7 @@
         <v>44769</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -48270,7 +48270,7 @@
         <v>44769</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -48348,7 +48348,7 @@
         <v>46258</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -48421,7 +48421,7 @@
         <v>46108</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -48494,7 +48494,7 @@
         <v>45740</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -48567,7 +48567,7 @@
         <v>46113</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -48640,7 +48640,7 @@
         <v>44537</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -48713,7 +48713,7 @@
         <v>46112</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -48786,7 +48786,7 @@
         <v>46112</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -48859,7 +48859,7 @@
         <v>45916</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -48932,7 +48932,7 @@
         <v>45384</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -49005,7 +49005,7 @@
         <v>45097</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -49083,7 +49083,7 @@
         <v>45267</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -49156,7 +49156,7 @@
         <v>45782</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -49229,7 +49229,7 @@
         <v>46261</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -49302,7 +49302,7 @@
         <v>45594</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -49380,7 +49380,7 @@
         <v>46304</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -49453,7 +49453,7 @@
         <v>46119</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -49526,7 +49526,7 @@
         <v>45594</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -49604,7 +49604,7 @@
         <v>45874</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -49677,7 +49677,7 @@
         <v>46183</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -49750,7 +49750,7 @@
         <v>46260</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -49823,7 +49823,7 @@
         <v>46304</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -49896,7 +49896,7 @@
         <v>46183</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -49969,7 +49969,7 @@
         <v>46262</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -50042,7 +50042,7 @@
         <v>44896</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -50115,7 +50115,7 @@
         <v>46129</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -50188,7 +50188,7 @@
         <v>46307</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -50261,7 +50261,7 @@
         <v>46307</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -50334,7 +50334,7 @@
         <v>45278</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -50407,7 +50407,7 @@
         <v>46308</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -50480,7 +50480,7 @@
         <v>46307</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -50553,7 +50553,7 @@
         <v>45148</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -50626,7 +50626,7 @@
         <v>45148</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -50699,7 +50699,7 @@
         <v>45161</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -50772,7 +50772,7 @@
         <v>45288</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -50845,7 +50845,7 @@
         <v>45190</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -50918,7 +50918,7 @@
         <v>45881</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -50991,7 +50991,7 @@
         <v>45638</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -51064,7 +51064,7 @@
         <v>45573</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -51137,7 +51137,7 @@
         <v>44867</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -51210,7 +51210,7 @@
         <v>45677</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -51283,7 +51283,7 @@
         <v>45835</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -51356,7 +51356,7 @@
         <v>45743</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -51429,7 +51429,7 @@
         <v>45827</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -51502,7 +51502,7 @@
         <v>44599</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -51575,7 +51575,7 @@
         <v>45698</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -51648,7 +51648,7 @@
         <v>45810</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -51726,7 +51726,7 @@
         <v>45826</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -51804,7 +51804,7 @@
         <v>45672</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -51877,7 +51877,7 @@
         <v>45056</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -51950,7 +51950,7 @@
         <v>45670</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -52023,7 +52023,7 @@
         <v>45905</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -52096,7 +52096,7 @@
         <v>45923</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -52169,7 +52169,7 @@
         <v>45833</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -52242,7 +52242,7 @@
         <v>45883</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -52315,7 +52315,7 @@
         <v>45883</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -52388,7 +52388,7 @@
         <v>45775</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -52461,7 +52461,7 @@
         <v>44896</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -52534,7 +52534,7 @@
         <v>45846</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -52607,7 +52607,7 @@
         <v>45782</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -52680,7 +52680,7 @@
         <v>46230</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -52753,7 +52753,7 @@
         <v>46245</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -52826,7 +52826,7 @@
         <v>45559</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -52899,7 +52899,7 @@
         <v>45923</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -52972,7 +52972,7 @@
         <v>45426</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -53045,7 +53045,7 @@
         <v>45939</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -53118,7 +53118,7 @@
         <v>45827</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -53191,7 +53191,7 @@
         <v>44532</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -53264,7 +53264,7 @@
         <v>45841</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -53337,7 +53337,7 @@
         <v>45686</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -53410,7 +53410,7 @@
         <v>45390</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -53483,7 +53483,7 @@
         <v>45877</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -53556,7 +53556,7 @@
         <v>45818</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -53629,7 +53629,7 @@
         <v>44595</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -53702,7 +53702,7 @@
         <v>45555</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -53775,7 +53775,7 @@
         <v>44903</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -53848,7 +53848,7 @@
         <v>45791</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -53921,7 +53921,7 @@
         <v>44938</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -53994,7 +53994,7 @@
         <v>46269</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -54067,7 +54067,7 @@
         <v>45419</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -54140,7 +54140,7 @@
         <v>45960</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -54213,7 +54213,7 @@
         <v>45014</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -54286,7 +54286,7 @@
         <v>45412</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -54359,7 +54359,7 @@
         <v>45412</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -54432,7 +54432,7 @@
         <v>45909</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -54505,7 +54505,7 @@
         <v>45582</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -54578,7 +54578,7 @@
         <v>46216</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -54651,7 +54651,7 @@
         <v>46272</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -54724,7 +54724,7 @@
         <v>46272</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -54797,7 +54797,7 @@
         <v>45140</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -54870,7 +54870,7 @@
         <v>45894</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -54943,7 +54943,7 @@
         <v>45552</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -55016,7 +55016,7 @@
         <v>46315</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -55089,7 +55089,7 @@
         <v>46216</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -55162,7 +55162,7 @@
         <v>46216</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -55235,7 +55235,7 @@
         <v>44522</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -55308,7 +55308,7 @@
         <v>45378</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -55381,7 +55381,7 @@
         <v>45534</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -55454,7 +55454,7 @@
         <v>45560</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -55527,7 +55527,7 @@
         <v>45369</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -55600,7 +55600,7 @@
         <v>44599</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -55673,7 +55673,7 @@
         <v>44869</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -55746,7 +55746,7 @@
         <v>45338</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -55819,7 +55819,7 @@
         <v>45244</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -55892,7 +55892,7 @@
         <v>45408</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -55965,7 +55965,7 @@
         <v>46315</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -56038,7 +56038,7 @@
         <v>46315</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -56111,7 +56111,7 @@
         <v>45222</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -56184,7 +56184,7 @@
         <v>45169</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -56257,7 +56257,7 @@
         <v>45583</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -56335,7 +56335,7 @@
         <v>45392</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -56413,7 +56413,7 @@
         <v>44670</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -56486,7 +56486,7 @@
         <v>46276</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -56559,7 +56559,7 @@
         <v>46317</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -56632,7 +56632,7 @@
         <v>46317</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -56705,7 +56705,7 @@
         <v>46276</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -56778,7 +56778,7 @@
         <v>46317</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -56851,7 +56851,7 @@
         <v>46317</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -56924,7 +56924,7 @@
         <v>45329</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -56997,7 +56997,7 @@
         <v>44577</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -57070,7 +57070,7 @@
         <v>44711</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -57143,7 +57143,7 @@
         <v>45071</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -57221,7 +57221,7 @@
         <v>45583</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -57294,7 +57294,7 @@
         <v>45757</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -57367,7 +57367,7 @@
         <v>45384</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -57440,7 +57440,7 @@
         <v>46146</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -57513,7 +57513,7 @@
         <v>46146</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -57586,7 +57586,7 @@
         <v>45345</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -57659,7 +57659,7 @@
         <v>46146</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -57732,7 +57732,7 @@
         <v>45579</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -57805,7 +57805,7 @@
         <v>44970</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -57878,7 +57878,7 @@
         <v>46147</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -57951,7 +57951,7 @@
         <v>46147</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -58024,7 +58024,7 @@
         <v>46148</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -58097,7 +58097,7 @@
         <v>46147</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -58170,7 +58170,7 @@
         <v>46147</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -58243,7 +58243,7 @@
         <v>45397</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -58316,7 +58316,7 @@
         <v>46147</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -58389,7 +58389,7 @@
         <v>46149</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -58462,7 +58462,7 @@
         <v>46021</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -58535,7 +58535,7 @@
         <v>45764</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -58608,7 +58608,7 @@
         <v>46153</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -58681,7 +58681,7 @@
         <v>45189</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -58754,7 +58754,7 @@
         <v>45189</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -58827,7 +58827,7 @@
         <v>45722</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -58900,7 +58900,7 @@
         <v>44963</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -58973,7 +58973,7 @@
         <v>45463</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -59046,7 +59046,7 @@
         <v>44960</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -59119,7 +59119,7 @@
         <v>45594</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -59197,7 +59197,7 @@
         <v>45594</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -59275,7 +59275,7 @@
         <v>45594</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -59353,7 +59353,7 @@
         <v>45594</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -59431,7 +59431,7 @@
         <v>45594</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -59509,7 +59509,7 @@
         <v>45594</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -59587,7 +59587,7 @@
         <v>45594</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -59665,7 +59665,7 @@
         <v>45586</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -59738,7 +59738,7 @@
         <v>45995</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -59811,7 +59811,7 @@
         <v>45517</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -59884,7 +59884,7 @@
         <v>45281</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -59957,7 +59957,7 @@
         <v>45631</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -60030,7 +60030,7 @@
         <v>45789</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -60103,7 +60103,7 @@
         <v>45180</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -60176,7 +60176,7 @@
         <v>45714</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -60249,7 +60249,7 @@
         <v>45670</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -60322,7 +60322,7 @@
         <v>45250</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -60395,7 +60395,7 @@
         <v>45629</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -60468,7 +60468,7 @@
         <v>45328</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -60541,7 +60541,7 @@
         <v>45328</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -60614,7 +60614,7 @@
         <v>44494</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -60687,7 +60687,7 @@
         <v>45638</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -60760,7 +60760,7 @@
         <v>45611</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -60833,7 +60833,7 @@
         <v>44743</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -60906,7 +60906,7 @@
         <v>44711</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -60979,7 +60979,7 @@
         <v>45224</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -61057,7 +61057,7 @@
         <v>44966</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -61130,7 +61130,7 @@
         <v>45089</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -61203,7 +61203,7 @@
         <v>44972</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -61276,7 +61276,7 @@
         <v>44972</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -61349,7 +61349,7 @@
         <v>45519</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -61422,7 +61422,7 @@
         <v>45702</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -61495,7 +61495,7 @@
         <v>44967</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -61568,7 +61568,7 @@
         <v>45012</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -61641,7 +61641,7 @@
         <v>44981</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -61714,7 +61714,7 @@
         <v>45166</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -61787,7 +61787,7 @@
         <v>44998</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -61860,7 +61860,7 @@
         <v>45385</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -61938,7 +61938,7 @@
         <v>45385</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -62016,7 +62016,7 @@
         <v>45495</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -62089,7 +62089,7 @@
         <v>45103</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -62162,7 +62162,7 @@
         <v>45103</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -62235,7 +62235,7 @@
         <v>45103</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -62308,7 +62308,7 @@
         <v>45558</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -62381,7 +62381,7 @@
         <v>45538</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -62454,7 +62454,7 @@
         <v>45114</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -62527,7 +62527,7 @@
         <v>45114</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -62600,7 +62600,7 @@
         <v>44739</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -62673,7 +62673,7 @@
         <v>45128</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -62746,7 +62746,7 @@
         <v>45568</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -62819,7 +62819,7 @@
         <v>44774</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -62892,7 +62892,7 @@
         <v>45692</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -62965,7 +62965,7 @@
         <v>45033</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -63043,7 +63043,7 @@
         <v>45121</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -63116,7 +63116,7 @@
         <v>44782</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -63194,7 +63194,7 @@
         <v>45645</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -63267,7 +63267,7 @@
         <v>45127</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -63340,7 +63340,7 @@
         <v>45168</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -63413,7 +63413,7 @@
         <v>45460</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -63486,7 +63486,7 @@
         <v>44995</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -63559,7 +63559,7 @@
         <v>45113</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -63632,7 +63632,7 @@
         <v>45113</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -63705,7 +63705,7 @@
         <v>44536</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -63778,7 +63778,7 @@
         <v>45692</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -63851,7 +63851,7 @@
         <v>45714</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -63924,7 +63924,7 @@
         <v>44858</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -63997,7 +63997,7 @@
         <v>44502</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -64070,7 +64070,7 @@
         <v>45091</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -64143,7 +64143,7 @@
         <v>45030</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -64216,7 +64216,7 @@
         <v>45691</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -64289,7 +64289,7 @@
         <v>44812</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -64362,7 +64362,7 @@
         <v>45715</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -64440,7 +64440,7 @@
         <v>45048</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -64513,7 +64513,7 @@
         <v>45190</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -64586,7 +64586,7 @@
         <v>44991</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -64659,7 +64659,7 @@
         <v>45513</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -64732,7 +64732,7 @@
         <v>45210</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -64805,7 +64805,7 @@
         <v>44909</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -64878,7 +64878,7 @@
         <v>44922</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -64951,7 +64951,7 @@
         <v>45753</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -65024,7 +65024,7 @@
         <v>44552</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -65097,7 +65097,7 @@
         <v>45250</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -65170,7 +65170,7 @@
         <v>45141</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -65243,7 +65243,7 @@
         <v>45614</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -65316,7 +65316,7 @@
         <v>45533</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -65389,7 +65389,7 @@
         <v>44529</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -65462,7 +65462,7 @@
         <v>44641</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -65535,7 +65535,7 @@
         <v>44874</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -65608,7 +65608,7 @@
         <v>45715</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -65686,7 +65686,7 @@
         <v>45111</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -65759,7 +65759,7 @@
         <v>45714</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -65832,7 +65832,7 @@
         <v>45267</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -65905,7 +65905,7 @@
         <v>44894</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -65978,7 +65978,7 @@
         <v>45036</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -66051,7 +66051,7 @@
         <v>45599</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -66124,7 +66124,7 @@
         <v>44523</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -66197,7 +66197,7 @@
         <v>45233</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -66270,7 +66270,7 @@
         <v>44600</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -66348,7 +66348,7 @@
         <v>45632</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -66421,7 +66421,7 @@
         <v>45153</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -66494,7 +66494,7 @@
         <v>44713</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -66567,7 +66567,7 @@
         <v>44908</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -66640,7 +66640,7 @@
         <v>44897</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -66713,7 +66713,7 @@
         <v>45204</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -66786,7 +66786,7 @@
         <v>45737</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -66859,7 +66859,7 @@
         <v>45557</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -66932,7 +66932,7 @@
         <v>44928</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -67005,7 +67005,7 @@
         <v>45279</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -67078,7 +67078,7 @@
         <v>45273</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -67151,7 +67151,7 @@
         <v>45436</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -67224,7 +67224,7 @@
         <v>45106</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -67297,7 +67297,7 @@
         <v>45090</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -67370,7 +67370,7 @@
         <v>45561</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -67443,7 +67443,7 @@
         <v>45392</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -67516,7 +67516,7 @@
         <v>45447</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -67589,7 +67589,7 @@
         <v>45211</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -67662,7 +67662,7 @@
         <v>45104</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -67735,7 +67735,7 @@
         <v>45078</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -67813,7 +67813,7 @@
         <v>45726</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -67886,7 +67886,7 @@
         <v>45341</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -67959,7 +67959,7 @@
         <v>45127</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -68032,7 +68032,7 @@
         <v>45538</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -68110,7 +68110,7 @@
         <v>45128</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -68183,7 +68183,7 @@
         <v>45128</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -68256,7 +68256,7 @@
         <v>45387</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -68329,7 +68329,7 @@
         <v>45240</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -68402,7 +68402,7 @@
         <v>45121</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -68475,7 +68475,7 @@
         <v>45121</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -68548,7 +68548,7 @@
         <v>45121</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -68621,7 +68621,7 @@
         <v>45387</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -68694,7 +68694,7 @@
         <v>44959</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -68767,7 +68767,7 @@
         <v>45030</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -68840,7 +68840,7 @@
         <v>45236</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -68913,7 +68913,7 @@
         <v>45166</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -68986,7 +68986,7 @@
         <v>45446</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -69059,7 +69059,7 @@
         <v>45392</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -69137,7 +69137,7 @@
         <v>45324</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -69210,7 +69210,7 @@
         <v>45558</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -69283,7 +69283,7 @@
         <v>45309</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -69356,7 +69356,7 @@
         <v>45309</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -69429,7 +69429,7 @@
         <v>45113</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -69502,7 +69502,7 @@
         <v>45037</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -69575,7 +69575,7 @@
         <v>45037</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -69648,7 +69648,7 @@
         <v>45222</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -69721,7 +69721,7 @@
         <v>44988</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -69794,7 +69794,7 @@
         <v>45127</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -69867,7 +69867,7 @@
         <v>45048</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -69940,7 +69940,7 @@
         <v>45638</v>
       </c>
       <c r="E900" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -70013,7 +70013,7 @@
         <v>45685</v>
       </c>
       <c r="E901" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>
@@ -70086,7 +70086,7 @@
         <v>45611</v>
       </c>
       <c r="E902" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F902" t="inlineStr">
         <is>
@@ -70159,7 +70159,7 @@
         <v>45161</v>
       </c>
       <c r="E903" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F903" t="inlineStr">
         <is>
@@ -70232,7 +70232,7 @@
         <v>44866</v>
       </c>
       <c r="E904" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F904" t="inlineStr">
         <is>
@@ -70305,7 +70305,7 @@
         <v>45139</v>
       </c>
       <c r="E905" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F905" t="inlineStr">
         <is>
@@ -70378,7 +70378,7 @@
         <v>45112</v>
       </c>
       <c r="E906" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F906" t="inlineStr">
         <is>
@@ -70451,7 +70451,7 @@
         <v>45580</v>
       </c>
       <c r="E907" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F907" t="inlineStr">
         <is>
@@ -70524,7 +70524,7 @@
         <v>45014</v>
       </c>
       <c r="E908" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F908" t="inlineStr">
         <is>
@@ -70602,7 +70602,7 @@
         <v>45316</v>
       </c>
       <c r="E909" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F909" t="inlineStr">
         <is>
@@ -70675,7 +70675,7 @@
         <v>45330</v>
       </c>
       <c r="E910" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F910" t="inlineStr">
         <is>
@@ -70753,7 +70753,7 @@
         <v>45219</v>
       </c>
       <c r="E911" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F911" t="inlineStr">
         <is>
@@ -70826,7 +70826,7 @@
         <v>45330</v>
       </c>
       <c r="E912" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F912" t="inlineStr">
         <is>
@@ -70899,7 +70899,7 @@
         <v>45644</v>
       </c>
       <c r="E913" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F913" t="inlineStr">
         <is>
@@ -70972,7 +70972,7 @@
         <v>45198</v>
       </c>
       <c r="E914" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F914" t="inlineStr">
         <is>
@@ -71045,7 +71045,7 @@
         <v>45008</v>
       </c>
       <c r="E915" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F915" t="inlineStr">
         <is>
@@ -71118,7 +71118,7 @@
         <v>45000</v>
       </c>
       <c r="E916" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F916" t="inlineStr">
         <is>
@@ -71191,7 +71191,7 @@
         <v>44609</v>
       </c>
       <c r="E917" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F917" t="inlineStr">
         <is>
@@ -71264,7 +71264,7 @@
         <v>45733</v>
       </c>
       <c r="E918" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F918" t="inlineStr">
         <is>
@@ -71337,7 +71337,7 @@
         <v>45722</v>
       </c>
       <c r="E919" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F919" t="inlineStr">
         <is>
@@ -71410,7 +71410,7 @@
         <v>45036</v>
       </c>
       <c r="E920" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F920" t="inlineStr">
         <is>
@@ -71483,7 +71483,7 @@
         <v>45065</v>
       </c>
       <c r="E921" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F921" t="inlineStr">
         <is>
@@ -71556,7 +71556,7 @@
         <v>45028</v>
       </c>
       <c r="E922" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F922" t="inlineStr">
         <is>
@@ -71629,7 +71629,7 @@
         <v>45594</v>
       </c>
       <c r="E923" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F923" t="inlineStr">
         <is>
@@ -71707,7 +71707,7 @@
         <v>45594</v>
       </c>
       <c r="E924" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F924" t="inlineStr">
         <is>
@@ -71785,7 +71785,7 @@
         <v>45594</v>
       </c>
       <c r="E925" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F925" t="inlineStr">
         <is>
@@ -71863,7 +71863,7 @@
         <v>45594</v>
       </c>
       <c r="E926" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F926" t="inlineStr">
         <is>
@@ -71941,7 +71941,7 @@
         <v>45509</v>
       </c>
       <c r="E927" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F927" t="inlineStr">
         <is>
@@ -72014,7 +72014,7 @@
         <v>45644</v>
       </c>
       <c r="E928" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F928" t="inlineStr">
         <is>
@@ -72087,7 +72087,7 @@
         <v>45594</v>
       </c>
       <c r="E929" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F929" t="inlineStr">
         <is>
@@ -72165,7 +72165,7 @@
         <v>45594</v>
       </c>
       <c r="E930" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F930" t="inlineStr">
         <is>
@@ -72243,7 +72243,7 @@
         <v>45594</v>
       </c>
       <c r="E931" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F931" t="inlineStr">
         <is>
@@ -72321,7 +72321,7 @@
         <v>45601</v>
       </c>
       <c r="E932" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F932" t="inlineStr">
         <is>
@@ -72394,7 +72394,7 @@
         <v>45316</v>
       </c>
       <c r="E933" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F933" t="inlineStr">
         <is>
@@ -72467,7 +72467,7 @@
         <v>45316</v>
       </c>
       <c r="E934" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F934" t="inlineStr">
         <is>
@@ -72540,7 +72540,7 @@
         <v>45056</v>
       </c>
       <c r="E935" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F935" t="inlineStr">
         <is>
@@ -72613,7 +72613,7 @@
         <v>44858</v>
       </c>
       <c r="E936" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F936" t="inlineStr">
         <is>
@@ -72686,7 +72686,7 @@
         <v>45372</v>
       </c>
       <c r="E937" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F937" t="inlineStr">
         <is>
@@ -72759,7 +72759,7 @@
         <v>44764</v>
       </c>
       <c r="E938" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F938" t="inlineStr">
         <is>
@@ -72832,7 +72832,7 @@
         <v>45091</v>
       </c>
       <c r="E939" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F939" t="inlineStr">
         <is>
@@ -72910,7 +72910,7 @@
         <v>45579</v>
       </c>
       <c r="E940" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F940" t="inlineStr">
         <is>
@@ -72983,7 +72983,7 @@
         <v>45385</v>
       </c>
       <c r="E941" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F941" t="inlineStr">
         <is>
@@ -73061,7 +73061,7 @@
         <v>45385</v>
       </c>
       <c r="E942" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F942" t="inlineStr">
         <is>
@@ -73139,7 +73139,7 @@
         <v>45440</v>
       </c>
       <c r="E943" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F943" t="inlineStr">
         <is>
@@ -73212,7 +73212,7 @@
         <v>45679</v>
       </c>
       <c r="E944" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F944" t="inlineStr">
         <is>
@@ -73285,7 +73285,7 @@
         <v>45215</v>
       </c>
       <c r="E945" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F945" t="inlineStr">
         <is>
@@ -73358,7 +73358,7 @@
         <v>44876</v>
       </c>
       <c r="E946" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F946" t="inlineStr">
         <is>
@@ -73436,7 +73436,7 @@
         <v>45495</v>
       </c>
       <c r="E947" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F947" t="inlineStr">
         <is>
@@ -73509,7 +73509,7 @@
         <v>45210</v>
       </c>
       <c r="E948" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F948" t="inlineStr">
         <is>
@@ -73582,7 +73582,7 @@
         <v>45754</v>
       </c>
       <c r="E949" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F949" t="inlineStr">
         <is>
@@ -73655,7 +73655,7 @@
         <v>45244</v>
       </c>
       <c r="E950" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F950" t="inlineStr">
         <is>
@@ -73728,7 +73728,7 @@
         <v>44679</v>
       </c>
       <c r="E951" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F951" t="inlineStr">
         <is>
@@ -73801,7 +73801,7 @@
         <v>44678</v>
       </c>
       <c r="E952" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F952" t="inlineStr">
         <is>
@@ -73874,7 +73874,7 @@
         <v>45775</v>
       </c>
       <c r="E953" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F953" t="inlineStr">
         <is>
@@ -73947,7 +73947,7 @@
         <v>44802</v>
       </c>
       <c r="E954" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F954" t="inlineStr">
         <is>
@@ -74020,7 +74020,7 @@
         <v>45420</v>
       </c>
       <c r="E955" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F955" t="inlineStr">
         <is>
@@ -74093,7 +74093,7 @@
         <v>45140</v>
       </c>
       <c r="E956" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F956" t="inlineStr">
         <is>
@@ -74166,7 +74166,7 @@
         <v>45686</v>
       </c>
       <c r="E957" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F957" t="inlineStr">
         <is>
@@ -74239,7 +74239,7 @@
         <v>45686</v>
       </c>
       <c r="E958" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F958" t="inlineStr">
         <is>
@@ -74312,7 +74312,7 @@
         <v>45085</v>
       </c>
       <c r="E959" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F959" t="inlineStr">
         <is>
@@ -74385,7 +74385,7 @@
         <v>44676</v>
       </c>
       <c r="E960" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F960" t="inlineStr">
         <is>
@@ -74463,7 +74463,7 @@
         <v>44620</v>
       </c>
       <c r="E961" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F961" t="inlineStr">
         <is>
@@ -74536,7 +74536,7 @@
         <v>45253</v>
       </c>
       <c r="E962" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F962" t="inlineStr">
         <is>
@@ -74609,7 +74609,7 @@
         <v>45247</v>
       </c>
       <c r="E963" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F963" t="inlineStr">
         <is>
@@ -74682,7 +74682,7 @@
         <v>44676</v>
       </c>
       <c r="E964" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F964" t="inlineStr">
         <is>
@@ -74760,7 +74760,7 @@
         <v>45236</v>
       </c>
       <c r="E965" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F965" t="inlineStr">
         <is>
@@ -74833,7 +74833,7 @@
         <v>45236</v>
       </c>
       <c r="E966" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F966" t="inlineStr">
         <is>
@@ -74906,7 +74906,7 @@
         <v>45114</v>
       </c>
       <c r="E967" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F967" t="inlineStr">
         <is>
@@ -74979,7 +74979,7 @@
         <v>45679</v>
       </c>
       <c r="E968" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F968" t="inlineStr">
         <is>
@@ -75052,7 +75052,7 @@
         <v>44690</v>
       </c>
       <c r="E969" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F969" t="inlineStr">
         <is>
@@ -75125,7 +75125,7 @@
         <v>44705</v>
       </c>
       <c r="E970" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F970" t="inlineStr">
         <is>
@@ -75198,7 +75198,7 @@
         <v>44651</v>
       </c>
       <c r="E971" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F971" t="inlineStr">
         <is>
@@ -75271,7 +75271,7 @@
         <v>45460</v>
       </c>
       <c r="E972" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F972" t="inlineStr">
         <is>
@@ -75344,7 +75344,7 @@
         <v>45421</v>
       </c>
       <c r="E973" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F973" t="inlineStr">
         <is>
@@ -75417,7 +75417,7 @@
         <v>45188</v>
       </c>
       <c r="E974" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F974" t="inlineStr">
         <is>
@@ -75490,7 +75490,7 @@
         <v>45176</v>
       </c>
       <c r="E975" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F975" t="inlineStr">
         <is>
@@ -75563,7 +75563,7 @@
         <v>45121</v>
       </c>
       <c r="E976" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F976" t="inlineStr">
         <is>
@@ -75636,7 +75636,7 @@
         <v>45250</v>
       </c>
       <c r="E977" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F977" t="inlineStr">
         <is>
@@ -75709,7 +75709,7 @@
         <v>44746</v>
       </c>
       <c r="E978" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F978" t="inlineStr">
         <is>
@@ -75782,7 +75782,7 @@
         <v>45753</v>
       </c>
       <c r="E979" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F979" t="inlineStr">
         <is>
@@ -75855,7 +75855,7 @@
         <v>45288</v>
       </c>
       <c r="E980" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F980" t="inlineStr">
         <is>
@@ -75928,7 +75928,7 @@
         <v>44686</v>
       </c>
       <c r="E981" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F981" t="inlineStr">
         <is>
@@ -76001,7 +76001,7 @@
         <v>45260</v>
       </c>
       <c r="E982" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F982" t="inlineStr">
         <is>
@@ -76074,7 +76074,7 @@
         <v>44915</v>
       </c>
       <c r="E983" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F983" t="inlineStr">
         <is>
@@ -76147,7 +76147,7 @@
         <v>44651</v>
       </c>
       <c r="E984" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F984" t="inlineStr">
         <is>
@@ -76220,7 +76220,7 @@
         <v>44831</v>
       </c>
       <c r="E985" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F985" t="inlineStr">
         <is>
@@ -76293,7 +76293,7 @@
         <v>45301</v>
       </c>
       <c r="E986" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F986" t="inlineStr">
         <is>
@@ -76366,7 +76366,7 @@
         <v>45247</v>
       </c>
       <c r="E987" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F987" t="inlineStr">
         <is>
@@ -76439,7 +76439,7 @@
         <v>45309</v>
       </c>
       <c r="E988" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F988" t="inlineStr">
         <is>
@@ -76512,7 +76512,7 @@
         <v>45121</v>
       </c>
       <c r="E989" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F989" t="inlineStr">
         <is>
@@ -76585,7 +76585,7 @@
         <v>44677</v>
       </c>
       <c r="E990" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F990" t="inlineStr">
         <is>
@@ -76658,7 +76658,7 @@
         <v>44811</v>
       </c>
       <c r="E991" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F991" t="inlineStr">
         <is>
@@ -76731,7 +76731,7 @@
         <v>44749</v>
       </c>
       <c r="E992" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F992" t="inlineStr">
         <is>
@@ -76804,7 +76804,7 @@
         <v>45104</v>
       </c>
       <c r="E993" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F993" t="inlineStr">
         <is>
@@ -76877,7 +76877,7 @@
         <v>44496</v>
       </c>
       <c r="E994" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F994" t="inlineStr">
         <is>
@@ -76950,7 +76950,7 @@
         <v>44858</v>
       </c>
       <c r="E995" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F995" t="inlineStr">
         <is>
@@ -77023,7 +77023,7 @@
         <v>45274</v>
       </c>
       <c r="E996" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F996" t="inlineStr">
         <is>
@@ -77096,7 +77096,7 @@
         <v>45246</v>
       </c>
       <c r="E997" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F997" t="inlineStr">
         <is>
@@ -77169,7 +77169,7 @@
         <v>45743</v>
       </c>
       <c r="E998" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F998" t="inlineStr">
         <is>
@@ -77242,7 +77242,7 @@
         <v>45198</v>
       </c>
       <c r="E999" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F999" t="inlineStr">
         <is>
@@ -77315,7 +77315,7 @@
         <v>45644</v>
       </c>
       <c r="E1000" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1000" t="inlineStr">
         <is>
@@ -77388,7 +77388,7 @@
         <v>45128</v>
       </c>
       <c r="E1001" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1001" t="inlineStr">
         <is>
@@ -77461,7 +77461,7 @@
         <v>45686</v>
       </c>
       <c r="E1002" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1002" t="inlineStr">
         <is>
@@ -77534,7 +77534,7 @@
         <v>45278</v>
       </c>
       <c r="E1003" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1003" t="inlineStr">
         <is>
@@ -77607,7 +77607,7 @@
         <v>45559</v>
       </c>
       <c r="E1004" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1004" t="inlineStr">
         <is>
@@ -77680,7 +77680,7 @@
         <v>45181</v>
       </c>
       <c r="E1005" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1005" t="inlineStr">
         <is>
@@ -77753,7 +77753,7 @@
         <v>45141</v>
       </c>
       <c r="E1006" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1006" t="inlineStr">
         <is>
@@ -77826,7 +77826,7 @@
         <v>45194</v>
       </c>
       <c r="E1007" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1007" t="inlineStr">
         <is>
@@ -77899,7 +77899,7 @@
         <v>45302</v>
       </c>
       <c r="E1008" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1008" t="inlineStr">
         <is>
@@ -77972,7 +77972,7 @@
         <v>45726</v>
       </c>
       <c r="E1009" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1009" t="inlineStr">
         <is>
@@ -78045,7 +78045,7 @@
         <v>45401</v>
       </c>
       <c r="E1010" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1010" t="inlineStr">
         <is>
@@ -78118,7 +78118,7 @@
         <v>45244</v>
       </c>
       <c r="E1011" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1011" t="inlineStr">
         <is>
@@ -78191,7 +78191,7 @@
         <v>45152</v>
       </c>
       <c r="E1012" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1012" t="inlineStr">
         <is>
@@ -78264,7 +78264,7 @@
         <v>45702</v>
       </c>
       <c r="E1013" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1013" t="inlineStr">
         <is>
@@ -78337,7 +78337,7 @@
         <v>45541</v>
       </c>
       <c r="E1014" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1014" t="inlineStr">
         <is>
@@ -78410,7 +78410,7 @@
         <v>45300</v>
       </c>
       <c r="E1015" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1015" t="inlineStr">
         <is>
@@ -78483,7 +78483,7 @@
         <v>45300</v>
       </c>
       <c r="E1016" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1016" t="inlineStr">
         <is>
@@ -78556,7 +78556,7 @@
         <v>45342</v>
       </c>
       <c r="E1017" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1017" t="inlineStr">
         <is>
@@ -78629,7 +78629,7 @@
         <v>45302</v>
       </c>
       <c r="E1018" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1018" t="inlineStr">
         <is>
@@ -78702,7 +78702,7 @@
         <v>45322</v>
       </c>
       <c r="E1019" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1019" t="inlineStr">
         <is>
@@ -78775,7 +78775,7 @@
         <v>44915</v>
       </c>
       <c r="E1020" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1020" t="inlineStr">
         <is>
@@ -78848,7 +78848,7 @@
         <v>44652</v>
       </c>
       <c r="E1021" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1021" t="inlineStr">
         <is>
@@ -78921,7 +78921,7 @@
         <v>44537</v>
       </c>
       <c r="E1022" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1022" t="inlineStr">
         <is>
@@ -78994,7 +78994,7 @@
         <v>44609</v>
       </c>
       <c r="E1023" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1023" t="inlineStr">
         <is>
@@ -79067,7 +79067,7 @@
         <v>45183</v>
       </c>
       <c r="E1024" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1024" t="inlineStr">
         <is>
@@ -79140,7 +79140,7 @@
         <v>45121</v>
       </c>
       <c r="E1025" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1025" t="inlineStr">
         <is>
@@ -79213,7 +79213,7 @@
         <v>45420</v>
       </c>
       <c r="E1026" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1026" t="inlineStr">
         <is>
@@ -79286,7 +79286,7 @@
         <v>45253</v>
       </c>
       <c r="E1027" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1027" t="inlineStr">
         <is>
@@ -79359,7 +79359,7 @@
         <v>44845</v>
       </c>
       <c r="E1028" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1028" t="inlineStr">
         <is>
@@ -79432,7 +79432,7 @@
         <v>44915</v>
       </c>
       <c r="E1029" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1029" t="inlineStr">
         <is>
@@ -79505,7 +79505,7 @@
         <v>44552</v>
       </c>
       <c r="E1030" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1030" t="inlineStr">
         <is>
@@ -79578,7 +79578,7 @@
         <v>45070</v>
       </c>
       <c r="E1031" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1031" t="inlineStr">
         <is>
@@ -79651,7 +79651,7 @@
         <v>44715</v>
       </c>
       <c r="E1032" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1032" t="inlineStr">
         <is>
@@ -79724,7 +79724,7 @@
         <v>44722</v>
       </c>
       <c r="E1033" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1033" t="inlineStr">
         <is>
@@ -79797,7 +79797,7 @@
         <v>44588</v>
       </c>
       <c r="E1034" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1034" t="inlineStr">
         <is>
@@ -79870,7 +79870,7 @@
         <v>44727</v>
       </c>
       <c r="E1035" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1035" t="inlineStr">
         <is>
@@ -79943,7 +79943,7 @@
         <v>44722</v>
       </c>
       <c r="E1036" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1036" t="inlineStr">
         <is>
@@ -80016,7 +80016,7 @@
         <v>44603</v>
       </c>
       <c r="E1037" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1037" t="inlineStr">
         <is>
@@ -80089,7 +80089,7 @@
         <v>44693</v>
       </c>
       <c r="E1038" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1038" t="inlineStr">
         <is>
@@ -80162,7 +80162,7 @@
         <v>44726</v>
       </c>
       <c r="E1039" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1039" t="inlineStr">
         <is>
@@ -80235,7 +80235,7 @@
         <v>44712</v>
       </c>
       <c r="E1040" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1040" t="inlineStr">
         <is>
@@ -80308,7 +80308,7 @@
         <v>44722</v>
       </c>
       <c r="E1041" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1041" t="inlineStr">
         <is>
@@ -80381,7 +80381,7 @@
         <v>44712</v>
       </c>
       <c r="E1042" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1042" t="inlineStr">
         <is>
@@ -80454,7 +80454,7 @@
         <v>44704</v>
       </c>
       <c r="E1043" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1043" t="inlineStr">
         <is>
@@ -80527,7 +80527,7 @@
         <v>44596</v>
       </c>
       <c r="E1044" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1044" t="inlineStr">
         <is>
@@ -80600,7 +80600,7 @@
         <v>44704</v>
       </c>
       <c r="E1045" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1045" t="inlineStr">
         <is>
@@ -80673,7 +80673,7 @@
         <v>44588</v>
       </c>
       <c r="E1046" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1046" t="inlineStr">
         <is>
@@ -80746,7 +80746,7 @@
         <v>45054</v>
       </c>
       <c r="E1047" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1047" t="inlineStr">
         <is>
@@ -80819,7 +80819,7 @@
         <v>45230</v>
       </c>
       <c r="E1048" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1048" t="inlineStr">
         <is>
@@ -80897,7 +80897,7 @@
         <v>44498</v>
       </c>
       <c r="E1049" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1049" t="inlineStr">
         <is>
@@ -80970,7 +80970,7 @@
         <v>45622</v>
       </c>
       <c r="E1050" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1050" t="inlineStr">
         <is>
@@ -81043,7 +81043,7 @@
         <v>45054</v>
       </c>
       <c r="E1051" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1051" t="inlineStr">
         <is>
@@ -81116,7 +81116,7 @@
         <v>45054</v>
       </c>
       <c r="E1052" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1052" t="inlineStr">
         <is>
@@ -81189,7 +81189,7 @@
         <v>45056</v>
       </c>
       <c r="E1053" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1053" t="inlineStr">
         <is>
@@ -81262,7 +81262,7 @@
         <v>45434</v>
       </c>
       <c r="E1054" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1054" t="inlineStr">
         <is>
@@ -81335,7 +81335,7 @@
         <v>45054</v>
       </c>
       <c r="E1055" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1055" t="inlineStr">
         <is>
@@ -81408,7 +81408,7 @@
         <v>45407</v>
       </c>
       <c r="E1056" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1056" t="inlineStr">
         <is>
@@ -81481,7 +81481,7 @@
         <v>44802</v>
       </c>
       <c r="E1057" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1057" t="inlineStr">
         <is>
@@ -81554,7 +81554,7 @@
         <v>45071</v>
       </c>
       <c r="E1058" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1058" t="inlineStr">
         <is>
@@ -81627,7 +81627,7 @@
         <v>44495</v>
       </c>
       <c r="E1059" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1059" t="inlineStr">
         <is>
@@ -81700,7 +81700,7 @@
         <v>45224</v>
       </c>
       <c r="E1060" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1060" t="inlineStr">
         <is>
@@ -81778,7 +81778,7 @@
         <v>44972</v>
       </c>
       <c r="E1061" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1061" t="inlineStr">
         <is>
@@ -81851,7 +81851,7 @@
         <v>45230</v>
       </c>
       <c r="E1062" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1062" t="inlineStr">
         <is>
@@ -81924,7 +81924,7 @@
         <v>44939</v>
       </c>
       <c r="E1063" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1063" t="inlineStr">
         <is>
@@ -81997,7 +81997,7 @@
         <v>45468</v>
       </c>
       <c r="E1064" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1064" t="inlineStr">
         <is>
@@ -82070,7 +82070,7 @@
         <v>45218</v>
       </c>
       <c r="E1065" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1065" t="inlineStr">
         <is>
@@ -82143,7 +82143,7 @@
         <v>45054</v>
       </c>
       <c r="E1066" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1066" t="inlineStr">
         <is>
@@ -82216,7 +82216,7 @@
         <v>44930</v>
       </c>
       <c r="E1067" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1067" t="inlineStr">
         <is>
@@ -82294,7 +82294,7 @@
         <v>44973</v>
       </c>
       <c r="E1068" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1068" t="inlineStr">
         <is>
@@ -82367,7 +82367,7 @@
         <v>44908</v>
       </c>
       <c r="E1069" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1069" t="inlineStr">
         <is>
@@ -82460,7 +82460,7 @@
         <v>45583</v>
       </c>
       <c r="E1070" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1070" t="inlineStr">
         <is>
@@ -82533,7 +82533,7 @@
         <v>45054</v>
       </c>
       <c r="E1071" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1071" t="inlineStr">
         <is>
@@ -82606,7 +82606,7 @@
         <v>45054</v>
       </c>
       <c r="E1072" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1072" t="inlineStr">
         <is>
@@ -82679,7 +82679,7 @@
         <v>44908</v>
       </c>
       <c r="E1073" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1073" t="inlineStr">
         <is>
@@ -82752,7 +82752,7 @@
         <v>44972</v>
       </c>
       <c r="E1074" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1074" t="inlineStr">
         <is>
@@ -82825,7 +82825,7 @@
         <v>44978</v>
       </c>
       <c r="E1075" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1075" t="inlineStr">
         <is>
@@ -82898,7 +82898,7 @@
         <v>44887</v>
       </c>
       <c r="E1076" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1076" t="inlineStr">
         <is>
@@ -82971,7 +82971,7 @@
         <v>44909</v>
       </c>
       <c r="E1077" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1077" t="inlineStr">
         <is>
@@ -83044,7 +83044,7 @@
         <v>45408</v>
       </c>
       <c r="E1078" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1078" t="inlineStr">
         <is>
@@ -83117,7 +83117,7 @@
         <v>44908</v>
       </c>
       <c r="E1079" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1079" t="inlineStr">
         <is>
@@ -83190,7 +83190,7 @@
         <v>45054</v>
       </c>
       <c r="E1080" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1080" t="inlineStr">
         <is>
@@ -83263,7 +83263,7 @@
         <v>45526</v>
       </c>
       <c r="E1081" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1081" t="inlineStr">
         <is>
@@ -83336,7 +83336,7 @@
         <v>45436</v>
       </c>
       <c r="E1082" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1082" t="inlineStr">
         <is>
@@ -83409,7 +83409,7 @@
         <v>45485</v>
       </c>
       <c r="E1083" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1083" t="inlineStr">
         <is>
@@ -83482,7 +83482,7 @@
         <v>45727</v>
       </c>
       <c r="E1084" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1084" t="inlineStr">
         <is>
@@ -83555,7 +83555,7 @@
         <v>45740</v>
       </c>
       <c r="E1085" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1085" t="inlineStr">
         <is>
@@ -83628,7 +83628,7 @@
         <v>45726</v>
       </c>
       <c r="E1086" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1086" t="inlineStr">
         <is>
@@ -83701,7 +83701,7 @@
         <v>45797</v>
       </c>
       <c r="E1087" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1087" t="inlineStr">
         <is>
@@ -83774,7 +83774,7 @@
         <v>45805</v>
       </c>
       <c r="E1088" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1088" t="inlineStr">
         <is>
@@ -83847,7 +83847,7 @@
         <v>45831</v>
       </c>
       <c r="E1089" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1089" t="inlineStr">
         <is>
@@ -83920,7 +83920,7 @@
         <v>45951</v>
       </c>
       <c r="E1090" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1090" t="inlineStr">
         <is>
@@ -83993,7 +83993,7 @@
         <v>45958</v>
       </c>
       <c r="E1091" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1091" t="inlineStr">
         <is>
@@ -84066,7 +84066,7 @@
         <v>45964</v>
       </c>
       <c r="E1092" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1092" t="inlineStr">
         <is>
@@ -84139,7 +84139,7 @@
         <v>45965</v>
       </c>
       <c r="E1093" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1093" t="inlineStr">
         <is>
@@ -84212,7 +84212,7 @@
         <v>45981</v>
       </c>
       <c r="E1094" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1094" t="inlineStr">
         <is>
@@ -84290,7 +84290,7 @@
         <v>45988</v>
       </c>
       <c r="E1095" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1095" t="inlineStr">
         <is>
@@ -84363,7 +84363,7 @@
         <v>46092</v>
       </c>
       <c r="E1096" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1096" t="inlineStr">
         <is>
@@ -84441,7 +84441,7 @@
         <v>46202</v>
       </c>
       <c r="E1097" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1097" t="inlineStr">
         <is>
@@ -84514,7 +84514,7 @@
         <v>46300</v>
       </c>
       <c r="E1098" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1098" t="inlineStr">
         <is>
@@ -84587,7 +84587,7 @@
         <v>46262</v>
       </c>
       <c r="E1099" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1099" t="inlineStr">
         <is>
@@ -84660,7 +84660,7 @@
         <v>46304</v>
       </c>
       <c r="E1100" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1100" t="inlineStr">
         <is>

--- a/Översikt VÄXJÖ.xlsx
+++ b/Översikt VÄXJÖ.xlsx
@@ -601,7 +601,7 @@
         <v>44974</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         <v>45895</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -859,7 +859,7 @@
         <v>45468</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -976,7 +976,7 @@
         <v>45770</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         <v>45888</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1204,7 +1204,7 @@
         <v>46175</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
         <v>45812</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
         <v>45127</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1545,7 +1545,7 @@
         <v>45384</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         <v>45964</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1770,7 +1770,7 @@
         <v>46188</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1884,7 +1884,7 @@
         <v>46188</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1998,7 +1998,7 @@
         <v>46199</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2112,7 +2112,7 @@
         <v>44958</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
         <v>45081</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
         <v>45995</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2450,7 +2450,7 @@
         <v>45490</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2567,7 +2567,7 @@
         <v>46247</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2675,7 +2675,7 @@
         <v>45294</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2792,7 +2792,7 @@
         <v>46204</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2908,7 +2908,7 @@
         <v>46244</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3019,7 +3019,7 @@
         <v>45356</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3130,7 +3130,7 @@
         <v>45344</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3241,7 +3241,7 @@
         <v>46098</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3348,7 +3348,7 @@
         <v>46286</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3455,7 +3455,7 @@
         <v>45190</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3561,7 +3561,7 @@
         <v>46161</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3671,7 +3671,7 @@
         <v>46182</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3786,7 +3786,7 @@
         <v>45093</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3896,7 +3896,7 @@
         <v>45545</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4002,7 +4002,7 @@
         <v>45820</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4112,7 +4112,7 @@
         <v>46296</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4218,7 +4218,7 @@
         <v>45554</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4324,7 +4324,7 @@
         <v>45883</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4430,7 +4430,7 @@
         <v>45874</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4541,7 +4541,7 @@
         <v>45649</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4647,7 +4647,7 @@
         <v>46147</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4753,7 +4753,7 @@
         <v>44532</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4868,7 +4868,7 @@
         <v>45447</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4974,7 +4974,7 @@
         <v>45687</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5080,7 +5080,7 @@
         <v>45587</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5190,7 +5190,7 @@
         <v>44704</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5296,7 +5296,7 @@
         <v>44704</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5406,7 +5406,7 @@
         <v>45460</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5512,7 +5512,7 @@
         <v>45348</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5618,7 +5618,7 @@
         <v>45351</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5724,7 +5724,7 @@
         <v>45674</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         <v>46100</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5941,7 +5941,7 @@
         <v>44721</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6046,7 +6046,7 @@
         <v>44704</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6151,7 +6151,7 @@
         <v>44645</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6256,7 +6256,7 @@
         <v>44673</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6361,7 +6361,7 @@
         <v>46161</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6466,7 +6466,7 @@
         <v>46161</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6571,7 +6571,7 @@
         <v>45098</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6676,7 +6676,7 @@
         <v>45533</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6781,7 +6781,7 @@
         <v>45369</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6886,7 +6886,7 @@
         <v>45279</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6991,7 +6991,7 @@
         <v>45594</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7101,7 +7101,7 @@
         <v>45594</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7211,7 +7211,7 @@
         <v>45754</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7316,7 +7316,7 @@
         <v>45392</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7426,7 +7426,7 @@
         <v>45964</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7535,7 +7535,7 @@
         <v>45978</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7644,7 +7644,7 @@
         <v>46199</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7749,7 +7749,7 @@
         <v>45280</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7854,7 +7854,7 @@
         <v>44894</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7959,7 +7959,7 @@
         <v>46281</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8064,7 +8064,7 @@
         <v>46288</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8169,7 +8169,7 @@
         <v>46045</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8274,7 +8274,7 @@
         <v>45617</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8384,7 +8384,7 @@
         <v>45606</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8489,7 +8489,7 @@
         <v>46246</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8594,7 +8594,7 @@
         <v>46296</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8699,7 +8699,7 @@
         <v>46303</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8804,7 +8804,7 @@
         <v>45594</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8918,7 +8918,7 @@
         <v>45327</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9023,7 +9023,7 @@
         <v>44872</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9128,7 +9128,7 @@
         <v>45824</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9233,7 +9233,7 @@
         <v>45688</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9338,7 +9338,7 @@
         <v>45643</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         <v>45428</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9553,7 +9553,7 @@
         <v>45273</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9658,7 +9658,7 @@
         <v>45280</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9763,7 +9763,7 @@
         <v>44705</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9872,7 +9872,7 @@
         <v>44746</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9977,7 +9977,7 @@
         <v>44741</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10082,7 +10082,7 @@
         <v>44634</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10187,7 +10187,7 @@
         <v>44712</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10292,7 +10292,7 @@
         <v>44950</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10397,7 +10397,7 @@
         <v>45436</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10502,7 +10502,7 @@
         <v>45726</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10607,7 +10607,7 @@
         <v>45805</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10712,7 +10712,7 @@
         <v>45939</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10821,7 +10821,7 @@
         <v>46100</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10926,7 +10926,7 @@
         <v>44812</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10999,7 +10999,7 @@
         <v>44693</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11072,7 +11072,7 @@
         <v>44518</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11145,7 +11145,7 @@
         <v>44536</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11218,7 +11218,7 @@
         <v>44764</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11291,7 +11291,7 @@
         <v>44519</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11364,7 +11364,7 @@
         <v>44501</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11437,7 +11437,7 @@
         <v>44645</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11510,7 +11510,7 @@
         <v>44814</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11583,7 +11583,7 @@
         <v>44643</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11656,7 +11656,7 @@
         <v>44515</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11729,7 +11729,7 @@
         <v>44814</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11802,7 +11802,7 @@
         <v>44525</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11875,7 +11875,7 @@
         <v>44578</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11948,7 +11948,7 @@
         <v>44516</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12026,7 +12026,7 @@
         <v>44803</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12099,7 +12099,7 @@
         <v>44691</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12172,7 +12172,7 @@
         <v>44739</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12245,7 +12245,7 @@
         <v>44590</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12323,7 +12323,7 @@
         <v>44820</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12401,7 +12401,7 @@
         <v>44814</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12474,7 +12474,7 @@
         <v>44769</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12552,7 +12552,7 @@
         <v>44820</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12625,7 +12625,7 @@
         <v>44711</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12698,7 +12698,7 @@
         <v>44880</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12771,7 +12771,7 @@
         <v>44508</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12844,7 +12844,7 @@
         <v>44495</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12917,7 +12917,7 @@
         <v>44515</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12990,7 +12990,7 @@
         <v>44599</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13063,7 +13063,7 @@
         <v>44599</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13136,7 +13136,7 @@
         <v>44495</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13209,7 +13209,7 @@
         <v>44651</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13282,7 +13282,7 @@
         <v>44876</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13360,7 +13360,7 @@
         <v>44671</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13433,7 +13433,7 @@
         <v>44496</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13506,7 +13506,7 @@
         <v>44750</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13579,7 +13579,7 @@
         <v>44568</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13652,7 +13652,7 @@
         <v>44543</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13725,7 +13725,7 @@
         <v>44606</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13798,7 +13798,7 @@
         <v>44613</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13871,7 +13871,7 @@
         <v>44746</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13944,7 +13944,7 @@
         <v>44610</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14017,7 +14017,7 @@
         <v>44610</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14090,7 +14090,7 @@
         <v>44740</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14163,7 +14163,7 @@
         <v>44617</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14236,7 +14236,7 @@
         <v>44726</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14309,7 +14309,7 @@
         <v>44551</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14382,7 +14382,7 @@
         <v>44599</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14455,7 +14455,7 @@
         <v>44781</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14528,7 +14528,7 @@
         <v>44494</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14601,7 +14601,7 @@
         <v>44704</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14674,7 +14674,7 @@
         <v>44522</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14747,7 +14747,7 @@
         <v>44532</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14820,7 +14820,7 @@
         <v>44532</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14893,7 +14893,7 @@
         <v>44498</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14966,7 +14966,7 @@
         <v>44860</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15039,7 +15039,7 @@
         <v>44596</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15112,7 +15112,7 @@
         <v>44573</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15185,7 +15185,7 @@
         <v>44712</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15258,7 +15258,7 @@
         <v>44579</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15331,7 +15331,7 @@
         <v>44711</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15404,7 +15404,7 @@
         <v>44769</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15482,7 +15482,7 @@
         <v>44502</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15560,7 +15560,7 @@
         <v>44812</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15633,7 +15633,7 @@
         <v>44508</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15706,7 +15706,7 @@
         <v>44574</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15779,7 +15779,7 @@
         <v>44537</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15852,7 +15852,7 @@
         <v>44537</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15925,7 +15925,7 @@
         <v>44571</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15998,7 +15998,7 @@
         <v>44603</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16076,7 +16076,7 @@
         <v>44596</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16149,7 +16149,7 @@
         <v>44560</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16222,7 +16222,7 @@
         <v>44998</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16295,7 +16295,7 @@
         <v>44592</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16368,7 +16368,7 @@
         <v>44820</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16446,7 +16446,7 @@
         <v>44820</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16524,7 +16524,7 @@
         <v>45229</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16597,7 +16597,7 @@
         <v>45103</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16670,7 +16670,7 @@
         <v>45222</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16743,7 +16743,7 @@
         <v>45754</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16816,7 +16816,7 @@
         <v>45412</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16889,7 +16889,7 @@
         <v>44741</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16962,7 +16962,7 @@
         <v>44741</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17035,7 +17035,7 @@
         <v>45194</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17108,7 +17108,7 @@
         <v>45058</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17181,7 +17181,7 @@
         <v>45219</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17254,7 +17254,7 @@
         <v>44814</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17327,7 +17327,7 @@
         <v>44814</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17400,7 +17400,7 @@
         <v>44547</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17473,7 +17473,7 @@
         <v>44741</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17546,7 +17546,7 @@
         <v>45715</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17619,7 +17619,7 @@
         <v>45280</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17692,7 +17692,7 @@
         <v>45894</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17765,7 +17765,7 @@
         <v>45890</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17838,7 +17838,7 @@
         <v>44880</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17911,7 +17911,7 @@
         <v>45856</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17984,7 +17984,7 @@
         <v>45895</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18057,7 +18057,7 @@
         <v>45201</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18130,7 +18130,7 @@
         <v>45281</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18203,7 +18203,7 @@
         <v>45315</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18276,7 +18276,7 @@
         <v>45315</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18349,7 +18349,7 @@
         <v>45897</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18427,7 +18427,7 @@
         <v>45622</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18500,7 +18500,7 @@
         <v>45240</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18573,7 +18573,7 @@
         <v>45883</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18646,7 +18646,7 @@
         <v>45754</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18719,7 +18719,7 @@
         <v>45754</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18792,7 +18792,7 @@
         <v>44979</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18865,7 +18865,7 @@
         <v>45645</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18938,7 +18938,7 @@
         <v>45719</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19011,7 +19011,7 @@
         <v>45386</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19084,7 +19084,7 @@
         <v>45902</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19157,7 +19157,7 @@
         <v>45902</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19230,7 +19230,7 @@
         <v>45359</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19303,7 +19303,7 @@
         <v>45225</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19376,7 +19376,7 @@
         <v>45902</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19449,7 +19449,7 @@
         <v>45810</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19527,7 +19527,7 @@
         <v>45835</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19600,7 +19600,7 @@
         <v>44959</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19673,7 +19673,7 @@
         <v>44867</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19746,7 +19746,7 @@
         <v>45372</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19819,7 +19819,7 @@
         <v>45594</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19897,7 +19897,7 @@
         <v>45594</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19975,7 +19975,7 @@
         <v>45905</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20048,7 +20048,7 @@
         <v>45127</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20121,7 +20121,7 @@
         <v>45230</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20194,7 +20194,7 @@
         <v>45623</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20267,7 +20267,7 @@
         <v>44843</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20340,7 +20340,7 @@
         <v>45910</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20413,7 +20413,7 @@
         <v>44894</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20486,7 +20486,7 @@
         <v>46162</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20559,7 +20559,7 @@
         <v>45909</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20632,7 +20632,7 @@
         <v>46162</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20705,7 +20705,7 @@
         <v>45245</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20778,7 +20778,7 @@
         <v>44963</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20851,7 +20851,7 @@
         <v>45780</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20924,7 +20924,7 @@
         <v>45787</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20997,7 +20997,7 @@
         <v>46162</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21070,7 +21070,7 @@
         <v>45719</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21143,7 +21143,7 @@
         <v>45911</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21216,7 +21216,7 @@
         <v>46163</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21289,7 +21289,7 @@
         <v>45540</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21362,7 +21362,7 @@
         <v>46163</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21435,7 +21435,7 @@
         <v>45597</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21508,7 +21508,7 @@
         <v>46163</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21581,7 +21581,7 @@
         <v>46163</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21654,7 +21654,7 @@
         <v>45219</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21727,7 +21727,7 @@
         <v>45061</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21800,7 +21800,7 @@
         <v>45812</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21873,7 +21873,7 @@
         <v>45572</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21946,7 +21946,7 @@
         <v>46163</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22019,7 +22019,7 @@
         <v>45304</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22092,7 +22092,7 @@
         <v>45918</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22165,7 +22165,7 @@
         <v>46163</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22238,7 +22238,7 @@
         <v>46168</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22311,7 +22311,7 @@
         <v>45029</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22384,7 +22384,7 @@
         <v>44992</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22457,7 +22457,7 @@
         <v>45933</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22530,7 +22530,7 @@
         <v>45552</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22603,7 +22603,7 @@
         <v>45199</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22676,7 +22676,7 @@
         <v>45181</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22749,7 +22749,7 @@
         <v>46167</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22822,7 +22822,7 @@
         <v>45924</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22895,7 +22895,7 @@
         <v>45147</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22968,7 +22968,7 @@
         <v>46168</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23041,7 +23041,7 @@
         <v>45105</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23114,7 +23114,7 @@
         <v>44501</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23187,7 +23187,7 @@
         <v>45925</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23260,7 +23260,7 @@
         <v>45557</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23333,7 +23333,7 @@
         <v>46100</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23406,7 +23406,7 @@
         <v>45216</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23479,7 +23479,7 @@
         <v>46112</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23552,7 +23552,7 @@
         <v>46171</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23625,7 +23625,7 @@
         <v>46171</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23698,7 +23698,7 @@
         <v>45324</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23771,7 +23771,7 @@
         <v>46170</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23844,7 +23844,7 @@
         <v>45219</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23917,7 +23917,7 @@
         <v>46010</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23990,7 +23990,7 @@
         <v>46171</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24063,7 +24063,7 @@
         <v>45554</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24136,7 +24136,7 @@
         <v>44761</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24214,7 +24214,7 @@
         <v>45468</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24287,7 +24287,7 @@
         <v>45937</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24360,7 +24360,7 @@
         <v>45057</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24433,7 +24433,7 @@
         <v>45937</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24506,7 +24506,7 @@
         <v>45427</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24579,7 +24579,7 @@
         <v>45400</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24652,7 +24652,7 @@
         <v>45594</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24730,7 +24730,7 @@
         <v>45446</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24803,7 +24803,7 @@
         <v>44977</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24876,7 +24876,7 @@
         <v>45009</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24954,7 +24954,7 @@
         <v>45679</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25027,7 +25027,7 @@
         <v>44602</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25100,7 +25100,7 @@
         <v>44732</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25173,7 +25173,7 @@
         <v>45176</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25246,7 +25246,7 @@
         <v>45896</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25319,7 +25319,7 @@
         <v>45259</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25392,7 +25392,7 @@
         <v>44874</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25465,7 +25465,7 @@
         <v>44956</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25538,7 +25538,7 @@
         <v>45281</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25611,7 +25611,7 @@
         <v>45392</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25689,7 +25689,7 @@
         <v>44894</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25767,7 +25767,7 @@
         <v>45090</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25840,7 +25840,7 @@
         <v>45300</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25913,7 +25913,7 @@
         <v>45302</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25986,7 +25986,7 @@
         <v>45019</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26059,7 +26059,7 @@
         <v>45611</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26132,7 +26132,7 @@
         <v>46134</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26205,7 +26205,7 @@
         <v>45386</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26278,7 +26278,7 @@
         <v>45676</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26356,7 +26356,7 @@
         <v>45162</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26429,7 +26429,7 @@
         <v>45162</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26502,7 +26502,7 @@
         <v>46134</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26575,7 +26575,7 @@
         <v>45392</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26653,7 +26653,7 @@
         <v>45392</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26731,7 +26731,7 @@
         <v>45446</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26809,7 +26809,7 @@
         <v>44986</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26882,7 +26882,7 @@
         <v>45581</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26955,7 +26955,7 @@
         <v>45504</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27028,7 +27028,7 @@
         <v>45432</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27101,7 +27101,7 @@
         <v>44502</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27179,7 +27179,7 @@
         <v>45049</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27252,7 +27252,7 @@
         <v>44896</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27325,7 +27325,7 @@
         <v>45665</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27398,7 +27398,7 @@
         <v>45762</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27476,7 +27476,7 @@
         <v>46134</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27549,7 +27549,7 @@
         <v>46170</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27622,7 +27622,7 @@
         <v>45153</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27695,7 +27695,7 @@
         <v>46183</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27768,7 +27768,7 @@
         <v>45952</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27841,7 +27841,7 @@
         <v>45923</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27914,7 +27914,7 @@
         <v>45679</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27987,7 +27987,7 @@
         <v>45296</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28060,7 +28060,7 @@
         <v>46183</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28133,7 +28133,7 @@
         <v>46183</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28206,7 +28206,7 @@
         <v>45617</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28279,7 +28279,7 @@
         <v>45769</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28352,7 +28352,7 @@
         <v>46183</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28425,7 +28425,7 @@
         <v>44687</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28498,7 +28498,7 @@
         <v>45211</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28571,7 +28571,7 @@
         <v>45632</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28644,7 +28644,7 @@
         <v>45946</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28717,7 +28717,7 @@
         <v>45232</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28790,7 +28790,7 @@
         <v>45953</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28863,7 +28863,7 @@
         <v>45139</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28936,7 +28936,7 @@
         <v>45924</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29009,7 +29009,7 @@
         <v>46189</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29082,7 +29082,7 @@
         <v>45964</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29155,7 +29155,7 @@
         <v>45373</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29228,7 +29228,7 @@
         <v>45448</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29301,7 +29301,7 @@
         <v>46188</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29374,7 +29374,7 @@
         <v>45022</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29447,7 +29447,7 @@
         <v>46191</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29520,7 +29520,7 @@
         <v>45693</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29593,7 +29593,7 @@
         <v>45317</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29666,7 +29666,7 @@
         <v>45555</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29739,7 +29739,7 @@
         <v>46190</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29812,7 +29812,7 @@
         <v>45309</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29885,7 +29885,7 @@
         <v>45309</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29958,7 +29958,7 @@
         <v>46191</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30031,7 +30031,7 @@
         <v>46108</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30104,7 +30104,7 @@
         <v>45971</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30177,7 +30177,7 @@
         <v>45924</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30250,7 +30250,7 @@
         <v>45108</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30323,7 +30323,7 @@
         <v>45169</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30396,7 +30396,7 @@
         <v>45608</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30469,7 +30469,7 @@
         <v>45205</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30542,7 +30542,7 @@
         <v>45070</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30615,7 +30615,7 @@
         <v>46199</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30688,7 +30688,7 @@
         <v>44900</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30761,7 +30761,7 @@
         <v>45973</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30834,7 +30834,7 @@
         <v>44900</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30907,7 +30907,7 @@
         <v>46199</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30980,7 +30980,7 @@
         <v>46198</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31053,7 +31053,7 @@
         <v>44532</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31126,7 +31126,7 @@
         <v>46198</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31199,7 +31199,7 @@
         <v>45181</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31272,7 +31272,7 @@
         <v>45236</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31345,7 +31345,7 @@
         <v>45112</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31418,7 +31418,7 @@
         <v>46198</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31491,7 +31491,7 @@
         <v>46198</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31564,7 +31564,7 @@
         <v>45979</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31637,7 +31637,7 @@
         <v>44929</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31715,7 +31715,7 @@
         <v>45979</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31788,7 +31788,7 @@
         <v>45541</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31861,7 +31861,7 @@
         <v>46199</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31934,7 +31934,7 @@
         <v>44656</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32007,7 +32007,7 @@
         <v>45980</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32080,7 +32080,7 @@
         <v>45443</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32153,7 +32153,7 @@
         <v>45147</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32226,7 +32226,7 @@
         <v>45217</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32299,7 +32299,7 @@
         <v>44831</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32372,7 +32372,7 @@
         <v>46199</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32445,7 +32445,7 @@
         <v>45194</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32518,7 +32518,7 @@
         <v>45219</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32591,7 +32591,7 @@
         <v>45477</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32669,7 +32669,7 @@
         <v>45280</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32742,7 +32742,7 @@
         <v>46205</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32815,7 +32815,7 @@
         <v>45705</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32893,7 +32893,7 @@
         <v>46205</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32966,7 +32966,7 @@
         <v>45016</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33039,7 +33039,7 @@
         <v>45061</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33112,7 +33112,7 @@
         <v>45560</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33185,7 +33185,7 @@
         <v>44909</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33263,7 +33263,7 @@
         <v>44986</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33336,7 +33336,7 @@
         <v>46206</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33414,7 +33414,7 @@
         <v>45686</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33487,7 +33487,7 @@
         <v>45737</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33560,7 +33560,7 @@
         <v>45224</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33633,7 +33633,7 @@
         <v>46210</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33711,7 +33711,7 @@
         <v>45304</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33784,7 +33784,7 @@
         <v>45244</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33857,7 +33857,7 @@
         <v>45250</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33930,7 +33930,7 @@
         <v>46210</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34008,7 +34008,7 @@
         <v>45446</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34081,7 +34081,7 @@
         <v>44904</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34154,7 +34154,7 @@
         <v>44904</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34227,7 +34227,7 @@
         <v>44963</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34300,7 +34300,7 @@
         <v>44963</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34373,7 +34373,7 @@
         <v>44963</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34446,7 +34446,7 @@
         <v>45993</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34519,7 +34519,7 @@
         <v>45468</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34592,7 +34592,7 @@
         <v>45127</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34665,7 +34665,7 @@
         <v>45127</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34738,7 +34738,7 @@
         <v>45993</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34811,7 +34811,7 @@
         <v>45551</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34884,7 +34884,7 @@
         <v>45988</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34957,7 +34957,7 @@
         <v>45557</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35030,7 +35030,7 @@
         <v>44573</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35103,7 +35103,7 @@
         <v>45579</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35176,7 +35176,7 @@
         <v>45533</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35249,7 +35249,7 @@
         <v>45579</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35322,7 +35322,7 @@
         <v>45702</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35395,7 +35395,7 @@
         <v>45999</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35468,7 +35468,7 @@
         <v>46170</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35541,7 +35541,7 @@
         <v>45165</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35614,7 +35614,7 @@
         <v>46000</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35687,7 +35687,7 @@
         <v>45194</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35760,7 +35760,7 @@
         <v>46001</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35833,7 +35833,7 @@
         <v>45547</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35906,7 +35906,7 @@
         <v>45777</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35984,7 +35984,7 @@
         <v>45519</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36057,7 +36057,7 @@
         <v>45777</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36135,7 +36135,7 @@
         <v>45777</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36213,7 +36213,7 @@
         <v>45780</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36286,7 +36286,7 @@
         <v>45780</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36359,7 +36359,7 @@
         <v>44854</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36432,7 +36432,7 @@
         <v>45782</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36505,7 +36505,7 @@
         <v>45546</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36578,7 +36578,7 @@
         <v>45783</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36651,7 +36651,7 @@
         <v>46008</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36724,7 +36724,7 @@
         <v>45534</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36797,7 +36797,7 @@
         <v>46007</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36870,7 +36870,7 @@
         <v>45478</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36943,7 +36943,7 @@
         <v>46232</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37016,7 +37016,7 @@
         <v>46232</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37089,7 +37089,7 @@
         <v>46279</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37162,7 +37162,7 @@
         <v>46279</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37235,7 +37235,7 @@
         <v>45642</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37308,7 +37308,7 @@
         <v>44781</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37386,7 +37386,7 @@
         <v>46010</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37459,7 +37459,7 @@
         <v>45608</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37532,7 +37532,7 @@
         <v>46010</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37605,7 +37605,7 @@
         <v>46010</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37678,7 +37678,7 @@
         <v>45108</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37751,7 +37751,7 @@
         <v>46237</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37824,7 +37824,7 @@
         <v>46237</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37897,7 +37897,7 @@
         <v>45716</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37970,7 +37970,7 @@
         <v>45244</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38043,7 +38043,7 @@
         <v>45614</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38116,7 +38116,7 @@
         <v>46019</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38189,7 +38189,7 @@
         <v>46019</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38262,7 +38262,7 @@
         <v>45716</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38335,7 +38335,7 @@
         <v>46281</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38408,7 +38408,7 @@
         <v>46239</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38481,7 +38481,7 @@
         <v>44894</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38554,7 +38554,7 @@
         <v>46029</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38627,7 +38627,7 @@
         <v>46244</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38705,7 +38705,7 @@
         <v>46244</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38783,7 +38783,7 @@
         <v>46029</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38856,7 +38856,7 @@
         <v>46244</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38934,7 +38934,7 @@
         <v>46031</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39012,7 +39012,7 @@
         <v>46031</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39090,7 +39090,7 @@
         <v>46244</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39168,7 +39168,7 @@
         <v>45791</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39241,7 +39241,7 @@
         <v>46036</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39314,7 +39314,7 @@
         <v>46035</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39392,7 +39392,7 @@
         <v>46035</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39470,7 +39470,7 @@
         <v>46244</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39548,7 +39548,7 @@
         <v>45921</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39621,7 +39621,7 @@
         <v>46036</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39694,7 +39694,7 @@
         <v>45796</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39767,7 +39767,7 @@
         <v>46035</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39845,7 +39845,7 @@
         <v>46036</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39918,7 +39918,7 @@
         <v>46244</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39991,7 +39991,7 @@
         <v>45111</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40064,7 +40064,7 @@
         <v>46244</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40142,7 +40142,7 @@
         <v>46041</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40215,7 +40215,7 @@
         <v>46288</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40288,7 +40288,7 @@
         <v>46245</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40361,7 +40361,7 @@
         <v>46288</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40434,7 +40434,7 @@
         <v>46043</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40507,7 +40507,7 @@
         <v>46048</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40580,7 +40580,7 @@
         <v>46045</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40653,7 +40653,7 @@
         <v>45764</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40726,7 +40726,7 @@
         <v>46244</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40799,7 +40799,7 @@
         <v>46245</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -40872,7 +40872,7 @@
         <v>46045</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40945,7 +40945,7 @@
         <v>45574</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41018,7 +41018,7 @@
         <v>45665</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41091,7 +41091,7 @@
         <v>46049</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41164,7 +41164,7 @@
         <v>45154</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41237,7 +41237,7 @@
         <v>44824</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41310,7 +41310,7 @@
         <v>46289</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41383,7 +41383,7 @@
         <v>46049</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41456,7 +41456,7 @@
         <v>46049</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41529,7 +41529,7 @@
         <v>45749</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41602,7 +41602,7 @@
         <v>46051</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -41675,7 +41675,7 @@
         <v>45803</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -41748,7 +41748,7 @@
         <v>45145</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -41821,7 +41821,7 @@
         <v>46021</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -41894,7 +41894,7 @@
         <v>45294</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -41967,7 +41967,7 @@
         <v>46056</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42040,7 +42040,7 @@
         <v>45805</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42113,7 +42113,7 @@
         <v>46289</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42186,7 +42186,7 @@
         <v>45763</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42259,7 +42259,7 @@
         <v>46056</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42332,7 +42332,7 @@
         <v>46056</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42405,7 +42405,7 @@
         <v>45447</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42478,7 +42478,7 @@
         <v>46057</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42551,7 +42551,7 @@
         <v>46246</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42629,7 +42629,7 @@
         <v>46059</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42702,7 +42702,7 @@
         <v>46061</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -42775,7 +42775,7 @@
         <v>45342</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -42848,7 +42848,7 @@
         <v>46059</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -42921,7 +42921,7 @@
         <v>46059</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -42994,7 +42994,7 @@
         <v>45330</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43067,7 +43067,7 @@
         <v>44950</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43140,7 +43140,7 @@
         <v>46294</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43213,7 +43213,7 @@
         <v>46294</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43286,7 +43286,7 @@
         <v>46294</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43359,7 +43359,7 @@
         <v>46294</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -43432,7 +43432,7 @@
         <v>46237</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -43505,7 +43505,7 @@
         <v>46294</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -43578,7 +43578,7 @@
         <v>45769</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -43651,7 +43651,7 @@
         <v>45820</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -43724,7 +43724,7 @@
         <v>46294</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -43797,7 +43797,7 @@
         <v>46072</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -43870,7 +43870,7 @@
         <v>45820</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -43943,7 +43943,7 @@
         <v>46296</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44016,7 +44016,7 @@
         <v>46296</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44089,7 +44089,7 @@
         <v>46073</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44162,7 +44162,7 @@
         <v>45817</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44235,7 +44235,7 @@
         <v>46073</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44308,7 +44308,7 @@
         <v>45818</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -44381,7 +44381,7 @@
         <v>46075</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -44454,7 +44454,7 @@
         <v>46296</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -44527,7 +44527,7 @@
         <v>46296</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -44600,7 +44600,7 @@
         <v>45824</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -44673,7 +44673,7 @@
         <v>46252</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -44746,7 +44746,7 @@
         <v>45824</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -44819,7 +44819,7 @@
         <v>46296</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -44892,7 +44892,7 @@
         <v>46296</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -44965,7 +44965,7 @@
         <v>45825</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45038,7 +45038,7 @@
         <v>46253</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45111,7 +45111,7 @@
         <v>46079</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45184,7 +45184,7 @@
         <v>46079</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -45257,7 +45257,7 @@
         <v>46083</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -45330,7 +45330,7 @@
         <v>46083</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -45403,7 +45403,7 @@
         <v>46083</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -45476,7 +45476,7 @@
         <v>45827</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -45549,7 +45549,7 @@
         <v>45831</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -45622,7 +45622,7 @@
         <v>46295</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -45700,7 +45700,7 @@
         <v>46083</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -45773,7 +45773,7 @@
         <v>46083</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -45846,7 +45846,7 @@
         <v>46296</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -45919,7 +45919,7 @@
         <v>46084</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -45992,7 +45992,7 @@
         <v>45831</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46065,7 +46065,7 @@
         <v>46252</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -46138,7 +46138,7 @@
         <v>46300</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -46211,7 +46211,7 @@
         <v>45477</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -46289,7 +46289,7 @@
         <v>46087</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -46362,7 +46362,7 @@
         <v>45805</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -46435,7 +46435,7 @@
         <v>45832</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -46508,7 +46508,7 @@
         <v>45835</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -46581,7 +46581,7 @@
         <v>45835</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -46654,7 +46654,7 @@
         <v>45594</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -46732,7 +46732,7 @@
         <v>46300</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -46805,7 +46805,7 @@
         <v>45835</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -46878,7 +46878,7 @@
         <v>44545</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -46951,7 +46951,7 @@
         <v>45840</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47024,7 +47024,7 @@
         <v>45488</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47097,7 +47097,7 @@
         <v>45540</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -47170,7 +47170,7 @@
         <v>46099</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -47243,7 +47243,7 @@
         <v>46100</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -47316,7 +47316,7 @@
         <v>45846</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -47389,7 +47389,7 @@
         <v>45124</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -47462,7 +47462,7 @@
         <v>46100</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -47535,7 +47535,7 @@
         <v>46100</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -47608,7 +47608,7 @@
         <v>44880</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -47681,7 +47681,7 @@
         <v>46301</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -47754,7 +47754,7 @@
         <v>45847</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -47827,7 +47827,7 @@
         <v>44922</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -47900,7 +47900,7 @@
         <v>45390</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -47973,7 +47973,7 @@
         <v>46107</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48046,7 +48046,7 @@
         <v>46199</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -48119,7 +48119,7 @@
         <v>45853</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -48192,7 +48192,7 @@
         <v>44769</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -48270,7 +48270,7 @@
         <v>44769</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -48348,7 +48348,7 @@
         <v>46258</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -48421,7 +48421,7 @@
         <v>46108</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -48494,7 +48494,7 @@
         <v>45740</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -48567,7 +48567,7 @@
         <v>46113</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -48640,7 +48640,7 @@
         <v>44537</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -48713,7 +48713,7 @@
         <v>46112</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -48786,7 +48786,7 @@
         <v>46112</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -48859,7 +48859,7 @@
         <v>45916</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -48932,7 +48932,7 @@
         <v>45384</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -49005,7 +49005,7 @@
         <v>45097</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -49083,7 +49083,7 @@
         <v>45267</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -49156,7 +49156,7 @@
         <v>45782</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -49229,7 +49229,7 @@
         <v>46261</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -49302,7 +49302,7 @@
         <v>45594</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -49380,7 +49380,7 @@
         <v>46304</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -49453,7 +49453,7 @@
         <v>46119</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -49526,7 +49526,7 @@
         <v>45594</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -49604,7 +49604,7 @@
         <v>45874</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -49677,7 +49677,7 @@
         <v>46183</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -49750,7 +49750,7 @@
         <v>46260</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -49823,7 +49823,7 @@
         <v>46304</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -49896,7 +49896,7 @@
         <v>46183</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -49969,7 +49969,7 @@
         <v>46262</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -50042,7 +50042,7 @@
         <v>44896</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -50115,7 +50115,7 @@
         <v>46129</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -50188,7 +50188,7 @@
         <v>46307</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -50261,7 +50261,7 @@
         <v>46307</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -50334,7 +50334,7 @@
         <v>45278</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -50407,7 +50407,7 @@
         <v>46308</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -50480,7 +50480,7 @@
         <v>46307</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -50553,7 +50553,7 @@
         <v>45148</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -50626,7 +50626,7 @@
         <v>45148</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -50699,7 +50699,7 @@
         <v>45161</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -50772,7 +50772,7 @@
         <v>45288</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -50845,7 +50845,7 @@
         <v>45190</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -50918,7 +50918,7 @@
         <v>45881</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -50991,7 +50991,7 @@
         <v>45638</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -51064,7 +51064,7 @@
         <v>45573</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -51137,7 +51137,7 @@
         <v>44867</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -51210,7 +51210,7 @@
         <v>45677</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -51283,7 +51283,7 @@
         <v>45835</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -51356,7 +51356,7 @@
         <v>45743</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -51429,7 +51429,7 @@
         <v>45827</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -51502,7 +51502,7 @@
         <v>44599</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -51575,7 +51575,7 @@
         <v>45698</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -51648,7 +51648,7 @@
         <v>45810</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -51726,7 +51726,7 @@
         <v>45826</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -51804,7 +51804,7 @@
         <v>45672</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -51877,7 +51877,7 @@
         <v>45056</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -51950,7 +51950,7 @@
         <v>45670</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -52023,7 +52023,7 @@
         <v>45905</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -52096,7 +52096,7 @@
         <v>45923</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -52169,7 +52169,7 @@
         <v>45833</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -52242,7 +52242,7 @@
         <v>45883</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -52315,7 +52315,7 @@
         <v>45883</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -52388,7 +52388,7 @@
         <v>45775</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -52461,7 +52461,7 @@
         <v>44896</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -52534,7 +52534,7 @@
         <v>45846</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -52607,7 +52607,7 @@
         <v>45782</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -52680,7 +52680,7 @@
         <v>46230</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -52753,7 +52753,7 @@
         <v>46245</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -52826,7 +52826,7 @@
         <v>45559</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -52899,7 +52899,7 @@
         <v>45923</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -52972,7 +52972,7 @@
         <v>45426</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -53045,7 +53045,7 @@
         <v>45939</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -53118,7 +53118,7 @@
         <v>45827</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -53191,7 +53191,7 @@
         <v>44532</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -53264,7 +53264,7 @@
         <v>45841</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -53337,7 +53337,7 @@
         <v>45686</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -53410,7 +53410,7 @@
         <v>45390</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -53483,7 +53483,7 @@
         <v>45877</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -53556,7 +53556,7 @@
         <v>45818</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -53629,7 +53629,7 @@
         <v>44595</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -53702,7 +53702,7 @@
         <v>45555</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -53775,7 +53775,7 @@
         <v>44903</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -53848,7 +53848,7 @@
         <v>45791</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -53921,7 +53921,7 @@
         <v>44938</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -53994,7 +53994,7 @@
         <v>46269</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -54067,7 +54067,7 @@
         <v>45419</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -54140,7 +54140,7 @@
         <v>45960</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -54213,7 +54213,7 @@
         <v>45014</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -54286,7 +54286,7 @@
         <v>45412</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -54359,7 +54359,7 @@
         <v>45412</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -54432,7 +54432,7 @@
         <v>45909</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -54505,7 +54505,7 @@
         <v>45582</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -54578,7 +54578,7 @@
         <v>46216</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -54651,7 +54651,7 @@
         <v>46272</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -54724,7 +54724,7 @@
         <v>46272</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -54797,7 +54797,7 @@
         <v>45140</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -54870,7 +54870,7 @@
         <v>45894</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -54943,7 +54943,7 @@
         <v>45552</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -55016,7 +55016,7 @@
         <v>46315</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -55089,7 +55089,7 @@
         <v>46216</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -55162,7 +55162,7 @@
         <v>46216</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -55235,7 +55235,7 @@
         <v>44522</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -55308,7 +55308,7 @@
         <v>45378</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -55381,7 +55381,7 @@
         <v>45534</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -55454,7 +55454,7 @@
         <v>45560</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -55527,7 +55527,7 @@
         <v>45369</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -55600,7 +55600,7 @@
         <v>44599</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -55673,7 +55673,7 @@
         <v>44869</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -55746,7 +55746,7 @@
         <v>45338</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -55819,7 +55819,7 @@
         <v>45244</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -55892,7 +55892,7 @@
         <v>45408</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -55965,7 +55965,7 @@
         <v>46315</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -56038,7 +56038,7 @@
         <v>46315</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -56111,7 +56111,7 @@
         <v>45222</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -56184,7 +56184,7 @@
         <v>45169</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -56257,7 +56257,7 @@
         <v>45583</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -56335,7 +56335,7 @@
         <v>45392</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -56413,7 +56413,7 @@
         <v>44670</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -56486,7 +56486,7 @@
         <v>46276</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -56559,7 +56559,7 @@
         <v>46317</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -56632,7 +56632,7 @@
         <v>46317</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -56705,7 +56705,7 @@
         <v>46276</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -56778,7 +56778,7 @@
         <v>46317</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -56851,7 +56851,7 @@
         <v>46317</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -56924,7 +56924,7 @@
         <v>45329</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -56997,7 +56997,7 @@
         <v>44577</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -57070,7 +57070,7 @@
         <v>44711</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -57143,7 +57143,7 @@
         <v>45071</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -57221,7 +57221,7 @@
         <v>45583</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -57294,7 +57294,7 @@
         <v>45757</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -57367,7 +57367,7 @@
         <v>45384</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -57440,7 +57440,7 @@
         <v>46146</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -57513,7 +57513,7 @@
         <v>46146</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -57586,7 +57586,7 @@
         <v>45345</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -57659,7 +57659,7 @@
         <v>46146</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -57732,7 +57732,7 @@
         <v>45579</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -57805,7 +57805,7 @@
         <v>44970</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -57878,7 +57878,7 @@
         <v>46147</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -57951,7 +57951,7 @@
         <v>46147</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -58024,7 +58024,7 @@
         <v>46148</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -58097,7 +58097,7 @@
         <v>46147</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -58170,7 +58170,7 @@
         <v>46147</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -58243,7 +58243,7 @@
         <v>45397</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -58316,7 +58316,7 @@
         <v>46147</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -58389,7 +58389,7 @@
         <v>46149</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -58462,7 +58462,7 @@
         <v>46021</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -58535,7 +58535,7 @@
         <v>45764</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -58608,7 +58608,7 @@
         <v>46153</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -58681,7 +58681,7 @@
         <v>45189</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -58754,7 +58754,7 @@
         <v>45189</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -58827,7 +58827,7 @@
         <v>45722</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -58900,7 +58900,7 @@
         <v>44963</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -58973,7 +58973,7 @@
         <v>45463</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -59046,7 +59046,7 @@
         <v>44960</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -59119,7 +59119,7 @@
         <v>45594</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -59197,7 +59197,7 @@
         <v>45594</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -59275,7 +59275,7 @@
         <v>45594</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -59353,7 +59353,7 @@
         <v>45594</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -59431,7 +59431,7 @@
         <v>45594</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -59509,7 +59509,7 @@
         <v>45594</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -59587,7 +59587,7 @@
         <v>45594</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -59665,7 +59665,7 @@
         <v>45586</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -59738,7 +59738,7 @@
         <v>45995</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -59811,7 +59811,7 @@
         <v>45517</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -59884,7 +59884,7 @@
         <v>45281</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -59957,7 +59957,7 @@
         <v>45631</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -60030,7 +60030,7 @@
         <v>45789</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -60103,7 +60103,7 @@
         <v>45180</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -60176,7 +60176,7 @@
         <v>45714</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -60249,7 +60249,7 @@
         <v>45670</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -60322,7 +60322,7 @@
         <v>45250</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -60395,7 +60395,7 @@
         <v>45629</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -60468,7 +60468,7 @@
         <v>45328</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -60541,7 +60541,7 @@
         <v>45328</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -60614,7 +60614,7 @@
         <v>44494</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -60687,7 +60687,7 @@
         <v>45638</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -60760,7 +60760,7 @@
         <v>45611</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -60833,7 +60833,7 @@
         <v>44743</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -60906,7 +60906,7 @@
         <v>44711</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -60979,7 +60979,7 @@
         <v>45224</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -61057,7 +61057,7 @@
         <v>44966</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -61130,7 +61130,7 @@
         <v>45089</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -61203,7 +61203,7 @@
         <v>44972</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -61276,7 +61276,7 @@
         <v>44972</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -61349,7 +61349,7 @@
         <v>45519</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -61422,7 +61422,7 @@
         <v>45702</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -61495,7 +61495,7 @@
         <v>44967</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -61568,7 +61568,7 @@
         <v>45012</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -61641,7 +61641,7 @@
         <v>44981</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -61714,7 +61714,7 @@
         <v>45166</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -61787,7 +61787,7 @@
         <v>44998</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -61860,7 +61860,7 @@
         <v>45385</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -61938,7 +61938,7 @@
         <v>45385</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -62016,7 +62016,7 @@
         <v>45495</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -62089,7 +62089,7 @@
         <v>45103</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -62162,7 +62162,7 @@
         <v>45103</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -62235,7 +62235,7 @@
         <v>45103</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -62308,7 +62308,7 @@
         <v>45558</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -62381,7 +62381,7 @@
         <v>45538</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -62454,7 +62454,7 @@
         <v>45114</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -62527,7 +62527,7 @@
         <v>45114</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -62600,7 +62600,7 @@
         <v>44739</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -62673,7 +62673,7 @@
         <v>45128</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -62746,7 +62746,7 @@
         <v>45568</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -62819,7 +62819,7 @@
         <v>44774</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -62892,7 +62892,7 @@
         <v>45692</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -62965,7 +62965,7 @@
         <v>45033</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -63043,7 +63043,7 @@
         <v>45121</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -63116,7 +63116,7 @@
         <v>44782</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -63194,7 +63194,7 @@
         <v>45645</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -63267,7 +63267,7 @@
         <v>45127</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -63340,7 +63340,7 @@
         <v>45168</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -63413,7 +63413,7 @@
         <v>45460</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -63486,7 +63486,7 @@
         <v>44995</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -63559,7 +63559,7 @@
         <v>45113</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -63632,7 +63632,7 @@
         <v>45113</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -63705,7 +63705,7 @@
         <v>44536</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -63778,7 +63778,7 @@
         <v>45692</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -63851,7 +63851,7 @@
         <v>45714</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -63924,7 +63924,7 @@
         <v>44858</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -63997,7 +63997,7 @@
         <v>44502</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -64070,7 +64070,7 @@
         <v>45091</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -64143,7 +64143,7 @@
         <v>45030</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -64216,7 +64216,7 @@
         <v>45691</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -64289,7 +64289,7 @@
         <v>44812</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -64362,7 +64362,7 @@
         <v>45715</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -64440,7 +64440,7 @@
         <v>45048</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -64513,7 +64513,7 @@
         <v>45190</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -64586,7 +64586,7 @@
         <v>44991</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -64659,7 +64659,7 @@
         <v>45513</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -64732,7 +64732,7 @@
         <v>45210</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -64805,7 +64805,7 @@
         <v>44909</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -64878,7 +64878,7 @@
         <v>44922</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -64951,7 +64951,7 @@
         <v>45753</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -65024,7 +65024,7 @@
         <v>44552</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -65097,7 +65097,7 @@
         <v>45250</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -65170,7 +65170,7 @@
         <v>45141</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -65243,7 +65243,7 @@
         <v>45614</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -65316,7 +65316,7 @@
         <v>45533</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -65389,7 +65389,7 @@
         <v>44529</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -65462,7 +65462,7 @@
         <v>44641</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -65535,7 +65535,7 @@
         <v>44874</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -65608,7 +65608,7 @@
         <v>45715</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -65686,7 +65686,7 @@
         <v>45111</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -65759,7 +65759,7 @@
         <v>45714</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -65832,7 +65832,7 @@
         <v>45267</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -65905,7 +65905,7 @@
         <v>44894</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -65978,7 +65978,7 @@
         <v>45036</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -66051,7 +66051,7 @@
         <v>45599</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -66124,7 +66124,7 @@
         <v>44523</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -66197,7 +66197,7 @@
         <v>45233</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -66270,7 +66270,7 @@
         <v>44600</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -66348,7 +66348,7 @@
         <v>45632</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -66421,7 +66421,7 @@
         <v>45153</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -66494,7 +66494,7 @@
         <v>44713</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -66567,7 +66567,7 @@
         <v>44908</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -66640,7 +66640,7 @@
         <v>44897</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -66713,7 +66713,7 @@
         <v>45204</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -66786,7 +66786,7 @@
         <v>45737</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -66859,7 +66859,7 @@
         <v>45557</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -66932,7 +66932,7 @@
         <v>44928</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -67005,7 +67005,7 @@
         <v>45279</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -67078,7 +67078,7 @@
         <v>45273</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -67151,7 +67151,7 @@
         <v>45436</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -67224,7 +67224,7 @@
         <v>45106</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -67297,7 +67297,7 @@
         <v>45090</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -67370,7 +67370,7 @@
         <v>45561</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -67443,7 +67443,7 @@
         <v>45392</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -67516,7 +67516,7 @@
         <v>45447</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -67589,7 +67589,7 @@
         <v>45211</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -67662,7 +67662,7 @@
         <v>45104</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -67735,7 +67735,7 @@
         <v>45078</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -67813,7 +67813,7 @@
         <v>45726</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -67886,7 +67886,7 @@
         <v>45341</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -67959,7 +67959,7 @@
         <v>45127</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -68032,7 +68032,7 @@
         <v>45538</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -68110,7 +68110,7 @@
         <v>45128</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -68183,7 +68183,7 @@
         <v>45128</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -68256,7 +68256,7 @@
         <v>45387</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -68329,7 +68329,7 @@
         <v>45240</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -68402,7 +68402,7 @@
         <v>45121</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -68475,7 +68475,7 @@
         <v>45121</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -68548,7 +68548,7 @@
         <v>45121</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -68621,7 +68621,7 @@
         <v>45387</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -68694,7 +68694,7 @@
         <v>44959</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -68767,7 +68767,7 @@
         <v>45030</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -68840,7 +68840,7 @@
         <v>45236</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -68913,7 +68913,7 @@
         <v>45166</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -68986,7 +68986,7 @@
         <v>45446</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -69059,7 +69059,7 @@
         <v>45392</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -69137,7 +69137,7 @@
         <v>45324</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -69210,7 +69210,7 @@
         <v>45558</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -69283,7 +69283,7 @@
         <v>45309</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -69356,7 +69356,7 @@
         <v>45309</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -69429,7 +69429,7 @@
         <v>45113</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -69502,7 +69502,7 @@
         <v>45037</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -69575,7 +69575,7 @@
         <v>45037</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -69648,7 +69648,7 @@
         <v>45222</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -69721,7 +69721,7 @@
         <v>44988</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -69794,7 +69794,7 @@
         <v>45127</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -69867,7 +69867,7 @@
         <v>45048</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -69940,7 +69940,7 @@
         <v>45638</v>
       </c>
       <c r="E900" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -70013,7 +70013,7 @@
         <v>45685</v>
       </c>
       <c r="E901" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>
@@ -70086,7 +70086,7 @@
         <v>45611</v>
       </c>
       <c r="E902" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F902" t="inlineStr">
         <is>
@@ -70159,7 +70159,7 @@
         <v>45161</v>
       </c>
       <c r="E903" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F903" t="inlineStr">
         <is>
@@ -70232,7 +70232,7 @@
         <v>44866</v>
       </c>
       <c r="E904" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F904" t="inlineStr">
         <is>
@@ -70305,7 +70305,7 @@
         <v>45139</v>
       </c>
       <c r="E905" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F905" t="inlineStr">
         <is>
@@ -70378,7 +70378,7 @@
         <v>45112</v>
       </c>
       <c r="E906" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F906" t="inlineStr">
         <is>
@@ -70451,7 +70451,7 @@
         <v>45580</v>
       </c>
       <c r="E907" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F907" t="inlineStr">
         <is>
@@ -70524,7 +70524,7 @@
         <v>45014</v>
       </c>
       <c r="E908" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F908" t="inlineStr">
         <is>
@@ -70602,7 +70602,7 @@
         <v>45316</v>
       </c>
       <c r="E909" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F909" t="inlineStr">
         <is>
@@ -70675,7 +70675,7 @@
         <v>45330</v>
       </c>
       <c r="E910" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F910" t="inlineStr">
         <is>
@@ -70753,7 +70753,7 @@
         <v>45219</v>
       </c>
       <c r="E911" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F911" t="inlineStr">
         <is>
@@ -70826,7 +70826,7 @@
         <v>45330</v>
       </c>
       <c r="E912" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F912" t="inlineStr">
         <is>
@@ -70899,7 +70899,7 @@
         <v>45644</v>
       </c>
       <c r="E913" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F913" t="inlineStr">
         <is>
@@ -70972,7 +70972,7 @@
         <v>45198</v>
       </c>
       <c r="E914" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F914" t="inlineStr">
         <is>
@@ -71045,7 +71045,7 @@
         <v>45008</v>
       </c>
       <c r="E915" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F915" t="inlineStr">
         <is>
@@ -71118,7 +71118,7 @@
         <v>45000</v>
       </c>
       <c r="E916" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F916" t="inlineStr">
         <is>
@@ -71191,7 +71191,7 @@
         <v>44609</v>
       </c>
       <c r="E917" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F917" t="inlineStr">
         <is>
@@ -71264,7 +71264,7 @@
         <v>45733</v>
       </c>
       <c r="E918" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F918" t="inlineStr">
         <is>
@@ -71337,7 +71337,7 @@
         <v>45722</v>
       </c>
       <c r="E919" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F919" t="inlineStr">
         <is>
@@ -71410,7 +71410,7 @@
         <v>45036</v>
       </c>
       <c r="E920" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F920" t="inlineStr">
         <is>
@@ -71483,7 +71483,7 @@
         <v>45065</v>
       </c>
       <c r="E921" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F921" t="inlineStr">
         <is>
@@ -71556,7 +71556,7 @@
         <v>45028</v>
       </c>
       <c r="E922" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F922" t="inlineStr">
         <is>
@@ -71629,7 +71629,7 @@
         <v>45594</v>
       </c>
       <c r="E923" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F923" t="inlineStr">
         <is>
@@ -71707,7 +71707,7 @@
         <v>45594</v>
       </c>
       <c r="E924" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F924" t="inlineStr">
         <is>
@@ -71785,7 +71785,7 @@
         <v>45594</v>
       </c>
       <c r="E925" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F925" t="inlineStr">
         <is>
@@ -71863,7 +71863,7 @@
         <v>45594</v>
       </c>
       <c r="E926" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F926" t="inlineStr">
         <is>
@@ -71941,7 +71941,7 @@
         <v>45509</v>
       </c>
       <c r="E927" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F927" t="inlineStr">
         <is>
@@ -72014,7 +72014,7 @@
         <v>45644</v>
       </c>
       <c r="E928" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F928" t="inlineStr">
         <is>
@@ -72087,7 +72087,7 @@
         <v>45594</v>
       </c>
       <c r="E929" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F929" t="inlineStr">
         <is>
@@ -72165,7 +72165,7 @@
         <v>45594</v>
       </c>
       <c r="E930" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F930" t="inlineStr">
         <is>
@@ -72243,7 +72243,7 @@
         <v>45594</v>
       </c>
       <c r="E931" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F931" t="inlineStr">
         <is>
@@ -72321,7 +72321,7 @@
         <v>45601</v>
       </c>
       <c r="E932" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F932" t="inlineStr">
         <is>
@@ -72394,7 +72394,7 @@
         <v>45316</v>
       </c>
       <c r="E933" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F933" t="inlineStr">
         <is>
@@ -72467,7 +72467,7 @@
         <v>45316</v>
       </c>
       <c r="E934" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F934" t="inlineStr">
         <is>
@@ -72540,7 +72540,7 @@
         <v>45056</v>
       </c>
       <c r="E935" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F935" t="inlineStr">
         <is>
@@ -72613,7 +72613,7 @@
         <v>44858</v>
       </c>
       <c r="E936" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F936" t="inlineStr">
         <is>
@@ -72686,7 +72686,7 @@
         <v>45372</v>
       </c>
       <c r="E937" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F937" t="inlineStr">
         <is>
@@ -72759,7 +72759,7 @@
         <v>44764</v>
       </c>
       <c r="E938" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F938" t="inlineStr">
         <is>
@@ -72832,7 +72832,7 @@
         <v>45091</v>
       </c>
       <c r="E939" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F939" t="inlineStr">
         <is>
@@ -72910,7 +72910,7 @@
         <v>45579</v>
       </c>
       <c r="E940" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F940" t="inlineStr">
         <is>
@@ -72983,7 +72983,7 @@
         <v>45385</v>
       </c>
       <c r="E941" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F941" t="inlineStr">
         <is>
@@ -73061,7 +73061,7 @@
         <v>45385</v>
       </c>
       <c r="E942" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F942" t="inlineStr">
         <is>
@@ -73139,7 +73139,7 @@
         <v>45440</v>
       </c>
       <c r="E943" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F943" t="inlineStr">
         <is>
@@ -73212,7 +73212,7 @@
         <v>45679</v>
       </c>
       <c r="E944" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F944" t="inlineStr">
         <is>
@@ -73285,7 +73285,7 @@
         <v>45215</v>
       </c>
       <c r="E945" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F945" t="inlineStr">
         <is>
@@ -73358,7 +73358,7 @@
         <v>44876</v>
       </c>
       <c r="E946" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F946" t="inlineStr">
         <is>
@@ -73436,7 +73436,7 @@
         <v>45495</v>
       </c>
       <c r="E947" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F947" t="inlineStr">
         <is>
@@ -73509,7 +73509,7 @@
         <v>45210</v>
       </c>
       <c r="E948" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F948" t="inlineStr">
         <is>
@@ -73582,7 +73582,7 @@
         <v>45754</v>
       </c>
       <c r="E949" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F949" t="inlineStr">
         <is>
@@ -73655,7 +73655,7 @@
         <v>45244</v>
       </c>
       <c r="E950" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F950" t="inlineStr">
         <is>
@@ -73728,7 +73728,7 @@
         <v>44679</v>
       </c>
       <c r="E951" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F951" t="inlineStr">
         <is>
@@ -73801,7 +73801,7 @@
         <v>44678</v>
       </c>
       <c r="E952" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F952" t="inlineStr">
         <is>
@@ -73874,7 +73874,7 @@
         <v>45775</v>
       </c>
       <c r="E953" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F953" t="inlineStr">
         <is>
@@ -73947,7 +73947,7 @@
         <v>44802</v>
       </c>
       <c r="E954" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F954" t="inlineStr">
         <is>
@@ -74020,7 +74020,7 @@
         <v>45420</v>
       </c>
       <c r="E955" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F955" t="inlineStr">
         <is>
@@ -74093,7 +74093,7 @@
         <v>45140</v>
       </c>
       <c r="E956" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F956" t="inlineStr">
         <is>
@@ -74166,7 +74166,7 @@
         <v>45686</v>
       </c>
       <c r="E957" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F957" t="inlineStr">
         <is>
@@ -74239,7 +74239,7 @@
         <v>45686</v>
       </c>
       <c r="E958" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F958" t="inlineStr">
         <is>
@@ -74312,7 +74312,7 @@
         <v>45085</v>
       </c>
       <c r="E959" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F959" t="inlineStr">
         <is>
@@ -74385,7 +74385,7 @@
         <v>44676</v>
       </c>
       <c r="E960" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F960" t="inlineStr">
         <is>
@@ -74463,7 +74463,7 @@
         <v>44620</v>
       </c>
       <c r="E961" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F961" t="inlineStr">
         <is>
@@ -74536,7 +74536,7 @@
         <v>45253</v>
       </c>
       <c r="E962" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F962" t="inlineStr">
         <is>
@@ -74609,7 +74609,7 @@
         <v>45247</v>
       </c>
       <c r="E963" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F963" t="inlineStr">
         <is>
@@ -74682,7 +74682,7 @@
         <v>44676</v>
       </c>
       <c r="E964" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F964" t="inlineStr">
         <is>
@@ -74760,7 +74760,7 @@
         <v>45236</v>
       </c>
       <c r="E965" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F965" t="inlineStr">
         <is>
@@ -74833,7 +74833,7 @@
         <v>45236</v>
       </c>
       <c r="E966" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F966" t="inlineStr">
         <is>
@@ -74906,7 +74906,7 @@
         <v>45114</v>
       </c>
       <c r="E967" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F967" t="inlineStr">
         <is>
@@ -74979,7 +74979,7 @@
         <v>45679</v>
       </c>
       <c r="E968" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F968" t="inlineStr">
         <is>
@@ -75052,7 +75052,7 @@
         <v>44690</v>
       </c>
       <c r="E969" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F969" t="inlineStr">
         <is>
@@ -75125,7 +75125,7 @@
         <v>44705</v>
       </c>
       <c r="E970" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F970" t="inlineStr">
         <is>
@@ -75198,7 +75198,7 @@
         <v>44651</v>
       </c>
       <c r="E971" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F971" t="inlineStr">
         <is>
@@ -75271,7 +75271,7 @@
         <v>45460</v>
       </c>
       <c r="E972" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F972" t="inlineStr">
         <is>
@@ -75344,7 +75344,7 @@
         <v>45421</v>
       </c>
       <c r="E973" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F973" t="inlineStr">
         <is>
@@ -75417,7 +75417,7 @@
         <v>45188</v>
       </c>
       <c r="E974" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F974" t="inlineStr">
         <is>
@@ -75490,7 +75490,7 @@
         <v>45176</v>
       </c>
       <c r="E975" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F975" t="inlineStr">
         <is>
@@ -75563,7 +75563,7 @@
         <v>45121</v>
       </c>
       <c r="E976" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F976" t="inlineStr">
         <is>
@@ -75636,7 +75636,7 @@
         <v>45250</v>
       </c>
       <c r="E977" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F977" t="inlineStr">
         <is>
@@ -75709,7 +75709,7 @@
         <v>44746</v>
       </c>
       <c r="E978" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F978" t="inlineStr">
         <is>
@@ -75782,7 +75782,7 @@
         <v>45753</v>
       </c>
       <c r="E979" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F979" t="inlineStr">
         <is>
@@ -75855,7 +75855,7 @@
         <v>45288</v>
       </c>
       <c r="E980" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F980" t="inlineStr">
         <is>
@@ -75928,7 +75928,7 @@
         <v>44686</v>
       </c>
       <c r="E981" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F981" t="inlineStr">
         <is>
@@ -76001,7 +76001,7 @@
         <v>45260</v>
       </c>
       <c r="E982" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F982" t="inlineStr">
         <is>
@@ -76074,7 +76074,7 @@
         <v>44915</v>
       </c>
       <c r="E983" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F983" t="inlineStr">
         <is>
@@ -76147,7 +76147,7 @@
         <v>44651</v>
       </c>
       <c r="E984" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F984" t="inlineStr">
         <is>
@@ -76220,7 +76220,7 @@
         <v>44831</v>
       </c>
       <c r="E985" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F985" t="inlineStr">
         <is>
@@ -76293,7 +76293,7 @@
         <v>45301</v>
       </c>
       <c r="E986" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F986" t="inlineStr">
         <is>
@@ -76366,7 +76366,7 @@
         <v>45247</v>
       </c>
       <c r="E987" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F987" t="inlineStr">
         <is>
@@ -76439,7 +76439,7 @@
         <v>45309</v>
       </c>
       <c r="E988" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F988" t="inlineStr">
         <is>
@@ -76512,7 +76512,7 @@
         <v>45121</v>
       </c>
       <c r="E989" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F989" t="inlineStr">
         <is>
@@ -76585,7 +76585,7 @@
         <v>44677</v>
       </c>
       <c r="E990" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F990" t="inlineStr">
         <is>
@@ -76658,7 +76658,7 @@
         <v>44811</v>
       </c>
       <c r="E991" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F991" t="inlineStr">
         <is>
@@ -76731,7 +76731,7 @@
         <v>44749</v>
       </c>
       <c r="E992" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F992" t="inlineStr">
         <is>
@@ -76804,7 +76804,7 @@
         <v>45104</v>
       </c>
       <c r="E993" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F993" t="inlineStr">
         <is>
@@ -76877,7 +76877,7 @@
         <v>44496</v>
       </c>
       <c r="E994" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F994" t="inlineStr">
         <is>
@@ -76950,7 +76950,7 @@
         <v>44858</v>
       </c>
       <c r="E995" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F995" t="inlineStr">
         <is>
@@ -77023,7 +77023,7 @@
         <v>45274</v>
       </c>
       <c r="E996" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F996" t="inlineStr">
         <is>
@@ -77096,7 +77096,7 @@
         <v>45246</v>
       </c>
       <c r="E997" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F997" t="inlineStr">
         <is>
@@ -77169,7 +77169,7 @@
         <v>45743</v>
       </c>
       <c r="E998" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F998" t="inlineStr">
         <is>
@@ -77242,7 +77242,7 @@
         <v>45198</v>
       </c>
       <c r="E999" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F999" t="inlineStr">
         <is>
@@ -77315,7 +77315,7 @@
         <v>45644</v>
       </c>
       <c r="E1000" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F1000" t="inlineStr">
         <is>
@@ -77388,7 +77388,7 @@
         <v>45128</v>
       </c>
       <c r="E1001" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F1001" t="inlineStr">
         <is>
@@ -77461,7 +77461,7 @@
         <v>45686</v>
       </c>
       <c r="E1002" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F1002" t="inlineStr">
         <is>
@@ -77534,7 +77534,7 @@
         <v>45278</v>
       </c>
       <c r="E1003" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F1003" t="inlineStr">
         <is>
@@ -77607,7 +77607,7 @@
         <v>45559</v>
       </c>
       <c r="E1004" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F1004" t="inlineStr">
         <is>
@@ -77680,7 +77680,7 @@
         <v>45181</v>
       </c>
       <c r="E1005" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F1005" t="inlineStr">
         <is>
@@ -77753,7 +77753,7 @@
         <v>45141</v>
       </c>
       <c r="E1006" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F1006" t="inlineStr">
         <is>
@@ -77826,7 +77826,7 @@
         <v>45194</v>
       </c>
       <c r="E1007" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F1007" t="inlineStr">
         <is>
@@ -77899,7 +77899,7 @@
         <v>45302</v>
       </c>
       <c r="E1008" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F1008" t="inlineStr">
         <is>
@@ -77972,7 +77972,7 @@
         <v>45726</v>
       </c>
       <c r="E1009" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F1009" t="inlineStr">
         <is>
@@ -78045,7 +78045,7 @@
         <v>45401</v>
       </c>
       <c r="E1010" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F1010" t="inlineStr">
         <is>
@@ -78118,7 +78118,7 @@
         <v>45244</v>
       </c>
       <c r="E1011" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F1011" t="inlineStr">
         <is>
@@ -78191,7 +78191,7 @@
         <v>45152</v>
       </c>
       <c r="E1012" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F1012" t="inlineStr">
         <is>
@@ -78264,7 +78264,7 @@
         <v>45702</v>
       </c>
       <c r="E1013" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F1013" t="inlineStr">
         <is>
@@ -78337,7 +78337,7 @@
         <v>45541</v>
       </c>
       <c r="E1014" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F1014" t="inlineStr">
         <is>
@@ -78410,7 +78410,7 @@
         <v>45300</v>
       </c>
       <c r="E1015" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F1015" t="inlineStr">
         <is>
@@ -78483,7 +78483,7 @@
         <v>45300</v>
       </c>
       <c r="E1016" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F1016" t="inlineStr">
         <is>
@@ -78556,7 +78556,7 @@
         <v>45342</v>
       </c>
       <c r="E1017" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F1017" t="inlineStr">
         <is>
@@ -78629,7 +78629,7 @@
         <v>45302</v>
       </c>
       <c r="E1018" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F1018" t="inlineStr">
         <is>
@@ -78702,7 +78702,7 @@
         <v>45322</v>
       </c>
       <c r="E1019" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F1019" t="inlineStr">
         <is>
@@ -78775,7 +78775,7 @@
         <v>44915</v>
       </c>
       <c r="E1020" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F1020" t="inlineStr">
         <is>
@@ -78848,7 +78848,7 @@
         <v>44652</v>
       </c>
       <c r="E1021" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F1021" t="inlineStr">
         <is>
@@ -78921,7 +78921,7 @@
         <v>44537</v>
       </c>
       <c r="E1022" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F1022" t="inlineStr">
         <is>
@@ -78994,7 +78994,7 @@
         <v>44609</v>
       </c>
       <c r="E1023" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F1023" t="inlineStr">
         <is>
@@ -79067,7 +79067,7 @@
         <v>45183</v>
       </c>
       <c r="E1024" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F1024" t="inlineStr">
         <is>
@@ -79140,7 +79140,7 @@
         <v>45121</v>
       </c>
       <c r="E1025" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F1025" t="inlineStr">
         <is>
@@ -79213,7 +79213,7 @@
         <v>45420</v>
       </c>
       <c r="E1026" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F1026" t="inlineStr">
         <is>
@@ -79286,7 +79286,7 @@
         <v>45253</v>
       </c>
       <c r="E1027" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F1027" t="inlineStr">
         <is>
@@ -79359,7 +79359,7 @@
         <v>44845</v>
       </c>
       <c r="E1028" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F1028" t="inlineStr">
         <is>
@@ -79432,7 +79432,7 @@
         <v>44915</v>
       </c>
       <c r="E1029" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F1029" t="inlineStr">
         <is>
@@ -79505,7 +79505,7 @@
         <v>44552</v>
       </c>
       <c r="E1030" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F1030" t="inlineStr">
         <is>
@@ -79578,7 +79578,7 @@
         <v>45070</v>
       </c>
       <c r="E1031" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F1031" t="inlineStr">
         <is>
@@ -79651,7 +79651,7 @@
         <v>44715</v>
       </c>
       <c r="E1032" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F1032" t="inlineStr">
         <is>
@@ -79724,7 +79724,7 @@
         <v>44722</v>
       </c>
       <c r="E1033" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F1033" t="inlineStr">
         <is>
@@ -79797,7 +79797,7 @@
         <v>44588</v>
       </c>
       <c r="E1034" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F1034" t="inlineStr">
         <is>
@@ -79870,7 +79870,7 @@
         <v>44727</v>
       </c>
       <c r="E1035" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F1035" t="inlineStr">
         <is>
@@ -79943,7 +79943,7 @@
         <v>44722</v>
       </c>
       <c r="E1036" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F1036" t="inlineStr">
         <is>
@@ -80016,7 +80016,7 @@
         <v>44603</v>
       </c>
       <c r="E1037" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F1037" t="inlineStr">
         <is>
@@ -80089,7 +80089,7 @@
         <v>44693</v>
       </c>
       <c r="E1038" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F1038" t="inlineStr">
         <is>
@@ -80162,7 +80162,7 @@
         <v>44726</v>
       </c>
       <c r="E1039" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F1039" t="inlineStr">
         <is>
@@ -80235,7 +80235,7 @@
         <v>44712</v>
       </c>
       <c r="E1040" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F1040" t="inlineStr">
         <is>
@@ -80308,7 +80308,7 @@
         <v>44722</v>
       </c>
       <c r="E1041" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F1041" t="inlineStr">
         <is>
@@ -80381,7 +80381,7 @@
         <v>44712</v>
       </c>
       <c r="E1042" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F1042" t="inlineStr">
         <is>
@@ -80454,7 +80454,7 @@
         <v>44704</v>
       </c>
       <c r="E1043" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F1043" t="inlineStr">
         <is>
@@ -80527,7 +80527,7 @@
         <v>44596</v>
       </c>
       <c r="E1044" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F1044" t="inlineStr">
         <is>
@@ -80600,7 +80600,7 @@
         <v>44704</v>
       </c>
       <c r="E1045" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F1045" t="inlineStr">
         <is>
@@ -80673,7 +80673,7 @@
         <v>44588</v>
       </c>
       <c r="E1046" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F1046" t="inlineStr">
         <is>
@@ -80746,7 +80746,7 @@
         <v>45054</v>
       </c>
       <c r="E1047" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F1047" t="inlineStr">
         <is>
@@ -80819,7 +80819,7 @@
         <v>45230</v>
       </c>
       <c r="E1048" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F1048" t="inlineStr">
         <is>
@@ -80897,7 +80897,7 @@
         <v>44498</v>
       </c>
       <c r="E1049" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F1049" t="inlineStr">
         <is>
@@ -80970,7 +80970,7 @@
         <v>45622</v>
       </c>
       <c r="E1050" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F1050" t="inlineStr">
         <is>
@@ -81043,7 +81043,7 @@
         <v>45054</v>
       </c>
       <c r="E1051" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F1051" t="inlineStr">
         <is>
@@ -81116,7 +81116,7 @@
         <v>45054</v>
       </c>
       <c r="E1052" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F1052" t="inlineStr">
         <is>
@@ -81189,7 +81189,7 @@
         <v>45056</v>
       </c>
       <c r="E1053" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F1053" t="inlineStr">
         <is>
@@ -81262,7 +81262,7 @@
         <v>45434</v>
       </c>
       <c r="E1054" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F1054" t="inlineStr">
         <is>
@@ -81335,7 +81335,7 @@
         <v>45054</v>
       </c>
       <c r="E1055" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F1055" t="inlineStr">
         <is>
@@ -81408,7 +81408,7 @@
         <v>45407</v>
       </c>
       <c r="E1056" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F1056" t="inlineStr">
         <is>
@@ -81481,7 +81481,7 @@
         <v>44802</v>
       </c>
       <c r="E1057" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F1057" t="inlineStr">
         <is>
@@ -81554,7 +81554,7 @@
         <v>45071</v>
       </c>
       <c r="E1058" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F1058" t="inlineStr">
         <is>
@@ -81627,7 +81627,7 @@
         <v>44495</v>
       </c>
       <c r="E1059" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F1059" t="inlineStr">
         <is>
@@ -81700,7 +81700,7 @@
         <v>45224</v>
       </c>
       <c r="E1060" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F1060" t="inlineStr">
         <is>
@@ -81778,7 +81778,7 @@
         <v>44972</v>
       </c>
       <c r="E1061" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F1061" t="inlineStr">
         <is>
@@ -81851,7 +81851,7 @@
         <v>45230</v>
       </c>
       <c r="E1062" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F1062" t="inlineStr">
         <is>
@@ -81924,7 +81924,7 @@
         <v>44939</v>
       </c>
       <c r="E1063" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F1063" t="inlineStr">
         <is>
@@ -81997,7 +81997,7 @@
         <v>45468</v>
       </c>
       <c r="E1064" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F1064" t="inlineStr">
         <is>
@@ -82070,7 +82070,7 @@
         <v>45218</v>
       </c>
       <c r="E1065" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F1065" t="inlineStr">
         <is>
@@ -82143,7 +82143,7 @@
         <v>45054</v>
       </c>
       <c r="E1066" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F1066" t="inlineStr">
         <is>
@@ -82216,7 +82216,7 @@
         <v>44930</v>
       </c>
       <c r="E1067" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F1067" t="inlineStr">
         <is>
@@ -82294,7 +82294,7 @@
         <v>44973</v>
       </c>
       <c r="E1068" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F1068" t="inlineStr">
         <is>
@@ -82367,7 +82367,7 @@
         <v>44908</v>
       </c>
       <c r="E1069" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F1069" t="inlineStr">
         <is>
@@ -82460,7 +82460,7 @@
         <v>45583</v>
       </c>
       <c r="E1070" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F1070" t="inlineStr">
         <is>
@@ -82533,7 +82533,7 @@
         <v>45054</v>
       </c>
       <c r="E1071" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F1071" t="inlineStr">
         <is>
@@ -82606,7 +82606,7 @@
         <v>45054</v>
       </c>
       <c r="E1072" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F1072" t="inlineStr">
         <is>
@@ -82679,7 +82679,7 @@
         <v>44908</v>
       </c>
       <c r="E1073" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F1073" t="inlineStr">
         <is>
@@ -82752,7 +82752,7 @@
         <v>44972</v>
       </c>
       <c r="E1074" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F1074" t="inlineStr">
         <is>
@@ -82825,7 +82825,7 @@
         <v>44978</v>
       </c>
       <c r="E1075" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F1075" t="inlineStr">
         <is>
@@ -82898,7 +82898,7 @@
         <v>44887</v>
       </c>
       <c r="E1076" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F1076" t="inlineStr">
         <is>
@@ -82971,7 +82971,7 @@
         <v>44909</v>
       </c>
       <c r="E1077" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F1077" t="inlineStr">
         <is>
@@ -83044,7 +83044,7 @@
         <v>45408</v>
       </c>
       <c r="E1078" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F1078" t="inlineStr">
         <is>
@@ -83117,7 +83117,7 @@
         <v>44908</v>
       </c>
       <c r="E1079" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F1079" t="inlineStr">
         <is>
@@ -83190,7 +83190,7 @@
         <v>45054</v>
       </c>
       <c r="E1080" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F1080" t="inlineStr">
         <is>
@@ -83263,7 +83263,7 @@
         <v>45526</v>
       </c>
       <c r="E1081" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F1081" t="inlineStr">
         <is>
@@ -83336,7 +83336,7 @@
         <v>45436</v>
       </c>
       <c r="E1082" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F1082" t="inlineStr">
         <is>
@@ -83409,7 +83409,7 @@
         <v>45485</v>
       </c>
       <c r="E1083" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F1083" t="inlineStr">
         <is>
@@ -83482,7 +83482,7 @@
         <v>45727</v>
       </c>
       <c r="E1084" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F1084" t="inlineStr">
         <is>
@@ -83555,7 +83555,7 @@
         <v>45740</v>
       </c>
       <c r="E1085" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F1085" t="inlineStr">
         <is>
@@ -83628,7 +83628,7 @@
         <v>45726</v>
       </c>
       <c r="E1086" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F1086" t="inlineStr">
         <is>
@@ -83701,7 +83701,7 @@
         <v>45797</v>
       </c>
       <c r="E1087" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F1087" t="inlineStr">
         <is>
@@ -83774,7 +83774,7 @@
         <v>45805</v>
       </c>
       <c r="E1088" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F1088" t="inlineStr">
         <is>
@@ -83847,7 +83847,7 @@
         <v>45831</v>
       </c>
       <c r="E1089" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F1089" t="inlineStr">
         <is>
@@ -83920,7 +83920,7 @@
         <v>45951</v>
       </c>
       <c r="E1090" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F1090" t="inlineStr">
         <is>
@@ -83993,7 +83993,7 @@
         <v>45958</v>
       </c>
       <c r="E1091" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F1091" t="inlineStr">
         <is>
@@ -84066,7 +84066,7 @@
         <v>45964</v>
       </c>
       <c r="E1092" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F1092" t="inlineStr">
         <is>
@@ -84139,7 +84139,7 @@
         <v>45965</v>
       </c>
       <c r="E1093" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F1093" t="inlineStr">
         <is>
@@ -84212,7 +84212,7 @@
         <v>45981</v>
       </c>
       <c r="E1094" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F1094" t="inlineStr">
         <is>
@@ -84290,7 +84290,7 @@
         <v>45988</v>
       </c>
       <c r="E1095" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F1095" t="inlineStr">
         <is>
@@ -84363,7 +84363,7 @@
         <v>46092</v>
       </c>
       <c r="E1096" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F1096" t="inlineStr">
         <is>
@@ -84441,7 +84441,7 @@
         <v>46202</v>
       </c>
       <c r="E1097" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F1097" t="inlineStr">
         <is>
@@ -84514,7 +84514,7 @@
         <v>46300</v>
       </c>
       <c r="E1098" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F1098" t="inlineStr">
         <is>
@@ -84587,7 +84587,7 @@
         <v>46262</v>
       </c>
       <c r="E1099" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F1099" t="inlineStr">
         <is>
@@ -84660,7 +84660,7 @@
         <v>46304</v>
       </c>
       <c r="E1100" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F1100" t="inlineStr">
         <is>
